--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14106" uniqueCount="1551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14137" uniqueCount="1553">
   <si>
     <t>Year</t>
   </si>
@@ -4678,6 +4678,12 @@
   </si>
   <si>
     <t>2025-12-28</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>nwreadinglist v5.1.0</t>
   </si>
 </sst>
 </file>
@@ -65934,61 +65940,147 @@
         <v>279</v>
       </c>
       <c r="I1813" s="4">
-        <f t="shared" ref="I1813" si="778">YEAR(A1813)</f>
+        <f t="shared" ref="I1813:I1816" si="778">YEAR(A1813)</f>
         <v>2025</v>
       </c>
       <c r="J1813" s="4">
-        <f t="shared" ref="J1813" si="779">MONTH(A1813)</f>
+        <f t="shared" ref="J1813:J1816" si="779">MONTH(A1813)</f>
         <v>12</v>
       </c>
     </row>
     <row r="1814" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1814" s="3"/>
-      <c r="B1814" s="3"/>
-      <c r="C1814" s="3"/>
-      <c r="D1814" s="3"/>
-      <c r="E1814" s="3"/>
+      <c r="A1814" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B1814" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1814" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1814" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1814" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F1814" s="3"/>
-      <c r="G1814" s="3"/>
-      <c r="H1814" s="3"/>
-      <c r="I1814" s="4"/>
-      <c r="J1814" s="4"/>
+      <c r="G1814" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1814" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1814" s="4">
+        <f t="shared" si="778"/>
+        <v>2025</v>
+      </c>
+      <c r="J1814" s="4">
+        <f t="shared" si="779"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="1815" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1815" s="3"/>
-      <c r="B1815" s="3"/>
-      <c r="C1815" s="3"/>
-      <c r="D1815" s="3"/>
-      <c r="E1815" s="3"/>
-      <c r="F1815" s="3"/>
-      <c r="G1815" s="3"/>
-      <c r="H1815" s="3"/>
-      <c r="I1815" s="4"/>
-      <c r="J1815" s="4"/>
+      <c r="A1815" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B1815" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1815" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1815" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1815" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1815" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G1815" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1815" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1815" s="4">
+        <f t="shared" si="778"/>
+        <v>2025</v>
+      </c>
+      <c r="J1815" s="4">
+        <f t="shared" si="779"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="1816" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1816" s="3"/>
-      <c r="B1816" s="3"/>
-      <c r="C1816" s="3"/>
-      <c r="D1816" s="3"/>
-      <c r="E1816" s="3"/>
-      <c r="F1816" s="3"/>
-      <c r="G1816" s="3"/>
-      <c r="H1816" s="3"/>
-      <c r="I1816" s="4"/>
-      <c r="J1816" s="4"/>
+      <c r="A1816" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B1816" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1816" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1816" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1816" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1816" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G1816" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1816" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1816" s="4">
+        <f t="shared" si="778"/>
+        <v>2025</v>
+      </c>
+      <c r="J1816" s="4">
+        <f t="shared" si="779"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="1817" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1817" s="3"/>
-      <c r="B1817" s="3"/>
-      <c r="C1817" s="3"/>
-      <c r="D1817" s="3"/>
-      <c r="E1817" s="3"/>
-      <c r="F1817" s="3"/>
-      <c r="G1817" s="3"/>
-      <c r="H1817" s="3"/>
-      <c r="I1817" s="4"/>
-      <c r="J1817" s="4"/>
+      <c r="A1817" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B1817" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1817" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1817" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E1817" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1817" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G1817" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1817" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1817" s="4">
+        <f t="shared" ref="I1817" si="780">YEAR(A1817)</f>
+        <v>2025</v>
+      </c>
+      <c r="J1817" s="4">
+        <f t="shared" ref="J1817" si="781">MONTH(A1817)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="1818" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1818" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14137" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14193" uniqueCount="1556">
   <si>
     <t>Year</t>
   </si>
@@ -4684,6 +4684,15 @@
   </si>
   <si>
     <t>nwreadinglist v5.1.0</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
   </si>
 </sst>
 </file>
@@ -66074,97 +66083,251 @@
         <v>279</v>
       </c>
       <c r="I1817" s="4">
-        <f t="shared" ref="I1817" si="780">YEAR(A1817)</f>
+        <f>YEAR(A1817)</f>
         <v>2025</v>
       </c>
       <c r="J1817" s="4">
-        <f t="shared" ref="J1817" si="781">MONTH(A1817)</f>
+        <f>MONTH(A1817)</f>
         <v>12</v>
       </c>
     </row>
     <row r="1818" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1818" s="3"/>
-      <c r="B1818" s="3"/>
-      <c r="C1818" s="3"/>
-      <c r="D1818" s="3"/>
-      <c r="E1818" s="3"/>
-      <c r="F1818" s="3"/>
-      <c r="G1818" s="3"/>
-      <c r="H1818" s="3"/>
-      <c r="I1818" s="4"/>
-      <c r="J1818" s="4"/>
+      <c r="A1818" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B1818" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1818" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1818" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1818" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1818" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1818" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1818" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1818" s="4">
+        <f t="shared" ref="I1818" si="780">YEAR(A1818)</f>
+        <v>2025</v>
+      </c>
+      <c r="J1818" s="4">
+        <f t="shared" ref="J1818" si="781">MONTH(A1818)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="1819" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1819" s="3"/>
-      <c r="B1819" s="3"/>
-      <c r="C1819" s="3"/>
-      <c r="D1819" s="3"/>
-      <c r="E1819" s="3"/>
-      <c r="F1819" s="3"/>
-      <c r="G1819" s="3"/>
-      <c r="H1819" s="3"/>
-      <c r="I1819" s="4"/>
-      <c r="J1819" s="4"/>
+      <c r="A1819" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B1819" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1819" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1819" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1819" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1819" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1819" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1819" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1819" s="4">
+        <f t="shared" ref="I1819:I1821" si="782">YEAR(A1819)</f>
+        <v>2025</v>
+      </c>
+      <c r="J1819" s="4">
+        <f t="shared" ref="J1819:J1821" si="783">MONTH(A1819)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="1820" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1820" s="3"/>
-      <c r="B1820" s="3"/>
-      <c r="C1820" s="3"/>
-      <c r="D1820" s="3"/>
-      <c r="E1820" s="3"/>
-      <c r="F1820" s="3"/>
-      <c r="G1820" s="3"/>
-      <c r="H1820" s="3"/>
-      <c r="I1820" s="4"/>
-      <c r="J1820" s="4"/>
+      <c r="A1820" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B1820" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1820" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1820" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1820" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1820" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1820" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1820" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1820" s="4">
+        <f t="shared" si="782"/>
+        <v>2025</v>
+      </c>
+      <c r="J1820" s="4">
+        <f t="shared" si="783"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="1821" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1821" s="3"/>
-      <c r="B1821" s="3"/>
-      <c r="C1821" s="3"/>
-      <c r="D1821" s="3"/>
-      <c r="E1821" s="3"/>
-      <c r="F1821" s="3"/>
-      <c r="G1821" s="3"/>
-      <c r="H1821" s="3"/>
-      <c r="I1821" s="4"/>
-      <c r="J1821" s="4"/>
+      <c r="A1821" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B1821" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1821" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1821" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1821" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1821" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1821" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1821" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1821" s="4">
+        <f t="shared" si="782"/>
+        <v>2025</v>
+      </c>
+      <c r="J1821" s="4">
+        <f t="shared" si="783"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="1822" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1822" s="3"/>
-      <c r="B1822" s="3"/>
-      <c r="C1822" s="3"/>
-      <c r="D1822" s="3"/>
-      <c r="E1822" s="3"/>
-      <c r="F1822" s="3"/>
-      <c r="G1822" s="3"/>
-      <c r="H1822" s="3"/>
-      <c r="I1822" s="4"/>
-      <c r="J1822" s="4"/>
+      <c r="A1822" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1822" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1822" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1822" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1822" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1822" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1822" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1822" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1822" s="4">
+        <f t="shared" ref="I1822:I1824" si="784">YEAR(A1822)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1822" s="4">
+        <f t="shared" ref="J1822:J1824" si="785">MONTH(A1822)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1823" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1823" s="3"/>
-      <c r="B1823" s="3"/>
-      <c r="C1823" s="3"/>
-      <c r="D1823" s="3"/>
-      <c r="E1823" s="3"/>
-      <c r="F1823" s="3"/>
-      <c r="G1823" s="3"/>
-      <c r="H1823" s="3"/>
-      <c r="I1823" s="4"/>
-      <c r="J1823" s="4"/>
+      <c r="A1823" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1823" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1823" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1823" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1823" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1823" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1823" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1823" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1823" s="4">
+        <f t="shared" si="784"/>
+        <v>2026</v>
+      </c>
+      <c r="J1823" s="4">
+        <f t="shared" si="785"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1824" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1824" s="3"/>
-      <c r="B1824" s="3"/>
-      <c r="C1824" s="3"/>
-      <c r="D1824" s="3"/>
-      <c r="E1824" s="3"/>
-      <c r="F1824" s="3"/>
-      <c r="G1824" s="3"/>
-      <c r="H1824" s="3"/>
-      <c r="I1824" s="4"/>
-      <c r="J1824" s="4"/>
+      <c r="A1824" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1824" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1824" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1824" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1824" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1824" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G1824" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1824" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1824" s="4">
+        <f t="shared" si="784"/>
+        <v>2026</v>
+      </c>
+      <c r="J1824" s="4">
+        <f t="shared" si="785"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1825" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1825" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14193" uniqueCount="1556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14361" uniqueCount="1565">
   <si>
     <t>Year</t>
   </si>
@@ -4176,9 +4176,6 @@
     <t>2025-05-25</t>
   </si>
   <si>
-    <t>nwbuild v1.0.0</t>
-  </si>
-  <si>
     <t>2025-05-26</t>
   </si>
   <si>
@@ -4693,6 +4690,36 @@
   </si>
   <si>
     <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>nwbuilds v1.0.0</t>
+  </si>
+  <si>
+    <t>2026-01-03</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-01-10</t>
   </si>
 </sst>
 </file>
@@ -5101,7 +5128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1841"/>
+  <dimension ref="A1:J1867"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -54275,7 +54302,7 @@
         <v>389</v>
       </c>
       <c r="E1464" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1464" s="3" t="s">
         <v>1285</v>
@@ -54409,7 +54436,7 @@
         <v>94</v>
       </c>
       <c r="E1468" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1468" s="3" t="s">
         <v>1285</v>
@@ -54443,7 +54470,7 @@
         <v>105</v>
       </c>
       <c r="E1469" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1469" s="3" t="s">
         <v>1285</v>
@@ -54509,7 +54536,7 @@
         <v>243</v>
       </c>
       <c r="E1471" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1471" s="3" t="s">
         <v>1285</v>
@@ -54543,7 +54570,7 @@
         <v>220</v>
       </c>
       <c r="E1472" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1472" s="3" t="s">
         <v>1285</v>
@@ -54577,7 +54604,7 @@
         <v>239</v>
       </c>
       <c r="E1473" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1473" s="3" t="s">
         <v>1285</v>
@@ -55590,7 +55617,7 @@
         <v>127</v>
       </c>
       <c r="F1504" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1504" s="8" t="s">
         <v>279</v>
@@ -55624,7 +55651,7 @@
         <v>127</v>
       </c>
       <c r="F1505" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1505" s="8" t="s">
         <v>279</v>
@@ -55658,7 +55685,7 @@
         <v>127</v>
       </c>
       <c r="F1506" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1506" s="8" t="s">
         <v>279</v>
@@ -56192,7 +56219,7 @@
         <v>127</v>
       </c>
       <c r="F1522" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1522" s="8" t="s">
         <v>279</v>
@@ -56226,7 +56253,7 @@
         <v>127</v>
       </c>
       <c r="F1523" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1523" s="8" t="s">
         <v>279</v>
@@ -56260,7 +56287,7 @@
         <v>127</v>
       </c>
       <c r="F1524" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1524" s="8" t="s">
         <v>279</v>
@@ -56279,7 +56306,7 @@
     </row>
     <row r="1525" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1525" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1525" s="3" t="s">
         <v>338</v>
@@ -56294,7 +56321,7 @@
         <v>127</v>
       </c>
       <c r="F1525" s="3" t="s">
-        <v>1383</v>
+        <v>1556</v>
       </c>
       <c r="G1525" s="8" t="s">
         <v>279</v>
@@ -56313,7 +56340,7 @@
     </row>
     <row r="1526" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1526" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1526" s="3" t="s">
         <v>340</v>
@@ -56328,7 +56355,7 @@
         <v>127</v>
       </c>
       <c r="F1526" s="3" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G1526" s="8" t="s">
         <v>279</v>
@@ -56347,7 +56374,7 @@
     </row>
     <row r="1527" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1527" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1527" s="3" t="s">
         <v>790</v>
@@ -56362,7 +56389,7 @@
         <v>127</v>
       </c>
       <c r="F1527" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="G1527" s="8" t="s">
         <v>279</v>
@@ -56381,7 +56408,7 @@
     </row>
     <row r="1528" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1528" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1528" s="3" t="s">
         <v>119</v>
@@ -56396,7 +56423,7 @@
         <v>127</v>
       </c>
       <c r="F1528" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="G1528" s="8" t="s">
         <v>279</v>
@@ -56415,7 +56442,7 @@
     </row>
     <row r="1529" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1529" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1529" s="3" t="s">
         <v>113</v>
@@ -56430,7 +56457,7 @@
         <v>127</v>
       </c>
       <c r="F1529" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="G1529" s="8" t="s">
         <v>279</v>
@@ -56449,7 +56476,7 @@
     </row>
     <row r="1530" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1530" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1530" s="3" t="s">
         <v>233</v>
@@ -56464,7 +56491,7 @@
         <v>127</v>
       </c>
       <c r="F1530" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="G1530" s="8" t="s">
         <v>279</v>
@@ -56483,7 +56510,7 @@
     </row>
     <row r="1531" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1531" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B1531" s="3" t="s">
         <v>329</v>
@@ -56498,7 +56525,7 @@
         <v>127</v>
       </c>
       <c r="F1531" s="9" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G1531" s="8" t="s">
         <v>279</v>
@@ -56517,7 +56544,7 @@
     </row>
     <row r="1532" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1532" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B1532" s="3" t="s">
         <v>122</v>
@@ -56549,7 +56576,7 @@
     </row>
     <row r="1533" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1533" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B1533" s="3" t="s">
         <v>209</v>
@@ -56581,7 +56608,7 @@
     </row>
     <row r="1534" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1534" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B1534" s="3" t="s">
         <v>248</v>
@@ -56613,7 +56640,7 @@
     </row>
     <row r="1535" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1535" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B1535" s="3" t="s">
         <v>118</v>
@@ -56645,7 +56672,7 @@
     </row>
     <row r="1536" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1536" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B1536" s="3" t="s">
         <v>161</v>
@@ -56679,7 +56706,7 @@
     </row>
     <row r="1537" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1537" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B1537" s="3" t="s">
         <v>174</v>
@@ -56713,7 +56740,7 @@
     </row>
     <row r="1538" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1538" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1538" s="3" t="s">
         <v>122</v>
@@ -56747,7 +56774,7 @@
     </row>
     <row r="1539" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1539" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1539" s="3" t="s">
         <v>209</v>
@@ -56781,7 +56808,7 @@
     </row>
     <row r="1540" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1540" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1540" s="3" t="s">
         <v>311</v>
@@ -56815,7 +56842,7 @@
     </row>
     <row r="1541" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1541" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1541" s="3" t="s">
         <v>353</v>
@@ -56849,7 +56876,7 @@
     </row>
     <row r="1542" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1542" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B1542" s="3" t="s">
         <v>138</v>
@@ -56883,7 +56910,7 @@
     </row>
     <row r="1543" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1543" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1543" s="3" t="s">
         <v>331</v>
@@ -56917,7 +56944,7 @@
     </row>
     <row r="1544" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1544" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1544" s="3" t="s">
         <v>122</v>
@@ -56951,7 +56978,7 @@
     </row>
     <row r="1545" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1545" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1545" s="3" t="s">
         <v>150</v>
@@ -56985,7 +57012,7 @@
     </row>
     <row r="1546" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1546" s="3" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B1546" s="3" t="s">
         <v>202</v>
@@ -57000,7 +57027,7 @@
         <v>127</v>
       </c>
       <c r="F1546" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1546" s="8" t="s">
         <v>279</v>
@@ -57019,7 +57046,7 @@
     </row>
     <row r="1547" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1547" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B1547" s="3" t="s">
         <v>248</v>
@@ -57051,7 +57078,7 @@
     </row>
     <row r="1548" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1548" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B1548" s="3" t="s">
         <v>149</v>
@@ -57083,7 +57110,7 @@
     </row>
     <row r="1549" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1549" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B1549" s="3" t="s">
         <v>174</v>
@@ -57115,7 +57142,7 @@
     </row>
     <row r="1550" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1550" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B1550" s="3" t="s">
         <v>249</v>
@@ -57147,7 +57174,7 @@
     </row>
     <row r="1551" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1551" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B1551" s="3" t="s">
         <v>149</v>
@@ -57179,7 +57206,7 @@
     </row>
     <row r="1552" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1552" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B1552" s="3" t="s">
         <v>132</v>
@@ -57211,7 +57238,7 @@
     </row>
     <row r="1553" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1553" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B1553" s="3" t="s">
         <v>161</v>
@@ -57243,7 +57270,7 @@
     </row>
     <row r="1554" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1554" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B1554" s="3" t="s">
         <v>124</v>
@@ -57275,7 +57302,7 @@
     </row>
     <row r="1555" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1555" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B1555" s="3" t="s">
         <v>327</v>
@@ -57307,7 +57334,7 @@
     </row>
     <row r="1556" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1556" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B1556" s="3" t="s">
         <v>355</v>
@@ -57322,7 +57349,7 @@
         <v>127</v>
       </c>
       <c r="F1556" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1556" s="8" t="s">
         <v>279</v>
@@ -57341,7 +57368,7 @@
     </row>
     <row r="1557" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1557" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B1557" s="3" t="s">
         <v>114</v>
@@ -57356,7 +57383,7 @@
         <v>127</v>
       </c>
       <c r="F1557" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1557" s="8" t="s">
         <v>279</v>
@@ -57375,7 +57402,7 @@
     </row>
     <row r="1558" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1558" s="3" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B1558" s="3" t="s">
         <v>134</v>
@@ -57390,7 +57417,7 @@
         <v>127</v>
       </c>
       <c r="F1558" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1558" s="8" t="s">
         <v>279</v>
@@ -57409,7 +57436,7 @@
     </row>
     <row r="1559" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1559" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B1559" s="3" t="s">
         <v>248</v>
@@ -57441,7 +57468,7 @@
     </row>
     <row r="1560" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1560" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B1560" s="3" t="s">
         <v>171</v>
@@ -57473,7 +57500,7 @@
     </row>
     <row r="1561" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1561" s="3" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B1561" s="3" t="s">
         <v>248</v>
@@ -57505,7 +57532,7 @@
     </row>
     <row r="1562" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1562" s="3" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B1562" s="3" t="s">
         <v>118</v>
@@ -57537,7 +57564,7 @@
     </row>
     <row r="1563" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1563" s="3" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B1563" s="3" t="s">
         <v>395</v>
@@ -57552,7 +57579,7 @@
         <v>127</v>
       </c>
       <c r="F1563" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1563" s="8" t="s">
         <v>279</v>
@@ -57571,7 +57598,7 @@
     </row>
     <row r="1564" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1564" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B1564" s="3" t="s">
         <v>327</v>
@@ -57586,7 +57613,7 @@
         <v>127</v>
       </c>
       <c r="F1564" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1564" s="8" t="s">
         <v>279</v>
@@ -57605,7 +57632,7 @@
     </row>
     <row r="1565" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1565" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B1565" s="3" t="s">
         <v>174</v>
@@ -57620,7 +57647,7 @@
         <v>127</v>
       </c>
       <c r="F1565" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1565" s="8" t="s">
         <v>279</v>
@@ -57639,7 +57666,7 @@
     </row>
     <row r="1566" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1566" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B1566" s="3" t="s">
         <v>271</v>
@@ -57654,7 +57681,7 @@
         <v>127</v>
       </c>
       <c r="F1566" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1566" s="8" t="s">
         <v>279</v>
@@ -57673,7 +57700,7 @@
     </row>
     <row r="1567" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1567" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B1567" s="3" t="s">
         <v>287</v>
@@ -57688,7 +57715,7 @@
         <v>127</v>
       </c>
       <c r="F1567" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1567" s="8" t="s">
         <v>279</v>
@@ -57707,7 +57734,7 @@
     </row>
     <row r="1568" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1568" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B1568" s="3" t="s">
         <v>191</v>
@@ -57722,7 +57749,7 @@
         <v>127</v>
       </c>
       <c r="F1568" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1568" s="8" t="s">
         <v>279</v>
@@ -57741,7 +57768,7 @@
     </row>
     <row r="1569" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1569" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B1569" s="3" t="s">
         <v>134</v>
@@ -57756,7 +57783,7 @@
         <v>127</v>
       </c>
       <c r="F1569" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1569" s="8" t="s">
         <v>279</v>
@@ -57775,7 +57802,7 @@
     </row>
     <row r="1570" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1570" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B1570" s="3" t="s">
         <v>179</v>
@@ -57807,7 +57834,7 @@
     </row>
     <row r="1571" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1571" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B1571" s="3" t="s">
         <v>161</v>
@@ -57839,7 +57866,7 @@
     </row>
     <row r="1572" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1572" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B1572" s="3" t="s">
         <v>154</v>
@@ -57871,7 +57898,7 @@
     </row>
     <row r="1573" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1573" s="3" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B1573" s="3" t="s">
         <v>161</v>
@@ -57886,7 +57913,7 @@
         <v>127</v>
       </c>
       <c r="F1573" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1573" s="8" t="s">
         <v>279</v>
@@ -57905,7 +57932,7 @@
     </row>
     <row r="1574" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1574" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B1574" s="3" t="s">
         <v>248</v>
@@ -57937,7 +57964,7 @@
     </row>
     <row r="1575" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1575" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B1575" s="3" t="s">
         <v>149</v>
@@ -57969,7 +57996,7 @@
     </row>
     <row r="1576" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1576" s="3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B1576" s="3" t="s">
         <v>253</v>
@@ -58001,7 +58028,7 @@
     </row>
     <row r="1577" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1577" s="3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B1577" s="3" t="s">
         <v>118</v>
@@ -58033,7 +58060,7 @@
     </row>
     <row r="1578" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1578" s="3" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B1578" s="3" t="s">
         <v>174</v>
@@ -58048,7 +58075,7 @@
         <v>127</v>
       </c>
       <c r="F1578" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1578" s="8" t="s">
         <v>279</v>
@@ -58067,7 +58094,7 @@
     </row>
     <row r="1579" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1579" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B1579" s="3" t="s">
         <v>202</v>
@@ -58082,7 +58109,7 @@
         <v>127</v>
       </c>
       <c r="F1579" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1579" s="8" t="s">
         <v>279</v>
@@ -58101,7 +58128,7 @@
     </row>
     <row r="1580" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1580" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B1580" s="3" t="s">
         <v>209</v>
@@ -58116,7 +58143,7 @@
         <v>127</v>
       </c>
       <c r="F1580" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1580" s="8" t="s">
         <v>279</v>
@@ -58135,7 +58162,7 @@
     </row>
     <row r="1581" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1581" s="3" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B1581" s="3" t="s">
         <v>124</v>
@@ -58150,7 +58177,7 @@
         <v>127</v>
       </c>
       <c r="F1581" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1581" s="8" t="s">
         <v>279</v>
@@ -58169,7 +58196,7 @@
     </row>
     <row r="1582" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1582" s="3" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B1582" s="3" t="s">
         <v>329</v>
@@ -58184,7 +58211,7 @@
         <v>127</v>
       </c>
       <c r="F1582" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1582" s="8" t="s">
         <v>279</v>
@@ -58203,7 +58230,7 @@
     </row>
     <row r="1583" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1583" s="3" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B1583" s="3" t="s">
         <v>174</v>
@@ -58218,7 +58245,7 @@
         <v>127</v>
       </c>
       <c r="F1583" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1583" s="8" t="s">
         <v>279</v>
@@ -58237,7 +58264,7 @@
     </row>
     <row r="1584" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1584" s="3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B1584" s="3" t="s">
         <v>149</v>
@@ -58269,7 +58296,7 @@
     </row>
     <row r="1585" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1585" s="3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B1585" s="3" t="s">
         <v>124</v>
@@ -58284,7 +58311,7 @@
         <v>127</v>
       </c>
       <c r="F1585" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1585" s="8" t="s">
         <v>279</v>
@@ -58303,7 +58330,7 @@
     </row>
     <row r="1586" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1586" s="3" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B1586" s="3" t="s">
         <v>248</v>
@@ -58335,7 +58362,7 @@
     </row>
     <row r="1587" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1587" s="3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B1587" s="3" t="s">
         <v>196</v>
@@ -58350,7 +58377,7 @@
         <v>127</v>
       </c>
       <c r="F1587" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1587" s="8" t="s">
         <v>279</v>
@@ -58369,7 +58396,7 @@
     </row>
     <row r="1588" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1588" s="3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B1588" s="3" t="s">
         <v>271</v>
@@ -58384,7 +58411,7 @@
         <v>127</v>
       </c>
       <c r="F1588" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1588" s="8" t="s">
         <v>279</v>
@@ -58403,7 +58430,7 @@
     </row>
     <row r="1589" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1589" s="3" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B1589" s="3" t="s">
         <v>180</v>
@@ -58418,7 +58445,7 @@
         <v>127</v>
       </c>
       <c r="F1589" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1589" s="8" t="s">
         <v>279</v>
@@ -58437,7 +58464,7 @@
     </row>
     <row r="1590" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1590" s="3" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B1590" s="3" t="s">
         <v>361</v>
@@ -58452,7 +58479,7 @@
         <v>127</v>
       </c>
       <c r="F1590" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1590" s="8" t="s">
         <v>279</v>
@@ -58471,7 +58498,7 @@
     </row>
     <row r="1591" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1591" s="3" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B1591" s="3" t="s">
         <v>124</v>
@@ -58486,7 +58513,7 @@
         <v>127</v>
       </c>
       <c r="F1591" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1591" s="8" t="s">
         <v>279</v>
@@ -58505,7 +58532,7 @@
     </row>
     <row r="1592" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1592" s="3" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B1592" s="3" t="s">
         <v>355</v>
@@ -58520,7 +58547,7 @@
         <v>127</v>
       </c>
       <c r="F1592" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1592" s="8" t="s">
         <v>279</v>
@@ -58539,7 +58566,7 @@
     </row>
     <row r="1593" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1593" s="3" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B1593" s="3" t="s">
         <v>154</v>
@@ -58554,7 +58581,7 @@
         <v>127</v>
       </c>
       <c r="F1593" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1593" s="8" t="s">
         <v>279</v>
@@ -58573,7 +58600,7 @@
     </row>
     <row r="1594" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1594" s="3" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B1594" s="3" t="s">
         <v>359</v>
@@ -58588,7 +58615,7 @@
         <v>127</v>
       </c>
       <c r="F1594" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1594" s="8" t="s">
         <v>279</v>
@@ -58607,7 +58634,7 @@
     </row>
     <row r="1595" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1595" s="3" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B1595" s="3" t="s">
         <v>113</v>
@@ -58639,7 +58666,7 @@
     </row>
     <row r="1596" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1596" s="3" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B1596" s="3" t="s">
         <v>174</v>
@@ -58671,7 +58698,7 @@
     </row>
     <row r="1597" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1597" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B1597" s="3" t="s">
         <v>248</v>
@@ -58686,7 +58713,7 @@
         <v>127</v>
       </c>
       <c r="F1597" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1597" s="8" t="s">
         <v>279</v>
@@ -58705,7 +58732,7 @@
     </row>
     <row r="1598" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1598" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B1598" s="3" t="s">
         <v>149</v>
@@ -58720,7 +58747,7 @@
         <v>127</v>
       </c>
       <c r="F1598" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1598" s="8" t="s">
         <v>279</v>
@@ -58739,7 +58766,7 @@
     </row>
     <row r="1599" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1599" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B1599" s="3" t="s">
         <v>124</v>
@@ -58754,7 +58781,7 @@
         <v>127</v>
       </c>
       <c r="F1599" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1599" s="8" t="s">
         <v>279</v>
@@ -58773,7 +58800,7 @@
     </row>
     <row r="1600" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1600" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B1600" s="3" t="s">
         <v>329</v>
@@ -58788,7 +58815,7 @@
         <v>127</v>
       </c>
       <c r="F1600" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1600" s="8" t="s">
         <v>279</v>
@@ -58807,7 +58834,7 @@
     </row>
     <row r="1601" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1601" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B1601" s="3" t="s">
         <v>202</v>
@@ -58839,7 +58866,7 @@
     </row>
     <row r="1602" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1602" s="3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1602" s="3" t="s">
         <v>255</v>
@@ -58854,7 +58881,7 @@
         <v>127</v>
       </c>
       <c r="F1602" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1602" s="8" t="s">
         <v>279</v>
@@ -58873,7 +58900,7 @@
     </row>
     <row r="1603" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1603" s="3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1603" s="3" t="s">
         <v>353</v>
@@ -58888,7 +58915,7 @@
         <v>127</v>
       </c>
       <c r="F1603" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1603" s="8" t="s">
         <v>279</v>
@@ -58907,7 +58934,7 @@
     </row>
     <row r="1604" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1604" s="3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1604" s="3" t="s">
         <v>211</v>
@@ -58922,7 +58949,7 @@
         <v>127</v>
       </c>
       <c r="F1604" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1604" s="8" t="s">
         <v>279</v>
@@ -58941,7 +58968,7 @@
     </row>
     <row r="1605" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1605" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1605" s="3" t="s">
         <v>132</v>
@@ -58956,7 +58983,7 @@
         <v>127</v>
       </c>
       <c r="F1605" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1605" s="8" t="s">
         <v>279</v>
@@ -58975,7 +59002,7 @@
     </row>
     <row r="1606" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1606" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1606" s="3" t="s">
         <v>327</v>
@@ -58990,7 +59017,7 @@
         <v>127</v>
       </c>
       <c r="F1606" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1606" s="8" t="s">
         <v>279</v>
@@ -59009,7 +59036,7 @@
     </row>
     <row r="1607" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1607" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1607" s="3" t="s">
         <v>171</v>
@@ -59024,7 +59051,7 @@
         <v>127</v>
       </c>
       <c r="F1607" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1607" s="8" t="s">
         <v>279</v>
@@ -59043,7 +59070,7 @@
     </row>
     <row r="1608" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1608" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1608" s="3" t="s">
         <v>124</v>
@@ -59058,7 +59085,7 @@
         <v>127</v>
       </c>
       <c r="F1608" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1608" s="8" t="s">
         <v>279</v>
@@ -59077,7 +59104,7 @@
     </row>
     <row r="1609" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1609" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1609" s="3" t="s">
         <v>203</v>
@@ -59092,7 +59119,7 @@
         <v>127</v>
       </c>
       <c r="F1609" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1609" s="8" t="s">
         <v>279</v>
@@ -59111,7 +59138,7 @@
     </row>
     <row r="1610" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1610" s="3" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B1610" s="3" t="s">
         <v>202</v>
@@ -59143,7 +59170,7 @@
     </row>
     <row r="1611" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1611" s="3" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B1611" s="3" t="s">
         <v>154</v>
@@ -59175,7 +59202,7 @@
     </row>
     <row r="1612" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1612" s="3" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B1612" s="3" t="s">
         <v>564</v>
@@ -59190,7 +59217,7 @@
         <v>127</v>
       </c>
       <c r="F1612" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1612" s="8" t="s">
         <v>279</v>
@@ -59209,7 +59236,7 @@
     </row>
     <row r="1613" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1613" s="3" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B1613" s="3" t="s">
         <v>353</v>
@@ -59224,7 +59251,7 @@
         <v>127</v>
       </c>
       <c r="F1613" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1613" s="8" t="s">
         <v>279</v>
@@ -59243,7 +59270,7 @@
     </row>
     <row r="1614" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1614" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B1614" s="3" t="s">
         <v>248</v>
@@ -59275,7 +59302,7 @@
     </row>
     <row r="1615" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1615" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B1615" s="3" t="s">
         <v>149</v>
@@ -59307,7 +59334,7 @@
     </row>
     <row r="1616" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1616" s="3" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B1616" s="3" t="s">
         <v>248</v>
@@ -59339,7 +59366,7 @@
     </row>
     <row r="1617" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1617" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1617" s="3" t="s">
         <v>331</v>
@@ -59354,7 +59381,7 @@
         <v>127</v>
       </c>
       <c r="F1617" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1617" s="8" t="s">
         <v>279</v>
@@ -59373,7 +59400,7 @@
     </row>
     <row r="1618" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1618" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1618" s="3" t="s">
         <v>210</v>
@@ -59388,7 +59415,7 @@
         <v>127</v>
       </c>
       <c r="F1618" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1618" s="8" t="s">
         <v>279</v>
@@ -59407,7 +59434,7 @@
     </row>
     <row r="1619" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1619" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1619" s="3" t="s">
         <v>196</v>
@@ -59422,7 +59449,7 @@
         <v>127</v>
       </c>
       <c r="F1619" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1619" s="8" t="s">
         <v>279</v>
@@ -59441,7 +59468,7 @@
     </row>
     <row r="1620" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1620" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1620" s="3" t="s">
         <v>134</v>
@@ -59456,7 +59483,7 @@
         <v>127</v>
       </c>
       <c r="F1620" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1620" s="8" t="s">
         <v>279</v>
@@ -59475,7 +59502,7 @@
     </row>
     <row r="1621" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1621" s="3" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1621" s="3" t="s">
         <v>355</v>
@@ -59490,7 +59517,7 @@
         <v>127</v>
       </c>
       <c r="F1621" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1621" s="8" t="s">
         <v>279</v>
@@ -59509,7 +59536,7 @@
     </row>
     <row r="1622" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1622" s="3" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1622" s="3" t="s">
         <v>353</v>
@@ -59524,7 +59551,7 @@
         <v>127</v>
       </c>
       <c r="F1622" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1622" s="8" t="s">
         <v>279</v>
@@ -59543,7 +59570,7 @@
     </row>
     <row r="1623" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1623" s="3" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1623" s="3" t="s">
         <v>265</v>
@@ -59558,7 +59585,7 @@
         <v>127</v>
       </c>
       <c r="F1623" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1623" s="8" t="s">
         <v>279</v>
@@ -59577,7 +59604,7 @@
     </row>
     <row r="1624" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1624" s="3" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1624" s="3" t="s">
         <v>154</v>
@@ -59611,7 +59638,7 @@
     </row>
     <row r="1625" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1625" s="3" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1625" s="3" t="s">
         <v>248</v>
@@ -59626,7 +59653,7 @@
         <v>127</v>
       </c>
       <c r="F1625" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1625" s="8" t="s">
         <v>279</v>
@@ -59645,7 +59672,7 @@
     </row>
     <row r="1626" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1626" s="3" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1626" s="3" t="s">
         <v>149</v>
@@ -59660,7 +59687,7 @@
         <v>127</v>
       </c>
       <c r="F1626" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1626" s="8" t="s">
         <v>279</v>
@@ -59679,7 +59706,7 @@
     </row>
     <row r="1627" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1627" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B1627" s="3" t="s">
         <v>248</v>
@@ -59694,7 +59721,7 @@
         <v>127</v>
       </c>
       <c r="F1627" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1627" s="8" t="s">
         <v>279</v>
@@ -59713,7 +59740,7 @@
     </row>
     <row r="1628" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1628" s="3" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B1628" s="3" t="s">
         <v>200</v>
@@ -59728,7 +59755,7 @@
         <v>140</v>
       </c>
       <c r="F1628" s="3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="G1628" s="8" t="s">
         <v>280</v>
@@ -59747,7 +59774,7 @@
     </row>
     <row r="1629" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1629" s="3" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B1629" s="3" t="s">
         <v>180</v>
@@ -59762,7 +59789,7 @@
         <v>127</v>
       </c>
       <c r="F1629" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1629" s="8" t="s">
         <v>279</v>
@@ -59781,7 +59808,7 @@
     </row>
     <row r="1630" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1630" s="3" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B1630" s="3" t="s">
         <v>192</v>
@@ -59796,7 +59823,7 @@
         <v>127</v>
       </c>
       <c r="F1630" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1630" s="8" t="s">
         <v>279</v>
@@ -59815,7 +59842,7 @@
     </row>
     <row r="1631" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1631" s="3" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1631" s="3" t="s">
         <v>287</v>
@@ -59830,7 +59857,7 @@
         <v>127</v>
       </c>
       <c r="F1631" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1631" s="8" t="s">
         <v>279</v>
@@ -59849,7 +59876,7 @@
     </row>
     <row r="1632" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1632" s="3" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1632" s="3" t="s">
         <v>248</v>
@@ -59881,7 +59908,7 @@
     </row>
     <row r="1633" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1633" s="3" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B1633" s="3" t="s">
         <v>248</v>
@@ -59896,7 +59923,7 @@
         <v>127</v>
       </c>
       <c r="F1633" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1633" s="8" t="s">
         <v>279</v>
@@ -59915,7 +59942,7 @@
     </row>
     <row r="1634" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1634" s="3" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B1634" s="3" t="s">
         <v>123</v>
@@ -59947,7 +59974,7 @@
     </row>
     <row r="1635" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1635" s="3" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B1635" s="3" t="s">
         <v>154</v>
@@ -59979,7 +60006,7 @@
     </row>
     <row r="1636" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1636" s="3" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B1636" s="3" t="s">
         <v>180</v>
@@ -59994,7 +60021,7 @@
         <v>140</v>
       </c>
       <c r="F1636" s="3" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G1636" s="8" t="s">
         <v>280</v>
@@ -60013,7 +60040,7 @@
     </row>
     <row r="1637" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1637" s="3" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1637" s="3" t="s">
         <v>114</v>
@@ -60045,7 +60072,7 @@
     </row>
     <row r="1638" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1638" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1638" s="3" t="s">
         <v>248</v>
@@ -60077,7 +60104,7 @@
     </row>
     <row r="1639" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1639" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1639" s="3" t="s">
         <v>171</v>
@@ -60109,7 +60136,7 @@
     </row>
     <row r="1640" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1640" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1640" s="3" t="s">
         <v>174</v>
@@ -60141,7 +60168,7 @@
     </row>
     <row r="1641" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1641" s="3" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B1641" s="3" t="s">
         <v>248</v>
@@ -60173,7 +60200,7 @@
     </row>
     <row r="1642" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1642" s="3" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B1642" s="3" t="s">
         <v>154</v>
@@ -60205,7 +60232,7 @@
     </row>
     <row r="1643" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1643" s="3" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1643" s="3" t="s">
         <v>180</v>
@@ -60220,7 +60247,7 @@
         <v>140</v>
       </c>
       <c r="F1643" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G1643" s="8" t="s">
         <v>279</v>
@@ -60239,7 +60266,7 @@
     </row>
     <row r="1644" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1644" s="3" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1644" s="3" t="s">
         <v>191</v>
@@ -60254,7 +60281,7 @@
         <v>140</v>
       </c>
       <c r="F1644" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G1644" s="8" t="s">
         <v>279</v>
@@ -60273,7 +60300,7 @@
     </row>
     <row r="1645" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1645" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1645" s="3" t="s">
         <v>202</v>
@@ -60288,7 +60315,7 @@
         <v>140</v>
       </c>
       <c r="F1645" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G1645" s="8" t="s">
         <v>279</v>
@@ -60307,7 +60334,7 @@
     </row>
     <row r="1646" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1646" s="3" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1646" s="3" t="s">
         <v>248</v>
@@ -60339,7 +60366,7 @@
     </row>
     <row r="1647" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1647" s="3" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1647" s="3" t="s">
         <v>149</v>
@@ -60371,7 +60398,7 @@
     </row>
     <row r="1648" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1648" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1648" s="3" t="s">
         <v>248</v>
@@ -60403,7 +60430,7 @@
     </row>
     <row r="1649" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1649" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1649" s="3" t="s">
         <v>149</v>
@@ -60435,7 +60462,7 @@
     </row>
     <row r="1650" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1650" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1650" s="3" t="s">
         <v>132</v>
@@ -60447,10 +60474,10 @@
         <v>1305</v>
       </c>
       <c r="E1650" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F1650" s="3" t="s">
         <v>1457</v>
-      </c>
-      <c r="F1650" s="3" t="s">
-        <v>1458</v>
       </c>
       <c r="G1650" s="8" t="s">
         <v>279</v>
@@ -60469,7 +60496,7 @@
     </row>
     <row r="1651" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1651" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1651" s="3" t="s">
         <v>154</v>
@@ -60481,10 +60508,10 @@
         <v>168</v>
       </c>
       <c r="E1651" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F1651" s="3" t="s">
         <v>1457</v>
-      </c>
-      <c r="F1651" s="3" t="s">
-        <v>1458</v>
       </c>
       <c r="G1651" s="8" t="s">
         <v>279</v>
@@ -60503,7 +60530,7 @@
     </row>
     <row r="1652" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1652" s="3" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B1652" s="3" t="s">
         <v>154</v>
@@ -60515,10 +60542,10 @@
         <v>125</v>
       </c>
       <c r="E1652" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F1652" s="3" t="s">
         <v>1457</v>
-      </c>
-      <c r="F1652" s="3" t="s">
-        <v>1458</v>
       </c>
       <c r="G1652" s="8" t="s">
         <v>279</v>
@@ -60537,7 +60564,7 @@
     </row>
     <row r="1653" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1653" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1653" s="3" t="s">
         <v>248</v>
@@ -60569,7 +60596,7 @@
     </row>
     <row r="1654" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1654" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1654" s="3" t="s">
         <v>171</v>
@@ -60601,7 +60628,7 @@
     </row>
     <row r="1655" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1655" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1655" s="3" t="s">
         <v>355</v>
@@ -60613,10 +60640,10 @@
         <v>220</v>
       </c>
       <c r="E1655" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F1655" s="3" t="s">
         <v>1457</v>
-      </c>
-      <c r="F1655" s="3" t="s">
-        <v>1458</v>
       </c>
       <c r="G1655" s="8" t="s">
         <v>279</v>
@@ -60635,7 +60662,7 @@
     </row>
     <row r="1656" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1656" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1656" s="3" t="s">
         <v>209</v>
@@ -60647,10 +60674,10 @@
         <v>94</v>
       </c>
       <c r="E1656" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F1656" s="3" t="s">
         <v>1457</v>
-      </c>
-      <c r="F1656" s="3" t="s">
-        <v>1458</v>
       </c>
       <c r="G1656" s="8" t="s">
         <v>279</v>
@@ -60669,7 +60696,7 @@
     </row>
     <row r="1657" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1657" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1657" s="3" t="s">
         <v>333</v>
@@ -60681,7 +60708,7 @@
         <v>167</v>
       </c>
       <c r="E1657" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1657" s="3" t="s">
         <v>1285</v>
@@ -60703,7 +60730,7 @@
     </row>
     <row r="1658" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1658" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1658" s="3" t="s">
         <v>138</v>
@@ -60715,7 +60742,7 @@
         <v>115</v>
       </c>
       <c r="E1658" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1658" s="3" t="s">
         <v>1285</v>
@@ -60737,7 +60764,7 @@
     </row>
     <row r="1659" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1659" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1659" s="3" t="s">
         <v>329</v>
@@ -60749,7 +60776,7 @@
         <v>972</v>
       </c>
       <c r="E1659" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1659" s="3" t="s">
         <v>1285</v>
@@ -60771,7 +60798,7 @@
     </row>
     <row r="1660" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1660" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1660" s="3" t="s">
         <v>248</v>
@@ -60783,7 +60810,7 @@
         <v>184</v>
       </c>
       <c r="E1660" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1660" s="3" t="s">
         <v>1285</v>
@@ -60805,7 +60832,7 @@
     </row>
     <row r="1661" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1661" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1661" s="3" t="s">
         <v>149</v>
@@ -60817,7 +60844,7 @@
         <v>193</v>
       </c>
       <c r="E1661" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1661" s="3" t="s">
         <v>1285</v>
@@ -60839,7 +60866,7 @@
     </row>
     <row r="1662" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1662" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B1662" s="3" t="s">
         <v>355</v>
@@ -60851,7 +60878,7 @@
         <v>193</v>
       </c>
       <c r="E1662" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1662" s="3" t="s">
         <v>1285</v>
@@ -60873,7 +60900,7 @@
     </row>
     <row r="1663" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1663" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1663" s="3" t="s">
         <v>200</v>
@@ -60885,7 +60912,7 @@
         <v>136</v>
       </c>
       <c r="E1663" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1663" s="3" t="s">
         <v>1285</v>
@@ -60907,7 +60934,7 @@
     </row>
     <row r="1664" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1664" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1664" s="3" t="s">
         <v>375</v>
@@ -60919,7 +60946,7 @@
         <v>120</v>
       </c>
       <c r="E1664" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1664" s="3" t="s">
         <v>1285</v>
@@ -60941,7 +60968,7 @@
     </row>
     <row r="1665" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1665" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1665" s="3" t="s">
         <v>149</v>
@@ -60953,7 +60980,7 @@
         <v>239</v>
       </c>
       <c r="E1665" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1665" s="3" t="s">
         <v>1285</v>
@@ -60975,7 +61002,7 @@
     </row>
     <row r="1666" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1666" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B1666" s="3" t="s">
         <v>180</v>
@@ -60984,10 +61011,10 @@
         <v>267</v>
       </c>
       <c r="D1666" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="E1666" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1666" s="3" t="s">
         <v>1285</v>
@@ -61009,7 +61036,7 @@
     </row>
     <row r="1667" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1667" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B1667" s="3" t="s">
         <v>233</v>
@@ -61021,7 +61048,7 @@
         <v>120</v>
       </c>
       <c r="E1667" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1667" s="3" t="s">
         <v>1285</v>
@@ -61043,7 +61070,7 @@
     </row>
     <row r="1668" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1668" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1668" s="3" t="s">
         <v>359</v>
@@ -61055,7 +61082,7 @@
         <v>298</v>
       </c>
       <c r="E1668" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1668" s="3" t="s">
         <v>1285</v>
@@ -61077,7 +61104,7 @@
     </row>
     <row r="1669" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1669" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1669" s="3" t="s">
         <v>171</v>
@@ -61089,7 +61116,7 @@
         <v>120</v>
       </c>
       <c r="E1669" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1669" s="3" t="s">
         <v>1285</v>
@@ -61111,7 +61138,7 @@
     </row>
     <row r="1670" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1670" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1670" s="3" t="s">
         <v>248</v>
@@ -61123,7 +61150,7 @@
         <v>184</v>
       </c>
       <c r="E1670" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1670" s="3" t="s">
         <v>1285</v>
@@ -61145,7 +61172,7 @@
     </row>
     <row r="1671" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1671" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1671" s="3" t="s">
         <v>149</v>
@@ -61157,7 +61184,7 @@
         <v>193</v>
       </c>
       <c r="E1671" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1671" s="3" t="s">
         <v>1285</v>
@@ -61179,7 +61206,7 @@
     </row>
     <row r="1672" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1672" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B1672" s="3" t="s">
         <v>248</v>
@@ -61191,7 +61218,7 @@
         <v>184</v>
       </c>
       <c r="E1672" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1672" s="3" t="s">
         <v>1285</v>
@@ -61213,7 +61240,7 @@
     </row>
     <row r="1673" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1673" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B1673" s="3" t="s">
         <v>179</v>
@@ -61225,7 +61252,7 @@
         <v>1051</v>
       </c>
       <c r="E1673" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1673" s="3" t="s">
         <v>1285</v>
@@ -61247,7 +61274,7 @@
     </row>
     <row r="1674" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1674" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1674" s="3" t="s">
         <v>248</v>
@@ -61259,7 +61286,7 @@
         <v>184</v>
       </c>
       <c r="E1674" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1674" s="3" t="s">
         <v>1285</v>
@@ -61281,7 +61308,7 @@
     </row>
     <row r="1675" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1675" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1675" s="3" t="s">
         <v>149</v>
@@ -61293,7 +61320,7 @@
         <v>193</v>
       </c>
       <c r="E1675" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1675" s="3" t="s">
         <v>1285</v>
@@ -61315,7 +61342,7 @@
     </row>
     <row r="1676" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1676" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1676" s="3" t="s">
         <v>331</v>
@@ -61327,7 +61354,7 @@
         <v>126</v>
       </c>
       <c r="E1676" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1676" s="3" t="s">
         <v>1285</v>
@@ -61349,7 +61376,7 @@
     </row>
     <row r="1677" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1677" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1677" s="3" t="s">
         <v>333</v>
@@ -61361,7 +61388,7 @@
         <v>167</v>
       </c>
       <c r="E1677" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1677" s="3" t="s">
         <v>1285</v>
@@ -61383,7 +61410,7 @@
     </row>
     <row r="1678" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1678" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1678" s="3" t="s">
         <v>192</v>
@@ -61395,7 +61422,7 @@
         <v>115</v>
       </c>
       <c r="E1678" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1678" s="3" t="s">
         <v>1285</v>
@@ -61417,7 +61444,7 @@
     </row>
     <row r="1679" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1679" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1679" s="3" t="s">
         <v>271</v>
@@ -61429,7 +61456,7 @@
         <v>136</v>
       </c>
       <c r="E1679" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1679" s="3" t="s">
         <v>1285</v>
@@ -61451,7 +61478,7 @@
     </row>
     <row r="1680" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1680" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1680" s="3" t="s">
         <v>133</v>
@@ -61463,7 +61490,7 @@
         <v>875</v>
       </c>
       <c r="E1680" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1680" s="3" t="s">
         <v>1285</v>
@@ -61485,7 +61512,7 @@
     </row>
     <row r="1681" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1681" s="3" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B1681" s="3" t="s">
         <v>253</v>
@@ -61497,7 +61524,7 @@
         <v>193</v>
       </c>
       <c r="E1681" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1681" s="3" t="s">
         <v>1285</v>
@@ -61519,7 +61546,7 @@
     </row>
     <row r="1682" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1682" s="3" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B1682" s="3" t="s">
         <v>149</v>
@@ -61531,7 +61558,7 @@
         <v>193</v>
       </c>
       <c r="E1682" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1682" s="3" t="s">
         <v>1285</v>
@@ -61553,7 +61580,7 @@
     </row>
     <row r="1683" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1683" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B1683" s="3" t="s">
         <v>253</v>
@@ -61565,7 +61592,7 @@
         <v>193</v>
       </c>
       <c r="E1683" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1683" s="3" t="s">
         <v>1285</v>
@@ -61587,7 +61614,7 @@
     </row>
     <row r="1684" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1684" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1684" s="3" t="s">
         <v>253</v>
@@ -61599,7 +61626,7 @@
         <v>193</v>
       </c>
       <c r="E1684" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1684" s="3" t="s">
         <v>1285</v>
@@ -61621,7 +61648,7 @@
     </row>
     <row r="1685" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1685" s="3" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1685" s="3" t="s">
         <v>209</v>
@@ -61633,7 +61660,7 @@
         <v>120</v>
       </c>
       <c r="E1685" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1685" s="3" t="s">
         <v>1285</v>
@@ -61655,7 +61682,7 @@
     </row>
     <row r="1686" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1686" s="3" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1686" s="3" t="s">
         <v>179</v>
@@ -61667,7 +61694,7 @@
         <v>184</v>
       </c>
       <c r="E1686" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1686" s="3" t="s">
         <v>1285</v>
@@ -61689,7 +61716,7 @@
     </row>
     <row r="1687" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1687" s="3" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1687" s="3" t="s">
         <v>241</v>
@@ -61701,7 +61728,7 @@
         <v>184</v>
       </c>
       <c r="E1687" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1687" s="3" t="s">
         <v>1285</v>
@@ -61723,7 +61750,7 @@
     </row>
     <row r="1688" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1688" s="3" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1688" s="3" t="s">
         <v>179</v>
@@ -61735,7 +61762,7 @@
         <v>184</v>
       </c>
       <c r="E1688" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1688" s="3" t="s">
         <v>1285</v>
@@ -61757,7 +61784,7 @@
     </row>
     <row r="1689" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1689" s="3" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1689" s="3" t="s">
         <v>132</v>
@@ -61769,7 +61796,7 @@
         <v>184</v>
       </c>
       <c r="E1689" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1689" s="3" t="s">
         <v>1285</v>
@@ -61791,7 +61818,7 @@
     </row>
     <row r="1690" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1690" s="3" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B1690" s="3" t="s">
         <v>355</v>
@@ -61803,7 +61830,7 @@
         <v>105</v>
       </c>
       <c r="E1690" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1690" s="3" t="s">
         <v>1285</v>
@@ -61825,7 +61852,7 @@
     </row>
     <row r="1691" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1691" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1691" s="3" t="s">
         <v>253</v>
@@ -61837,7 +61864,7 @@
         <v>193</v>
       </c>
       <c r="E1691" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1691" s="3" t="s">
         <v>1285</v>
@@ -61859,7 +61886,7 @@
     </row>
     <row r="1692" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1692" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1692" s="3" t="s">
         <v>157</v>
@@ -61891,7 +61918,7 @@
     </row>
     <row r="1693" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1693" s="3" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1693" s="3" t="s">
         <v>249</v>
@@ -61903,7 +61930,7 @@
         <v>251</v>
       </c>
       <c r="E1693" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1693" s="3" t="s">
         <v>1285</v>
@@ -61925,7 +61952,7 @@
     </row>
     <row r="1694" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1694" s="3" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1694" s="3" t="s">
         <v>171</v>
@@ -61937,7 +61964,7 @@
         <v>251</v>
       </c>
       <c r="E1694" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1694" s="3" t="s">
         <v>1285</v>
@@ -61959,7 +61986,7 @@
     </row>
     <row r="1695" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1695" s="3" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1695" s="3" t="s">
         <v>200</v>
@@ -61991,7 +62018,7 @@
     </row>
     <row r="1696" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1696" s="3" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1696" s="3" t="s">
         <v>150</v>
@@ -62003,7 +62030,7 @@
         <v>115</v>
       </c>
       <c r="E1696" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1696" s="3" t="s">
         <v>1285</v>
@@ -62025,7 +62052,7 @@
     </row>
     <row r="1697" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1697" s="3" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1697" s="5" t="s">
         <v>200</v>
@@ -62037,7 +62064,7 @@
         <v>167</v>
       </c>
       <c r="E1697" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1697" s="3" t="s">
         <v>1285</v>
@@ -62059,7 +62086,7 @@
     </row>
     <row r="1698" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1698" s="3" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B1698" s="3" t="s">
         <v>329</v>
@@ -62071,7 +62098,7 @@
         <v>144</v>
       </c>
       <c r="E1698" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1698" s="3" t="s">
         <v>1285</v>
@@ -62093,7 +62120,7 @@
     </row>
     <row r="1699" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1699" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1699" s="3" t="s">
         <v>248</v>
@@ -62105,7 +62132,7 @@
         <v>184</v>
       </c>
       <c r="E1699" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1699" s="3" t="s">
         <v>1285</v>
@@ -62127,7 +62154,7 @@
     </row>
     <row r="1700" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1700" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1700" s="3" t="s">
         <v>219</v>
@@ -62139,7 +62166,7 @@
         <v>193</v>
       </c>
       <c r="E1700" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1700" s="3" t="s">
         <v>1285</v>
@@ -62161,7 +62188,7 @@
     </row>
     <row r="1701" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1701" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1701" s="3" t="s">
         <v>196</v>
@@ -62173,7 +62200,7 @@
         <v>193</v>
       </c>
       <c r="E1701" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1701" s="3" t="s">
         <v>1285</v>
@@ -62195,7 +62222,7 @@
     </row>
     <row r="1702" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1702" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1702" s="3" t="s">
         <v>157</v>
@@ -62207,7 +62234,7 @@
         <v>193</v>
       </c>
       <c r="E1702" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1702" s="3" t="s">
         <v>1285</v>
@@ -62229,7 +62256,7 @@
     </row>
     <row r="1703" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1703" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B1703" s="3" t="s">
         <v>114</v>
@@ -62241,7 +62268,7 @@
         <v>193</v>
       </c>
       <c r="E1703" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1703" s="3" t="s">
         <v>1285</v>
@@ -62263,7 +62290,7 @@
     </row>
     <row r="1704" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1704" s="3" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B1704" s="3" t="s">
         <v>248</v>
@@ -62275,7 +62302,7 @@
         <v>184</v>
       </c>
       <c r="E1704" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1704" s="3" t="s">
         <v>1285</v>
@@ -62297,7 +62324,7 @@
     </row>
     <row r="1705" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1705" s="3" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B1705" s="3" t="s">
         <v>154</v>
@@ -62309,7 +62336,7 @@
         <v>168</v>
       </c>
       <c r="E1705" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1705" s="3" t="s">
         <v>1285</v>
@@ -62331,7 +62358,7 @@
     </row>
     <row r="1706" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1706" s="3" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B1706" s="3" t="s">
         <v>338</v>
@@ -62343,7 +62370,7 @@
         <v>272</v>
       </c>
       <c r="E1706" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1706" s="3" t="s">
         <v>1285</v>
@@ -62365,7 +62392,7 @@
     </row>
     <row r="1707" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1707" s="3" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B1707" s="3" t="s">
         <v>161</v>
@@ -62377,7 +62404,7 @@
         <v>184</v>
       </c>
       <c r="E1707" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1707" s="3" t="s">
         <v>1285</v>
@@ -62399,7 +62426,7 @@
     </row>
     <row r="1708" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1708" s="3" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B1708" s="3" t="s">
         <v>248</v>
@@ -62411,7 +62438,7 @@
         <v>184</v>
       </c>
       <c r="E1708" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1708" s="3" t="s">
         <v>1285</v>
@@ -62433,7 +62460,7 @@
     </row>
     <row r="1709" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1709" s="3" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B1709" s="3" t="s">
         <v>219</v>
@@ -62445,7 +62472,7 @@
         <v>184</v>
       </c>
       <c r="E1709" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1709" s="3" t="s">
         <v>1285</v>
@@ -62467,7 +62494,7 @@
     </row>
     <row r="1710" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1710" s="3" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B1710" s="3" t="s">
         <v>355</v>
@@ -62479,7 +62506,7 @@
         <v>220</v>
       </c>
       <c r="E1710" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1710" s="3" t="s">
         <v>1285</v>
@@ -62501,7 +62528,7 @@
     </row>
     <row r="1711" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1711" s="3" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B1711" s="3" t="s">
         <v>209</v>
@@ -62513,7 +62540,7 @@
         <v>167</v>
       </c>
       <c r="E1711" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1711" s="3" t="s">
         <v>1285</v>
@@ -62535,7 +62562,7 @@
     </row>
     <row r="1712" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1712" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B1712" s="3" t="s">
         <v>340</v>
@@ -62547,7 +62574,7 @@
         <v>347</v>
       </c>
       <c r="E1712" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1712" s="3" t="s">
         <v>1285</v>
@@ -62569,7 +62596,7 @@
     </row>
     <row r="1713" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1713" s="3" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B1713" s="3" t="s">
         <v>202</v>
@@ -62581,7 +62608,7 @@
         <v>168</v>
       </c>
       <c r="E1713" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1713" s="3" t="s">
         <v>1285</v>
@@ -62603,7 +62630,7 @@
     </row>
     <row r="1714" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1714" s="3" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B1714" s="3" t="s">
         <v>171</v>
@@ -62615,7 +62642,7 @@
         <v>120</v>
       </c>
       <c r="E1714" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1714" s="3" t="s">
         <v>1285</v>
@@ -62637,10 +62664,10 @@
     </row>
     <row r="1715" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1715" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B1715" s="3" t="s">
         <v>1497</v>
-      </c>
-      <c r="B1715" s="3" t="s">
-        <v>1498</v>
       </c>
       <c r="C1715" s="3" t="s">
         <v>249</v>
@@ -62649,7 +62676,7 @@
         <v>184</v>
       </c>
       <c r="E1715" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1715" s="3" t="s">
         <v>1285</v>
@@ -62671,7 +62698,7 @@
     </row>
     <row r="1716" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1716" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B1716" s="3" t="s">
         <v>171</v>
@@ -62683,7 +62710,7 @@
         <v>184</v>
       </c>
       <c r="E1716" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1716" s="3" t="s">
         <v>1285</v>
@@ -62705,7 +62732,7 @@
     </row>
     <row r="1717" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1717" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1717" s="3" t="s">
         <v>200</v>
@@ -62717,7 +62744,7 @@
         <v>105</v>
       </c>
       <c r="E1717" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1717" s="3" t="s">
         <v>1285</v>
@@ -62739,7 +62766,7 @@
     </row>
     <row r="1718" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1718" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1718" s="3" t="s">
         <v>160</v>
@@ -62751,7 +62778,7 @@
         <v>217</v>
       </c>
       <c r="E1718" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1718" s="3" t="s">
         <v>1285</v>
@@ -62773,7 +62800,7 @@
     </row>
     <row r="1719" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1719" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1719" s="3" t="s">
         <v>196</v>
@@ -62785,7 +62812,7 @@
         <v>115</v>
       </c>
       <c r="E1719" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1719" s="3" t="s">
         <v>1285</v>
@@ -62807,7 +62834,7 @@
     </row>
     <row r="1720" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1720" s="3" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B1720" s="3" t="s">
         <v>329</v>
@@ -62819,7 +62846,7 @@
         <v>584</v>
       </c>
       <c r="E1720" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1720" s="3" t="s">
         <v>1285</v>
@@ -62841,7 +62868,7 @@
     </row>
     <row r="1721" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1721" s="3" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B1721" s="3" t="s">
         <v>119</v>
@@ -62853,7 +62880,7 @@
         <v>193</v>
       </c>
       <c r="E1721" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1721" s="3" t="s">
         <v>1285</v>
@@ -62875,7 +62902,7 @@
     </row>
     <row r="1722" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1722" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B1722" s="3" t="s">
         <v>114</v>
@@ -62887,7 +62914,7 @@
         <v>193</v>
       </c>
       <c r="E1722" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1722" s="3" t="s">
         <v>1285</v>
@@ -62909,7 +62936,7 @@
     </row>
     <row r="1723" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1723" s="3" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B1723" s="3" t="s">
         <v>331</v>
@@ -62921,7 +62948,7 @@
         <v>125</v>
       </c>
       <c r="E1723" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1723" s="3" t="s">
         <v>1285</v>
@@ -62943,7 +62970,7 @@
     </row>
     <row r="1724" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1724" s="3" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B1724" s="3" t="s">
         <v>242</v>
@@ -62955,7 +62982,7 @@
         <v>272</v>
       </c>
       <c r="E1724" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1724" s="3" t="s">
         <v>1285</v>
@@ -62977,7 +63004,7 @@
     </row>
     <row r="1725" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1725" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B1725" s="3" t="s">
         <v>287</v>
@@ -62989,7 +63016,7 @@
         <v>272</v>
       </c>
       <c r="E1725" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1725" s="3" t="s">
         <v>1285</v>
@@ -63011,7 +63038,7 @@
     </row>
     <row r="1726" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1726" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B1726" s="3" t="s">
         <v>149</v>
@@ -63023,7 +63050,7 @@
         <v>126</v>
       </c>
       <c r="E1726" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1726" s="3" t="s">
         <v>1285</v>
@@ -63045,7 +63072,7 @@
     </row>
     <row r="1727" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1727" s="3" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B1727" s="3" t="s">
         <v>359</v>
@@ -63057,7 +63084,7 @@
         <v>94</v>
       </c>
       <c r="E1727" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1727" s="3" t="s">
         <v>1285</v>
@@ -63079,7 +63106,7 @@
     </row>
     <row r="1728" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1728" s="3" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B1728" s="3" t="s">
         <v>248</v>
@@ -63091,7 +63118,7 @@
         <v>184</v>
       </c>
       <c r="E1728" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1728" s="3" t="s">
         <v>1285</v>
@@ -63113,7 +63140,7 @@
     </row>
     <row r="1729" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1729" s="3" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B1729" s="3" t="s">
         <v>248</v>
@@ -63125,7 +63152,7 @@
         <v>184</v>
       </c>
       <c r="E1729" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1729" s="3" t="s">
         <v>1285</v>
@@ -63147,7 +63174,7 @@
     </row>
     <row r="1730" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1730" s="3" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B1730" s="3" t="s">
         <v>171</v>
@@ -63159,7 +63186,7 @@
         <v>184</v>
       </c>
       <c r="E1730" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1730" s="3" t="s">
         <v>1285</v>
@@ -63181,7 +63208,7 @@
     </row>
     <row r="1731" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1731" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B1731" s="3" t="s">
         <v>359</v>
@@ -63193,7 +63220,7 @@
         <v>111</v>
       </c>
       <c r="E1731" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1731" s="3" t="s">
         <v>1285</v>
@@ -63215,7 +63242,7 @@
     </row>
     <row r="1732" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1732" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B1732" s="3" t="s">
         <v>375</v>
@@ -63227,7 +63254,7 @@
         <v>94</v>
       </c>
       <c r="E1732" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1732" s="3" t="s">
         <v>1285</v>
@@ -63249,7 +63276,7 @@
     </row>
     <row r="1733" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1733" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B1733" s="3" t="s">
         <v>174</v>
@@ -63261,7 +63288,7 @@
         <v>105</v>
       </c>
       <c r="E1733" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1733" s="3" t="s">
         <v>1285</v>
@@ -63283,7 +63310,7 @@
     </row>
     <row r="1734" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1734" s="3" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B1734" s="3" t="s">
         <v>564</v>
@@ -63295,7 +63322,7 @@
         <v>870</v>
       </c>
       <c r="E1734" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1734" s="3" t="s">
         <v>1285</v>
@@ -63317,7 +63344,7 @@
     </row>
     <row r="1735" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1735" s="3" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B1735" s="3" t="s">
         <v>154</v>
@@ -63329,7 +63356,7 @@
         <v>120</v>
       </c>
       <c r="E1735" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1735" s="3" t="s">
         <v>1285</v>
@@ -63351,7 +63378,7 @@
     </row>
     <row r="1736" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1736" s="3" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B1736" s="3" t="s">
         <v>287</v>
@@ -63363,7 +63390,7 @@
         <v>1051</v>
       </c>
       <c r="E1736" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1736" s="3" t="s">
         <v>1285</v>
@@ -63385,7 +63412,7 @@
     </row>
     <row r="1737" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1737" s="3" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B1737" s="3" t="s">
         <v>171</v>
@@ -63417,7 +63444,7 @@
     </row>
     <row r="1738" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1738" s="3" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B1738" s="3" t="s">
         <v>353</v>
@@ -63449,7 +63476,7 @@
     </row>
     <row r="1739" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1739" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B1739" s="3" t="s">
         <v>248</v>
@@ -63481,7 +63508,7 @@
     </row>
     <row r="1740" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1740" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B1740" s="3" t="s">
         <v>171</v>
@@ -63513,7 +63540,7 @@
     </row>
     <row r="1741" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1741" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B1741" s="3" t="s">
         <v>196</v>
@@ -63545,7 +63572,7 @@
     </row>
     <row r="1742" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1742" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1742" s="3" t="s">
         <v>359</v>
@@ -63577,7 +63604,7 @@
     </row>
     <row r="1743" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1743" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1743" s="3" t="s">
         <v>375</v>
@@ -63609,7 +63636,7 @@
     </row>
     <row r="1744" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1744" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1744" s="3" t="s">
         <v>191</v>
@@ -63641,7 +63668,7 @@
     </row>
     <row r="1745" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1745" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1745" s="3" t="s">
         <v>353</v>
@@ -63673,7 +63700,7 @@
     </row>
     <row r="1746" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1746" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B1746" s="3" t="s">
         <v>287</v>
@@ -63705,7 +63732,7 @@
     </row>
     <row r="1747" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1747" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B1747" s="3" t="s">
         <v>288</v>
@@ -63737,7 +63764,7 @@
     </row>
     <row r="1748" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1748" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B1748" s="3" t="s">
         <v>353</v>
@@ -63769,7 +63796,7 @@
     </row>
     <row r="1749" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1749" s="3" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B1749" s="3" t="s">
         <v>233</v>
@@ -63801,7 +63828,7 @@
     </row>
     <row r="1750" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1750" s="3" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B1750" s="3" t="s">
         <v>149</v>
@@ -63833,7 +63860,7 @@
     </row>
     <row r="1751" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1751" s="3" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B1751" s="3" t="s">
         <v>361</v>
@@ -63865,7 +63892,7 @@
     </row>
     <row r="1752" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1752" s="3" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B1752" s="3" t="s">
         <v>134</v>
@@ -63897,7 +63924,7 @@
     </row>
     <row r="1753" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1753" s="3" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B1753" s="3" t="s">
         <v>200</v>
@@ -63929,7 +63956,7 @@
     </row>
     <row r="1754" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1754" s="3" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B1754" s="3" t="s">
         <v>459</v>
@@ -63961,7 +63988,7 @@
     </row>
     <row r="1755" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1755" s="3" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B1755" s="3" t="s">
         <v>200</v>
@@ -63973,7 +64000,7 @@
         <v>870</v>
       </c>
       <c r="E1755" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1755" s="3" t="s">
         <v>1285</v>
@@ -63995,7 +64022,7 @@
     </row>
     <row r="1756" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1756" s="3" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B1756" s="3" t="s">
         <v>233</v>
@@ -64027,7 +64054,7 @@
     </row>
     <row r="1757" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1757" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B1757" s="3" t="s">
         <v>253</v>
@@ -64059,7 +64086,7 @@
     </row>
     <row r="1758" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1758" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B1758" s="3" t="s">
         <v>149</v>
@@ -64091,7 +64118,7 @@
     </row>
     <row r="1759" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1759" s="3" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B1759" s="3" t="s">
         <v>253</v>
@@ -64123,7 +64150,7 @@
     </row>
     <row r="1760" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1760" s="3" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B1760" s="3" t="s">
         <v>202</v>
@@ -64135,7 +64162,7 @@
         <v>94</v>
       </c>
       <c r="E1760" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1760" s="3" t="s">
         <v>1285</v>
@@ -64157,7 +64184,7 @@
     </row>
     <row r="1761" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1761" s="3" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B1761" s="3" t="s">
         <v>154</v>
@@ -64169,7 +64196,7 @@
         <v>184</v>
       </c>
       <c r="E1761" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1761" s="3" t="s">
         <v>1285</v>
@@ -64191,7 +64218,7 @@
     </row>
     <row r="1762" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1762" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1762" s="3" t="s">
         <v>202</v>
@@ -64203,7 +64230,7 @@
         <v>220</v>
       </c>
       <c r="E1762" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1762" s="3" t="s">
         <v>1285</v>
@@ -64225,7 +64252,7 @@
     </row>
     <row r="1763" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1763" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1763" s="3" t="s">
         <v>209</v>
@@ -64237,7 +64264,7 @@
         <v>111</v>
       </c>
       <c r="E1763" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1763" s="3" t="s">
         <v>1285</v>
@@ -64259,7 +64286,7 @@
     </row>
     <row r="1764" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1764" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1764" s="3" t="s">
         <v>119</v>
@@ -64271,7 +64298,7 @@
         <v>220</v>
       </c>
       <c r="E1764" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1764" s="3" t="s">
         <v>1285</v>
@@ -64293,7 +64320,7 @@
     </row>
     <row r="1765" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1765" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1765" s="3" t="s">
         <v>124</v>
@@ -64305,7 +64332,7 @@
         <v>193</v>
       </c>
       <c r="E1765" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1765" s="3" t="s">
         <v>1285</v>
@@ -64327,7 +64354,7 @@
     </row>
     <row r="1766" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1766" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1766" s="3" t="s">
         <v>135</v>
@@ -64339,7 +64366,7 @@
         <v>115</v>
       </c>
       <c r="E1766" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1766" s="3" t="s">
         <v>1285</v>
@@ -64361,7 +64388,7 @@
     </row>
     <row r="1767" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1767" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B1767" s="3" t="s">
         <v>355</v>
@@ -64373,7 +64400,7 @@
         <v>9</v>
       </c>
       <c r="E1767" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1767" s="3" t="s">
         <v>1285</v>
@@ -64395,7 +64422,7 @@
     </row>
     <row r="1768" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1768" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B1768" s="3" t="s">
         <v>124</v>
@@ -64407,7 +64434,7 @@
         <v>251</v>
       </c>
       <c r="E1768" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1768" s="3" t="s">
         <v>1285</v>
@@ -64429,7 +64456,7 @@
     </row>
     <row r="1769" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1769" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B1769" s="3" t="s">
         <v>331</v>
@@ -64441,7 +64468,7 @@
         <v>9</v>
       </c>
       <c r="E1769" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1769" s="3" t="s">
         <v>1285</v>
@@ -64463,7 +64490,7 @@
     </row>
     <row r="1770" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1770" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B1770" s="3" t="s">
         <v>209</v>
@@ -64475,7 +64502,7 @@
         <v>167</v>
       </c>
       <c r="E1770" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1770" s="3" t="s">
         <v>1285</v>
@@ -64497,7 +64524,7 @@
     </row>
     <row r="1771" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1771" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B1771" s="3" t="s">
         <v>132</v>
@@ -64509,7 +64536,7 @@
         <v>875</v>
       </c>
       <c r="E1771" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1771" s="3" t="s">
         <v>1285</v>
@@ -64531,7 +64558,7 @@
     </row>
     <row r="1772" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1772" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B1772" s="3" t="s">
         <v>353</v>
@@ -64543,7 +64570,7 @@
         <v>136</v>
       </c>
       <c r="E1772" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1772" s="3" t="s">
         <v>1285</v>
@@ -64565,7 +64592,7 @@
     </row>
     <row r="1773" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1773" s="3" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B1773" s="3" t="s">
         <v>288</v>
@@ -64577,7 +64604,7 @@
         <v>272</v>
       </c>
       <c r="E1773" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1773" s="3" t="s">
         <v>1285</v>
@@ -64599,7 +64626,7 @@
     </row>
     <row r="1774" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1774" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B1774" s="3" t="s">
         <v>241</v>
@@ -64611,7 +64638,7 @@
         <v>136</v>
       </c>
       <c r="E1774" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1774" s="3" t="s">
         <v>1285</v>
@@ -64633,7 +64660,7 @@
     </row>
     <row r="1775" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1775" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B1775" s="3" t="s">
         <v>160</v>
@@ -64645,7 +64672,7 @@
         <v>136</v>
       </c>
       <c r="E1775" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1775" s="3" t="s">
         <v>1285</v>
@@ -64667,7 +64694,7 @@
     </row>
     <row r="1776" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1776" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B1776" s="3" t="s">
         <v>134</v>
@@ -64679,7 +64706,7 @@
         <v>105</v>
       </c>
       <c r="E1776" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1776" s="3" t="s">
         <v>1285</v>
@@ -64701,7 +64728,7 @@
     </row>
     <row r="1777" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1777" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B1777" s="3" t="s">
         <v>203</v>
@@ -64713,7 +64740,7 @@
         <v>115</v>
       </c>
       <c r="E1777" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1777" s="3" t="s">
         <v>1285</v>
@@ -64735,7 +64762,7 @@
     </row>
     <row r="1778" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1778" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B1778" s="3" t="s">
         <v>133</v>
@@ -64747,7 +64774,7 @@
         <v>870</v>
       </c>
       <c r="E1778" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1778" s="3" t="s">
         <v>1285</v>
@@ -64769,7 +64796,7 @@
     </row>
     <row r="1779" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1779" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B1779" s="3" t="s">
         <v>124</v>
@@ -64781,7 +64808,7 @@
         <v>217</v>
       </c>
       <c r="E1779" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1779" s="3" t="s">
         <v>1285</v>
@@ -64803,7 +64830,7 @@
     </row>
     <row r="1780" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1780" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B1780" s="3" t="s">
         <v>336</v>
@@ -64815,7 +64842,7 @@
         <v>1305</v>
       </c>
       <c r="E1780" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1780" s="3" t="s">
         <v>1285</v>
@@ -64837,7 +64864,7 @@
     </row>
     <row r="1781" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1781" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B1781" s="3" t="s">
         <v>157</v>
@@ -64849,7 +64876,7 @@
         <v>105</v>
       </c>
       <c r="E1781" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1781" s="3" t="s">
         <v>1285</v>
@@ -64871,7 +64898,7 @@
     </row>
     <row r="1782" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1782" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B1782" s="3" t="s">
         <v>304</v>
@@ -64883,7 +64910,7 @@
         <v>115</v>
       </c>
       <c r="E1782" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1782" s="3" t="s">
         <v>1285</v>
@@ -64905,7 +64932,7 @@
     </row>
     <row r="1783" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1783" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B1783" s="3" t="s">
         <v>200</v>
@@ -64917,7 +64944,7 @@
         <v>94</v>
       </c>
       <c r="E1783" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1783" s="3" t="s">
         <v>1285</v>
@@ -64939,7 +64966,7 @@
     </row>
     <row r="1784" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1784" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B1784" s="3" t="s">
         <v>191</v>
@@ -64951,7 +64978,7 @@
         <v>193</v>
       </c>
       <c r="E1784" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1784" s="3" t="s">
         <v>1285</v>
@@ -64973,7 +65000,7 @@
     </row>
     <row r="1785" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1785" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B1785" s="3" t="s">
         <v>387</v>
@@ -64985,7 +65012,7 @@
         <v>220</v>
       </c>
       <c r="E1785" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1785" s="3" t="s">
         <v>1285</v>
@@ -65007,7 +65034,7 @@
     </row>
     <row r="1786" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1786" s="3" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B1786" s="3" t="s">
         <v>459</v>
@@ -65019,7 +65046,7 @@
         <v>272</v>
       </c>
       <c r="E1786" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1786" s="3" t="s">
         <v>1285</v>
@@ -65041,7 +65068,7 @@
     </row>
     <row r="1787" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1787" s="3" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B1787" s="3" t="s">
         <v>160</v>
@@ -65053,7 +65080,7 @@
         <v>239</v>
       </c>
       <c r="E1787" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1787" s="3" t="s">
         <v>1285</v>
@@ -65075,7 +65102,7 @@
     </row>
     <row r="1788" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1788" s="3" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B1788" s="3" t="s">
         <v>203</v>
@@ -65087,7 +65114,7 @@
         <v>115</v>
       </c>
       <c r="E1788" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1788" s="3" t="s">
         <v>1285</v>
@@ -65109,7 +65136,7 @@
     </row>
     <row r="1789" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1789" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B1789" s="3" t="s">
         <v>209</v>
@@ -65121,7 +65148,7 @@
         <v>167</v>
       </c>
       <c r="E1789" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1789" s="3" t="s">
         <v>1285</v>
@@ -65143,7 +65170,7 @@
     </row>
     <row r="1790" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1790" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B1790" s="3" t="s">
         <v>114</v>
@@ -65155,7 +65182,7 @@
         <v>126</v>
       </c>
       <c r="E1790" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1790" s="3" t="s">
         <v>1285</v>
@@ -65177,7 +65204,7 @@
     </row>
     <row r="1791" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1791" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B1791" s="3" t="s">
         <v>271</v>
@@ -65189,7 +65216,7 @@
         <v>105</v>
       </c>
       <c r="E1791" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1791" s="3" t="s">
         <v>1285</v>
@@ -65211,7 +65238,7 @@
     </row>
     <row r="1792" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1792" s="3" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B1792" s="3" t="s">
         <v>340</v>
@@ -65223,7 +65250,7 @@
         <v>875</v>
       </c>
       <c r="E1792" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1792" s="3" t="s">
         <v>1285</v>
@@ -65245,7 +65272,7 @@
     </row>
     <row r="1793" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1793" s="3" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B1793" s="3" t="s">
         <v>114</v>
@@ -65257,7 +65284,7 @@
         <v>105</v>
       </c>
       <c r="E1793" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1793" s="3" t="s">
         <v>1285</v>
@@ -65279,7 +65306,7 @@
     </row>
     <row r="1794" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1794" s="3" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1794" s="3" t="s">
         <v>122</v>
@@ -65291,7 +65318,7 @@
         <v>389</v>
       </c>
       <c r="E1794" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F1794" s="3" t="s">
         <v>1285</v>
@@ -65313,7 +65340,7 @@
     </row>
     <row r="1795" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1795" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B1795" s="3" t="s">
         <v>200</v>
@@ -65347,7 +65374,7 @@
     </row>
     <row r="1796" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1796" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B1796" s="3" t="s">
         <v>210</v>
@@ -65362,7 +65389,7 @@
         <v>127</v>
       </c>
       <c r="F1796" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1796" s="8" t="s">
         <v>279</v>
@@ -65381,7 +65408,7 @@
     </row>
     <row r="1797" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1797" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B1797" s="3" t="s">
         <v>336</v>
@@ -65396,7 +65423,7 @@
         <v>127</v>
       </c>
       <c r="F1797" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1797" s="8" t="s">
         <v>279</v>
@@ -65415,7 +65442,7 @@
     </row>
     <row r="1798" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1798" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B1798" s="3" t="s">
         <v>135</v>
@@ -65430,7 +65457,7 @@
         <v>127</v>
       </c>
       <c r="F1798" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1798" s="8" t="s">
         <v>279</v>
@@ -65449,7 +65476,7 @@
     </row>
     <row r="1799" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1799" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B1799" s="3" t="s">
         <v>361</v>
@@ -65464,7 +65491,7 @@
         <v>127</v>
       </c>
       <c r="F1799" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1799" s="8" t="s">
         <v>279</v>
@@ -65483,7 +65510,7 @@
     </row>
     <row r="1800" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1800" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B1800" s="3" t="s">
         <v>119</v>
@@ -65498,7 +65525,7 @@
         <v>127</v>
       </c>
       <c r="F1800" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1800" s="8" t="s">
         <v>279</v>
@@ -65517,7 +65544,7 @@
     </row>
     <row r="1801" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1801" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B1801" s="3" t="s">
         <v>285</v>
@@ -65532,7 +65559,7 @@
         <v>127</v>
       </c>
       <c r="F1801" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1801" s="8" t="s">
         <v>279</v>
@@ -65551,7 +65578,7 @@
     </row>
     <row r="1802" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1802" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B1802" s="3" t="s">
         <v>147</v>
@@ -65566,7 +65593,7 @@
         <v>127</v>
       </c>
       <c r="F1802" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1802" s="8" t="s">
         <v>279</v>
@@ -65585,7 +65612,7 @@
     </row>
     <row r="1803" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1803" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B1803" s="3" t="s">
         <v>288</v>
@@ -65594,13 +65621,13 @@
         <v>124</v>
       </c>
       <c r="D1803" s="3" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="E1803" s="3" t="s">
         <v>127</v>
       </c>
       <c r="F1803" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1803" s="8" t="s">
         <v>279</v>
@@ -65619,7 +65646,7 @@
     </row>
     <row r="1804" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1804" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B1804" s="3" t="s">
         <v>203</v>
@@ -65634,7 +65661,7 @@
         <v>127</v>
       </c>
       <c r="F1804" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G1804" s="8" t="s">
         <v>279</v>
@@ -65653,7 +65680,7 @@
     </row>
     <row r="1805" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1805" s="3" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B1805" s="3" t="s">
         <v>150</v>
@@ -65668,7 +65695,7 @@
         <v>127</v>
       </c>
       <c r="F1805" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1805" s="8" t="s">
         <v>279</v>
@@ -65687,7 +65714,7 @@
     </row>
     <row r="1806" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1806" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B1806" s="3" t="s">
         <v>160</v>
@@ -65702,7 +65729,7 @@
         <v>127</v>
       </c>
       <c r="F1806" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1806" s="8" t="s">
         <v>279</v>
@@ -65721,7 +65748,7 @@
     </row>
     <row r="1807" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1807" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B1807" s="3" t="s">
         <v>353</v>
@@ -65736,7 +65763,7 @@
         <v>127</v>
       </c>
       <c r="F1807" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1807" s="8" t="s">
         <v>279</v>
@@ -65755,7 +65782,7 @@
     </row>
     <row r="1808" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1808" s="3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1808" s="3" t="s">
         <v>288</v>
@@ -65770,7 +65797,7 @@
         <v>127</v>
       </c>
       <c r="F1808" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1808" s="8" t="s">
         <v>279</v>
@@ -65789,7 +65816,7 @@
     </row>
     <row r="1809" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1809" s="3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1809" s="3" t="s">
         <v>233</v>
@@ -65804,7 +65831,7 @@
         <v>127</v>
       </c>
       <c r="F1809" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1809" s="8" t="s">
         <v>279</v>
@@ -65823,7 +65850,7 @@
     </row>
     <row r="1810" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1810" s="3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1810" s="3" t="s">
         <v>304</v>
@@ -65838,7 +65865,7 @@
         <v>127</v>
       </c>
       <c r="F1810" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1810" s="8" t="s">
         <v>279</v>
@@ -65857,7 +65884,7 @@
     </row>
     <row r="1811" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1811" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B1811" s="3" t="s">
         <v>327</v>
@@ -65872,7 +65899,7 @@
         <v>127</v>
       </c>
       <c r="F1811" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1811" s="8" t="s">
         <v>279</v>
@@ -65891,7 +65918,7 @@
     </row>
     <row r="1812" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1812" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B1812" s="3" t="s">
         <v>211</v>
@@ -65906,7 +65933,7 @@
         <v>127</v>
       </c>
       <c r="F1812" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1812" s="8" t="s">
         <v>279</v>
@@ -65925,7 +65952,7 @@
     </row>
     <row r="1813" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1813" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B1813" s="3" t="s">
         <v>123</v>
@@ -65940,7 +65967,7 @@
         <v>127</v>
       </c>
       <c r="F1813" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="G1813" s="8" t="s">
         <v>279</v>
@@ -65959,7 +65986,7 @@
     </row>
     <row r="1814" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1814" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B1814" s="3" t="s">
         <v>233</v>
@@ -65991,7 +66018,7 @@
     </row>
     <row r="1815" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1815" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B1815" s="3" t="s">
         <v>271</v>
@@ -66006,7 +66033,7 @@
         <v>127</v>
       </c>
       <c r="F1815" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="G1815" s="8" t="s">
         <v>279</v>
@@ -66025,7 +66052,7 @@
     </row>
     <row r="1816" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1816" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B1816" s="3" t="s">
         <v>204</v>
@@ -66040,7 +66067,7 @@
         <v>127</v>
       </c>
       <c r="F1816" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="G1816" s="8" t="s">
         <v>279</v>
@@ -66059,7 +66086,7 @@
     </row>
     <row r="1817" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1817" s="3" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B1817" s="3" t="s">
         <v>333</v>
@@ -66074,7 +66101,7 @@
         <v>127</v>
       </c>
       <c r="F1817" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="G1817" s="8" t="s">
         <v>279</v>
@@ -66093,7 +66120,7 @@
     </row>
     <row r="1818" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1818" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B1818" s="3" t="s">
         <v>340</v>
@@ -66108,7 +66135,7 @@
         <v>127</v>
       </c>
       <c r="F1818" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1818" s="8" t="s">
         <v>279</v>
@@ -66127,7 +66154,7 @@
     </row>
     <row r="1819" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1819" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1819" s="3" t="s">
         <v>459</v>
@@ -66142,7 +66169,7 @@
         <v>127</v>
       </c>
       <c r="F1819" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1819" s="8" t="s">
         <v>279</v>
@@ -66161,7 +66188,7 @@
     </row>
     <row r="1820" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1820" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1820" s="3" t="s">
         <v>271</v>
@@ -66176,7 +66203,7 @@
         <v>127</v>
       </c>
       <c r="F1820" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1820" s="8" t="s">
         <v>279</v>
@@ -66195,7 +66222,7 @@
     </row>
     <row r="1821" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1821" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1821" s="3" t="s">
         <v>302</v>
@@ -66210,7 +66237,7 @@
         <v>127</v>
       </c>
       <c r="F1821" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1821" s="8" t="s">
         <v>279</v>
@@ -66229,7 +66256,7 @@
     </row>
     <row r="1822" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1822" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B1822" s="3" t="s">
         <v>288</v>
@@ -66244,7 +66271,7 @@
         <v>127</v>
       </c>
       <c r="F1822" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1822" s="8" t="s">
         <v>279</v>
@@ -66263,7 +66290,7 @@
     </row>
     <row r="1823" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1823" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B1823" s="3" t="s">
         <v>124</v>
@@ -66278,7 +66305,7 @@
         <v>127</v>
       </c>
       <c r="F1823" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1823" s="8" t="s">
         <v>279</v>
@@ -66297,7 +66324,7 @@
     </row>
     <row r="1824" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1824" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B1824" s="3" t="s">
         <v>135</v>
@@ -66312,7 +66339,7 @@
         <v>127</v>
       </c>
       <c r="F1824" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G1824" s="8" t="s">
         <v>279</v>
@@ -66330,208 +66357,982 @@
       </c>
     </row>
     <row r="1825" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1825" s="3"/>
-      <c r="B1825" s="3"/>
-      <c r="C1825" s="3"/>
-      <c r="D1825" s="3"/>
-      <c r="E1825" s="3"/>
-      <c r="F1825" s="3"/>
-      <c r="G1825" s="3"/>
-      <c r="H1825" s="3"/>
-      <c r="I1825" s="4"/>
-      <c r="J1825" s="4"/>
+      <c r="A1825" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1825" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1825" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1825" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1825" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1825" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1825" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1825" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1825" s="4">
+        <f t="shared" ref="I1825" si="786">YEAR(A1825)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1825" s="4">
+        <f t="shared" ref="J1825" si="787">MONTH(A1825)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1826" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1826" s="3"/>
-      <c r="B1826" s="3"/>
-      <c r="C1826" s="3"/>
-      <c r="D1826" s="3"/>
-      <c r="E1826" s="3"/>
-      <c r="F1826" s="3"/>
-      <c r="G1826" s="3"/>
-      <c r="H1826" s="3"/>
-      <c r="I1826" s="4"/>
-      <c r="J1826" s="4"/>
+      <c r="A1826" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B1826" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1826" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1826" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1826" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1826" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1826" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1826" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1826" s="4">
+        <f t="shared" ref="I1826:I1828" si="788">YEAR(A1826)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1826" s="4">
+        <f t="shared" ref="J1826:J1828" si="789">MONTH(A1826)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1827" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1827" s="3"/>
-      <c r="B1827" s="3"/>
-      <c r="C1827" s="3"/>
-      <c r="D1827" s="3"/>
-      <c r="E1827" s="3"/>
-      <c r="F1827" s="3"/>
-      <c r="G1827" s="3"/>
-      <c r="H1827" s="3"/>
-      <c r="I1827" s="4"/>
-      <c r="J1827" s="4"/>
+      <c r="A1827" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B1827" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1827" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1827" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1827" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1827" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1827" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1827" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1827" s="4">
+        <f t="shared" si="788"/>
+        <v>2026</v>
+      </c>
+      <c r="J1827" s="4">
+        <f t="shared" si="789"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1828" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1828" s="3"/>
-      <c r="B1828" s="3"/>
-      <c r="C1828" s="3"/>
-      <c r="D1828" s="3"/>
-      <c r="E1828" s="3"/>
-      <c r="F1828" s="3"/>
-      <c r="G1828" s="3"/>
-      <c r="H1828" s="3"/>
-      <c r="I1828" s="4"/>
-      <c r="J1828" s="4"/>
+      <c r="A1828" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B1828" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1828" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1828" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1828" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1828" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1828" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1828" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1828" s="4">
+        <f t="shared" si="788"/>
+        <v>2026</v>
+      </c>
+      <c r="J1828" s="4">
+        <f t="shared" si="789"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1829" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1829" s="3"/>
-      <c r="B1829" s="3"/>
-      <c r="C1829" s="3"/>
-      <c r="D1829" s="3"/>
-      <c r="E1829" s="3"/>
-      <c r="F1829" s="3"/>
-      <c r="G1829" s="3"/>
-      <c r="H1829" s="3"/>
-      <c r="I1829" s="4"/>
-      <c r="J1829" s="4"/>
+      <c r="A1829" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B1829" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1829" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1829" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1829" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1829" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1829" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1829" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1829" s="4">
+        <f t="shared" ref="I1829:I1831" si="790">YEAR(A1829)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1829" s="4">
+        <f t="shared" ref="J1829:J1831" si="791">MONTH(A1829)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1830" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1830" s="3"/>
-      <c r="B1830" s="3"/>
-      <c r="C1830" s="3"/>
-      <c r="D1830" s="3"/>
-      <c r="E1830" s="3"/>
-      <c r="F1830" s="3"/>
-      <c r="G1830" s="3"/>
-      <c r="H1830" s="3"/>
-      <c r="I1830" s="4"/>
-      <c r="J1830" s="4"/>
+      <c r="A1830" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B1830" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1830" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1830" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1830" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1830" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1830" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1830" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1830" s="4">
+        <f t="shared" si="790"/>
+        <v>2026</v>
+      </c>
+      <c r="J1830" s="4">
+        <f t="shared" si="791"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1831" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1831" s="3"/>
-      <c r="B1831" s="3"/>
-      <c r="C1831" s="3"/>
-      <c r="D1831" s="3"/>
-      <c r="E1831" s="3"/>
-      <c r="F1831" s="3"/>
-      <c r="G1831" s="3"/>
-      <c r="H1831" s="3"/>
-      <c r="I1831" s="4"/>
-      <c r="J1831" s="4"/>
+      <c r="A1831" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B1831" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1831" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1831" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1831" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1831" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1831" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1831" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1831" s="4">
+        <f t="shared" si="790"/>
+        <v>2026</v>
+      </c>
+      <c r="J1831" s="4">
+        <f t="shared" si="791"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1832" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1832" s="3"/>
-      <c r="B1832" s="3"/>
-      <c r="C1832" s="3"/>
-      <c r="D1832" s="3"/>
-      <c r="E1832" s="3"/>
-      <c r="F1832" s="3"/>
-      <c r="G1832" s="3"/>
-      <c r="H1832" s="3"/>
-      <c r="I1832" s="4"/>
-      <c r="J1832" s="4"/>
+      <c r="A1832" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1832" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1832" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1832" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="E1832" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1832" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1832" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1832" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1832" s="4">
+        <f t="shared" ref="I1832:I1834" si="792">YEAR(A1832)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1832" s="4">
+        <f t="shared" ref="J1832:J1834" si="793">MONTH(A1832)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1833" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1833" s="3"/>
-      <c r="B1833" s="3"/>
-      <c r="C1833" s="3"/>
-      <c r="D1833" s="3"/>
-      <c r="E1833" s="3"/>
-      <c r="F1833" s="3"/>
-      <c r="G1833" s="3"/>
-      <c r="H1833" s="3"/>
-      <c r="I1833" s="4"/>
-      <c r="J1833" s="4"/>
+      <c r="A1833" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1833" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1833" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1833" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1833" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1833" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1833" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1833" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1833" s="4">
+        <f t="shared" si="792"/>
+        <v>2026</v>
+      </c>
+      <c r="J1833" s="4">
+        <f t="shared" si="793"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1834" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1834" s="3"/>
-      <c r="B1834" s="3"/>
-      <c r="C1834" s="3"/>
-      <c r="D1834" s="3"/>
-      <c r="E1834" s="3"/>
-      <c r="F1834" s="3"/>
-      <c r="G1834" s="3"/>
-      <c r="H1834" s="3"/>
-      <c r="I1834" s="4"/>
-      <c r="J1834" s="4"/>
+      <c r="A1834" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1834" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1834" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1834" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1834" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1834" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1834" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1834" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1834" s="4">
+        <f t="shared" si="792"/>
+        <v>2026</v>
+      </c>
+      <c r="J1834" s="4">
+        <f t="shared" si="793"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1835" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1835" s="3"/>
-      <c r="B1835" s="3"/>
-      <c r="C1835" s="3"/>
-      <c r="D1835" s="3"/>
-      <c r="E1835" s="3"/>
-      <c r="F1835" s="3"/>
-      <c r="G1835" s="3"/>
-      <c r="H1835" s="3"/>
-      <c r="I1835" s="4"/>
-      <c r="J1835" s="4"/>
+      <c r="A1835" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B1835" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1835" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="D1835" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1835" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1835" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1835" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1835" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1835" s="4">
+        <f t="shared" ref="I1835:I1837" si="794">YEAR(A1835)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1835" s="4">
+        <f t="shared" ref="J1835:J1837" si="795">MONTH(A1835)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1836" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1836" s="3"/>
-      <c r="B1836" s="3"/>
-      <c r="C1836" s="3"/>
-      <c r="D1836" s="3"/>
-      <c r="E1836" s="3"/>
-      <c r="F1836" s="3"/>
-      <c r="G1836" s="3"/>
-      <c r="H1836" s="3"/>
-      <c r="I1836" s="4"/>
-      <c r="J1836" s="4"/>
+      <c r="A1836" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B1836" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C1836" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1836" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1836" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1836" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1836" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1836" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1836" s="4">
+        <f t="shared" si="794"/>
+        <v>2026</v>
+      </c>
+      <c r="J1836" s="4">
+        <f t="shared" si="795"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1837" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1837" s="3"/>
-      <c r="B1837" s="3"/>
-      <c r="C1837" s="3"/>
-      <c r="D1837" s="3"/>
-      <c r="E1837" s="3"/>
-      <c r="F1837" s="3"/>
-      <c r="G1837" s="3"/>
-      <c r="H1837" s="3"/>
-      <c r="I1837" s="4"/>
-      <c r="J1837" s="4"/>
+      <c r="A1837" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B1837" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1837" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1837" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1837" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1837" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1837" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1837" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1837" s="4">
+        <f t="shared" si="794"/>
+        <v>2026</v>
+      </c>
+      <c r="J1837" s="4">
+        <f t="shared" si="795"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1838" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1838" s="3"/>
-      <c r="B1838" s="3"/>
-      <c r="C1838" s="3"/>
-      <c r="D1838" s="3"/>
-      <c r="E1838" s="3"/>
-      <c r="F1838" s="3"/>
-      <c r="G1838" s="3"/>
-      <c r="H1838" s="3"/>
-      <c r="I1838" s="4"/>
-      <c r="J1838" s="4"/>
+      <c r="A1838" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B1838" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="C1838" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1838" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1838" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1838" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1838" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1838" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1838" s="4">
+        <f t="shared" ref="I1838:I1839" si="796">YEAR(A1838)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1838" s="4">
+        <f t="shared" ref="J1838:J1839" si="797">MONTH(A1838)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1839" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1839" s="3"/>
-      <c r="B1839" s="3"/>
-      <c r="C1839" s="3"/>
-      <c r="D1839" s="3"/>
-      <c r="E1839" s="3"/>
-      <c r="F1839" s="3"/>
-      <c r="G1839" s="3"/>
-      <c r="H1839" s="3"/>
-      <c r="I1839" s="4"/>
-      <c r="J1839" s="4"/>
+      <c r="A1839" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B1839" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1839" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1839" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1839" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1839" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1839" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1839" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1839" s="4">
+        <f t="shared" si="796"/>
+        <v>2026</v>
+      </c>
+      <c r="J1839" s="4">
+        <f t="shared" si="797"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1840" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1840" s="3"/>
-      <c r="B1840" s="3"/>
-      <c r="C1840" s="3"/>
-      <c r="D1840" s="3"/>
-      <c r="E1840" s="3"/>
-      <c r="F1840" s="3"/>
-      <c r="G1840" s="3"/>
-      <c r="H1840" s="3"/>
-      <c r="I1840" s="4"/>
-      <c r="J1840" s="4"/>
+      <c r="A1840" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B1840" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1840" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1840" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1840" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1840" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1840" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1840" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1840" s="4">
+        <f t="shared" ref="I1840:I1841" si="798">YEAR(A1840)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1840" s="4">
+        <f t="shared" ref="J1840:J1841" si="799">MONTH(A1840)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1841" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1841" s="3"/>
-      <c r="B1841" s="3"/>
-      <c r="C1841" s="3"/>
-      <c r="D1841" s="3"/>
-      <c r="E1841" s="3"/>
-      <c r="F1841" s="3"/>
-      <c r="G1841" s="3"/>
-      <c r="H1841" s="3"/>
-      <c r="I1841" s="4"/>
-      <c r="J1841" s="4"/>
+      <c r="A1841" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B1841" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1841" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1841" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1841" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1841" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1841" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1841" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1841" s="4">
+        <f t="shared" si="798"/>
+        <v>2026</v>
+      </c>
+      <c r="J1841" s="4">
+        <f t="shared" si="799"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1842" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B1842" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1842" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1842" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1842" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1842" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1842" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1842" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1842" s="4">
+        <f t="shared" ref="I1842:I1844" si="800">YEAR(A1842)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1842" s="4">
+        <f t="shared" ref="J1842:J1844" si="801">MONTH(A1842)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1843" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B1843" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1843" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1843" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1843" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1843" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1843" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1843" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1843" s="4">
+        <f t="shared" si="800"/>
+        <v>2026</v>
+      </c>
+      <c r="J1843" s="4">
+        <f t="shared" si="801"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1844" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B1844" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1844" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1844" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1844" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1844" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1844" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1844" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1844" s="4">
+        <f t="shared" si="800"/>
+        <v>2026</v>
+      </c>
+      <c r="J1844" s="4">
+        <f t="shared" si="801"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1845" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B1845" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1845" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1845" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1845" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1845" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1845" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1845" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1845" s="4">
+        <f t="shared" ref="I1845" si="802">YEAR(A1845)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1845" s="4">
+        <f t="shared" ref="J1845" si="803">MONTH(A1845)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1846" s="3"/>
+      <c r="B1846" s="3"/>
+      <c r="C1846" s="3"/>
+      <c r="D1846" s="3"/>
+      <c r="E1846" s="3"/>
+      <c r="F1846" s="3"/>
+      <c r="G1846" s="3"/>
+      <c r="H1846" s="3"/>
+      <c r="I1846" s="4"/>
+      <c r="J1846" s="4"/>
+    </row>
+    <row r="1847" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1847" s="3"/>
+      <c r="B1847" s="3"/>
+      <c r="C1847" s="3"/>
+      <c r="D1847" s="3"/>
+      <c r="E1847" s="3"/>
+      <c r="F1847" s="3"/>
+      <c r="G1847" s="3"/>
+      <c r="H1847" s="3"/>
+      <c r="I1847" s="4"/>
+      <c r="J1847" s="4"/>
+    </row>
+    <row r="1848" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1848" s="3"/>
+      <c r="B1848" s="3"/>
+      <c r="C1848" s="3"/>
+      <c r="D1848" s="3"/>
+      <c r="E1848" s="3"/>
+      <c r="F1848" s="3"/>
+      <c r="G1848" s="3"/>
+      <c r="H1848" s="3"/>
+      <c r="I1848" s="4"/>
+      <c r="J1848" s="4"/>
+    </row>
+    <row r="1849" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1849" s="3"/>
+      <c r="B1849" s="3"/>
+      <c r="C1849" s="3"/>
+      <c r="D1849" s="3"/>
+      <c r="E1849" s="3"/>
+      <c r="F1849" s="3"/>
+      <c r="G1849" s="3"/>
+      <c r="H1849" s="3"/>
+      <c r="I1849" s="4"/>
+      <c r="J1849" s="4"/>
+    </row>
+    <row r="1850" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1850" s="3"/>
+      <c r="B1850" s="3"/>
+      <c r="C1850" s="3"/>
+      <c r="D1850" s="3"/>
+      <c r="E1850" s="3"/>
+      <c r="F1850" s="3"/>
+      <c r="G1850" s="3"/>
+      <c r="H1850" s="3"/>
+      <c r="I1850" s="4"/>
+      <c r="J1850" s="4"/>
+    </row>
+    <row r="1851" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1851" s="3"/>
+      <c r="B1851" s="3"/>
+      <c r="C1851" s="3"/>
+      <c r="D1851" s="3"/>
+      <c r="E1851" s="3"/>
+      <c r="F1851" s="3"/>
+      <c r="G1851" s="3"/>
+      <c r="H1851" s="3"/>
+      <c r="I1851" s="4"/>
+      <c r="J1851" s="4"/>
+    </row>
+    <row r="1852" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1852" s="3"/>
+      <c r="B1852" s="3"/>
+      <c r="C1852" s="3"/>
+      <c r="D1852" s="3"/>
+      <c r="E1852" s="3"/>
+      <c r="F1852" s="3"/>
+      <c r="G1852" s="3"/>
+      <c r="H1852" s="3"/>
+      <c r="I1852" s="4"/>
+      <c r="J1852" s="4"/>
+    </row>
+    <row r="1853" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1853" s="3"/>
+      <c r="B1853" s="3"/>
+      <c r="C1853" s="3"/>
+      <c r="D1853" s="3"/>
+      <c r="E1853" s="3"/>
+      <c r="F1853" s="3"/>
+      <c r="G1853" s="3"/>
+      <c r="H1853" s="3"/>
+      <c r="I1853" s="4"/>
+      <c r="J1853" s="4"/>
+    </row>
+    <row r="1854" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1854" s="3"/>
+      <c r="B1854" s="3"/>
+      <c r="C1854" s="3"/>
+      <c r="D1854" s="3"/>
+      <c r="E1854" s="3"/>
+      <c r="F1854" s="3"/>
+      <c r="G1854" s="3"/>
+      <c r="H1854" s="3"/>
+      <c r="I1854" s="4"/>
+      <c r="J1854" s="4"/>
+    </row>
+    <row r="1855" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1855" s="3"/>
+      <c r="B1855" s="3"/>
+      <c r="C1855" s="3"/>
+      <c r="D1855" s="3"/>
+      <c r="E1855" s="3"/>
+      <c r="F1855" s="3"/>
+      <c r="G1855" s="3"/>
+      <c r="H1855" s="3"/>
+      <c r="I1855" s="4"/>
+      <c r="J1855" s="4"/>
+    </row>
+    <row r="1856" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1856" s="3"/>
+      <c r="B1856" s="3"/>
+      <c r="C1856" s="3"/>
+      <c r="D1856" s="3"/>
+      <c r="E1856" s="3"/>
+      <c r="F1856" s="3"/>
+      <c r="G1856" s="3"/>
+      <c r="H1856" s="3"/>
+      <c r="I1856" s="4"/>
+      <c r="J1856" s="4"/>
+    </row>
+    <row r="1857" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1857" s="3"/>
+      <c r="B1857" s="3"/>
+      <c r="C1857" s="3"/>
+      <c r="D1857" s="3"/>
+      <c r="E1857" s="3"/>
+      <c r="F1857" s="3"/>
+      <c r="G1857" s="3"/>
+      <c r="H1857" s="3"/>
+      <c r="I1857" s="4"/>
+      <c r="J1857" s="4"/>
+    </row>
+    <row r="1858" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1858" s="3"/>
+      <c r="B1858" s="3"/>
+      <c r="C1858" s="3"/>
+      <c r="D1858" s="3"/>
+      <c r="E1858" s="3"/>
+      <c r="F1858" s="3"/>
+      <c r="G1858" s="3"/>
+      <c r="H1858" s="3"/>
+      <c r="I1858" s="4"/>
+      <c r="J1858" s="4"/>
+    </row>
+    <row r="1859" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1859" s="3"/>
+      <c r="B1859" s="3"/>
+      <c r="C1859" s="3"/>
+      <c r="D1859" s="3"/>
+      <c r="E1859" s="3"/>
+      <c r="F1859" s="3"/>
+      <c r="G1859" s="3"/>
+      <c r="H1859" s="3"/>
+      <c r="I1859" s="4"/>
+      <c r="J1859" s="4"/>
+    </row>
+    <row r="1860" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1860" s="3"/>
+      <c r="B1860" s="3"/>
+      <c r="C1860" s="3"/>
+      <c r="D1860" s="3"/>
+      <c r="E1860" s="3"/>
+      <c r="F1860" s="3"/>
+      <c r="G1860" s="3"/>
+      <c r="H1860" s="3"/>
+      <c r="I1860" s="4"/>
+      <c r="J1860" s="4"/>
+    </row>
+    <row r="1861" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1861" s="3"/>
+      <c r="B1861" s="3"/>
+      <c r="C1861" s="3"/>
+      <c r="D1861" s="3"/>
+      <c r="E1861" s="3"/>
+      <c r="F1861" s="3"/>
+      <c r="G1861" s="3"/>
+      <c r="H1861" s="3"/>
+      <c r="I1861" s="4"/>
+      <c r="J1861" s="4"/>
+    </row>
+    <row r="1862" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1862" s="3"/>
+      <c r="B1862" s="3"/>
+      <c r="C1862" s="3"/>
+      <c r="D1862" s="3"/>
+      <c r="E1862" s="3"/>
+      <c r="F1862" s="3"/>
+      <c r="G1862" s="3"/>
+      <c r="H1862" s="3"/>
+      <c r="I1862" s="4"/>
+      <c r="J1862" s="4"/>
+    </row>
+    <row r="1863" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1863" s="3"/>
+      <c r="B1863" s="3"/>
+      <c r="C1863" s="3"/>
+      <c r="D1863" s="3"/>
+      <c r="E1863" s="3"/>
+      <c r="F1863" s="3"/>
+      <c r="G1863" s="3"/>
+      <c r="H1863" s="3"/>
+      <c r="I1863" s="4"/>
+      <c r="J1863" s="4"/>
+    </row>
+    <row r="1864" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1864" s="3"/>
+      <c r="B1864" s="3"/>
+      <c r="C1864" s="3"/>
+      <c r="D1864" s="3"/>
+      <c r="E1864" s="3"/>
+      <c r="F1864" s="3"/>
+      <c r="G1864" s="3"/>
+      <c r="H1864" s="3"/>
+      <c r="I1864" s="4"/>
+      <c r="J1864" s="4"/>
+    </row>
+    <row r="1865" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1865" s="3"/>
+      <c r="B1865" s="3"/>
+      <c r="C1865" s="3"/>
+      <c r="D1865" s="3"/>
+      <c r="E1865" s="3"/>
+      <c r="F1865" s="3"/>
+      <c r="G1865" s="3"/>
+      <c r="H1865" s="3"/>
+      <c r="I1865" s="4"/>
+      <c r="J1865" s="4"/>
+    </row>
+    <row r="1866" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1866" s="3"/>
+      <c r="B1866" s="3"/>
+      <c r="C1866" s="3"/>
+      <c r="D1866" s="3"/>
+      <c r="E1866" s="3"/>
+      <c r="F1866" s="3"/>
+      <c r="G1866" s="3"/>
+      <c r="H1866" s="3"/>
+      <c r="I1866" s="4"/>
+      <c r="J1866" s="4"/>
+    </row>
+    <row r="1867" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1867" s="3"/>
+      <c r="B1867" s="3"/>
+      <c r="C1867" s="3"/>
+      <c r="D1867" s="3"/>
+      <c r="E1867" s="3"/>
+      <c r="F1867" s="3"/>
+      <c r="G1867" s="3"/>
+      <c r="H1867" s="3"/>
+      <c r="I1867" s="4"/>
+      <c r="J1867" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14361" uniqueCount="1565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14409" uniqueCount="1569">
   <si>
     <t>Year</t>
   </si>
@@ -4720,6 +4720,18 @@
   </si>
   <si>
     <t>2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>nwmakefiler v2.0.0</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
   </si>
 </sst>
 </file>
@@ -67062,85 +67074,217 @@
         <v>280</v>
       </c>
       <c r="I1845" s="4">
-        <f t="shared" ref="I1845" si="802">YEAR(A1845)</f>
+        <f t="shared" ref="I1845:I1847" si="802">YEAR(A1845)</f>
         <v>2026</v>
       </c>
       <c r="J1845" s="4">
-        <f t="shared" ref="J1845" si="803">MONTH(A1845)</f>
+        <f t="shared" ref="J1845:J1847" si="803">MONTH(A1845)</f>
         <v>1</v>
       </c>
     </row>
     <row r="1846" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1846" s="3"/>
-      <c r="B1846" s="3"/>
-      <c r="C1846" s="3"/>
-      <c r="D1846" s="3"/>
-      <c r="E1846" s="3"/>
-      <c r="F1846" s="3"/>
-      <c r="G1846" s="3"/>
-      <c r="H1846" s="3"/>
-      <c r="I1846" s="4"/>
-      <c r="J1846" s="4"/>
+      <c r="A1846" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B1846" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1846" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1846" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1846" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1846" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1846" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1846" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1846" s="4">
+        <f t="shared" si="802"/>
+        <v>2026</v>
+      </c>
+      <c r="J1846" s="4">
+        <f t="shared" si="803"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1847" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1847" s="3"/>
-      <c r="B1847" s="3"/>
-      <c r="C1847" s="3"/>
-      <c r="D1847" s="3"/>
-      <c r="E1847" s="3"/>
-      <c r="F1847" s="3"/>
-      <c r="G1847" s="3"/>
-      <c r="H1847" s="3"/>
-      <c r="I1847" s="4"/>
-      <c r="J1847" s="4"/>
+      <c r="A1847" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B1847" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1847" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1847" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E1847" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1847" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1847" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1847" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1847" s="4">
+        <f t="shared" si="802"/>
+        <v>2026</v>
+      </c>
+      <c r="J1847" s="4">
+        <f t="shared" si="803"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1848" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1848" s="3"/>
-      <c r="B1848" s="3"/>
-      <c r="C1848" s="3"/>
-      <c r="D1848" s="3"/>
-      <c r="E1848" s="3"/>
-      <c r="F1848" s="3"/>
-      <c r="G1848" s="3"/>
-      <c r="H1848" s="3"/>
-      <c r="I1848" s="4"/>
-      <c r="J1848" s="4"/>
+      <c r="A1848" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B1848" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1848" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1848" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1848" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1848" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1848" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1848" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1848" s="4">
+        <f t="shared" ref="I1848" si="804">YEAR(A1848)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1848" s="4">
+        <f t="shared" ref="J1848" si="805">MONTH(A1848)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1849" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1849" s="3"/>
-      <c r="B1849" s="3"/>
-      <c r="C1849" s="3"/>
-      <c r="D1849" s="3"/>
-      <c r="E1849" s="3"/>
-      <c r="F1849" s="3"/>
-      <c r="G1849" s="3"/>
-      <c r="H1849" s="3"/>
-      <c r="I1849" s="4"/>
-      <c r="J1849" s="4"/>
+      <c r="A1849" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1849" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1849" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1849" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1849" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1849" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1849" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1849" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1849" s="4">
+        <f t="shared" ref="I1849:I1850" si="806">YEAR(A1849)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1849" s="4">
+        <f t="shared" ref="J1849:J1850" si="807">MONTH(A1849)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1850" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1850" s="3"/>
-      <c r="B1850" s="3"/>
-      <c r="C1850" s="3"/>
-      <c r="D1850" s="3"/>
-      <c r="E1850" s="3"/>
-      <c r="F1850" s="3"/>
-      <c r="G1850" s="3"/>
-      <c r="H1850" s="3"/>
-      <c r="I1850" s="4"/>
-      <c r="J1850" s="4"/>
+      <c r="A1850" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1850" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1850" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1850" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1850" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F1850" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1850" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1850" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1850" s="4">
+        <f t="shared" si="806"/>
+        <v>2026</v>
+      </c>
+      <c r="J1850" s="4">
+        <f t="shared" si="807"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1851" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1851" s="3"/>
-      <c r="B1851" s="3"/>
-      <c r="C1851" s="3"/>
-      <c r="D1851" s="3"/>
-      <c r="E1851" s="3"/>
-      <c r="F1851" s="3"/>
-      <c r="G1851" s="3"/>
-      <c r="H1851" s="3"/>
-      <c r="I1851" s="4"/>
-      <c r="J1851" s="4"/>
+      <c r="A1851" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B1851" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1851" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1851" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="E1851" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1851" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1851" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1851" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1851" s="4">
+        <f t="shared" ref="I1851" si="808">YEAR(A1851)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1851" s="4">
+        <f t="shared" ref="J1851" si="809">MONTH(A1851)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1852" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1852" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14409" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14545" uniqueCount="1577">
   <si>
     <t>Year</t>
   </si>
@@ -4732,6 +4732,30 @@
   </si>
   <si>
     <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>nwversioninfofiles v1.0.0</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
   </si>
 </sst>
 </file>
@@ -5140,7 +5164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1867"/>
+  <dimension ref="A1:J1900"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -67287,196 +67311,966 @@
       </c>
     </row>
     <row r="1852" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1852" s="3"/>
-      <c r="B1852" s="3"/>
-      <c r="C1852" s="3"/>
-      <c r="D1852" s="3"/>
-      <c r="E1852" s="3"/>
-      <c r="F1852" s="3"/>
-      <c r="G1852" s="3"/>
-      <c r="H1852" s="3"/>
-      <c r="I1852" s="4"/>
-      <c r="J1852" s="4"/>
+      <c r="A1852" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1852" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1852" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1852" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1852" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1852" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1852" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1852" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1852" s="4">
+        <f t="shared" ref="I1852:I1854" si="810">YEAR(A1852)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1852" s="4">
+        <f t="shared" ref="J1852:J1854" si="811">MONTH(A1852)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1853" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1853" s="3"/>
-      <c r="B1853" s="3"/>
-      <c r="C1853" s="3"/>
-      <c r="D1853" s="3"/>
-      <c r="E1853" s="3"/>
-      <c r="F1853" s="3"/>
-      <c r="G1853" s="3"/>
-      <c r="H1853" s="3"/>
-      <c r="I1853" s="4"/>
-      <c r="J1853" s="4"/>
+      <c r="A1853" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1853" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1853" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1853" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1853" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1853" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1853" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1853" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1853" s="4">
+        <f t="shared" si="810"/>
+        <v>2026</v>
+      </c>
+      <c r="J1853" s="4">
+        <f t="shared" si="811"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1854" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1854" s="3"/>
-      <c r="B1854" s="3"/>
-      <c r="C1854" s="3"/>
-      <c r="D1854" s="3"/>
-      <c r="E1854" s="3"/>
-      <c r="F1854" s="3"/>
-      <c r="G1854" s="3"/>
-      <c r="H1854" s="3"/>
-      <c r="I1854" s="4"/>
-      <c r="J1854" s="4"/>
+      <c r="A1854" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1854" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1854" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1854" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1854" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1854" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1854" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1854" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1854" s="4">
+        <f t="shared" si="810"/>
+        <v>2026</v>
+      </c>
+      <c r="J1854" s="4">
+        <f t="shared" si="811"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1855" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1855" s="3"/>
-      <c r="B1855" s="3"/>
-      <c r="C1855" s="3"/>
-      <c r="D1855" s="3"/>
-      <c r="E1855" s="3"/>
-      <c r="F1855" s="3"/>
-      <c r="G1855" s="3"/>
-      <c r="H1855" s="3"/>
-      <c r="I1855" s="4"/>
-      <c r="J1855" s="4"/>
+      <c r="A1855" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1855" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1855" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1855" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1855" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1855" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1855" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1855" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1855" s="4">
+        <f t="shared" ref="I1855" si="812">YEAR(A1855)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1855" s="4">
+        <f t="shared" ref="J1855" si="813">MONTH(A1855)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1856" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1856" s="3"/>
-      <c r="B1856" s="3"/>
-      <c r="C1856" s="3"/>
-      <c r="D1856" s="3"/>
-      <c r="E1856" s="3"/>
-      <c r="F1856" s="3"/>
-      <c r="G1856" s="3"/>
-      <c r="H1856" s="3"/>
-      <c r="I1856" s="4"/>
-      <c r="J1856" s="4"/>
+      <c r="A1856" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1856" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1856" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1856" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1856" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1856" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G1856" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1856" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1856" s="4">
+        <f t="shared" ref="I1856" si="814">YEAR(A1856)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1856" s="4">
+        <f t="shared" ref="J1856" si="815">MONTH(A1856)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1857" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1857" s="3"/>
-      <c r="B1857" s="3"/>
-      <c r="C1857" s="3"/>
-      <c r="D1857" s="3"/>
-      <c r="E1857" s="3"/>
-      <c r="F1857" s="3"/>
-      <c r="G1857" s="3"/>
-      <c r="H1857" s="3"/>
-      <c r="I1857" s="4"/>
-      <c r="J1857" s="4"/>
+      <c r="A1857" s="3" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1857" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1857" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1857" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1857" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1857" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1857" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1857" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1857" s="4">
+        <f t="shared" ref="I1857" si="816">YEAR(A1857)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1857" s="4">
+        <f t="shared" ref="J1857" si="817">MONTH(A1857)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1858" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1858" s="3"/>
-      <c r="B1858" s="3"/>
-      <c r="C1858" s="3"/>
-      <c r="D1858" s="3"/>
-      <c r="E1858" s="3"/>
-      <c r="F1858" s="3"/>
-      <c r="G1858" s="3"/>
-      <c r="H1858" s="3"/>
-      <c r="I1858" s="4"/>
-      <c r="J1858" s="4"/>
+      <c r="A1858" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B1858" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1858" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1858" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1858" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1858" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1858" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1858" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1858" s="4">
+        <f t="shared" ref="I1858:I1860" si="818">YEAR(A1858)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1858" s="4">
+        <f t="shared" ref="J1858:J1860" si="819">MONTH(A1858)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1859" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1859" s="3"/>
-      <c r="B1859" s="3"/>
-      <c r="C1859" s="3"/>
-      <c r="D1859" s="3"/>
-      <c r="E1859" s="3"/>
-      <c r="F1859" s="3"/>
-      <c r="G1859" s="3"/>
-      <c r="H1859" s="3"/>
-      <c r="I1859" s="4"/>
-      <c r="J1859" s="4"/>
+      <c r="A1859" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B1859" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1859" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1859" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1859" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1859" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G1859" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1859" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1859" s="4">
+        <f t="shared" si="818"/>
+        <v>2026</v>
+      </c>
+      <c r="J1859" s="4">
+        <f t="shared" si="819"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1860" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1860" s="3"/>
-      <c r="B1860" s="3"/>
-      <c r="C1860" s="3"/>
-      <c r="D1860" s="3"/>
-      <c r="E1860" s="3"/>
-      <c r="F1860" s="3"/>
-      <c r="G1860" s="3"/>
-      <c r="H1860" s="3"/>
-      <c r="I1860" s="4"/>
-      <c r="J1860" s="4"/>
+      <c r="A1860" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B1860" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1860" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1860" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1860" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1860" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G1860" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1860" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1860" s="4">
+        <f t="shared" si="818"/>
+        <v>2026</v>
+      </c>
+      <c r="J1860" s="4">
+        <f t="shared" si="819"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1861" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1861" s="3"/>
-      <c r="B1861" s="3"/>
-      <c r="C1861" s="3"/>
-      <c r="D1861" s="3"/>
-      <c r="E1861" s="3"/>
-      <c r="F1861" s="3"/>
-      <c r="G1861" s="3"/>
-      <c r="H1861" s="3"/>
-      <c r="I1861" s="4"/>
-      <c r="J1861" s="4"/>
+      <c r="A1861" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B1861" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1861" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1861" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1861" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1861" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G1861" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1861" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1861" s="4">
+        <f t="shared" ref="I1861:I1862" si="820">YEAR(A1861)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1861" s="4">
+        <f t="shared" ref="J1861:J1862" si="821">MONTH(A1861)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1862" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1862" s="3"/>
-      <c r="B1862" s="3"/>
-      <c r="C1862" s="3"/>
-      <c r="D1862" s="3"/>
-      <c r="E1862" s="3"/>
-      <c r="F1862" s="3"/>
-      <c r="G1862" s="3"/>
-      <c r="H1862" s="3"/>
-      <c r="I1862" s="4"/>
-      <c r="J1862" s="4"/>
+      <c r="A1862" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B1862" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1862" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1862" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1862" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1862" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G1862" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1862" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1862" s="4">
+        <f t="shared" si="820"/>
+        <v>2026</v>
+      </c>
+      <c r="J1862" s="4">
+        <f t="shared" si="821"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1863" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1863" s="3"/>
-      <c r="B1863" s="3"/>
-      <c r="C1863" s="3"/>
-      <c r="D1863" s="3"/>
-      <c r="E1863" s="3"/>
-      <c r="F1863" s="3"/>
-      <c r="G1863" s="3"/>
-      <c r="H1863" s="3"/>
-      <c r="I1863" s="4"/>
-      <c r="J1863" s="4"/>
+      <c r="A1863" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B1863" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1863" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1863" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1863" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1863" s="3" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G1863" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1863" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1863" s="4">
+        <f t="shared" ref="I1863:I1866" si="822">YEAR(A1863)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1863" s="4">
+        <f t="shared" ref="J1863:J1866" si="823">MONTH(A1863)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1864" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1864" s="3"/>
-      <c r="B1864" s="3"/>
-      <c r="C1864" s="3"/>
-      <c r="D1864" s="3"/>
-      <c r="E1864" s="3"/>
-      <c r="F1864" s="3"/>
-      <c r="G1864" s="3"/>
-      <c r="H1864" s="3"/>
-      <c r="I1864" s="4"/>
-      <c r="J1864" s="4"/>
+      <c r="A1864" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B1864" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1864" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1864" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1864" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1864" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1864" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1864" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1864" s="4">
+        <f t="shared" si="822"/>
+        <v>2026</v>
+      </c>
+      <c r="J1864" s="4">
+        <f t="shared" si="823"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1865" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1865" s="3"/>
-      <c r="B1865" s="3"/>
-      <c r="C1865" s="3"/>
-      <c r="D1865" s="3"/>
-      <c r="E1865" s="3"/>
-      <c r="F1865" s="3"/>
-      <c r="G1865" s="3"/>
-      <c r="H1865" s="3"/>
-      <c r="I1865" s="4"/>
-      <c r="J1865" s="4"/>
+      <c r="A1865" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B1865" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1865" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1865" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1865" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1865" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1865" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1865" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1865" s="4">
+        <f t="shared" si="822"/>
+        <v>2026</v>
+      </c>
+      <c r="J1865" s="4">
+        <f t="shared" si="823"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1866" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1866" s="3"/>
-      <c r="B1866" s="3"/>
-      <c r="C1866" s="3"/>
-      <c r="D1866" s="3"/>
-      <c r="E1866" s="3"/>
-      <c r="F1866" s="3"/>
-      <c r="G1866" s="3"/>
-      <c r="H1866" s="3"/>
-      <c r="I1866" s="4"/>
-      <c r="J1866" s="4"/>
+      <c r="A1866" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B1866" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1866" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1866" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1866" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1866" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1866" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1866" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1866" s="4">
+        <f t="shared" si="822"/>
+        <v>2026</v>
+      </c>
+      <c r="J1866" s="4">
+        <f t="shared" si="823"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1867" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1867" s="3"/>
-      <c r="B1867" s="3"/>
-      <c r="C1867" s="3"/>
-      <c r="D1867" s="3"/>
-      <c r="E1867" s="3"/>
-      <c r="F1867" s="3"/>
-      <c r="G1867" s="3"/>
-      <c r="H1867" s="3"/>
-      <c r="I1867" s="4"/>
-      <c r="J1867" s="4"/>
+      <c r="A1867" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B1867" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1867" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1867" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1867" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1867" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1867" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1867" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1867" s="4">
+        <f t="shared" ref="I1867:I1868" si="824">YEAR(A1867)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1867" s="4">
+        <f t="shared" ref="J1867:J1868" si="825">MONTH(A1867)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1868" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B1868" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1868" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1868" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1868" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1868" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G1868" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1868" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1868" s="4">
+        <f t="shared" si="824"/>
+        <v>2026</v>
+      </c>
+      <c r="J1868" s="4">
+        <f t="shared" si="825"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1869" s="3"/>
+      <c r="B1869" s="3"/>
+      <c r="C1869" s="3"/>
+      <c r="D1869" s="3"/>
+      <c r="E1869" s="3"/>
+      <c r="F1869" s="3"/>
+      <c r="G1869" s="3"/>
+      <c r="H1869" s="3"/>
+      <c r="I1869" s="4"/>
+      <c r="J1869" s="4"/>
+    </row>
+    <row r="1870" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1870" s="3"/>
+      <c r="B1870" s="3"/>
+      <c r="C1870" s="3"/>
+      <c r="D1870" s="3"/>
+      <c r="E1870" s="3"/>
+      <c r="F1870" s="3"/>
+      <c r="G1870" s="3"/>
+      <c r="H1870" s="3"/>
+      <c r="I1870" s="4"/>
+      <c r="J1870" s="4"/>
+    </row>
+    <row r="1871" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1871" s="3"/>
+      <c r="B1871" s="3"/>
+      <c r="C1871" s="3"/>
+      <c r="D1871" s="3"/>
+      <c r="E1871" s="3"/>
+      <c r="F1871" s="3"/>
+      <c r="G1871" s="3"/>
+      <c r="H1871" s="3"/>
+      <c r="I1871" s="4"/>
+      <c r="J1871" s="4"/>
+    </row>
+    <row r="1872" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1872" s="3"/>
+      <c r="B1872" s="3"/>
+      <c r="C1872" s="3"/>
+      <c r="D1872" s="3"/>
+      <c r="E1872" s="3"/>
+      <c r="F1872" s="3"/>
+      <c r="G1872" s="3"/>
+      <c r="H1872" s="3"/>
+      <c r="I1872" s="4"/>
+      <c r="J1872" s="4"/>
+    </row>
+    <row r="1873" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1873" s="3"/>
+      <c r="B1873" s="3"/>
+      <c r="C1873" s="3"/>
+      <c r="D1873" s="3"/>
+      <c r="E1873" s="3"/>
+      <c r="F1873" s="3"/>
+      <c r="G1873" s="3"/>
+      <c r="H1873" s="3"/>
+      <c r="I1873" s="4"/>
+      <c r="J1873" s="4"/>
+    </row>
+    <row r="1874" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1874" s="3"/>
+      <c r="B1874" s="3"/>
+      <c r="C1874" s="3"/>
+      <c r="D1874" s="3"/>
+      <c r="E1874" s="3"/>
+      <c r="F1874" s="3"/>
+      <c r="G1874" s="3"/>
+      <c r="H1874" s="3"/>
+      <c r="I1874" s="4"/>
+      <c r="J1874" s="4"/>
+    </row>
+    <row r="1875" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1875" s="3"/>
+      <c r="B1875" s="3"/>
+      <c r="C1875" s="3"/>
+      <c r="D1875" s="3"/>
+      <c r="E1875" s="3"/>
+      <c r="F1875" s="3"/>
+      <c r="G1875" s="3"/>
+      <c r="H1875" s="3"/>
+      <c r="I1875" s="4"/>
+      <c r="J1875" s="4"/>
+    </row>
+    <row r="1876" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1876" s="3"/>
+      <c r="B1876" s="3"/>
+      <c r="C1876" s="3"/>
+      <c r="D1876" s="3"/>
+      <c r="E1876" s="3"/>
+      <c r="F1876" s="3"/>
+      <c r="G1876" s="3"/>
+      <c r="H1876" s="3"/>
+      <c r="I1876" s="4"/>
+      <c r="J1876" s="4"/>
+    </row>
+    <row r="1877" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1877" s="3"/>
+      <c r="B1877" s="3"/>
+      <c r="C1877" s="3"/>
+      <c r="D1877" s="3"/>
+      <c r="E1877" s="3"/>
+      <c r="F1877" s="3"/>
+      <c r="G1877" s="3"/>
+      <c r="H1877" s="3"/>
+      <c r="I1877" s="4"/>
+      <c r="J1877" s="4"/>
+    </row>
+    <row r="1878" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1878" s="3"/>
+      <c r="B1878" s="3"/>
+      <c r="C1878" s="3"/>
+      <c r="D1878" s="3"/>
+      <c r="E1878" s="3"/>
+      <c r="F1878" s="3"/>
+      <c r="G1878" s="3"/>
+      <c r="H1878" s="3"/>
+      <c r="I1878" s="4"/>
+      <c r="J1878" s="4"/>
+    </row>
+    <row r="1879" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1879" s="3"/>
+      <c r="B1879" s="3"/>
+      <c r="C1879" s="3"/>
+      <c r="D1879" s="3"/>
+      <c r="E1879" s="3"/>
+      <c r="F1879" s="3"/>
+      <c r="G1879" s="3"/>
+      <c r="H1879" s="3"/>
+      <c r="I1879" s="4"/>
+      <c r="J1879" s="4"/>
+    </row>
+    <row r="1880" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1880" s="3"/>
+      <c r="B1880" s="3"/>
+      <c r="C1880" s="3"/>
+      <c r="D1880" s="3"/>
+      <c r="E1880" s="3"/>
+      <c r="F1880" s="3"/>
+      <c r="G1880" s="3"/>
+      <c r="H1880" s="3"/>
+      <c r="I1880" s="4"/>
+      <c r="J1880" s="4"/>
+    </row>
+    <row r="1881" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1881" s="3"/>
+      <c r="B1881" s="3"/>
+      <c r="C1881" s="3"/>
+      <c r="D1881" s="3"/>
+      <c r="E1881" s="3"/>
+      <c r="F1881" s="3"/>
+      <c r="G1881" s="3"/>
+      <c r="H1881" s="3"/>
+      <c r="I1881" s="4"/>
+      <c r="J1881" s="4"/>
+    </row>
+    <row r="1882" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1882" s="3"/>
+      <c r="B1882" s="3"/>
+      <c r="C1882" s="3"/>
+      <c r="D1882" s="3"/>
+      <c r="E1882" s="3"/>
+      <c r="F1882" s="3"/>
+      <c r="G1882" s="3"/>
+      <c r="H1882" s="3"/>
+      <c r="I1882" s="4"/>
+      <c r="J1882" s="4"/>
+    </row>
+    <row r="1883" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1883" s="3"/>
+      <c r="B1883" s="3"/>
+      <c r="C1883" s="3"/>
+      <c r="D1883" s="3"/>
+      <c r="E1883" s="3"/>
+      <c r="F1883" s="3"/>
+      <c r="G1883" s="3"/>
+      <c r="H1883" s="3"/>
+      <c r="I1883" s="4"/>
+      <c r="J1883" s="4"/>
+    </row>
+    <row r="1884" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1884" s="3"/>
+      <c r="B1884" s="3"/>
+      <c r="C1884" s="3"/>
+      <c r="D1884" s="3"/>
+      <c r="E1884" s="3"/>
+      <c r="F1884" s="3"/>
+      <c r="G1884" s="3"/>
+      <c r="H1884" s="3"/>
+      <c r="I1884" s="4"/>
+      <c r="J1884" s="4"/>
+    </row>
+    <row r="1885" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1885" s="3"/>
+      <c r="B1885" s="3"/>
+      <c r="C1885" s="3"/>
+      <c r="D1885" s="3"/>
+      <c r="E1885" s="3"/>
+      <c r="F1885" s="3"/>
+      <c r="G1885" s="3"/>
+      <c r="H1885" s="3"/>
+      <c r="I1885" s="4"/>
+      <c r="J1885" s="4"/>
+    </row>
+    <row r="1886" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1886" s="3"/>
+      <c r="B1886" s="3"/>
+      <c r="C1886" s="3"/>
+      <c r="D1886" s="3"/>
+      <c r="E1886" s="3"/>
+      <c r="F1886" s="3"/>
+      <c r="G1886" s="3"/>
+      <c r="H1886" s="3"/>
+      <c r="I1886" s="4"/>
+      <c r="J1886" s="4"/>
+    </row>
+    <row r="1887" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1887" s="3"/>
+      <c r="B1887" s="3"/>
+      <c r="C1887" s="3"/>
+      <c r="D1887" s="3"/>
+      <c r="E1887" s="3"/>
+      <c r="F1887" s="3"/>
+      <c r="G1887" s="3"/>
+      <c r="H1887" s="3"/>
+      <c r="I1887" s="4"/>
+      <c r="J1887" s="4"/>
+    </row>
+    <row r="1888" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1888" s="3"/>
+      <c r="B1888" s="3"/>
+      <c r="C1888" s="3"/>
+      <c r="D1888" s="3"/>
+      <c r="E1888" s="3"/>
+      <c r="F1888" s="3"/>
+      <c r="G1888" s="3"/>
+      <c r="H1888" s="3"/>
+      <c r="I1888" s="4"/>
+      <c r="J1888" s="4"/>
+    </row>
+    <row r="1889" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1889" s="3"/>
+      <c r="B1889" s="3"/>
+      <c r="C1889" s="3"/>
+      <c r="D1889" s="3"/>
+      <c r="E1889" s="3"/>
+      <c r="F1889" s="3"/>
+      <c r="G1889" s="3"/>
+      <c r="H1889" s="3"/>
+      <c r="I1889" s="4"/>
+      <c r="J1889" s="4"/>
+    </row>
+    <row r="1890" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1890" s="3"/>
+      <c r="B1890" s="3"/>
+      <c r="C1890" s="3"/>
+      <c r="D1890" s="3"/>
+      <c r="E1890" s="3"/>
+      <c r="F1890" s="3"/>
+      <c r="G1890" s="3"/>
+      <c r="H1890" s="3"/>
+      <c r="I1890" s="4"/>
+      <c r="J1890" s="4"/>
+    </row>
+    <row r="1891" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1891" s="3"/>
+      <c r="B1891" s="3"/>
+      <c r="C1891" s="3"/>
+      <c r="D1891" s="3"/>
+      <c r="E1891" s="3"/>
+      <c r="F1891" s="3"/>
+      <c r="G1891" s="3"/>
+      <c r="H1891" s="3"/>
+      <c r="I1891" s="4"/>
+      <c r="J1891" s="4"/>
+    </row>
+    <row r="1892" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1892" s="3"/>
+      <c r="B1892" s="3"/>
+      <c r="C1892" s="3"/>
+      <c r="D1892" s="3"/>
+      <c r="E1892" s="3"/>
+      <c r="F1892" s="3"/>
+      <c r="G1892" s="3"/>
+      <c r="H1892" s="3"/>
+      <c r="I1892" s="4"/>
+      <c r="J1892" s="4"/>
+    </row>
+    <row r="1893" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1893" s="3"/>
+      <c r="B1893" s="3"/>
+      <c r="C1893" s="3"/>
+      <c r="D1893" s="3"/>
+      <c r="E1893" s="3"/>
+      <c r="F1893" s="3"/>
+      <c r="G1893" s="3"/>
+      <c r="H1893" s="3"/>
+      <c r="I1893" s="4"/>
+      <c r="J1893" s="4"/>
+    </row>
+    <row r="1894" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1894" s="3"/>
+      <c r="B1894" s="3"/>
+      <c r="C1894" s="3"/>
+      <c r="D1894" s="3"/>
+      <c r="E1894" s="3"/>
+      <c r="F1894" s="3"/>
+      <c r="G1894" s="3"/>
+      <c r="H1894" s="3"/>
+      <c r="I1894" s="4"/>
+      <c r="J1894" s="4"/>
+    </row>
+    <row r="1895" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1895" s="3"/>
+      <c r="B1895" s="3"/>
+      <c r="C1895" s="3"/>
+      <c r="D1895" s="3"/>
+      <c r="E1895" s="3"/>
+      <c r="F1895" s="3"/>
+      <c r="G1895" s="3"/>
+      <c r="H1895" s="3"/>
+      <c r="I1895" s="4"/>
+      <c r="J1895" s="4"/>
+    </row>
+    <row r="1896" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1896" s="3"/>
+      <c r="B1896" s="3"/>
+      <c r="C1896" s="3"/>
+      <c r="D1896" s="3"/>
+      <c r="E1896" s="3"/>
+      <c r="F1896" s="3"/>
+      <c r="G1896" s="3"/>
+      <c r="H1896" s="3"/>
+      <c r="I1896" s="4"/>
+      <c r="J1896" s="4"/>
+    </row>
+    <row r="1897" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1897" s="3"/>
+      <c r="B1897" s="3"/>
+      <c r="C1897" s="3"/>
+      <c r="D1897" s="3"/>
+      <c r="E1897" s="3"/>
+      <c r="F1897" s="3"/>
+      <c r="G1897" s="3"/>
+      <c r="H1897" s="3"/>
+      <c r="I1897" s="4"/>
+      <c r="J1897" s="4"/>
+    </row>
+    <row r="1898" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1898" s="3"/>
+      <c r="B1898" s="3"/>
+      <c r="C1898" s="3"/>
+      <c r="D1898" s="3"/>
+      <c r="E1898" s="3"/>
+      <c r="F1898" s="3"/>
+      <c r="G1898" s="3"/>
+      <c r="H1898" s="3"/>
+      <c r="I1898" s="4"/>
+      <c r="J1898" s="4"/>
+    </row>
+    <row r="1899" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1899" s="3"/>
+      <c r="B1899" s="3"/>
+      <c r="C1899" s="3"/>
+      <c r="D1899" s="3"/>
+      <c r="E1899" s="3"/>
+      <c r="F1899" s="3"/>
+      <c r="G1899" s="3"/>
+      <c r="H1899" s="3"/>
+      <c r="I1899" s="4"/>
+      <c r="J1899" s="4"/>
+    </row>
+    <row r="1900" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1900" s="3"/>
+      <c r="B1900" s="3"/>
+      <c r="C1900" s="3"/>
+      <c r="D1900" s="3"/>
+      <c r="E1900" s="3"/>
+      <c r="F1900" s="3"/>
+      <c r="G1900" s="3"/>
+      <c r="H1900" s="3"/>
+      <c r="I1900" s="4"/>
+      <c r="J1900" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14545" uniqueCount="1577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14665" uniqueCount="1586">
   <si>
     <t>Year</t>
   </si>
@@ -4756,6 +4756,33 @@
   </si>
   <si>
     <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>ARM64 Builder (QEMU, ProxMox).</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>ARM64 Builder (ProxMox, RPI3B+).</t>
   </si>
 </sst>
 </file>
@@ -5164,7 +5191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1900"/>
+  <dimension ref="A1:J1931"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -67846,11 +67873,11 @@
         <v>280</v>
       </c>
       <c r="I1867" s="4">
-        <f t="shared" ref="I1867:I1868" si="824">YEAR(A1867)</f>
+        <f t="shared" ref="I1867:I1870" si="824">YEAR(A1867)</f>
         <v>2026</v>
       </c>
       <c r="J1867" s="4">
-        <f t="shared" ref="J1867:J1868" si="825">MONTH(A1867)</f>
+        <f t="shared" ref="J1867:J1870" si="825">MONTH(A1867)</f>
         <v>1</v>
       </c>
     </row>
@@ -67889,184 +67916,514 @@
       </c>
     </row>
     <row r="1869" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1869" s="3"/>
-      <c r="B1869" s="3"/>
-      <c r="C1869" s="3"/>
-      <c r="D1869" s="3"/>
-      <c r="E1869" s="3"/>
-      <c r="F1869" s="3"/>
-      <c r="G1869" s="3"/>
-      <c r="H1869" s="3"/>
-      <c r="I1869" s="4"/>
-      <c r="J1869" s="4"/>
+      <c r="A1869" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1869" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1869" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1869" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1869" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1869" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1869" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1869" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1869" s="4">
+        <f t="shared" si="824"/>
+        <v>2026</v>
+      </c>
+      <c r="J1869" s="4">
+        <f t="shared" si="825"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1870" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1870" s="3"/>
-      <c r="B1870" s="3"/>
-      <c r="C1870" s="3"/>
-      <c r="D1870" s="3"/>
-      <c r="E1870" s="3"/>
-      <c r="F1870" s="3"/>
-      <c r="G1870" s="3"/>
-      <c r="H1870" s="3"/>
-      <c r="I1870" s="4"/>
-      <c r="J1870" s="4"/>
+      <c r="A1870" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1870" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1870" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1870" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1870" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1870" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1870" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1870" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1870" s="4">
+        <f t="shared" si="824"/>
+        <v>2026</v>
+      </c>
+      <c r="J1870" s="4">
+        <f t="shared" si="825"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1871" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1871" s="3"/>
-      <c r="B1871" s="3"/>
-      <c r="C1871" s="3"/>
-      <c r="D1871" s="3"/>
-      <c r="E1871" s="3"/>
-      <c r="F1871" s="3"/>
-      <c r="G1871" s="3"/>
-      <c r="H1871" s="3"/>
-      <c r="I1871" s="4"/>
-      <c r="J1871" s="4"/>
+      <c r="A1871" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1871" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1871" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1871" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="E1871" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1871" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1871" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1871" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1871" s="4">
+        <f t="shared" ref="I1871:I1872" si="826">YEAR(A1871)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1871" s="4">
+        <f t="shared" ref="J1871:J1872" si="827">MONTH(A1871)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1872" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1872" s="3"/>
-      <c r="B1872" s="3"/>
-      <c r="C1872" s="3"/>
-      <c r="D1872" s="3"/>
-      <c r="E1872" s="3"/>
-      <c r="F1872" s="3"/>
-      <c r="G1872" s="3"/>
-      <c r="H1872" s="3"/>
-      <c r="I1872" s="4"/>
-      <c r="J1872" s="4"/>
+      <c r="A1872" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B1872" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1872" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1872" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1872" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1872" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1872" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1872" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1872" s="4">
+        <f t="shared" si="826"/>
+        <v>2026</v>
+      </c>
+      <c r="J1872" s="4">
+        <f t="shared" si="827"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1873" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1873" s="3"/>
-      <c r="B1873" s="3"/>
-      <c r="C1873" s="3"/>
-      <c r="D1873" s="3"/>
-      <c r="E1873" s="3"/>
-      <c r="F1873" s="3"/>
-      <c r="G1873" s="3"/>
-      <c r="H1873" s="3"/>
-      <c r="I1873" s="4"/>
-      <c r="J1873" s="4"/>
+      <c r="A1873" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B1873" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1873" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1873" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1873" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1873" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1873" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1873" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1873" s="4">
+        <f t="shared" ref="I1873" si="828">YEAR(A1873)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1873" s="4">
+        <f t="shared" ref="J1873" si="829">MONTH(A1873)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1874" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1874" s="3"/>
-      <c r="B1874" s="3"/>
-      <c r="C1874" s="3"/>
-      <c r="D1874" s="3"/>
-      <c r="E1874" s="3"/>
-      <c r="F1874" s="3"/>
-      <c r="G1874" s="3"/>
-      <c r="H1874" s="3"/>
-      <c r="I1874" s="4"/>
-      <c r="J1874" s="4"/>
+      <c r="A1874" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B1874" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1874" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1874" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1874" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1874" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1874" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1874" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1874" s="4">
+        <f t="shared" ref="I1874:I1876" si="830">YEAR(A1874)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1874" s="4">
+        <f t="shared" ref="J1874:J1876" si="831">MONTH(A1874)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1875" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1875" s="3"/>
-      <c r="B1875" s="3"/>
-      <c r="C1875" s="3"/>
-      <c r="D1875" s="3"/>
-      <c r="E1875" s="3"/>
-      <c r="F1875" s="3"/>
-      <c r="G1875" s="3"/>
-      <c r="H1875" s="3"/>
-      <c r="I1875" s="4"/>
-      <c r="J1875" s="4"/>
+      <c r="A1875" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B1875" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1875" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1875" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1875" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1875" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1875" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1875" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1875" s="4">
+        <f t="shared" si="830"/>
+        <v>2026</v>
+      </c>
+      <c r="J1875" s="4">
+        <f t="shared" si="831"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1876" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1876" s="3"/>
-      <c r="B1876" s="3"/>
-      <c r="C1876" s="3"/>
-      <c r="D1876" s="3"/>
-      <c r="E1876" s="3"/>
-      <c r="F1876" s="3"/>
-      <c r="G1876" s="3"/>
-      <c r="H1876" s="3"/>
-      <c r="I1876" s="4"/>
-      <c r="J1876" s="4"/>
+      <c r="A1876" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B1876" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1876" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1876" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1876" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1876" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1876" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1876" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1876" s="4">
+        <f t="shared" si="830"/>
+        <v>2026</v>
+      </c>
+      <c r="J1876" s="4">
+        <f t="shared" si="831"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="1877" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1877" s="3"/>
-      <c r="B1877" s="3"/>
-      <c r="C1877" s="3"/>
-      <c r="D1877" s="3"/>
-      <c r="E1877" s="3"/>
-      <c r="F1877" s="3"/>
-      <c r="G1877" s="3"/>
-      <c r="H1877" s="3"/>
-      <c r="I1877" s="4"/>
-      <c r="J1877" s="4"/>
+      <c r="A1877" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B1877" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1877" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1877" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1877" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1877" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1877" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1877" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1877" s="4">
+        <f t="shared" ref="I1877:I1880" si="832">YEAR(A1877)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1877" s="4">
+        <f t="shared" ref="J1877:J1880" si="833">MONTH(A1877)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="1878" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1878" s="3"/>
-      <c r="B1878" s="3"/>
-      <c r="C1878" s="3"/>
-      <c r="D1878" s="3"/>
-      <c r="E1878" s="3"/>
-      <c r="F1878" s="3"/>
-      <c r="G1878" s="3"/>
-      <c r="H1878" s="3"/>
-      <c r="I1878" s="4"/>
-      <c r="J1878" s="4"/>
+      <c r="A1878" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1878" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1878" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1878" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1878" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1878" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G1878" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1878" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1878" s="4">
+        <f t="shared" si="832"/>
+        <v>2026</v>
+      </c>
+      <c r="J1878" s="4">
+        <f t="shared" si="833"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1879" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1879" s="3"/>
-      <c r="B1879" s="3"/>
-      <c r="C1879" s="3"/>
-      <c r="D1879" s="3"/>
-      <c r="E1879" s="3"/>
-      <c r="F1879" s="3"/>
-      <c r="G1879" s="3"/>
-      <c r="H1879" s="3"/>
-      <c r="I1879" s="4"/>
-      <c r="J1879" s="4"/>
+      <c r="A1879" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1879" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1879" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1879" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1879" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1879" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G1879" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1879" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1879" s="4">
+        <f t="shared" si="832"/>
+        <v>2026</v>
+      </c>
+      <c r="J1879" s="4">
+        <f t="shared" si="833"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1880" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1880" s="3"/>
-      <c r="B1880" s="3"/>
-      <c r="C1880" s="3"/>
-      <c r="D1880" s="3"/>
-      <c r="E1880" s="3"/>
-      <c r="F1880" s="3"/>
-      <c r="G1880" s="3"/>
-      <c r="H1880" s="3"/>
-      <c r="I1880" s="4"/>
-      <c r="J1880" s="4"/>
+      <c r="A1880" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1880" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1880" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1880" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1880" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1880" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G1880" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1880" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1880" s="4">
+        <f t="shared" si="832"/>
+        <v>2026</v>
+      </c>
+      <c r="J1880" s="4">
+        <f t="shared" si="833"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1881" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1881" s="3"/>
-      <c r="B1881" s="3"/>
-      <c r="C1881" s="3"/>
-      <c r="D1881" s="3"/>
-      <c r="E1881" s="3"/>
-      <c r="F1881" s="3"/>
-      <c r="G1881" s="3"/>
-      <c r="H1881" s="3"/>
-      <c r="I1881" s="4"/>
-      <c r="J1881" s="4"/>
+      <c r="A1881" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1881" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1881" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D1881" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1881" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1881" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G1881" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1881" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1881" s="4">
+        <f t="shared" ref="I1881:I1882" si="834">YEAR(A1881)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1881" s="4">
+        <f t="shared" ref="J1881:J1882" si="835">MONTH(A1881)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1882" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1882" s="3"/>
-      <c r="B1882" s="3"/>
-      <c r="C1882" s="3"/>
-      <c r="D1882" s="3"/>
-      <c r="E1882" s="3"/>
-      <c r="F1882" s="3"/>
-      <c r="G1882" s="3"/>
-      <c r="H1882" s="3"/>
-      <c r="I1882" s="4"/>
-      <c r="J1882" s="4"/>
+      <c r="A1882" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B1882" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1882" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1882" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1882" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1882" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G1882" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1882" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1882" s="4">
+        <f t="shared" si="834"/>
+        <v>2026</v>
+      </c>
+      <c r="J1882" s="4">
+        <f t="shared" si="835"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1883" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1883" s="3"/>
-      <c r="B1883" s="3"/>
-      <c r="C1883" s="3"/>
-      <c r="D1883" s="3"/>
-      <c r="E1883" s="3"/>
-      <c r="F1883" s="3"/>
-      <c r="G1883" s="3"/>
-      <c r="H1883" s="3"/>
-      <c r="I1883" s="4"/>
-      <c r="J1883" s="4"/>
+      <c r="A1883" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B1883" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1883" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1883" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1883" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1883" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G1883" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1883" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1883" s="4">
+        <f t="shared" ref="I1883" si="836">YEAR(A1883)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1883" s="4">
+        <f t="shared" ref="J1883" si="837">MONTH(A1883)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1884" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1884" s="3"/>
@@ -68272,6 +68629,378 @@
       <c r="I1900" s="4"/>
       <c r="J1900" s="4"/>
     </row>
+    <row r="1901" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1901" s="3"/>
+      <c r="B1901" s="3"/>
+      <c r="C1901" s="3"/>
+      <c r="D1901" s="3"/>
+      <c r="E1901" s="3"/>
+      <c r="F1901" s="3"/>
+      <c r="G1901" s="3"/>
+      <c r="H1901" s="3"/>
+      <c r="I1901" s="4"/>
+      <c r="J1901" s="4"/>
+    </row>
+    <row r="1902" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1902" s="3"/>
+      <c r="B1902" s="3"/>
+      <c r="C1902" s="3"/>
+      <c r="D1902" s="3"/>
+      <c r="E1902" s="3"/>
+      <c r="F1902" s="3"/>
+      <c r="G1902" s="3"/>
+      <c r="H1902" s="3"/>
+      <c r="I1902" s="4"/>
+      <c r="J1902" s="4"/>
+    </row>
+    <row r="1903" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1903" s="3"/>
+      <c r="B1903" s="3"/>
+      <c r="C1903" s="3"/>
+      <c r="D1903" s="3"/>
+      <c r="E1903" s="3"/>
+      <c r="F1903" s="3"/>
+      <c r="G1903" s="3"/>
+      <c r="H1903" s="3"/>
+      <c r="I1903" s="4"/>
+      <c r="J1903" s="4"/>
+    </row>
+    <row r="1904" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1904" s="3"/>
+      <c r="B1904" s="3"/>
+      <c r="C1904" s="3"/>
+      <c r="D1904" s="3"/>
+      <c r="E1904" s="3"/>
+      <c r="F1904" s="3"/>
+      <c r="G1904" s="3"/>
+      <c r="H1904" s="3"/>
+      <c r="I1904" s="4"/>
+      <c r="J1904" s="4"/>
+    </row>
+    <row r="1905" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1905" s="3"/>
+      <c r="B1905" s="3"/>
+      <c r="C1905" s="3"/>
+      <c r="D1905" s="3"/>
+      <c r="E1905" s="3"/>
+      <c r="F1905" s="3"/>
+      <c r="G1905" s="3"/>
+      <c r="H1905" s="3"/>
+      <c r="I1905" s="4"/>
+      <c r="J1905" s="4"/>
+    </row>
+    <row r="1906" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1906" s="3"/>
+      <c r="B1906" s="3"/>
+      <c r="C1906" s="3"/>
+      <c r="D1906" s="3"/>
+      <c r="E1906" s="3"/>
+      <c r="F1906" s="3"/>
+      <c r="G1906" s="3"/>
+      <c r="H1906" s="3"/>
+      <c r="I1906" s="4"/>
+      <c r="J1906" s="4"/>
+    </row>
+    <row r="1907" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1907" s="3"/>
+      <c r="B1907" s="3"/>
+      <c r="C1907" s="3"/>
+      <c r="D1907" s="3"/>
+      <c r="E1907" s="3"/>
+      <c r="F1907" s="3"/>
+      <c r="G1907" s="3"/>
+      <c r="H1907" s="3"/>
+      <c r="I1907" s="4"/>
+      <c r="J1907" s="4"/>
+    </row>
+    <row r="1908" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1908" s="3"/>
+      <c r="B1908" s="3"/>
+      <c r="C1908" s="3"/>
+      <c r="D1908" s="3"/>
+      <c r="E1908" s="3"/>
+      <c r="F1908" s="3"/>
+      <c r="G1908" s="3"/>
+      <c r="H1908" s="3"/>
+      <c r="I1908" s="4"/>
+      <c r="J1908" s="4"/>
+    </row>
+    <row r="1909" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1909" s="3"/>
+      <c r="B1909" s="3"/>
+      <c r="C1909" s="3"/>
+      <c r="D1909" s="3"/>
+      <c r="E1909" s="3"/>
+      <c r="F1909" s="3"/>
+      <c r="G1909" s="3"/>
+      <c r="H1909" s="3"/>
+      <c r="I1909" s="4"/>
+      <c r="J1909" s="4"/>
+    </row>
+    <row r="1910" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1910" s="3"/>
+      <c r="B1910" s="3"/>
+      <c r="C1910" s="3"/>
+      <c r="D1910" s="3"/>
+      <c r="E1910" s="3"/>
+      <c r="F1910" s="3"/>
+      <c r="G1910" s="3"/>
+      <c r="H1910" s="3"/>
+      <c r="I1910" s="4"/>
+      <c r="J1910" s="4"/>
+    </row>
+    <row r="1911" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1911" s="3"/>
+      <c r="B1911" s="3"/>
+      <c r="C1911" s="3"/>
+      <c r="D1911" s="3"/>
+      <c r="E1911" s="3"/>
+      <c r="F1911" s="3"/>
+      <c r="G1911" s="3"/>
+      <c r="H1911" s="3"/>
+      <c r="I1911" s="4"/>
+      <c r="J1911" s="4"/>
+    </row>
+    <row r="1912" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1912" s="3"/>
+      <c r="B1912" s="3"/>
+      <c r="C1912" s="3"/>
+      <c r="D1912" s="3"/>
+      <c r="E1912" s="3"/>
+      <c r="F1912" s="3"/>
+      <c r="G1912" s="3"/>
+      <c r="H1912" s="3"/>
+      <c r="I1912" s="4"/>
+      <c r="J1912" s="4"/>
+    </row>
+    <row r="1913" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1913" s="3"/>
+      <c r="B1913" s="3"/>
+      <c r="C1913" s="3"/>
+      <c r="D1913" s="3"/>
+      <c r="E1913" s="3"/>
+      <c r="F1913" s="3"/>
+      <c r="G1913" s="3"/>
+      <c r="H1913" s="3"/>
+      <c r="I1913" s="4"/>
+      <c r="J1913" s="4"/>
+    </row>
+    <row r="1914" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1914" s="3"/>
+      <c r="B1914" s="3"/>
+      <c r="C1914" s="3"/>
+      <c r="D1914" s="3"/>
+      <c r="E1914" s="3"/>
+      <c r="F1914" s="3"/>
+      <c r="G1914" s="3"/>
+      <c r="H1914" s="3"/>
+      <c r="I1914" s="4"/>
+      <c r="J1914" s="4"/>
+    </row>
+    <row r="1915" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1915" s="3"/>
+      <c r="B1915" s="3"/>
+      <c r="C1915" s="3"/>
+      <c r="D1915" s="3"/>
+      <c r="E1915" s="3"/>
+      <c r="F1915" s="3"/>
+      <c r="G1915" s="3"/>
+      <c r="H1915" s="3"/>
+      <c r="I1915" s="4"/>
+      <c r="J1915" s="4"/>
+    </row>
+    <row r="1916" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1916" s="3"/>
+      <c r="B1916" s="3"/>
+      <c r="C1916" s="3"/>
+      <c r="D1916" s="3"/>
+      <c r="E1916" s="3"/>
+      <c r="F1916" s="3"/>
+      <c r="G1916" s="3"/>
+      <c r="H1916" s="3"/>
+      <c r="I1916" s="4"/>
+      <c r="J1916" s="4"/>
+    </row>
+    <row r="1917" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1917" s="3"/>
+      <c r="B1917" s="3"/>
+      <c r="C1917" s="3"/>
+      <c r="D1917" s="3"/>
+      <c r="E1917" s="3"/>
+      <c r="F1917" s="3"/>
+      <c r="G1917" s="3"/>
+      <c r="H1917" s="3"/>
+      <c r="I1917" s="4"/>
+      <c r="J1917" s="4"/>
+    </row>
+    <row r="1918" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1918" s="3"/>
+      <c r="B1918" s="3"/>
+      <c r="C1918" s="3"/>
+      <c r="D1918" s="3"/>
+      <c r="E1918" s="3"/>
+      <c r="F1918" s="3"/>
+      <c r="G1918" s="3"/>
+      <c r="H1918" s="3"/>
+      <c r="I1918" s="4"/>
+      <c r="J1918" s="4"/>
+    </row>
+    <row r="1919" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1919" s="3"/>
+      <c r="B1919" s="3"/>
+      <c r="C1919" s="3"/>
+      <c r="D1919" s="3"/>
+      <c r="E1919" s="3"/>
+      <c r="F1919" s="3"/>
+      <c r="G1919" s="3"/>
+      <c r="H1919" s="3"/>
+      <c r="I1919" s="4"/>
+      <c r="J1919" s="4"/>
+    </row>
+    <row r="1920" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1920" s="3"/>
+      <c r="B1920" s="3"/>
+      <c r="C1920" s="3"/>
+      <c r="D1920" s="3"/>
+      <c r="E1920" s="3"/>
+      <c r="F1920" s="3"/>
+      <c r="G1920" s="3"/>
+      <c r="H1920" s="3"/>
+      <c r="I1920" s="4"/>
+      <c r="J1920" s="4"/>
+    </row>
+    <row r="1921" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1921" s="3"/>
+      <c r="B1921" s="3"/>
+      <c r="C1921" s="3"/>
+      <c r="D1921" s="3"/>
+      <c r="E1921" s="3"/>
+      <c r="F1921" s="3"/>
+      <c r="G1921" s="3"/>
+      <c r="H1921" s="3"/>
+      <c r="I1921" s="4"/>
+      <c r="J1921" s="4"/>
+    </row>
+    <row r="1922" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1922" s="3"/>
+      <c r="B1922" s="3"/>
+      <c r="C1922" s="3"/>
+      <c r="D1922" s="3"/>
+      <c r="E1922" s="3"/>
+      <c r="F1922" s="3"/>
+      <c r="G1922" s="3"/>
+      <c r="H1922" s="3"/>
+      <c r="I1922" s="4"/>
+      <c r="J1922" s="4"/>
+    </row>
+    <row r="1923" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1923" s="3"/>
+      <c r="B1923" s="3"/>
+      <c r="C1923" s="3"/>
+      <c r="D1923" s="3"/>
+      <c r="E1923" s="3"/>
+      <c r="F1923" s="3"/>
+      <c r="G1923" s="3"/>
+      <c r="H1923" s="3"/>
+      <c r="I1923" s="4"/>
+      <c r="J1923" s="4"/>
+    </row>
+    <row r="1924" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1924" s="3"/>
+      <c r="B1924" s="3"/>
+      <c r="C1924" s="3"/>
+      <c r="D1924" s="3"/>
+      <c r="E1924" s="3"/>
+      <c r="F1924" s="3"/>
+      <c r="G1924" s="3"/>
+      <c r="H1924" s="3"/>
+      <c r="I1924" s="4"/>
+      <c r="J1924" s="4"/>
+    </row>
+    <row r="1925" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1925" s="3"/>
+      <c r="B1925" s="3"/>
+      <c r="C1925" s="3"/>
+      <c r="D1925" s="3"/>
+      <c r="E1925" s="3"/>
+      <c r="F1925" s="3"/>
+      <c r="G1925" s="3"/>
+      <c r="H1925" s="3"/>
+      <c r="I1925" s="4"/>
+      <c r="J1925" s="4"/>
+    </row>
+    <row r="1926" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1926" s="3"/>
+      <c r="B1926" s="3"/>
+      <c r="C1926" s="3"/>
+      <c r="D1926" s="3"/>
+      <c r="E1926" s="3"/>
+      <c r="F1926" s="3"/>
+      <c r="G1926" s="3"/>
+      <c r="H1926" s="3"/>
+      <c r="I1926" s="4"/>
+      <c r="J1926" s="4"/>
+    </row>
+    <row r="1927" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1927" s="3"/>
+      <c r="B1927" s="3"/>
+      <c r="C1927" s="3"/>
+      <c r="D1927" s="3"/>
+      <c r="E1927" s="3"/>
+      <c r="F1927" s="3"/>
+      <c r="G1927" s="3"/>
+      <c r="H1927" s="3"/>
+      <c r="I1927" s="4"/>
+      <c r="J1927" s="4"/>
+    </row>
+    <row r="1928" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1928" s="3"/>
+      <c r="B1928" s="3"/>
+      <c r="C1928" s="3"/>
+      <c r="D1928" s="3"/>
+      <c r="E1928" s="3"/>
+      <c r="F1928" s="3"/>
+      <c r="G1928" s="3"/>
+      <c r="H1928" s="3"/>
+      <c r="I1928" s="4"/>
+      <c r="J1928" s="4"/>
+    </row>
+    <row r="1929" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1929" s="3"/>
+      <c r="B1929" s="3"/>
+      <c r="C1929" s="3"/>
+      <c r="D1929" s="3"/>
+      <c r="E1929" s="3"/>
+      <c r="F1929" s="3"/>
+      <c r="G1929" s="3"/>
+      <c r="H1929" s="3"/>
+      <c r="I1929" s="4"/>
+      <c r="J1929" s="4"/>
+    </row>
+    <row r="1930" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1930" s="3"/>
+      <c r="B1930" s="3"/>
+      <c r="C1930" s="3"/>
+      <c r="D1930" s="3"/>
+      <c r="E1930" s="3"/>
+      <c r="F1930" s="3"/>
+      <c r="G1930" s="3"/>
+      <c r="H1930" s="3"/>
+      <c r="I1930" s="4"/>
+      <c r="J1930" s="4"/>
+    </row>
+    <row r="1931" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1931" s="3"/>
+      <c r="B1931" s="3"/>
+      <c r="C1931" s="3"/>
+      <c r="D1931" s="3"/>
+      <c r="E1931" s="3"/>
+      <c r="F1931" s="3"/>
+      <c r="G1931" s="3"/>
+      <c r="H1931" s="3"/>
+      <c r="I1931" s="4"/>
+      <c r="J1931" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14944" uniqueCount="1605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15024" uniqueCount="1612">
   <si>
     <t>Year</t>
   </si>
@@ -4840,6 +4840,27 @@
   </si>
   <si>
     <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>7h 15m</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
   </si>
 </sst>
 </file>
@@ -5248,7 +5269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1931"/>
+  <dimension ref="A1:J1956"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -69662,133 +69683,353 @@
         <v>280</v>
       </c>
       <c r="I1918" s="4">
-        <f t="shared" ref="I1918" si="866">YEAR(A1918)</f>
+        <f t="shared" ref="I1918:I1919" si="866">YEAR(A1918)</f>
         <v>2026</v>
       </c>
       <c r="J1918" s="4">
-        <f t="shared" ref="J1918" si="867">MONTH(A1918)</f>
+        <f t="shared" ref="J1918:J1919" si="867">MONTH(A1918)</f>
         <v>2</v>
       </c>
     </row>
     <row r="1919" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1919" s="3"/>
-      <c r="B1919" s="3"/>
-      <c r="C1919" s="3"/>
-      <c r="D1919" s="3"/>
-      <c r="E1919" s="3"/>
-      <c r="F1919" s="3"/>
-      <c r="G1919" s="3"/>
-      <c r="H1919" s="3"/>
-      <c r="I1919" s="4"/>
-      <c r="J1919" s="4"/>
+      <c r="A1919" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B1919" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1919" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1919" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1919" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1919" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1919" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1919" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1919" s="4">
+        <f t="shared" si="866"/>
+        <v>2026</v>
+      </c>
+      <c r="J1919" s="4">
+        <f t="shared" si="867"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1920" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1920" s="3"/>
-      <c r="B1920" s="3"/>
-      <c r="C1920" s="3"/>
-      <c r="D1920" s="3"/>
-      <c r="E1920" s="3"/>
-      <c r="F1920" s="3"/>
-      <c r="G1920" s="3"/>
-      <c r="H1920" s="3"/>
-      <c r="I1920" s="4"/>
-      <c r="J1920" s="4"/>
+      <c r="A1920" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B1920" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1920" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1920" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1920" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1920" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1920" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1920" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1920" s="4">
+        <f t="shared" ref="I1920:I1921" si="868">YEAR(A1920)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1920" s="4">
+        <f t="shared" ref="J1920:J1921" si="869">MONTH(A1920)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1921" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1921" s="3"/>
-      <c r="B1921" s="3"/>
-      <c r="C1921" s="3"/>
-      <c r="D1921" s="3"/>
-      <c r="E1921" s="3"/>
-      <c r="F1921" s="3"/>
-      <c r="G1921" s="3"/>
-      <c r="H1921" s="3"/>
-      <c r="I1921" s="4"/>
-      <c r="J1921" s="4"/>
+      <c r="A1921" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1921" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1921" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1921" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1921" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1921" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1921" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1921" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1921" s="4">
+        <f t="shared" si="868"/>
+        <v>2026</v>
+      </c>
+      <c r="J1921" s="4">
+        <f t="shared" si="869"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1922" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1922" s="3"/>
-      <c r="B1922" s="3"/>
-      <c r="C1922" s="3"/>
-      <c r="D1922" s="3"/>
-      <c r="E1922" s="3"/>
-      <c r="F1922" s="3"/>
-      <c r="G1922" s="3"/>
-      <c r="H1922" s="3"/>
-      <c r="I1922" s="4"/>
-      <c r="J1922" s="4"/>
+      <c r="A1922" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1922" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1922" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1922" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1922" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1922" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1922" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1922" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1922" s="4">
+        <f t="shared" ref="I1922:I1923" si="870">YEAR(A1922)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1922" s="4">
+        <f t="shared" ref="J1922:J1923" si="871">MONTH(A1922)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1923" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1923" s="3"/>
-      <c r="B1923" s="3"/>
-      <c r="C1923" s="3"/>
-      <c r="D1923" s="3"/>
-      <c r="E1923" s="3"/>
-      <c r="F1923" s="3"/>
-      <c r="G1923" s="3"/>
-      <c r="H1923" s="3"/>
-      <c r="I1923" s="4"/>
-      <c r="J1923" s="4"/>
+      <c r="A1923" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1923" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1923" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1923" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1923" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1923" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1923" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1923" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1923" s="4">
+        <f t="shared" si="870"/>
+        <v>2026</v>
+      </c>
+      <c r="J1923" s="4">
+        <f t="shared" si="871"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1924" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1924" s="3"/>
-      <c r="B1924" s="3"/>
-      <c r="C1924" s="3"/>
-      <c r="D1924" s="3"/>
-      <c r="E1924" s="3"/>
-      <c r="F1924" s="3"/>
-      <c r="G1924" s="3"/>
-      <c r="H1924" s="3"/>
-      <c r="I1924" s="4"/>
-      <c r="J1924" s="4"/>
+      <c r="A1924" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1924" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1924" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1924" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1924" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1924" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1924" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1924" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1924" s="4">
+        <f t="shared" ref="I1924:I1925" si="872">YEAR(A1924)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1924" s="4">
+        <f t="shared" ref="J1924:J1925" si="873">MONTH(A1924)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1925" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1925" s="3"/>
-      <c r="B1925" s="3"/>
-      <c r="C1925" s="3"/>
-      <c r="D1925" s="3"/>
-      <c r="E1925" s="3"/>
-      <c r="F1925" s="3"/>
-      <c r="G1925" s="3"/>
-      <c r="H1925" s="3"/>
-      <c r="I1925" s="4"/>
-      <c r="J1925" s="4"/>
+      <c r="A1925" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1925" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1925" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1925" s="3" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E1925" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1925" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1925" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1925" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1925" s="4">
+        <f t="shared" si="872"/>
+        <v>2026</v>
+      </c>
+      <c r="J1925" s="4">
+        <f t="shared" si="873"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="1926" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1926" s="3"/>
-      <c r="B1926" s="3"/>
-      <c r="C1926" s="3"/>
-      <c r="D1926" s="3"/>
-      <c r="E1926" s="3"/>
-      <c r="F1926" s="3"/>
-      <c r="G1926" s="3"/>
-      <c r="H1926" s="3"/>
-      <c r="I1926" s="4"/>
-      <c r="J1926" s="4"/>
+      <c r="A1926" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1926" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1926" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1926" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1926" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1926" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1926" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1926" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1926" s="4">
+        <f t="shared" ref="I1926" si="874">YEAR(A1926)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1926" s="4">
+        <f t="shared" ref="J1926" si="875">MONTH(A1926)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1927" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1927" s="3"/>
-      <c r="B1927" s="3"/>
-      <c r="C1927" s="3"/>
-      <c r="D1927" s="3"/>
-      <c r="E1927" s="3"/>
-      <c r="F1927" s="3"/>
-      <c r="G1927" s="3"/>
-      <c r="H1927" s="3"/>
-      <c r="I1927" s="4"/>
-      <c r="J1927" s="4"/>
+      <c r="A1927" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B1927" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1927" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1927" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="E1927" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1927" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1927" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1927" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1927" s="4">
+        <f t="shared" ref="I1927" si="876">YEAR(A1927)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1927" s="4">
+        <f t="shared" ref="J1927" si="877">MONTH(A1927)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1928" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1928" s="3"/>
-      <c r="B1928" s="3"/>
-      <c r="C1928" s="3"/>
-      <c r="D1928" s="3"/>
-      <c r="E1928" s="3"/>
-      <c r="F1928" s="3"/>
-      <c r="G1928" s="3"/>
-      <c r="H1928" s="3"/>
-      <c r="I1928" s="4"/>
-      <c r="J1928" s="4"/>
+      <c r="A1928" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1928" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1928" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1928" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1928" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1928" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1928" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1928" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1928" s="4">
+        <f t="shared" ref="I1928" si="878">YEAR(A1928)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1928" s="4">
+        <f t="shared" ref="J1928" si="879">MONTH(A1928)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="1929" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1929" s="3"/>
@@ -69826,6 +70067,306 @@
       <c r="I1931" s="4"/>
       <c r="J1931" s="4"/>
     </row>
+    <row r="1932" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1932" s="3"/>
+      <c r="B1932" s="3"/>
+      <c r="C1932" s="3"/>
+      <c r="D1932" s="3"/>
+      <c r="E1932" s="3"/>
+      <c r="F1932" s="3"/>
+      <c r="G1932" s="3"/>
+      <c r="H1932" s="3"/>
+      <c r="I1932" s="4"/>
+      <c r="J1932" s="4"/>
+    </row>
+    <row r="1933" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1933" s="3"/>
+      <c r="B1933" s="3"/>
+      <c r="C1933" s="3"/>
+      <c r="D1933" s="3"/>
+      <c r="E1933" s="3"/>
+      <c r="F1933" s="3"/>
+      <c r="G1933" s="3"/>
+      <c r="H1933" s="3"/>
+      <c r="I1933" s="4"/>
+      <c r="J1933" s="4"/>
+    </row>
+    <row r="1934" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1934" s="3"/>
+      <c r="B1934" s="3"/>
+      <c r="C1934" s="3"/>
+      <c r="D1934" s="3"/>
+      <c r="E1934" s="3"/>
+      <c r="F1934" s="3"/>
+      <c r="G1934" s="3"/>
+      <c r="H1934" s="3"/>
+      <c r="I1934" s="4"/>
+      <c r="J1934" s="4"/>
+    </row>
+    <row r="1935" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1935" s="3"/>
+      <c r="B1935" s="3"/>
+      <c r="C1935" s="3"/>
+      <c r="D1935" s="3"/>
+      <c r="E1935" s="3"/>
+      <c r="F1935" s="3"/>
+      <c r="G1935" s="3"/>
+      <c r="H1935" s="3"/>
+      <c r="I1935" s="4"/>
+      <c r="J1935" s="4"/>
+    </row>
+    <row r="1936" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1936" s="3"/>
+      <c r="B1936" s="3"/>
+      <c r="C1936" s="3"/>
+      <c r="D1936" s="3"/>
+      <c r="E1936" s="3"/>
+      <c r="F1936" s="3"/>
+      <c r="G1936" s="3"/>
+      <c r="H1936" s="3"/>
+      <c r="I1936" s="4"/>
+      <c r="J1936" s="4"/>
+    </row>
+    <row r="1937" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1937" s="3"/>
+      <c r="B1937" s="3"/>
+      <c r="C1937" s="3"/>
+      <c r="D1937" s="3"/>
+      <c r="E1937" s="3"/>
+      <c r="F1937" s="3"/>
+      <c r="G1937" s="3"/>
+      <c r="H1937" s="3"/>
+      <c r="I1937" s="4"/>
+      <c r="J1937" s="4"/>
+    </row>
+    <row r="1938" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1938" s="3"/>
+      <c r="B1938" s="3"/>
+      <c r="C1938" s="3"/>
+      <c r="D1938" s="3"/>
+      <c r="E1938" s="3"/>
+      <c r="F1938" s="3"/>
+      <c r="G1938" s="3"/>
+      <c r="H1938" s="3"/>
+      <c r="I1938" s="4"/>
+      <c r="J1938" s="4"/>
+    </row>
+    <row r="1939" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1939" s="3"/>
+      <c r="B1939" s="3"/>
+      <c r="C1939" s="3"/>
+      <c r="D1939" s="3"/>
+      <c r="E1939" s="3"/>
+      <c r="F1939" s="3"/>
+      <c r="G1939" s="3"/>
+      <c r="H1939" s="3"/>
+      <c r="I1939" s="4"/>
+      <c r="J1939" s="4"/>
+    </row>
+    <row r="1940" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1940" s="3"/>
+      <c r="B1940" s="3"/>
+      <c r="C1940" s="3"/>
+      <c r="D1940" s="3"/>
+      <c r="E1940" s="3"/>
+      <c r="F1940" s="3"/>
+      <c r="G1940" s="3"/>
+      <c r="H1940" s="3"/>
+      <c r="I1940" s="4"/>
+      <c r="J1940" s="4"/>
+    </row>
+    <row r="1941" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1941" s="3"/>
+      <c r="B1941" s="3"/>
+      <c r="C1941" s="3"/>
+      <c r="D1941" s="3"/>
+      <c r="E1941" s="3"/>
+      <c r="F1941" s="3"/>
+      <c r="G1941" s="3"/>
+      <c r="H1941" s="3"/>
+      <c r="I1941" s="4"/>
+      <c r="J1941" s="4"/>
+    </row>
+    <row r="1942" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1942" s="3"/>
+      <c r="B1942" s="3"/>
+      <c r="C1942" s="3"/>
+      <c r="D1942" s="3"/>
+      <c r="E1942" s="3"/>
+      <c r="F1942" s="3"/>
+      <c r="G1942" s="3"/>
+      <c r="H1942" s="3"/>
+      <c r="I1942" s="4"/>
+      <c r="J1942" s="4"/>
+    </row>
+    <row r="1943" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1943" s="3"/>
+      <c r="B1943" s="3"/>
+      <c r="C1943" s="3"/>
+      <c r="D1943" s="3"/>
+      <c r="E1943" s="3"/>
+      <c r="F1943" s="3"/>
+      <c r="G1943" s="3"/>
+      <c r="H1943" s="3"/>
+      <c r="I1943" s="4"/>
+      <c r="J1943" s="4"/>
+    </row>
+    <row r="1944" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1944" s="3"/>
+      <c r="B1944" s="3"/>
+      <c r="C1944" s="3"/>
+      <c r="D1944" s="3"/>
+      <c r="E1944" s="3"/>
+      <c r="F1944" s="3"/>
+      <c r="G1944" s="3"/>
+      <c r="H1944" s="3"/>
+      <c r="I1944" s="4"/>
+      <c r="J1944" s="4"/>
+    </row>
+    <row r="1945" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1945" s="3"/>
+      <c r="B1945" s="3"/>
+      <c r="C1945" s="3"/>
+      <c r="D1945" s="3"/>
+      <c r="E1945" s="3"/>
+      <c r="F1945" s="3"/>
+      <c r="G1945" s="3"/>
+      <c r="H1945" s="3"/>
+      <c r="I1945" s="4"/>
+      <c r="J1945" s="4"/>
+    </row>
+    <row r="1946" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1946" s="3"/>
+      <c r="B1946" s="3"/>
+      <c r="C1946" s="3"/>
+      <c r="D1946" s="3"/>
+      <c r="E1946" s="3"/>
+      <c r="F1946" s="3"/>
+      <c r="G1946" s="3"/>
+      <c r="H1946" s="3"/>
+      <c r="I1946" s="4"/>
+      <c r="J1946" s="4"/>
+    </row>
+    <row r="1947" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1947" s="3"/>
+      <c r="B1947" s="3"/>
+      <c r="C1947" s="3"/>
+      <c r="D1947" s="3"/>
+      <c r="E1947" s="3"/>
+      <c r="F1947" s="3"/>
+      <c r="G1947" s="3"/>
+      <c r="H1947" s="3"/>
+      <c r="I1947" s="4"/>
+      <c r="J1947" s="4"/>
+    </row>
+    <row r="1948" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1948" s="3"/>
+      <c r="B1948" s="3"/>
+      <c r="C1948" s="3"/>
+      <c r="D1948" s="3"/>
+      <c r="E1948" s="3"/>
+      <c r="F1948" s="3"/>
+      <c r="G1948" s="3"/>
+      <c r="H1948" s="3"/>
+      <c r="I1948" s="4"/>
+      <c r="J1948" s="4"/>
+    </row>
+    <row r="1949" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1949" s="3"/>
+      <c r="B1949" s="3"/>
+      <c r="C1949" s="3"/>
+      <c r="D1949" s="3"/>
+      <c r="E1949" s="3"/>
+      <c r="F1949" s="3"/>
+      <c r="G1949" s="3"/>
+      <c r="H1949" s="3"/>
+      <c r="I1949" s="4"/>
+      <c r="J1949" s="4"/>
+    </row>
+    <row r="1950" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1950" s="3"/>
+      <c r="B1950" s="3"/>
+      <c r="C1950" s="3"/>
+      <c r="D1950" s="3"/>
+      <c r="E1950" s="3"/>
+      <c r="F1950" s="3"/>
+      <c r="G1950" s="3"/>
+      <c r="H1950" s="3"/>
+      <c r="I1950" s="4"/>
+      <c r="J1950" s="4"/>
+    </row>
+    <row r="1951" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1951" s="3"/>
+      <c r="B1951" s="3"/>
+      <c r="C1951" s="3"/>
+      <c r="D1951" s="3"/>
+      <c r="E1951" s="3"/>
+      <c r="F1951" s="3"/>
+      <c r="G1951" s="3"/>
+      <c r="H1951" s="3"/>
+      <c r="I1951" s="4"/>
+      <c r="J1951" s="4"/>
+    </row>
+    <row r="1952" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1952" s="3"/>
+      <c r="B1952" s="3"/>
+      <c r="C1952" s="3"/>
+      <c r="D1952" s="3"/>
+      <c r="E1952" s="3"/>
+      <c r="F1952" s="3"/>
+      <c r="G1952" s="3"/>
+      <c r="H1952" s="3"/>
+      <c r="I1952" s="4"/>
+      <c r="J1952" s="4"/>
+    </row>
+    <row r="1953" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1953" s="3"/>
+      <c r="B1953" s="3"/>
+      <c r="C1953" s="3"/>
+      <c r="D1953" s="3"/>
+      <c r="E1953" s="3"/>
+      <c r="F1953" s="3"/>
+      <c r="G1953" s="3"/>
+      <c r="H1953" s="3"/>
+      <c r="I1953" s="4"/>
+      <c r="J1953" s="4"/>
+    </row>
+    <row r="1954" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1954" s="3"/>
+      <c r="B1954" s="3"/>
+      <c r="C1954" s="3"/>
+      <c r="D1954" s="3"/>
+      <c r="E1954" s="3"/>
+      <c r="F1954" s="3"/>
+      <c r="G1954" s="3"/>
+      <c r="H1954" s="3"/>
+      <c r="I1954" s="4"/>
+      <c r="J1954" s="4"/>
+    </row>
+    <row r="1955" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1955" s="3"/>
+      <c r="B1955" s="3"/>
+      <c r="C1955" s="3"/>
+      <c r="D1955" s="3"/>
+      <c r="E1955" s="3"/>
+      <c r="F1955" s="3"/>
+      <c r="G1955" s="3"/>
+      <c r="H1955" s="3"/>
+      <c r="I1955" s="4"/>
+      <c r="J1955" s="4"/>
+    </row>
+    <row r="1956" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1956" s="3"/>
+      <c r="B1956" s="3"/>
+      <c r="C1956" s="3"/>
+      <c r="D1956" s="3"/>
+      <c r="E1956" s="3"/>
+      <c r="F1956" s="3"/>
+      <c r="G1956" s="3"/>
+      <c r="H1956" s="3"/>
+      <c r="I1956" s="4"/>
+      <c r="J1956" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15024" uniqueCount="1612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15285" uniqueCount="1628">
   <si>
     <t>Year</t>
   </si>
@@ -4861,6 +4861,54 @@
   </si>
   <si>
     <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>config-nwbuilders v1.0.0</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
   </si>
 </sst>
 </file>
@@ -5269,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1956"/>
+  <dimension ref="A1:J1998"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -70023,349 +70071,1573 @@
         <v>280</v>
       </c>
       <c r="I1928" s="4">
-        <f t="shared" ref="I1928" si="878">YEAR(A1928)</f>
+        <f t="shared" ref="I1928:I1929" si="878">YEAR(A1928)</f>
         <v>2026</v>
       </c>
       <c r="J1928" s="4">
-        <f t="shared" ref="J1928" si="879">MONTH(A1928)</f>
+        <f t="shared" ref="J1928:J1929" si="879">MONTH(A1928)</f>
         <v>2</v>
       </c>
     </row>
     <row r="1929" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1929" s="3"/>
-      <c r="B1929" s="3"/>
-      <c r="C1929" s="3"/>
-      <c r="D1929" s="3"/>
-      <c r="E1929" s="3"/>
-      <c r="F1929" s="3"/>
-      <c r="G1929" s="3"/>
-      <c r="H1929" s="3"/>
-      <c r="I1929" s="4"/>
-      <c r="J1929" s="4"/>
+      <c r="A1929" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1929" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1929" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1929" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1929" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1929" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1929" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1929" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1929" s="4">
+        <f t="shared" si="878"/>
+        <v>2026</v>
+      </c>
+      <c r="J1929" s="4">
+        <f t="shared" si="879"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1930" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1930" s="3"/>
-      <c r="B1930" s="3"/>
-      <c r="C1930" s="3"/>
-      <c r="D1930" s="3"/>
-      <c r="E1930" s="3"/>
-      <c r="F1930" s="3"/>
-      <c r="G1930" s="3"/>
-      <c r="H1930" s="3"/>
-      <c r="I1930" s="4"/>
-      <c r="J1930" s="4"/>
+      <c r="A1930" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1930" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1930" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1930" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1930" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1930" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1930" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1930" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1930" s="4">
+        <f t="shared" ref="I1930:I1931" si="880">YEAR(A1930)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1930" s="4">
+        <f t="shared" ref="J1930:J1931" si="881">MONTH(A1930)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1931" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1931" s="3"/>
-      <c r="B1931" s="3"/>
-      <c r="C1931" s="3"/>
-      <c r="D1931" s="3"/>
-      <c r="E1931" s="3"/>
-      <c r="F1931" s="3"/>
-      <c r="G1931" s="3"/>
-      <c r="H1931" s="3"/>
-      <c r="I1931" s="4"/>
-      <c r="J1931" s="4"/>
+      <c r="A1931" s="3" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1931" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1931" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1931" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1931" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1931" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1931" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1931" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1931" s="4">
+        <f t="shared" si="880"/>
+        <v>2026</v>
+      </c>
+      <c r="J1931" s="4">
+        <f t="shared" si="881"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1932" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1932" s="3"/>
-      <c r="B1932" s="3"/>
-      <c r="C1932" s="3"/>
-      <c r="D1932" s="3"/>
-      <c r="E1932" s="3"/>
-      <c r="F1932" s="3"/>
-      <c r="G1932" s="3"/>
-      <c r="H1932" s="3"/>
-      <c r="I1932" s="4"/>
-      <c r="J1932" s="4"/>
+      <c r="A1932" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1932" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1932" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1932" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="E1932" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1932" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1932" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1932" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1932" s="4">
+        <f t="shared" ref="I1932" si="882">YEAR(A1932)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1932" s="4">
+        <f t="shared" ref="J1932" si="883">MONTH(A1932)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1933" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1933" s="3"/>
-      <c r="B1933" s="3"/>
-      <c r="C1933" s="3"/>
-      <c r="D1933" s="3"/>
-      <c r="E1933" s="3"/>
-      <c r="F1933" s="3"/>
-      <c r="G1933" s="3"/>
-      <c r="H1933" s="3"/>
-      <c r="I1933" s="4"/>
-      <c r="J1933" s="4"/>
+      <c r="A1933" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1933" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1933" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1933" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1933" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1933" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1933" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1933" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1933" s="4">
+        <f t="shared" ref="I1933" si="884">YEAR(A1933)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1933" s="4">
+        <f t="shared" ref="J1933" si="885">MONTH(A1933)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1934" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1934" s="3"/>
-      <c r="B1934" s="3"/>
-      <c r="C1934" s="3"/>
-      <c r="D1934" s="3"/>
-      <c r="E1934" s="3"/>
-      <c r="F1934" s="3"/>
-      <c r="G1934" s="3"/>
-      <c r="H1934" s="3"/>
-      <c r="I1934" s="4"/>
-      <c r="J1934" s="4"/>
+      <c r="A1934" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1934" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1934" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1934" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1934" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1934" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1934" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1934" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1934" s="4">
+        <f t="shared" ref="I1934:I1935" si="886">YEAR(A1934)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1934" s="4">
+        <f t="shared" ref="J1934:J1935" si="887">MONTH(A1934)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1935" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1935" s="3"/>
-      <c r="B1935" s="3"/>
-      <c r="C1935" s="3"/>
-      <c r="D1935" s="3"/>
-      <c r="E1935" s="3"/>
-      <c r="F1935" s="3"/>
-      <c r="G1935" s="3"/>
-      <c r="H1935" s="3"/>
-      <c r="I1935" s="4"/>
-      <c r="J1935" s="4"/>
+      <c r="A1935" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1935" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1935" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1935" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1935" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1935" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1935" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1935" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1935" s="4">
+        <f t="shared" si="886"/>
+        <v>2026</v>
+      </c>
+      <c r="J1935" s="4">
+        <f t="shared" si="887"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1936" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1936" s="3"/>
-      <c r="B1936" s="3"/>
-      <c r="C1936" s="3"/>
-      <c r="D1936" s="3"/>
-      <c r="E1936" s="3"/>
-      <c r="F1936" s="3"/>
-      <c r="G1936" s="3"/>
-      <c r="H1936" s="3"/>
-      <c r="I1936" s="4"/>
-      <c r="J1936" s="4"/>
+      <c r="A1936" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1936" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1936" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1936" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1936" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1936" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1936" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1936" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1936" s="4">
+        <f t="shared" ref="I1936:I1937" si="888">YEAR(A1936)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1936" s="4">
+        <f t="shared" ref="J1936:J1937" si="889">MONTH(A1936)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1937" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1937" s="3"/>
-      <c r="B1937" s="3"/>
-      <c r="C1937" s="3"/>
-      <c r="D1937" s="3"/>
-      <c r="E1937" s="3"/>
-      <c r="F1937" s="3"/>
-      <c r="G1937" s="3"/>
-      <c r="H1937" s="3"/>
-      <c r="I1937" s="4"/>
-      <c r="J1937" s="4"/>
+      <c r="A1937" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1937" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1937" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1937" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1937" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1937" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1937" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1937" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1937" s="4">
+        <f t="shared" si="888"/>
+        <v>2026</v>
+      </c>
+      <c r="J1937" s="4">
+        <f t="shared" si="889"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1938" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1938" s="3"/>
-      <c r="B1938" s="3"/>
-      <c r="C1938" s="3"/>
-      <c r="D1938" s="3"/>
-      <c r="E1938" s="3"/>
-      <c r="F1938" s="3"/>
-      <c r="G1938" s="3"/>
-      <c r="H1938" s="3"/>
-      <c r="I1938" s="4"/>
-      <c r="J1938" s="4"/>
+      <c r="A1938" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1938" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1938" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1938" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1938" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1938" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1938" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1938" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1938" s="4">
+        <f t="shared" ref="I1938:I1942" si="890">YEAR(A1938)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1938" s="4">
+        <f t="shared" ref="J1938:J1942" si="891">MONTH(A1938)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1939" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1939" s="3"/>
-      <c r="B1939" s="3"/>
-      <c r="C1939" s="3"/>
-      <c r="D1939" s="3"/>
-      <c r="E1939" s="3"/>
-      <c r="F1939" s="3"/>
-      <c r="G1939" s="3"/>
-      <c r="H1939" s="3"/>
-      <c r="I1939" s="4"/>
-      <c r="J1939" s="4"/>
+      <c r="A1939" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1939" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1939" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1939" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1939" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1939" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1939" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1939" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1939" s="4">
+        <f t="shared" si="890"/>
+        <v>2026</v>
+      </c>
+      <c r="J1939" s="4">
+        <f t="shared" si="891"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1940" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1940" s="3"/>
-      <c r="B1940" s="3"/>
-      <c r="C1940" s="3"/>
-      <c r="D1940" s="3"/>
-      <c r="E1940" s="3"/>
-      <c r="F1940" s="3"/>
-      <c r="G1940" s="3"/>
-      <c r="H1940" s="3"/>
-      <c r="I1940" s="4"/>
-      <c r="J1940" s="4"/>
+      <c r="A1940" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B1940" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1940" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1940" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E1940" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1940" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1940" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1940" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1940" s="4">
+        <f t="shared" si="890"/>
+        <v>2026</v>
+      </c>
+      <c r="J1940" s="4">
+        <f t="shared" si="891"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1941" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1941" s="3"/>
-      <c r="B1941" s="3"/>
-      <c r="C1941" s="3"/>
-      <c r="D1941" s="3"/>
-      <c r="E1941" s="3"/>
-      <c r="F1941" s="3"/>
-      <c r="G1941" s="3"/>
-      <c r="H1941" s="3"/>
-      <c r="I1941" s="4"/>
-      <c r="J1941" s="4"/>
+      <c r="A1941" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B1941" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1941" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1941" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1941" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1941" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1941" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1941" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1941" s="4">
+        <f t="shared" si="890"/>
+        <v>2026</v>
+      </c>
+      <c r="J1941" s="4">
+        <f t="shared" si="891"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1942" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1942" s="3"/>
-      <c r="B1942" s="3"/>
-      <c r="C1942" s="3"/>
-      <c r="D1942" s="3"/>
-      <c r="E1942" s="3"/>
-      <c r="F1942" s="3"/>
-      <c r="G1942" s="3"/>
-      <c r="H1942" s="3"/>
-      <c r="I1942" s="4"/>
-      <c r="J1942" s="4"/>
+      <c r="A1942" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B1942" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1942" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1942" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1942" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1942" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1942" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1942" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1942" s="4">
+        <f t="shared" si="890"/>
+        <v>2026</v>
+      </c>
+      <c r="J1942" s="4">
+        <f t="shared" si="891"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1943" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1943" s="3"/>
-      <c r="B1943" s="3"/>
-      <c r="C1943" s="3"/>
-      <c r="D1943" s="3"/>
-      <c r="E1943" s="3"/>
-      <c r="F1943" s="3"/>
-      <c r="G1943" s="3"/>
-      <c r="H1943" s="3"/>
-      <c r="I1943" s="4"/>
-      <c r="J1943" s="4"/>
+      <c r="A1943" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1943" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1943" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1943" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1943" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1943" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1943" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1943" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1943" s="4">
+        <f t="shared" ref="I1943:I1945" si="892">YEAR(A1943)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1943" s="4">
+        <f t="shared" ref="J1943:J1945" si="893">MONTH(A1943)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1944" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1944" s="3"/>
-      <c r="B1944" s="3"/>
-      <c r="C1944" s="3"/>
-      <c r="D1944" s="3"/>
-      <c r="E1944" s="3"/>
-      <c r="F1944" s="3"/>
-      <c r="G1944" s="3"/>
-      <c r="H1944" s="3"/>
-      <c r="I1944" s="4"/>
-      <c r="J1944" s="4"/>
+      <c r="A1944" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1944" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1944" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1944" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1944" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1944" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1944" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1944" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1944" s="4">
+        <f t="shared" si="892"/>
+        <v>2026</v>
+      </c>
+      <c r="J1944" s="4">
+        <f t="shared" si="893"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1945" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1945" s="3"/>
-      <c r="B1945" s="3"/>
-      <c r="C1945" s="3"/>
-      <c r="D1945" s="3"/>
-      <c r="E1945" s="3"/>
-      <c r="F1945" s="3"/>
-      <c r="G1945" s="3"/>
-      <c r="H1945" s="3"/>
-      <c r="I1945" s="4"/>
-      <c r="J1945" s="4"/>
+      <c r="A1945" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1945" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1945" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1945" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1945" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1945" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1945" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1945" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1945" s="4">
+        <f t="shared" si="892"/>
+        <v>2026</v>
+      </c>
+      <c r="J1945" s="4">
+        <f t="shared" si="893"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1946" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1946" s="3"/>
-      <c r="B1946" s="3"/>
-      <c r="C1946" s="3"/>
-      <c r="D1946" s="3"/>
-      <c r="E1946" s="3"/>
-      <c r="F1946" s="3"/>
-      <c r="G1946" s="3"/>
-      <c r="H1946" s="3"/>
-      <c r="I1946" s="4"/>
-      <c r="J1946" s="4"/>
+      <c r="A1946" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1946" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1946" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1946" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1946" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1946" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1946" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1946" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1946" s="4">
+        <f t="shared" ref="I1946:I1950" si="894">YEAR(A1946)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1946" s="4">
+        <f t="shared" ref="J1946:J1950" si="895">MONTH(A1946)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1947" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1947" s="3"/>
-      <c r="B1947" s="3"/>
-      <c r="C1947" s="3"/>
-      <c r="D1947" s="3"/>
-      <c r="E1947" s="3"/>
-      <c r="F1947" s="3"/>
-      <c r="G1947" s="3"/>
-      <c r="H1947" s="3"/>
-      <c r="I1947" s="4"/>
-      <c r="J1947" s="4"/>
+      <c r="A1947" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1947" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1947" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1947" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1947" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1947" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1947" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1947" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1947" s="4">
+        <f t="shared" si="894"/>
+        <v>2026</v>
+      </c>
+      <c r="J1947" s="4">
+        <f t="shared" si="895"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1948" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1948" s="3"/>
-      <c r="B1948" s="3"/>
-      <c r="C1948" s="3"/>
-      <c r="D1948" s="3"/>
-      <c r="E1948" s="3"/>
-      <c r="F1948" s="3"/>
-      <c r="G1948" s="3"/>
-      <c r="H1948" s="3"/>
-      <c r="I1948" s="4"/>
-      <c r="J1948" s="4"/>
+      <c r="A1948" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1948" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1948" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1948" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1948" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1948" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1948" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1948" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1948" s="4">
+        <f t="shared" si="894"/>
+        <v>2026</v>
+      </c>
+      <c r="J1948" s="4">
+        <f t="shared" si="895"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1949" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1949" s="3"/>
-      <c r="B1949" s="3"/>
-      <c r="C1949" s="3"/>
-      <c r="D1949" s="3"/>
-      <c r="E1949" s="3"/>
+      <c r="A1949" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1949" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1949" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1949" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1949" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F1949" s="3"/>
-      <c r="G1949" s="3"/>
-      <c r="H1949" s="3"/>
-      <c r="I1949" s="4"/>
-      <c r="J1949" s="4"/>
+      <c r="G1949" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1949" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1949" s="4">
+        <f t="shared" si="894"/>
+        <v>2026</v>
+      </c>
+      <c r="J1949" s="4">
+        <f t="shared" si="895"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1950" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1950" s="3"/>
-      <c r="B1950" s="3"/>
-      <c r="C1950" s="3"/>
-      <c r="D1950" s="3"/>
-      <c r="E1950" s="3"/>
+      <c r="A1950" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1950" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1950" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1950" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1950" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F1950" s="3"/>
-      <c r="G1950" s="3"/>
-      <c r="H1950" s="3"/>
-      <c r="I1950" s="4"/>
-      <c r="J1950" s="4"/>
+      <c r="G1950" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1950" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1950" s="4">
+        <f t="shared" si="894"/>
+        <v>2026</v>
+      </c>
+      <c r="J1950" s="4">
+        <f t="shared" si="895"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1951" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1951" s="3"/>
-      <c r="B1951" s="3"/>
-      <c r="C1951" s="3"/>
-      <c r="D1951" s="3"/>
-      <c r="E1951" s="3"/>
+      <c r="A1951" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1951" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1951" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1951" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1951" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F1951" s="3"/>
-      <c r="G1951" s="3"/>
-      <c r="H1951" s="3"/>
-      <c r="I1951" s="4"/>
-      <c r="J1951" s="4"/>
+      <c r="G1951" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1951" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1951" s="4">
+        <f t="shared" ref="I1951:I1954" si="896">YEAR(A1951)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1951" s="4">
+        <f t="shared" ref="J1951:J1954" si="897">MONTH(A1951)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1952" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1952" s="3"/>
-      <c r="B1952" s="3"/>
-      <c r="C1952" s="3"/>
-      <c r="D1952" s="3"/>
-      <c r="E1952" s="3"/>
-      <c r="F1952" s="3"/>
-      <c r="G1952" s="3"/>
-      <c r="H1952" s="3"/>
-      <c r="I1952" s="4"/>
-      <c r="J1952" s="4"/>
+      <c r="A1952" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1952" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1952" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1952" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1952" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1952" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1952" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1952" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1952" s="4">
+        <f t="shared" si="896"/>
+        <v>2026</v>
+      </c>
+      <c r="J1952" s="4">
+        <f t="shared" si="897"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1953" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1953" s="3"/>
-      <c r="B1953" s="3"/>
-      <c r="C1953" s="3"/>
-      <c r="D1953" s="3"/>
-      <c r="E1953" s="3"/>
-      <c r="F1953" s="3"/>
-      <c r="G1953" s="3"/>
-      <c r="H1953" s="3"/>
-      <c r="I1953" s="4"/>
-      <c r="J1953" s="4"/>
+      <c r="A1953" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1953" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1953" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1953" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1953" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1953" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1953" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1953" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1953" s="4">
+        <f t="shared" si="896"/>
+        <v>2026</v>
+      </c>
+      <c r="J1953" s="4">
+        <f t="shared" si="897"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1954" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1954" s="3"/>
-      <c r="B1954" s="3"/>
-      <c r="C1954" s="3"/>
-      <c r="D1954" s="3"/>
-      <c r="E1954" s="3"/>
-      <c r="F1954" s="3"/>
-      <c r="G1954" s="3"/>
-      <c r="H1954" s="3"/>
-      <c r="I1954" s="4"/>
-      <c r="J1954" s="4"/>
+      <c r="A1954" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1954" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1954" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1954" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1954" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1954" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1954" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1954" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1954" s="4">
+        <f t="shared" si="896"/>
+        <v>2026</v>
+      </c>
+      <c r="J1954" s="4">
+        <f t="shared" si="897"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1955" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1955" s="3"/>
-      <c r="B1955" s="3"/>
-      <c r="C1955" s="3"/>
-      <c r="D1955" s="3"/>
-      <c r="E1955" s="3"/>
-      <c r="F1955" s="3"/>
-      <c r="G1955" s="3"/>
-      <c r="H1955" s="3"/>
-      <c r="I1955" s="4"/>
-      <c r="J1955" s="4"/>
+      <c r="A1955" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1955" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1955" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1955" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E1955" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1955" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1955" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1955" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1955" s="4">
+        <f t="shared" ref="I1955:I1956" si="898">YEAR(A1955)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1955" s="4">
+        <f t="shared" ref="J1955:J1956" si="899">MONTH(A1955)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1956" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1956" s="3"/>
-      <c r="B1956" s="3"/>
-      <c r="C1956" s="3"/>
-      <c r="D1956" s="3"/>
-      <c r="E1956" s="3"/>
-      <c r="F1956" s="3"/>
-      <c r="G1956" s="3"/>
-      <c r="H1956" s="3"/>
-      <c r="I1956" s="4"/>
-      <c r="J1956" s="4"/>
+      <c r="A1956" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1956" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1956" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1956" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1956" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1956" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1956" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1956" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1956" s="4">
+        <f t="shared" si="898"/>
+        <v>2026</v>
+      </c>
+      <c r="J1956" s="4">
+        <f t="shared" si="899"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1957" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1957" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1957" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1957" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E1957" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1957" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1957" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1957" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1957" s="4">
+        <f t="shared" ref="I1957:I1958" si="900">YEAR(A1957)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1957" s="4">
+        <f t="shared" ref="J1957:J1958" si="901">MONTH(A1957)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1958" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1958" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1958" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1958" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1958" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1958" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1958" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1958" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1958" s="4">
+        <f t="shared" si="900"/>
+        <v>2026</v>
+      </c>
+      <c r="J1958" s="4">
+        <f t="shared" si="901"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1959" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1959" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1959" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1959" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1959" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1959" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G1959" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1959" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1959" s="4">
+        <f t="shared" ref="I1959:I1960" si="902">YEAR(A1959)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1959" s="4">
+        <f t="shared" ref="J1959:J1960" si="903">MONTH(A1959)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1960" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1960" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1960" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1960" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1960" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1960" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1960" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1960" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1960" s="4">
+        <f t="shared" si="902"/>
+        <v>2026</v>
+      </c>
+      <c r="J1960" s="4">
+        <f t="shared" si="903"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1961" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1961" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1961" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1961" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1961" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1961" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G1961" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1961" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1961" s="4">
+        <f t="shared" ref="I1961" si="904">YEAR(A1961)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1961" s="4">
+        <f t="shared" ref="J1961" si="905">MONTH(A1961)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1962" s="3"/>
+      <c r="B1962" s="3"/>
+      <c r="C1962" s="3"/>
+      <c r="D1962" s="3"/>
+      <c r="E1962" s="3"/>
+      <c r="F1962" s="3"/>
+      <c r="G1962" s="3"/>
+      <c r="H1962" s="3"/>
+      <c r="I1962" s="4"/>
+      <c r="J1962" s="4"/>
+    </row>
+    <row r="1963" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1963" s="3"/>
+      <c r="B1963" s="3"/>
+      <c r="C1963" s="3"/>
+      <c r="D1963" s="3"/>
+      <c r="E1963" s="3"/>
+      <c r="F1963" s="3"/>
+      <c r="G1963" s="3"/>
+      <c r="H1963" s="3"/>
+      <c r="I1963" s="4"/>
+      <c r="J1963" s="4"/>
+    </row>
+    <row r="1964" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1964" s="3"/>
+      <c r="B1964" s="3"/>
+      <c r="C1964" s="3"/>
+      <c r="D1964" s="3"/>
+      <c r="E1964" s="3"/>
+      <c r="F1964" s="3"/>
+      <c r="G1964" s="3"/>
+      <c r="H1964" s="3"/>
+      <c r="I1964" s="4"/>
+      <c r="J1964" s="4"/>
+    </row>
+    <row r="1965" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1965" s="3"/>
+      <c r="B1965" s="3"/>
+      <c r="C1965" s="3"/>
+      <c r="D1965" s="3"/>
+      <c r="E1965" s="3"/>
+      <c r="F1965" s="3"/>
+      <c r="G1965" s="3"/>
+      <c r="H1965" s="3"/>
+      <c r="I1965" s="4"/>
+      <c r="J1965" s="4"/>
+    </row>
+    <row r="1966" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1966" s="3"/>
+      <c r="B1966" s="3"/>
+      <c r="C1966" s="3"/>
+      <c r="D1966" s="3"/>
+      <c r="E1966" s="3"/>
+      <c r="F1966" s="3"/>
+      <c r="G1966" s="3"/>
+      <c r="H1966" s="3"/>
+      <c r="I1966" s="4"/>
+      <c r="J1966" s="4"/>
+    </row>
+    <row r="1967" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1967" s="3"/>
+      <c r="B1967" s="3"/>
+      <c r="C1967" s="3"/>
+      <c r="D1967" s="3"/>
+      <c r="E1967" s="3"/>
+      <c r="F1967" s="3"/>
+      <c r="G1967" s="3"/>
+      <c r="H1967" s="3"/>
+      <c r="I1967" s="4"/>
+      <c r="J1967" s="4"/>
+    </row>
+    <row r="1968" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1968" s="3"/>
+      <c r="B1968" s="3"/>
+      <c r="C1968" s="3"/>
+      <c r="D1968" s="3"/>
+      <c r="E1968" s="3"/>
+      <c r="F1968" s="3"/>
+      <c r="G1968" s="3"/>
+      <c r="H1968" s="3"/>
+      <c r="I1968" s="4"/>
+      <c r="J1968" s="4"/>
+    </row>
+    <row r="1969" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1969" s="3"/>
+      <c r="B1969" s="3"/>
+      <c r="C1969" s="3"/>
+      <c r="D1969" s="3"/>
+      <c r="E1969" s="3"/>
+      <c r="F1969" s="3"/>
+      <c r="G1969" s="3"/>
+      <c r="H1969" s="3"/>
+      <c r="I1969" s="4"/>
+      <c r="J1969" s="4"/>
+    </row>
+    <row r="1970" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1970" s="3"/>
+      <c r="B1970" s="3"/>
+      <c r="C1970" s="3"/>
+      <c r="D1970" s="3"/>
+      <c r="E1970" s="3"/>
+      <c r="F1970" s="3"/>
+      <c r="G1970" s="3"/>
+      <c r="H1970" s="3"/>
+      <c r="I1970" s="4"/>
+      <c r="J1970" s="4"/>
+    </row>
+    <row r="1971" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1971" s="3"/>
+      <c r="B1971" s="3"/>
+      <c r="C1971" s="3"/>
+      <c r="D1971" s="3"/>
+      <c r="E1971" s="3"/>
+      <c r="F1971" s="3"/>
+      <c r="G1971" s="3"/>
+      <c r="H1971" s="3"/>
+      <c r="I1971" s="4"/>
+      <c r="J1971" s="4"/>
+    </row>
+    <row r="1972" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1972" s="3"/>
+      <c r="B1972" s="3"/>
+      <c r="C1972" s="3"/>
+      <c r="D1972" s="3"/>
+      <c r="E1972" s="3"/>
+      <c r="F1972" s="3"/>
+      <c r="G1972" s="3"/>
+      <c r="H1972" s="3"/>
+      <c r="I1972" s="4"/>
+      <c r="J1972" s="4"/>
+    </row>
+    <row r="1973" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1973" s="3"/>
+      <c r="B1973" s="3"/>
+      <c r="C1973" s="3"/>
+      <c r="D1973" s="3"/>
+      <c r="E1973" s="3"/>
+      <c r="F1973" s="3"/>
+      <c r="G1973" s="3"/>
+      <c r="H1973" s="3"/>
+      <c r="I1973" s="4"/>
+      <c r="J1973" s="4"/>
+    </row>
+    <row r="1974" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1974" s="3"/>
+      <c r="B1974" s="3"/>
+      <c r="C1974" s="3"/>
+      <c r="D1974" s="3"/>
+      <c r="E1974" s="3"/>
+      <c r="F1974" s="3"/>
+      <c r="G1974" s="3"/>
+      <c r="H1974" s="3"/>
+      <c r="I1974" s="4"/>
+      <c r="J1974" s="4"/>
+    </row>
+    <row r="1975" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1975" s="3"/>
+      <c r="B1975" s="3"/>
+      <c r="C1975" s="3"/>
+      <c r="D1975" s="3"/>
+      <c r="E1975" s="3"/>
+      <c r="F1975" s="3"/>
+      <c r="G1975" s="3"/>
+      <c r="H1975" s="3"/>
+      <c r="I1975" s="4"/>
+      <c r="J1975" s="4"/>
+    </row>
+    <row r="1976" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1976" s="3"/>
+      <c r="B1976" s="3"/>
+      <c r="C1976" s="3"/>
+      <c r="D1976" s="3"/>
+      <c r="E1976" s="3"/>
+      <c r="F1976" s="3"/>
+      <c r="G1976" s="3"/>
+      <c r="H1976" s="3"/>
+      <c r="I1976" s="4"/>
+      <c r="J1976" s="4"/>
+    </row>
+    <row r="1977" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1977" s="3"/>
+      <c r="B1977" s="3"/>
+      <c r="C1977" s="3"/>
+      <c r="D1977" s="3"/>
+      <c r="E1977" s="3"/>
+      <c r="F1977" s="3"/>
+      <c r="G1977" s="3"/>
+      <c r="H1977" s="3"/>
+      <c r="I1977" s="4"/>
+      <c r="J1977" s="4"/>
+    </row>
+    <row r="1978" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1978" s="3"/>
+      <c r="B1978" s="3"/>
+      <c r="C1978" s="3"/>
+      <c r="D1978" s="3"/>
+      <c r="E1978" s="3"/>
+      <c r="F1978" s="3"/>
+      <c r="G1978" s="3"/>
+      <c r="H1978" s="3"/>
+      <c r="I1978" s="4"/>
+      <c r="J1978" s="4"/>
+    </row>
+    <row r="1979" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1979" s="3"/>
+      <c r="B1979" s="3"/>
+      <c r="C1979" s="3"/>
+      <c r="D1979" s="3"/>
+      <c r="E1979" s="3"/>
+      <c r="F1979" s="3"/>
+      <c r="G1979" s="3"/>
+      <c r="H1979" s="3"/>
+      <c r="I1979" s="4"/>
+      <c r="J1979" s="4"/>
+    </row>
+    <row r="1980" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1980" s="3"/>
+      <c r="B1980" s="3"/>
+      <c r="C1980" s="3"/>
+      <c r="D1980" s="3"/>
+      <c r="E1980" s="3"/>
+      <c r="F1980" s="3"/>
+      <c r="G1980" s="3"/>
+      <c r="H1980" s="3"/>
+      <c r="I1980" s="4"/>
+      <c r="J1980" s="4"/>
+    </row>
+    <row r="1981" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1981" s="3"/>
+      <c r="B1981" s="3"/>
+      <c r="C1981" s="3"/>
+      <c r="D1981" s="3"/>
+      <c r="E1981" s="3"/>
+      <c r="F1981" s="3"/>
+      <c r="G1981" s="3"/>
+      <c r="H1981" s="3"/>
+      <c r="I1981" s="4"/>
+      <c r="J1981" s="4"/>
+    </row>
+    <row r="1982" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1982" s="3"/>
+      <c r="B1982" s="3"/>
+      <c r="C1982" s="3"/>
+      <c r="D1982" s="3"/>
+      <c r="E1982" s="3"/>
+      <c r="F1982" s="3"/>
+      <c r="G1982" s="3"/>
+      <c r="H1982" s="3"/>
+      <c r="I1982" s="4"/>
+      <c r="J1982" s="4"/>
+    </row>
+    <row r="1983" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1983" s="3"/>
+      <c r="B1983" s="3"/>
+      <c r="C1983" s="3"/>
+      <c r="D1983" s="3"/>
+      <c r="E1983" s="3"/>
+      <c r="F1983" s="3"/>
+      <c r="G1983" s="3"/>
+      <c r="H1983" s="3"/>
+      <c r="I1983" s="4"/>
+      <c r="J1983" s="4"/>
+    </row>
+    <row r="1984" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1984" s="3"/>
+      <c r="B1984" s="3"/>
+      <c r="C1984" s="3"/>
+      <c r="D1984" s="3"/>
+      <c r="E1984" s="3"/>
+      <c r="F1984" s="3"/>
+      <c r="G1984" s="3"/>
+      <c r="H1984" s="3"/>
+      <c r="I1984" s="4"/>
+      <c r="J1984" s="4"/>
+    </row>
+    <row r="1985" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1985" s="3"/>
+      <c r="B1985" s="3"/>
+      <c r="C1985" s="3"/>
+      <c r="D1985" s="3"/>
+      <c r="E1985" s="3"/>
+      <c r="F1985" s="3"/>
+      <c r="G1985" s="3"/>
+      <c r="H1985" s="3"/>
+      <c r="I1985" s="4"/>
+      <c r="J1985" s="4"/>
+    </row>
+    <row r="1986" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1986" s="3"/>
+      <c r="B1986" s="3"/>
+      <c r="C1986" s="3"/>
+      <c r="D1986" s="3"/>
+      <c r="E1986" s="3"/>
+      <c r="F1986" s="3"/>
+      <c r="G1986" s="3"/>
+      <c r="H1986" s="3"/>
+      <c r="I1986" s="4"/>
+      <c r="J1986" s="4"/>
+    </row>
+    <row r="1987" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1987" s="3"/>
+      <c r="B1987" s="3"/>
+      <c r="C1987" s="3"/>
+      <c r="D1987" s="3"/>
+      <c r="E1987" s="3"/>
+      <c r="F1987" s="3"/>
+      <c r="G1987" s="3"/>
+      <c r="H1987" s="3"/>
+      <c r="I1987" s="4"/>
+      <c r="J1987" s="4"/>
+    </row>
+    <row r="1988" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1988" s="3"/>
+      <c r="B1988" s="3"/>
+      <c r="C1988" s="3"/>
+      <c r="D1988" s="3"/>
+      <c r="E1988" s="3"/>
+      <c r="F1988" s="3"/>
+      <c r="G1988" s="3"/>
+      <c r="H1988" s="3"/>
+      <c r="I1988" s="4"/>
+      <c r="J1988" s="4"/>
+    </row>
+    <row r="1989" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1989" s="3"/>
+      <c r="B1989" s="3"/>
+      <c r="C1989" s="3"/>
+      <c r="D1989" s="3"/>
+      <c r="E1989" s="3"/>
+      <c r="F1989" s="3"/>
+      <c r="G1989" s="3"/>
+      <c r="H1989" s="3"/>
+      <c r="I1989" s="4"/>
+      <c r="J1989" s="4"/>
+    </row>
+    <row r="1990" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1990" s="3"/>
+      <c r="B1990" s="3"/>
+      <c r="C1990" s="3"/>
+      <c r="D1990" s="3"/>
+      <c r="E1990" s="3"/>
+      <c r="F1990" s="3"/>
+      <c r="G1990" s="3"/>
+      <c r="H1990" s="3"/>
+      <c r="I1990" s="4"/>
+      <c r="J1990" s="4"/>
+    </row>
+    <row r="1991" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1991" s="3"/>
+      <c r="B1991" s="3"/>
+      <c r="C1991" s="3"/>
+      <c r="D1991" s="3"/>
+      <c r="E1991" s="3"/>
+      <c r="F1991" s="3"/>
+      <c r="G1991" s="3"/>
+      <c r="H1991" s="3"/>
+      <c r="I1991" s="4"/>
+      <c r="J1991" s="4"/>
+    </row>
+    <row r="1992" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1992" s="3"/>
+      <c r="B1992" s="3"/>
+      <c r="C1992" s="3"/>
+      <c r="D1992" s="3"/>
+      <c r="E1992" s="3"/>
+      <c r="F1992" s="3"/>
+      <c r="G1992" s="3"/>
+      <c r="H1992" s="3"/>
+      <c r="I1992" s="4"/>
+      <c r="J1992" s="4"/>
+    </row>
+    <row r="1993" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1993" s="3"/>
+      <c r="B1993" s="3"/>
+      <c r="C1993" s="3"/>
+      <c r="D1993" s="3"/>
+      <c r="E1993" s="3"/>
+      <c r="F1993" s="3"/>
+      <c r="G1993" s="3"/>
+      <c r="H1993" s="3"/>
+      <c r="I1993" s="4"/>
+      <c r="J1993" s="4"/>
+    </row>
+    <row r="1994" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1994" s="3"/>
+      <c r="B1994" s="3"/>
+      <c r="C1994" s="3"/>
+      <c r="D1994" s="3"/>
+      <c r="E1994" s="3"/>
+      <c r="F1994" s="3"/>
+      <c r="G1994" s="3"/>
+      <c r="H1994" s="3"/>
+      <c r="I1994" s="4"/>
+      <c r="J1994" s="4"/>
+    </row>
+    <row r="1995" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1995" s="3"/>
+      <c r="B1995" s="3"/>
+      <c r="C1995" s="3"/>
+      <c r="D1995" s="3"/>
+      <c r="E1995" s="3"/>
+      <c r="F1995" s="3"/>
+      <c r="G1995" s="3"/>
+      <c r="H1995" s="3"/>
+      <c r="I1995" s="4"/>
+      <c r="J1995" s="4"/>
+    </row>
+    <row r="1996" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1996" s="3"/>
+      <c r="B1996" s="3"/>
+      <c r="C1996" s="3"/>
+      <c r="D1996" s="3"/>
+      <c r="E1996" s="3"/>
+      <c r="F1996" s="3"/>
+      <c r="G1996" s="3"/>
+      <c r="H1996" s="3"/>
+      <c r="I1996" s="4"/>
+      <c r="J1996" s="4"/>
+    </row>
+    <row r="1997" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1997" s="3"/>
+      <c r="B1997" s="3"/>
+      <c r="C1997" s="3"/>
+      <c r="D1997" s="3"/>
+      <c r="E1997" s="3"/>
+      <c r="F1997" s="3"/>
+      <c r="G1997" s="3"/>
+      <c r="H1997" s="3"/>
+      <c r="I1997" s="4"/>
+      <c r="J1997" s="4"/>
+    </row>
+    <row r="1998" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1998" s="3"/>
+      <c r="B1998" s="3"/>
+      <c r="C1998" s="3"/>
+      <c r="D1998" s="3"/>
+      <c r="E1998" s="3"/>
+      <c r="F1998" s="3"/>
+      <c r="G1998" s="3"/>
+      <c r="H1998" s="3"/>
+      <c r="I1998" s="4"/>
+      <c r="J1998" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sessions!$A$1:$J$1325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sessions!$A$1:$J$1961</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15285" uniqueCount="1628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15285" uniqueCount="1620">
   <si>
     <t>Year</t>
   </si>
@@ -4173,21 +4173,6 @@
     <t>2025-05-26</t>
   </si>
   <si>
-    <t>nwtimetracking v5.0.2</t>
-  </si>
-  <si>
-    <t>nwreadinglist v4.3.2</t>
-  </si>
-  <si>
-    <t>nwtraderaanalytics v4.5.2</t>
-  </si>
-  <si>
-    <t>nwshared v1.8.2</t>
-  </si>
-  <si>
-    <t>nwpackageversions v1.8.2</t>
-  </si>
-  <si>
     <t>2025-05-27</t>
   </si>
   <si>
@@ -4686,9 +4671,6 @@
     <t>2026-01-02</t>
   </si>
   <si>
-    <t>nwbuilds v1.0.0</t>
-  </si>
-  <si>
     <t>2026-01-03</t>
   </si>
   <si>
@@ -4767,15 +4749,9 @@
     <t>2026-02-01</t>
   </si>
   <si>
-    <t>ARM64 Builder (QEMU, ProxMox).</t>
-  </si>
-  <si>
     <t>2026-02-02</t>
   </si>
   <si>
-    <t>ARM64 Builder (ProxMox, RPI3B+).</t>
-  </si>
-  <si>
     <t>nwbsidedownloader v1.0.0</t>
   </si>
   <si>
@@ -4872,9 +4848,6 @@
     <t>2026-03-03</t>
   </si>
   <si>
-    <t>config-nwbuilders v1.0.0</t>
-  </si>
-  <si>
     <t>2026-03-04</t>
   </si>
   <si>
@@ -4909,6 +4882,9 @@
   </si>
   <si>
     <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>nwbuilders v1.0.0</t>
   </si>
 </sst>
 </file>
@@ -11508,7 +11484,7 @@
         <v>433</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>279</v>
@@ -11576,7 +11552,7 @@
         <v>433</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G192" s="8" t="s">
         <v>279</v>
@@ -11644,7 +11620,7 @@
         <v>433</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>279</v>
@@ -11814,7 +11790,7 @@
         <v>433</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>279</v>
@@ -11848,7 +11824,7 @@
         <v>433</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G200" s="8" t="s">
         <v>279</v>
@@ -11882,7 +11858,7 @@
         <v>433</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>279</v>
@@ -11916,7 +11892,7 @@
         <v>433</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>279</v>
@@ -11950,7 +11926,7 @@
         <v>433</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G203" s="8" t="s">
         <v>279</v>
@@ -11984,7 +11960,7 @@
         <v>433</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G204" s="8" t="s">
         <v>279</v>
@@ -12018,7 +11994,7 @@
         <v>433</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>279</v>
@@ -12052,7 +12028,7 @@
         <v>433</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>279</v>
@@ -12086,7 +12062,7 @@
         <v>433</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G207" s="8" t="s">
         <v>279</v>
@@ -12120,7 +12096,7 @@
         <v>433</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>279</v>
@@ -12154,7 +12130,7 @@
         <v>433</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G209" s="8" t="s">
         <v>279</v>
@@ -12188,7 +12164,7 @@
         <v>433</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>279</v>
@@ -12222,7 +12198,7 @@
         <v>433</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>279</v>
@@ -12290,7 +12266,7 @@
         <v>433</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G213" s="8" t="s">
         <v>279</v>
@@ -17184,7 +17160,7 @@
         <v>433</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="G357" s="8" t="s">
         <v>279</v>
@@ -27026,7 +27002,7 @@
         <v>433</v>
       </c>
       <c r="F647" s="3" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="G647" s="8" t="s">
         <v>279</v>
@@ -30934,7 +30910,7 @@
         <v>433</v>
       </c>
       <c r="F762" s="3" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="G762" s="8" t="s">
         <v>279</v>
@@ -30968,7 +30944,7 @@
         <v>433</v>
       </c>
       <c r="F763" s="3" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="G763" s="8" t="s">
         <v>279</v>
@@ -54491,7 +54467,7 @@
         <v>389</v>
       </c>
       <c r="E1464" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1464" s="3" t="s">
         <v>1283</v>
@@ -54625,7 +54601,7 @@
         <v>94</v>
       </c>
       <c r="E1468" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1468" s="3" t="s">
         <v>1283</v>
@@ -54659,7 +54635,7 @@
         <v>105</v>
       </c>
       <c r="E1469" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1469" s="3" t="s">
         <v>1283</v>
@@ -54725,7 +54701,7 @@
         <v>243</v>
       </c>
       <c r="E1471" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1471" s="3" t="s">
         <v>1283</v>
@@ -54759,7 +54735,7 @@
         <v>220</v>
       </c>
       <c r="E1472" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1472" s="3" t="s">
         <v>1283</v>
@@ -54793,7 +54769,7 @@
         <v>239</v>
       </c>
       <c r="E1473" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1473" s="3" t="s">
         <v>1283</v>
@@ -55806,7 +55782,7 @@
         <v>127</v>
       </c>
       <c r="F1504" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1504" s="8" t="s">
         <v>279</v>
@@ -55840,7 +55816,7 @@
         <v>127</v>
       </c>
       <c r="F1505" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1505" s="8" t="s">
         <v>279</v>
@@ -55874,7 +55850,7 @@
         <v>127</v>
       </c>
       <c r="F1506" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1506" s="8" t="s">
         <v>279</v>
@@ -56408,7 +56384,7 @@
         <v>127</v>
       </c>
       <c r="F1522" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1522" s="8" t="s">
         <v>279</v>
@@ -56442,7 +56418,7 @@
         <v>127</v>
       </c>
       <c r="F1523" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1523" s="8" t="s">
         <v>279</v>
@@ -56476,7 +56452,7 @@
         <v>127</v>
       </c>
       <c r="F1524" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1524" s="8" t="s">
         <v>279</v>
@@ -56510,7 +56486,7 @@
         <v>127</v>
       </c>
       <c r="F1525" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1525" s="8" t="s">
         <v>279</v>
@@ -56544,7 +56520,7 @@
         <v>127</v>
       </c>
       <c r="F1526" s="3" t="s">
-        <v>1382</v>
+        <v>1619</v>
       </c>
       <c r="G1526" s="8" t="s">
         <v>279</v>
@@ -56578,7 +56554,7 @@
         <v>127</v>
       </c>
       <c r="F1527" s="3" t="s">
-        <v>1383</v>
+        <v>1619</v>
       </c>
       <c r="G1527" s="8" t="s">
         <v>279</v>
@@ -56612,7 +56588,7 @@
         <v>127</v>
       </c>
       <c r="F1528" s="3" t="s">
-        <v>1384</v>
+        <v>1619</v>
       </c>
       <c r="G1528" s="8" t="s">
         <v>279</v>
@@ -56646,7 +56622,7 @@
         <v>127</v>
       </c>
       <c r="F1529" s="3" t="s">
-        <v>1385</v>
+        <v>1619</v>
       </c>
       <c r="G1529" s="8" t="s">
         <v>279</v>
@@ -56680,7 +56656,7 @@
         <v>127</v>
       </c>
       <c r="F1530" s="3" t="s">
-        <v>1386</v>
+        <v>1619</v>
       </c>
       <c r="G1530" s="8" t="s">
         <v>279</v>
@@ -56699,7 +56675,7 @@
     </row>
     <row r="1531" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1531" s="3" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="B1531" s="3" t="s">
         <v>329</v>
@@ -56714,7 +56690,7 @@
         <v>127</v>
       </c>
       <c r="F1531" s="9" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="G1531" s="8" t="s">
         <v>279</v>
@@ -56733,7 +56709,7 @@
     </row>
     <row r="1532" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1532" s="3" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="B1532" s="3" t="s">
         <v>122</v>
@@ -56765,7 +56741,7 @@
     </row>
     <row r="1533" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1533" s="3" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="B1533" s="3" t="s">
         <v>209</v>
@@ -56797,7 +56773,7 @@
     </row>
     <row r="1534" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1534" s="3" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="B1534" s="3" t="s">
         <v>248</v>
@@ -56829,7 +56805,7 @@
     </row>
     <row r="1535" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1535" s="3" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="B1535" s="3" t="s">
         <v>118</v>
@@ -56861,7 +56837,7 @@
     </row>
     <row r="1536" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1536" s="3" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="B1536" s="3" t="s">
         <v>161</v>
@@ -56895,7 +56871,7 @@
     </row>
     <row r="1537" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1537" s="3" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="B1537" s="3" t="s">
         <v>174</v>
@@ -56929,7 +56905,7 @@
     </row>
     <row r="1538" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1538" s="3" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="B1538" s="3" t="s">
         <v>122</v>
@@ -56963,7 +56939,7 @@
     </row>
     <row r="1539" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1539" s="3" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="B1539" s="3" t="s">
         <v>209</v>
@@ -56997,7 +56973,7 @@
     </row>
     <row r="1540" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1540" s="3" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="B1540" s="3" t="s">
         <v>311</v>
@@ -57031,7 +57007,7 @@
     </row>
     <row r="1541" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1541" s="3" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="B1541" s="3" t="s">
         <v>353</v>
@@ -57065,7 +57041,7 @@
     </row>
     <row r="1542" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1542" s="3" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="B1542" s="3" t="s">
         <v>138</v>
@@ -57099,7 +57075,7 @@
     </row>
     <row r="1543" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1543" s="3" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="B1543" s="3" t="s">
         <v>331</v>
@@ -57133,7 +57109,7 @@
     </row>
     <row r="1544" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1544" s="3" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="B1544" s="3" t="s">
         <v>122</v>
@@ -57167,7 +57143,7 @@
     </row>
     <row r="1545" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1545" s="3" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="B1545" s="3" t="s">
         <v>150</v>
@@ -57201,7 +57177,7 @@
     </row>
     <row r="1546" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1546" s="3" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="B1546" s="3" t="s">
         <v>202</v>
@@ -57216,7 +57192,7 @@
         <v>127</v>
       </c>
       <c r="F1546" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1546" s="8" t="s">
         <v>279</v>
@@ -57235,7 +57211,7 @@
     </row>
     <row r="1547" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1547" s="3" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B1547" s="3" t="s">
         <v>248</v>
@@ -57267,7 +57243,7 @@
     </row>
     <row r="1548" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1548" s="3" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B1548" s="3" t="s">
         <v>149</v>
@@ -57299,7 +57275,7 @@
     </row>
     <row r="1549" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1549" s="3" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B1549" s="3" t="s">
         <v>174</v>
@@ -57331,7 +57307,7 @@
     </row>
     <row r="1550" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1550" s="3" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="B1550" s="3" t="s">
         <v>249</v>
@@ -57363,7 +57339,7 @@
     </row>
     <row r="1551" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1551" s="3" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="B1551" s="3" t="s">
         <v>149</v>
@@ -57395,7 +57371,7 @@
     </row>
     <row r="1552" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1552" s="3" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="B1552" s="3" t="s">
         <v>132</v>
@@ -57427,7 +57403,7 @@
     </row>
     <row r="1553" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1553" s="3" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="B1553" s="3" t="s">
         <v>161</v>
@@ -57459,7 +57435,7 @@
     </row>
     <row r="1554" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1554" s="3" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="B1554" s="3" t="s">
         <v>124</v>
@@ -57491,7 +57467,7 @@
     </row>
     <row r="1555" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1555" s="3" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="B1555" s="3" t="s">
         <v>327</v>
@@ -57523,7 +57499,7 @@
     </row>
     <row r="1556" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1556" s="3" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="B1556" s="3" t="s">
         <v>355</v>
@@ -57538,7 +57514,7 @@
         <v>127</v>
       </c>
       <c r="F1556" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1556" s="8" t="s">
         <v>279</v>
@@ -57557,7 +57533,7 @@
     </row>
     <row r="1557" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1557" s="3" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="B1557" s="3" t="s">
         <v>114</v>
@@ -57572,7 +57548,7 @@
         <v>127</v>
       </c>
       <c r="F1557" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1557" s="8" t="s">
         <v>279</v>
@@ -57591,7 +57567,7 @@
     </row>
     <row r="1558" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1558" s="3" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="B1558" s="3" t="s">
         <v>134</v>
@@ -57606,7 +57582,7 @@
         <v>127</v>
       </c>
       <c r="F1558" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1558" s="8" t="s">
         <v>279</v>
@@ -57625,7 +57601,7 @@
     </row>
     <row r="1559" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1559" s="3" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="B1559" s="3" t="s">
         <v>248</v>
@@ -57657,7 +57633,7 @@
     </row>
     <row r="1560" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1560" s="3" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="B1560" s="3" t="s">
         <v>171</v>
@@ -57689,7 +57665,7 @@
     </row>
     <row r="1561" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1561" s="3" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="B1561" s="3" t="s">
         <v>248</v>
@@ -57721,7 +57697,7 @@
     </row>
     <row r="1562" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1562" s="3" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="B1562" s="3" t="s">
         <v>118</v>
@@ -57753,7 +57729,7 @@
     </row>
     <row r="1563" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1563" s="3" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="B1563" s="3" t="s">
         <v>395</v>
@@ -57768,7 +57744,7 @@
         <v>127</v>
       </c>
       <c r="F1563" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1563" s="8" t="s">
         <v>279</v>
@@ -57787,7 +57763,7 @@
     </row>
     <row r="1564" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1564" s="3" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="B1564" s="3" t="s">
         <v>327</v>
@@ -57802,7 +57778,7 @@
         <v>127</v>
       </c>
       <c r="F1564" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1564" s="8" t="s">
         <v>279</v>
@@ -57821,7 +57797,7 @@
     </row>
     <row r="1565" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1565" s="3" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="B1565" s="3" t="s">
         <v>174</v>
@@ -57836,7 +57812,7 @@
         <v>127</v>
       </c>
       <c r="F1565" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1565" s="8" t="s">
         <v>279</v>
@@ -57855,7 +57831,7 @@
     </row>
     <row r="1566" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1566" s="3" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="B1566" s="3" t="s">
         <v>271</v>
@@ -57870,7 +57846,7 @@
         <v>127</v>
       </c>
       <c r="F1566" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1566" s="8" t="s">
         <v>279</v>
@@ -57889,7 +57865,7 @@
     </row>
     <row r="1567" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1567" s="3" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="B1567" s="3" t="s">
         <v>287</v>
@@ -57904,7 +57880,7 @@
         <v>127</v>
       </c>
       <c r="F1567" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1567" s="8" t="s">
         <v>279</v>
@@ -57923,7 +57899,7 @@
     </row>
     <row r="1568" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1568" s="3" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="B1568" s="3" t="s">
         <v>191</v>
@@ -57938,7 +57914,7 @@
         <v>127</v>
       </c>
       <c r="F1568" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1568" s="8" t="s">
         <v>279</v>
@@ -57957,7 +57933,7 @@
     </row>
     <row r="1569" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1569" s="3" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="B1569" s="3" t="s">
         <v>134</v>
@@ -57972,7 +57948,7 @@
         <v>127</v>
       </c>
       <c r="F1569" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1569" s="8" t="s">
         <v>279</v>
@@ -57991,7 +57967,7 @@
     </row>
     <row r="1570" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1570" s="3" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="B1570" s="3" t="s">
         <v>179</v>
@@ -58023,7 +57999,7 @@
     </row>
     <row r="1571" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1571" s="3" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="B1571" s="3" t="s">
         <v>161</v>
@@ -58055,7 +58031,7 @@
     </row>
     <row r="1572" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1572" s="3" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="B1572" s="3" t="s">
         <v>154</v>
@@ -58087,7 +58063,7 @@
     </row>
     <row r="1573" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1573" s="3" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="B1573" s="3" t="s">
         <v>161</v>
@@ -58102,7 +58078,7 @@
         <v>127</v>
       </c>
       <c r="F1573" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1573" s="8" t="s">
         <v>279</v>
@@ -58121,7 +58097,7 @@
     </row>
     <row r="1574" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1574" s="3" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="B1574" s="3" t="s">
         <v>248</v>
@@ -58153,7 +58129,7 @@
     </row>
     <row r="1575" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1575" s="3" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="B1575" s="3" t="s">
         <v>149</v>
@@ -58185,7 +58161,7 @@
     </row>
     <row r="1576" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1576" s="3" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="B1576" s="3" t="s">
         <v>253</v>
@@ -58217,7 +58193,7 @@
     </row>
     <row r="1577" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1577" s="3" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="B1577" s="3" t="s">
         <v>118</v>
@@ -58249,7 +58225,7 @@
     </row>
     <row r="1578" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1578" s="3" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="B1578" s="3" t="s">
         <v>174</v>
@@ -58264,7 +58240,7 @@
         <v>127</v>
       </c>
       <c r="F1578" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1578" s="8" t="s">
         <v>279</v>
@@ -58283,7 +58259,7 @@
     </row>
     <row r="1579" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1579" s="3" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="B1579" s="3" t="s">
         <v>202</v>
@@ -58298,7 +58274,7 @@
         <v>127</v>
       </c>
       <c r="F1579" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1579" s="8" t="s">
         <v>279</v>
@@ -58317,7 +58293,7 @@
     </row>
     <row r="1580" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1580" s="3" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="B1580" s="3" t="s">
         <v>209</v>
@@ -58332,7 +58308,7 @@
         <v>127</v>
       </c>
       <c r="F1580" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1580" s="8" t="s">
         <v>279</v>
@@ -58351,7 +58327,7 @@
     </row>
     <row r="1581" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1581" s="3" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="B1581" s="3" t="s">
         <v>124</v>
@@ -58366,7 +58342,7 @@
         <v>127</v>
       </c>
       <c r="F1581" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1581" s="8" t="s">
         <v>279</v>
@@ -58385,7 +58361,7 @@
     </row>
     <row r="1582" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1582" s="3" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="B1582" s="3" t="s">
         <v>329</v>
@@ -58400,7 +58376,7 @@
         <v>127</v>
       </c>
       <c r="F1582" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1582" s="8" t="s">
         <v>279</v>
@@ -58419,7 +58395,7 @@
     </row>
     <row r="1583" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1583" s="3" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="B1583" s="3" t="s">
         <v>174</v>
@@ -58434,7 +58410,7 @@
         <v>127</v>
       </c>
       <c r="F1583" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1583" s="8" t="s">
         <v>279</v>
@@ -58453,7 +58429,7 @@
     </row>
     <row r="1584" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1584" s="3" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="B1584" s="3" t="s">
         <v>149</v>
@@ -58485,7 +58461,7 @@
     </row>
     <row r="1585" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1585" s="3" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="B1585" s="3" t="s">
         <v>124</v>
@@ -58500,7 +58476,7 @@
         <v>127</v>
       </c>
       <c r="F1585" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1585" s="8" t="s">
         <v>279</v>
@@ -58519,7 +58495,7 @@
     </row>
     <row r="1586" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1586" s="3" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="B1586" s="3" t="s">
         <v>248</v>
@@ -58551,7 +58527,7 @@
     </row>
     <row r="1587" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1587" s="3" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="B1587" s="3" t="s">
         <v>196</v>
@@ -58566,7 +58542,7 @@
         <v>127</v>
       </c>
       <c r="F1587" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1587" s="8" t="s">
         <v>279</v>
@@ -58585,7 +58561,7 @@
     </row>
     <row r="1588" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1588" s="3" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="B1588" s="3" t="s">
         <v>271</v>
@@ -58600,7 +58576,7 @@
         <v>127</v>
       </c>
       <c r="F1588" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1588" s="8" t="s">
         <v>279</v>
@@ -58619,7 +58595,7 @@
     </row>
     <row r="1589" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1589" s="3" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="B1589" s="3" t="s">
         <v>180</v>
@@ -58634,7 +58610,7 @@
         <v>127</v>
       </c>
       <c r="F1589" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1589" s="8" t="s">
         <v>279</v>
@@ -58653,7 +58629,7 @@
     </row>
     <row r="1590" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1590" s="3" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="B1590" s="3" t="s">
         <v>361</v>
@@ -58668,7 +58644,7 @@
         <v>127</v>
       </c>
       <c r="F1590" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1590" s="8" t="s">
         <v>279</v>
@@ -58687,7 +58663,7 @@
     </row>
     <row r="1591" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1591" s="3" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="B1591" s="3" t="s">
         <v>124</v>
@@ -58702,7 +58678,7 @@
         <v>127</v>
       </c>
       <c r="F1591" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1591" s="8" t="s">
         <v>279</v>
@@ -58721,7 +58697,7 @@
     </row>
     <row r="1592" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1592" s="3" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="B1592" s="3" t="s">
         <v>355</v>
@@ -58736,7 +58712,7 @@
         <v>127</v>
       </c>
       <c r="F1592" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1592" s="8" t="s">
         <v>279</v>
@@ -58755,7 +58731,7 @@
     </row>
     <row r="1593" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1593" s="3" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="B1593" s="3" t="s">
         <v>154</v>
@@ -58770,7 +58746,7 @@
         <v>127</v>
       </c>
       <c r="F1593" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1593" s="8" t="s">
         <v>279</v>
@@ -58789,7 +58765,7 @@
     </row>
     <row r="1594" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1594" s="3" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="B1594" s="3" t="s">
         <v>359</v>
@@ -58804,7 +58780,7 @@
         <v>127</v>
       </c>
       <c r="F1594" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1594" s="8" t="s">
         <v>279</v>
@@ -58823,7 +58799,7 @@
     </row>
     <row r="1595" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1595" s="3" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="B1595" s="3" t="s">
         <v>113</v>
@@ -58855,7 +58831,7 @@
     </row>
     <row r="1596" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1596" s="3" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="B1596" s="3" t="s">
         <v>174</v>
@@ -58887,7 +58863,7 @@
     </row>
     <row r="1597" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1597" s="3" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="B1597" s="3" t="s">
         <v>248</v>
@@ -58902,7 +58878,7 @@
         <v>127</v>
       </c>
       <c r="F1597" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1597" s="8" t="s">
         <v>279</v>
@@ -58921,7 +58897,7 @@
     </row>
     <row r="1598" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1598" s="3" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="B1598" s="3" t="s">
         <v>149</v>
@@ -58936,7 +58912,7 @@
         <v>127</v>
       </c>
       <c r="F1598" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1598" s="8" t="s">
         <v>279</v>
@@ -58955,7 +58931,7 @@
     </row>
     <row r="1599" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1599" s="3" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="B1599" s="3" t="s">
         <v>124</v>
@@ -58970,7 +58946,7 @@
         <v>127</v>
       </c>
       <c r="F1599" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1599" s="8" t="s">
         <v>279</v>
@@ -58989,7 +58965,7 @@
     </row>
     <row r="1600" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1600" s="3" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="B1600" s="3" t="s">
         <v>329</v>
@@ -59004,7 +58980,7 @@
         <v>127</v>
       </c>
       <c r="F1600" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1600" s="8" t="s">
         <v>279</v>
@@ -59023,7 +58999,7 @@
     </row>
     <row r="1601" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1601" s="3" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="B1601" s="3" t="s">
         <v>202</v>
@@ -59055,7 +59031,7 @@
     </row>
     <row r="1602" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1602" s="3" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="B1602" s="3" t="s">
         <v>255</v>
@@ -59070,7 +59046,7 @@
         <v>127</v>
       </c>
       <c r="F1602" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1602" s="8" t="s">
         <v>279</v>
@@ -59089,7 +59065,7 @@
     </row>
     <row r="1603" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1603" s="3" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="B1603" s="3" t="s">
         <v>353</v>
@@ -59104,7 +59080,7 @@
         <v>127</v>
       </c>
       <c r="F1603" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1603" s="8" t="s">
         <v>279</v>
@@ -59123,7 +59099,7 @@
     </row>
     <row r="1604" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1604" s="3" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="B1604" s="3" t="s">
         <v>211</v>
@@ -59138,7 +59114,7 @@
         <v>127</v>
       </c>
       <c r="F1604" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1604" s="8" t="s">
         <v>279</v>
@@ -59157,7 +59133,7 @@
     </row>
     <row r="1605" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1605" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="B1605" s="3" t="s">
         <v>132</v>
@@ -59172,7 +59148,7 @@
         <v>127</v>
       </c>
       <c r="F1605" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1605" s="8" t="s">
         <v>279</v>
@@ -59191,7 +59167,7 @@
     </row>
     <row r="1606" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1606" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="B1606" s="3" t="s">
         <v>327</v>
@@ -59206,7 +59182,7 @@
         <v>127</v>
       </c>
       <c r="F1606" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1606" s="8" t="s">
         <v>279</v>
@@ -59225,7 +59201,7 @@
     </row>
     <row r="1607" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1607" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="B1607" s="3" t="s">
         <v>171</v>
@@ -59240,7 +59216,7 @@
         <v>127</v>
       </c>
       <c r="F1607" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1607" s="8" t="s">
         <v>279</v>
@@ -59259,7 +59235,7 @@
     </row>
     <row r="1608" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1608" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="B1608" s="3" t="s">
         <v>124</v>
@@ -59274,7 +59250,7 @@
         <v>127</v>
       </c>
       <c r="F1608" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1608" s="8" t="s">
         <v>279</v>
@@ -59293,7 +59269,7 @@
     </row>
     <row r="1609" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1609" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="B1609" s="3" t="s">
         <v>203</v>
@@ -59308,7 +59284,7 @@
         <v>127</v>
       </c>
       <c r="F1609" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1609" s="8" t="s">
         <v>279</v>
@@ -59327,7 +59303,7 @@
     </row>
     <row r="1610" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1610" s="3" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="B1610" s="3" t="s">
         <v>202</v>
@@ -59359,7 +59335,7 @@
     </row>
     <row r="1611" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1611" s="3" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="B1611" s="3" t="s">
         <v>154</v>
@@ -59391,7 +59367,7 @@
     </row>
     <row r="1612" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1612" s="3" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="B1612" s="3" t="s">
         <v>563</v>
@@ -59406,7 +59382,7 @@
         <v>127</v>
       </c>
       <c r="F1612" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1612" s="8" t="s">
         <v>279</v>
@@ -59425,7 +59401,7 @@
     </row>
     <row r="1613" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1613" s="3" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="B1613" s="3" t="s">
         <v>353</v>
@@ -59440,7 +59416,7 @@
         <v>127</v>
       </c>
       <c r="F1613" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1613" s="8" t="s">
         <v>279</v>
@@ -59459,7 +59435,7 @@
     </row>
     <row r="1614" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1614" s="3" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="B1614" s="3" t="s">
         <v>248</v>
@@ -59491,7 +59467,7 @@
     </row>
     <row r="1615" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1615" s="3" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="B1615" s="3" t="s">
         <v>149</v>
@@ -59523,7 +59499,7 @@
     </row>
     <row r="1616" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1616" s="3" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="B1616" s="3" t="s">
         <v>248</v>
@@ -59555,7 +59531,7 @@
     </row>
     <row r="1617" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1617" s="3" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="B1617" s="3" t="s">
         <v>331</v>
@@ -59570,7 +59546,7 @@
         <v>127</v>
       </c>
       <c r="F1617" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1617" s="8" t="s">
         <v>279</v>
@@ -59589,7 +59565,7 @@
     </row>
     <row r="1618" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1618" s="3" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="B1618" s="3" t="s">
         <v>210</v>
@@ -59604,7 +59580,7 @@
         <v>127</v>
       </c>
       <c r="F1618" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1618" s="8" t="s">
         <v>279</v>
@@ -59623,7 +59599,7 @@
     </row>
     <row r="1619" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1619" s="3" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="B1619" s="3" t="s">
         <v>196</v>
@@ -59638,7 +59614,7 @@
         <v>127</v>
       </c>
       <c r="F1619" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1619" s="8" t="s">
         <v>279</v>
@@ -59657,7 +59633,7 @@
     </row>
     <row r="1620" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1620" s="3" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="B1620" s="3" t="s">
         <v>134</v>
@@ -59672,7 +59648,7 @@
         <v>127</v>
       </c>
       <c r="F1620" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1620" s="8" t="s">
         <v>279</v>
@@ -59691,7 +59667,7 @@
     </row>
     <row r="1621" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1621" s="3" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="B1621" s="3" t="s">
         <v>355</v>
@@ -59706,7 +59682,7 @@
         <v>127</v>
       </c>
       <c r="F1621" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1621" s="8" t="s">
         <v>279</v>
@@ -59725,7 +59701,7 @@
     </row>
     <row r="1622" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1622" s="3" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="B1622" s="3" t="s">
         <v>353</v>
@@ -59740,7 +59716,7 @@
         <v>127</v>
       </c>
       <c r="F1622" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1622" s="8" t="s">
         <v>279</v>
@@ -59759,7 +59735,7 @@
     </row>
     <row r="1623" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1623" s="3" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="B1623" s="3" t="s">
         <v>265</v>
@@ -59774,7 +59750,7 @@
         <v>127</v>
       </c>
       <c r="F1623" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1623" s="8" t="s">
         <v>279</v>
@@ -59793,7 +59769,7 @@
     </row>
     <row r="1624" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1624" s="3" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="B1624" s="3" t="s">
         <v>154</v>
@@ -59827,7 +59803,7 @@
     </row>
     <row r="1625" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1625" s="3" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="B1625" s="3" t="s">
         <v>248</v>
@@ -59842,7 +59818,7 @@
         <v>127</v>
       </c>
       <c r="F1625" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1625" s="8" t="s">
         <v>279</v>
@@ -59861,7 +59837,7 @@
     </row>
     <row r="1626" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1626" s="3" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="B1626" s="3" t="s">
         <v>149</v>
@@ -59876,7 +59852,7 @@
         <v>127</v>
       </c>
       <c r="F1626" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1626" s="8" t="s">
         <v>279</v>
@@ -59895,7 +59871,7 @@
     </row>
     <row r="1627" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1627" s="3" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="B1627" s="3" t="s">
         <v>248</v>
@@ -59910,7 +59886,7 @@
         <v>127</v>
       </c>
       <c r="F1627" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1627" s="8" t="s">
         <v>279</v>
@@ -59929,7 +59905,7 @@
     </row>
     <row r="1628" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1628" s="3" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="B1628" s="3" t="s">
         <v>200</v>
@@ -59944,7 +59920,7 @@
         <v>140</v>
       </c>
       <c r="F1628" s="3" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="G1628" s="8" t="s">
         <v>280</v>
@@ -59963,7 +59939,7 @@
     </row>
     <row r="1629" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1629" s="3" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="B1629" s="3" t="s">
         <v>180</v>
@@ -59978,7 +59954,7 @@
         <v>127</v>
       </c>
       <c r="F1629" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1629" s="8" t="s">
         <v>279</v>
@@ -59997,7 +59973,7 @@
     </row>
     <row r="1630" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1630" s="3" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="B1630" s="3" t="s">
         <v>192</v>
@@ -60012,7 +59988,7 @@
         <v>127</v>
       </c>
       <c r="F1630" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1630" s="8" t="s">
         <v>279</v>
@@ -60031,7 +60007,7 @@
     </row>
     <row r="1631" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1631" s="3" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="B1631" s="3" t="s">
         <v>287</v>
@@ -60046,7 +60022,7 @@
         <v>127</v>
       </c>
       <c r="F1631" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1631" s="8" t="s">
         <v>279</v>
@@ -60065,7 +60041,7 @@
     </row>
     <row r="1632" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1632" s="3" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="B1632" s="3" t="s">
         <v>248</v>
@@ -60097,7 +60073,7 @@
     </row>
     <row r="1633" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1633" s="3" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="B1633" s="3" t="s">
         <v>248</v>
@@ -60112,7 +60088,7 @@
         <v>127</v>
       </c>
       <c r="F1633" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1633" s="8" t="s">
         <v>279</v>
@@ -60131,7 +60107,7 @@
     </row>
     <row r="1634" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1634" s="3" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="B1634" s="3" t="s">
         <v>123</v>
@@ -60163,7 +60139,7 @@
     </row>
     <row r="1635" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1635" s="3" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="B1635" s="3" t="s">
         <v>154</v>
@@ -60195,7 +60171,7 @@
     </row>
     <row r="1636" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1636" s="3" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="B1636" s="3" t="s">
         <v>180</v>
@@ -60210,7 +60186,7 @@
         <v>140</v>
       </c>
       <c r="F1636" s="3" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="G1636" s="8" t="s">
         <v>280</v>
@@ -60229,7 +60205,7 @@
     </row>
     <row r="1637" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1637" s="3" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="B1637" s="3" t="s">
         <v>114</v>
@@ -60261,7 +60237,7 @@
     </row>
     <row r="1638" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1638" s="3" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="B1638" s="3" t="s">
         <v>248</v>
@@ -60293,7 +60269,7 @@
     </row>
     <row r="1639" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1639" s="3" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="B1639" s="3" t="s">
         <v>171</v>
@@ -60325,7 +60301,7 @@
     </row>
     <row r="1640" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1640" s="3" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="B1640" s="3" t="s">
         <v>174</v>
@@ -60357,7 +60333,7 @@
     </row>
     <row r="1641" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1641" s="3" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="B1641" s="3" t="s">
         <v>248</v>
@@ -60389,7 +60365,7 @@
     </row>
     <row r="1642" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1642" s="3" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="B1642" s="3" t="s">
         <v>154</v>
@@ -60421,7 +60397,7 @@
     </row>
     <row r="1643" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1643" s="3" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B1643" s="3" t="s">
         <v>180</v>
@@ -60436,7 +60412,7 @@
         <v>140</v>
       </c>
       <c r="F1643" s="3" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="G1643" s="8" t="s">
         <v>279</v>
@@ -60455,7 +60431,7 @@
     </row>
     <row r="1644" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1644" s="3" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B1644" s="3" t="s">
         <v>191</v>
@@ -60470,7 +60446,7 @@
         <v>140</v>
       </c>
       <c r="F1644" s="3" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="G1644" s="8" t="s">
         <v>279</v>
@@ -60489,7 +60465,7 @@
     </row>
     <row r="1645" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1645" s="3" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B1645" s="3" t="s">
         <v>202</v>
@@ -60504,7 +60480,7 @@
         <v>140</v>
       </c>
       <c r="F1645" s="3" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="G1645" s="8" t="s">
         <v>279</v>
@@ -60523,7 +60499,7 @@
     </row>
     <row r="1646" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1646" s="3" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B1646" s="3" t="s">
         <v>248</v>
@@ -60555,7 +60531,7 @@
     </row>
     <row r="1647" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1647" s="3" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B1647" s="3" t="s">
         <v>149</v>
@@ -60587,7 +60563,7 @@
     </row>
     <row r="1648" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1648" s="3" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B1648" s="3" t="s">
         <v>248</v>
@@ -60619,7 +60595,7 @@
     </row>
     <row r="1649" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1649" s="3" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B1649" s="3" t="s">
         <v>149</v>
@@ -60651,7 +60627,7 @@
     </row>
     <row r="1650" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1650" s="3" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B1650" s="3" t="s">
         <v>132</v>
@@ -60663,10 +60639,10 @@
         <v>1303</v>
       </c>
       <c r="E1650" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F1650" s="3" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G1650" s="8" t="s">
         <v>279</v>
@@ -60685,7 +60661,7 @@
     </row>
     <row r="1651" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1651" s="3" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B1651" s="3" t="s">
         <v>154</v>
@@ -60697,10 +60673,10 @@
         <v>168</v>
       </c>
       <c r="E1651" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F1651" s="3" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G1651" s="8" t="s">
         <v>279</v>
@@ -60719,7 +60695,7 @@
     </row>
     <row r="1652" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1652" s="3" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="B1652" s="3" t="s">
         <v>154</v>
@@ -60731,10 +60707,10 @@
         <v>125</v>
       </c>
       <c r="E1652" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F1652" s="3" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G1652" s="8" t="s">
         <v>279</v>
@@ -60753,7 +60729,7 @@
     </row>
     <row r="1653" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1653" s="3" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="B1653" s="3" t="s">
         <v>248</v>
@@ -60785,7 +60761,7 @@
     </row>
     <row r="1654" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1654" s="3" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="B1654" s="3" t="s">
         <v>171</v>
@@ -60817,7 +60793,7 @@
     </row>
     <row r="1655" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1655" s="3" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B1655" s="3" t="s">
         <v>355</v>
@@ -60829,10 +60805,10 @@
         <v>220</v>
       </c>
       <c r="E1655" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F1655" s="3" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G1655" s="8" t="s">
         <v>279</v>
@@ -60851,7 +60827,7 @@
     </row>
     <row r="1656" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1656" s="3" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B1656" s="3" t="s">
         <v>209</v>
@@ -60863,10 +60839,10 @@
         <v>94</v>
       </c>
       <c r="E1656" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F1656" s="3" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G1656" s="8" t="s">
         <v>279</v>
@@ -60885,7 +60861,7 @@
     </row>
     <row r="1657" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1657" s="3" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B1657" s="3" t="s">
         <v>333</v>
@@ -60897,7 +60873,7 @@
         <v>167</v>
       </c>
       <c r="E1657" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1657" s="3" t="s">
         <v>1283</v>
@@ -60919,7 +60895,7 @@
     </row>
     <row r="1658" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1658" s="3" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B1658" s="3" t="s">
         <v>138</v>
@@ -60931,7 +60907,7 @@
         <v>115</v>
       </c>
       <c r="E1658" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1658" s="3" t="s">
         <v>1283</v>
@@ -60953,7 +60929,7 @@
     </row>
     <row r="1659" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1659" s="3" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="B1659" s="3" t="s">
         <v>329</v>
@@ -60965,7 +60941,7 @@
         <v>970</v>
       </c>
       <c r="E1659" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1659" s="3" t="s">
         <v>1283</v>
@@ -60987,7 +60963,7 @@
     </row>
     <row r="1660" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1660" s="3" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B1660" s="3" t="s">
         <v>248</v>
@@ -60999,7 +60975,7 @@
         <v>184</v>
       </c>
       <c r="E1660" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1660" s="3" t="s">
         <v>1283</v>
@@ -61021,7 +60997,7 @@
     </row>
     <row r="1661" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1661" s="3" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B1661" s="3" t="s">
         <v>149</v>
@@ -61033,7 +61009,7 @@
         <v>193</v>
       </c>
       <c r="E1661" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1661" s="3" t="s">
         <v>1283</v>
@@ -61055,7 +61031,7 @@
     </row>
     <row r="1662" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1662" s="3" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="B1662" s="3" t="s">
         <v>355</v>
@@ -61067,7 +61043,7 @@
         <v>193</v>
       </c>
       <c r="E1662" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1662" s="3" t="s">
         <v>1283</v>
@@ -61089,7 +61065,7 @@
     </row>
     <row r="1663" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1663" s="3" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="B1663" s="3" t="s">
         <v>200</v>
@@ -61101,7 +61077,7 @@
         <v>136</v>
       </c>
       <c r="E1663" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1663" s="3" t="s">
         <v>1283</v>
@@ -61123,7 +61099,7 @@
     </row>
     <row r="1664" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1664" s="3" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="B1664" s="3" t="s">
         <v>375</v>
@@ -61135,7 +61111,7 @@
         <v>120</v>
       </c>
       <c r="E1664" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1664" s="3" t="s">
         <v>1283</v>
@@ -61157,7 +61133,7 @@
     </row>
     <row r="1665" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1665" s="3" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="B1665" s="3" t="s">
         <v>149</v>
@@ -61169,7 +61145,7 @@
         <v>239</v>
       </c>
       <c r="E1665" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1665" s="3" t="s">
         <v>1283</v>
@@ -61191,7 +61167,7 @@
     </row>
     <row r="1666" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1666" s="3" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="B1666" s="3" t="s">
         <v>180</v>
@@ -61200,10 +61176,10 @@
         <v>267</v>
       </c>
       <c r="D1666" s="3" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="E1666" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1666" s="3" t="s">
         <v>1283</v>
@@ -61225,7 +61201,7 @@
     </row>
     <row r="1667" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1667" s="3" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="B1667" s="3" t="s">
         <v>233</v>
@@ -61237,7 +61213,7 @@
         <v>120</v>
       </c>
       <c r="E1667" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1667" s="3" t="s">
         <v>1283</v>
@@ -61259,7 +61235,7 @@
     </row>
     <row r="1668" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1668" s="3" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="B1668" s="3" t="s">
         <v>359</v>
@@ -61271,7 +61247,7 @@
         <v>298</v>
       </c>
       <c r="E1668" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1668" s="3" t="s">
         <v>1283</v>
@@ -61293,7 +61269,7 @@
     </row>
     <row r="1669" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1669" s="3" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="B1669" s="3" t="s">
         <v>171</v>
@@ -61305,7 +61281,7 @@
         <v>120</v>
       </c>
       <c r="E1669" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1669" s="3" t="s">
         <v>1283</v>
@@ -61327,7 +61303,7 @@
     </row>
     <row r="1670" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1670" s="3" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="B1670" s="3" t="s">
         <v>248</v>
@@ -61339,7 +61315,7 @@
         <v>184</v>
       </c>
       <c r="E1670" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1670" s="3" t="s">
         <v>1283</v>
@@ -61361,7 +61337,7 @@
     </row>
     <row r="1671" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1671" s="3" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="B1671" s="3" t="s">
         <v>149</v>
@@ -61373,7 +61349,7 @@
         <v>193</v>
       </c>
       <c r="E1671" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1671" s="3" t="s">
         <v>1283</v>
@@ -61395,7 +61371,7 @@
     </row>
     <row r="1672" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1672" s="3" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="B1672" s="3" t="s">
         <v>248</v>
@@ -61407,7 +61383,7 @@
         <v>184</v>
       </c>
       <c r="E1672" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1672" s="3" t="s">
         <v>1283</v>
@@ -61429,7 +61405,7 @@
     </row>
     <row r="1673" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1673" s="3" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="B1673" s="3" t="s">
         <v>179</v>
@@ -61441,7 +61417,7 @@
         <v>1049</v>
       </c>
       <c r="E1673" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1673" s="3" t="s">
         <v>1283</v>
@@ -61463,7 +61439,7 @@
     </row>
     <row r="1674" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1674" s="3" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="B1674" s="3" t="s">
         <v>248</v>
@@ -61475,7 +61451,7 @@
         <v>184</v>
       </c>
       <c r="E1674" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1674" s="3" t="s">
         <v>1283</v>
@@ -61497,7 +61473,7 @@
     </row>
     <row r="1675" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1675" s="3" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="B1675" s="3" t="s">
         <v>149</v>
@@ -61509,7 +61485,7 @@
         <v>193</v>
       </c>
       <c r="E1675" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1675" s="3" t="s">
         <v>1283</v>
@@ -61531,7 +61507,7 @@
     </row>
     <row r="1676" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1676" s="3" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="B1676" s="3" t="s">
         <v>331</v>
@@ -61543,7 +61519,7 @@
         <v>126</v>
       </c>
       <c r="E1676" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1676" s="3" t="s">
         <v>1283</v>
@@ -61565,7 +61541,7 @@
     </row>
     <row r="1677" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1677" s="3" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="B1677" s="3" t="s">
         <v>333</v>
@@ -61577,7 +61553,7 @@
         <v>167</v>
       </c>
       <c r="E1677" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1677" s="3" t="s">
         <v>1283</v>
@@ -61599,7 +61575,7 @@
     </row>
     <row r="1678" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1678" s="3" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="B1678" s="3" t="s">
         <v>192</v>
@@ -61611,7 +61587,7 @@
         <v>115</v>
       </c>
       <c r="E1678" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1678" s="3" t="s">
         <v>1283</v>
@@ -61633,7 +61609,7 @@
     </row>
     <row r="1679" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1679" s="3" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="B1679" s="3" t="s">
         <v>271</v>
@@ -61645,7 +61621,7 @@
         <v>136</v>
       </c>
       <c r="E1679" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1679" s="3" t="s">
         <v>1283</v>
@@ -61667,7 +61643,7 @@
     </row>
     <row r="1680" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1680" s="3" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="B1680" s="3" t="s">
         <v>133</v>
@@ -61679,7 +61655,7 @@
         <v>873</v>
       </c>
       <c r="E1680" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1680" s="3" t="s">
         <v>1283</v>
@@ -61701,7 +61677,7 @@
     </row>
     <row r="1681" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1681" s="3" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="B1681" s="3" t="s">
         <v>253</v>
@@ -61713,7 +61689,7 @@
         <v>193</v>
       </c>
       <c r="E1681" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1681" s="3" t="s">
         <v>1283</v>
@@ -61735,7 +61711,7 @@
     </row>
     <row r="1682" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1682" s="3" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="B1682" s="3" t="s">
         <v>149</v>
@@ -61747,7 +61723,7 @@
         <v>193</v>
       </c>
       <c r="E1682" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1682" s="3" t="s">
         <v>1283</v>
@@ -61769,7 +61745,7 @@
     </row>
     <row r="1683" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1683" s="3" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="B1683" s="3" t="s">
         <v>253</v>
@@ -61781,7 +61757,7 @@
         <v>193</v>
       </c>
       <c r="E1683" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1683" s="3" t="s">
         <v>1283</v>
@@ -61803,7 +61779,7 @@
     </row>
     <row r="1684" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1684" s="3" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="B1684" s="3" t="s">
         <v>253</v>
@@ -61815,7 +61791,7 @@
         <v>193</v>
       </c>
       <c r="E1684" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1684" s="3" t="s">
         <v>1283</v>
@@ -61837,7 +61813,7 @@
     </row>
     <row r="1685" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1685" s="3" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="B1685" s="3" t="s">
         <v>209</v>
@@ -61849,7 +61825,7 @@
         <v>120</v>
       </c>
       <c r="E1685" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1685" s="3" t="s">
         <v>1283</v>
@@ -61871,7 +61847,7 @@
     </row>
     <row r="1686" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1686" s="3" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="B1686" s="3" t="s">
         <v>179</v>
@@ -61883,7 +61859,7 @@
         <v>184</v>
       </c>
       <c r="E1686" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1686" s="3" t="s">
         <v>1283</v>
@@ -61905,7 +61881,7 @@
     </row>
     <row r="1687" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1687" s="3" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="B1687" s="3" t="s">
         <v>241</v>
@@ -61917,7 +61893,7 @@
         <v>184</v>
       </c>
       <c r="E1687" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1687" s="3" t="s">
         <v>1283</v>
@@ -61939,7 +61915,7 @@
     </row>
     <row r="1688" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1688" s="3" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="B1688" s="3" t="s">
         <v>179</v>
@@ -61951,7 +61927,7 @@
         <v>184</v>
       </c>
       <c r="E1688" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1688" s="3" t="s">
         <v>1283</v>
@@ -61973,7 +61949,7 @@
     </row>
     <row r="1689" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1689" s="3" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="B1689" s="3" t="s">
         <v>132</v>
@@ -61985,7 +61961,7 @@
         <v>184</v>
       </c>
       <c r="E1689" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1689" s="3" t="s">
         <v>1283</v>
@@ -62007,7 +61983,7 @@
     </row>
     <row r="1690" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1690" s="3" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="B1690" s="3" t="s">
         <v>355</v>
@@ -62019,7 +61995,7 @@
         <v>105</v>
       </c>
       <c r="E1690" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1690" s="3" t="s">
         <v>1283</v>
@@ -62041,7 +62017,7 @@
     </row>
     <row r="1691" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1691" s="3" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="B1691" s="3" t="s">
         <v>253</v>
@@ -62053,7 +62029,7 @@
         <v>193</v>
       </c>
       <c r="E1691" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1691" s="3" t="s">
         <v>1283</v>
@@ -62075,7 +62051,7 @@
     </row>
     <row r="1692" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1692" s="3" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="B1692" s="3" t="s">
         <v>157</v>
@@ -62107,7 +62083,7 @@
     </row>
     <row r="1693" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1693" s="3" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="B1693" s="3" t="s">
         <v>249</v>
@@ -62119,7 +62095,7 @@
         <v>251</v>
       </c>
       <c r="E1693" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1693" s="3" t="s">
         <v>1283</v>
@@ -62141,7 +62117,7 @@
     </row>
     <row r="1694" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1694" s="3" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="B1694" s="3" t="s">
         <v>171</v>
@@ -62153,7 +62129,7 @@
         <v>251</v>
       </c>
       <c r="E1694" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1694" s="3" t="s">
         <v>1283</v>
@@ -62175,7 +62151,7 @@
     </row>
     <row r="1695" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1695" s="3" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="B1695" s="3" t="s">
         <v>200</v>
@@ -62207,7 +62183,7 @@
     </row>
     <row r="1696" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1696" s="3" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="B1696" s="3" t="s">
         <v>150</v>
@@ -62219,7 +62195,7 @@
         <v>115</v>
       </c>
       <c r="E1696" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1696" s="3" t="s">
         <v>1283</v>
@@ -62241,7 +62217,7 @@
     </row>
     <row r="1697" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1697" s="3" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="B1697" s="5" t="s">
         <v>200</v>
@@ -62253,7 +62229,7 @@
         <v>167</v>
       </c>
       <c r="E1697" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1697" s="3" t="s">
         <v>1283</v>
@@ -62275,7 +62251,7 @@
     </row>
     <row r="1698" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1698" s="3" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="B1698" s="3" t="s">
         <v>329</v>
@@ -62287,7 +62263,7 @@
         <v>144</v>
       </c>
       <c r="E1698" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1698" s="3" t="s">
         <v>1283</v>
@@ -62309,7 +62285,7 @@
     </row>
     <row r="1699" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1699" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="B1699" s="3" t="s">
         <v>248</v>
@@ -62321,7 +62297,7 @@
         <v>184</v>
       </c>
       <c r="E1699" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1699" s="3" t="s">
         <v>1283</v>
@@ -62343,7 +62319,7 @@
     </row>
     <row r="1700" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1700" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="B1700" s="3" t="s">
         <v>219</v>
@@ -62355,7 +62331,7 @@
         <v>193</v>
       </c>
       <c r="E1700" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1700" s="3" t="s">
         <v>1283</v>
@@ -62377,7 +62353,7 @@
     </row>
     <row r="1701" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1701" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="B1701" s="3" t="s">
         <v>196</v>
@@ -62389,7 +62365,7 @@
         <v>193</v>
       </c>
       <c r="E1701" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1701" s="3" t="s">
         <v>1283</v>
@@ -62411,7 +62387,7 @@
     </row>
     <row r="1702" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1702" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="B1702" s="3" t="s">
         <v>157</v>
@@ -62423,7 +62399,7 @@
         <v>193</v>
       </c>
       <c r="E1702" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1702" s="3" t="s">
         <v>1283</v>
@@ -62445,7 +62421,7 @@
     </row>
     <row r="1703" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1703" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="B1703" s="3" t="s">
         <v>114</v>
@@ -62457,7 +62433,7 @@
         <v>193</v>
       </c>
       <c r="E1703" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1703" s="3" t="s">
         <v>1283</v>
@@ -62479,7 +62455,7 @@
     </row>
     <row r="1704" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1704" s="3" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="B1704" s="3" t="s">
         <v>248</v>
@@ -62491,7 +62467,7 @@
         <v>184</v>
       </c>
       <c r="E1704" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1704" s="3" t="s">
         <v>1283</v>
@@ -62513,7 +62489,7 @@
     </row>
     <row r="1705" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1705" s="3" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="B1705" s="3" t="s">
         <v>154</v>
@@ -62525,7 +62501,7 @@
         <v>168</v>
       </c>
       <c r="E1705" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1705" s="3" t="s">
         <v>1283</v>
@@ -62547,7 +62523,7 @@
     </row>
     <row r="1706" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1706" s="3" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="B1706" s="3" t="s">
         <v>338</v>
@@ -62559,7 +62535,7 @@
         <v>272</v>
       </c>
       <c r="E1706" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1706" s="3" t="s">
         <v>1283</v>
@@ -62581,7 +62557,7 @@
     </row>
     <row r="1707" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1707" s="3" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="B1707" s="3" t="s">
         <v>161</v>
@@ -62593,7 +62569,7 @@
         <v>184</v>
       </c>
       <c r="E1707" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1707" s="3" t="s">
         <v>1283</v>
@@ -62615,7 +62591,7 @@
     </row>
     <row r="1708" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1708" s="3" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="B1708" s="3" t="s">
         <v>248</v>
@@ -62627,7 +62603,7 @@
         <v>184</v>
       </c>
       <c r="E1708" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1708" s="3" t="s">
         <v>1283</v>
@@ -62649,7 +62625,7 @@
     </row>
     <row r="1709" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1709" s="3" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="B1709" s="3" t="s">
         <v>219</v>
@@ -62661,7 +62637,7 @@
         <v>184</v>
       </c>
       <c r="E1709" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1709" s="3" t="s">
         <v>1283</v>
@@ -62683,7 +62659,7 @@
     </row>
     <row r="1710" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1710" s="3" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="B1710" s="3" t="s">
         <v>355</v>
@@ -62695,7 +62671,7 @@
         <v>220</v>
       </c>
       <c r="E1710" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1710" s="3" t="s">
         <v>1283</v>
@@ -62717,7 +62693,7 @@
     </row>
     <row r="1711" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1711" s="3" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="B1711" s="3" t="s">
         <v>209</v>
@@ -62729,7 +62705,7 @@
         <v>167</v>
       </c>
       <c r="E1711" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1711" s="3" t="s">
         <v>1283</v>
@@ -62751,7 +62727,7 @@
     </row>
     <row r="1712" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1712" s="3" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="B1712" s="3" t="s">
         <v>340</v>
@@ -62763,7 +62739,7 @@
         <v>347</v>
       </c>
       <c r="E1712" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1712" s="3" t="s">
         <v>1283</v>
@@ -62785,7 +62761,7 @@
     </row>
     <row r="1713" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1713" s="3" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="B1713" s="3" t="s">
         <v>202</v>
@@ -62797,7 +62773,7 @@
         <v>168</v>
       </c>
       <c r="E1713" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1713" s="3" t="s">
         <v>1283</v>
@@ -62819,7 +62795,7 @@
     </row>
     <row r="1714" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1714" s="3" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="B1714" s="3" t="s">
         <v>171</v>
@@ -62831,7 +62807,7 @@
         <v>120</v>
       </c>
       <c r="E1714" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1714" s="3" t="s">
         <v>1283</v>
@@ -62853,10 +62829,10 @@
     </row>
     <row r="1715" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1715" s="3" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="B1715" s="3" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="C1715" s="3" t="s">
         <v>249</v>
@@ -62865,7 +62841,7 @@
         <v>184</v>
       </c>
       <c r="E1715" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1715" s="3" t="s">
         <v>1283</v>
@@ -62887,7 +62863,7 @@
     </row>
     <row r="1716" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1716" s="3" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="B1716" s="3" t="s">
         <v>171</v>
@@ -62899,7 +62875,7 @@
         <v>184</v>
       </c>
       <c r="E1716" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1716" s="3" t="s">
         <v>1283</v>
@@ -62921,7 +62897,7 @@
     </row>
     <row r="1717" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1717" s="3" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="B1717" s="3" t="s">
         <v>200</v>
@@ -62933,7 +62909,7 @@
         <v>105</v>
       </c>
       <c r="E1717" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1717" s="3" t="s">
         <v>1283</v>
@@ -62955,7 +62931,7 @@
     </row>
     <row r="1718" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1718" s="3" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="B1718" s="3" t="s">
         <v>160</v>
@@ -62967,7 +62943,7 @@
         <v>217</v>
       </c>
       <c r="E1718" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1718" s="3" t="s">
         <v>1283</v>
@@ -62989,7 +62965,7 @@
     </row>
     <row r="1719" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1719" s="3" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="B1719" s="3" t="s">
         <v>196</v>
@@ -63001,7 +62977,7 @@
         <v>115</v>
       </c>
       <c r="E1719" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1719" s="3" t="s">
         <v>1283</v>
@@ -63023,7 +62999,7 @@
     </row>
     <row r="1720" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1720" s="3" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="B1720" s="3" t="s">
         <v>329</v>
@@ -63035,7 +63011,7 @@
         <v>583</v>
       </c>
       <c r="E1720" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1720" s="3" t="s">
         <v>1283</v>
@@ -63057,7 +63033,7 @@
     </row>
     <row r="1721" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1721" s="3" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="B1721" s="3" t="s">
         <v>119</v>
@@ -63069,7 +63045,7 @@
         <v>193</v>
       </c>
       <c r="E1721" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1721" s="3" t="s">
         <v>1283</v>
@@ -63091,7 +63067,7 @@
     </row>
     <row r="1722" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1722" s="3" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="B1722" s="3" t="s">
         <v>114</v>
@@ -63103,7 +63079,7 @@
         <v>193</v>
       </c>
       <c r="E1722" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1722" s="3" t="s">
         <v>1283</v>
@@ -63125,7 +63101,7 @@
     </row>
     <row r="1723" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1723" s="3" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="B1723" s="3" t="s">
         <v>331</v>
@@ -63137,7 +63113,7 @@
         <v>125</v>
       </c>
       <c r="E1723" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1723" s="3" t="s">
         <v>1283</v>
@@ -63159,7 +63135,7 @@
     </row>
     <row r="1724" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1724" s="3" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="B1724" s="3" t="s">
         <v>242</v>
@@ -63171,7 +63147,7 @@
         <v>272</v>
       </c>
       <c r="E1724" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1724" s="3" t="s">
         <v>1283</v>
@@ -63193,7 +63169,7 @@
     </row>
     <row r="1725" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1725" s="3" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="B1725" s="3" t="s">
         <v>287</v>
@@ -63205,7 +63181,7 @@
         <v>272</v>
       </c>
       <c r="E1725" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1725" s="3" t="s">
         <v>1283</v>
@@ -63227,7 +63203,7 @@
     </row>
     <row r="1726" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1726" s="3" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="B1726" s="3" t="s">
         <v>149</v>
@@ -63239,7 +63215,7 @@
         <v>126</v>
       </c>
       <c r="E1726" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1726" s="3" t="s">
         <v>1283</v>
@@ -63261,7 +63237,7 @@
     </row>
     <row r="1727" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1727" s="3" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="B1727" s="3" t="s">
         <v>359</v>
@@ -63273,7 +63249,7 @@
         <v>94</v>
       </c>
       <c r="E1727" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1727" s="3" t="s">
         <v>1283</v>
@@ -63295,7 +63271,7 @@
     </row>
     <row r="1728" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1728" s="3" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="B1728" s="3" t="s">
         <v>248</v>
@@ -63307,7 +63283,7 @@
         <v>184</v>
       </c>
       <c r="E1728" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1728" s="3" t="s">
         <v>1283</v>
@@ -63329,7 +63305,7 @@
     </row>
     <row r="1729" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1729" s="3" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="B1729" s="3" t="s">
         <v>248</v>
@@ -63341,7 +63317,7 @@
         <v>184</v>
       </c>
       <c r="E1729" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1729" s="3" t="s">
         <v>1283</v>
@@ -63363,7 +63339,7 @@
     </row>
     <row r="1730" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1730" s="3" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="B1730" s="3" t="s">
         <v>171</v>
@@ -63375,7 +63351,7 @@
         <v>184</v>
       </c>
       <c r="E1730" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1730" s="3" t="s">
         <v>1283</v>
@@ -63397,7 +63373,7 @@
     </row>
     <row r="1731" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1731" s="3" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="B1731" s="3" t="s">
         <v>359</v>
@@ -63409,7 +63385,7 @@
         <v>111</v>
       </c>
       <c r="E1731" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1731" s="3" t="s">
         <v>1283</v>
@@ -63431,7 +63407,7 @@
     </row>
     <row r="1732" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1732" s="3" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="B1732" s="3" t="s">
         <v>375</v>
@@ -63443,7 +63419,7 @@
         <v>94</v>
       </c>
       <c r="E1732" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1732" s="3" t="s">
         <v>1283</v>
@@ -63465,7 +63441,7 @@
     </row>
     <row r="1733" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1733" s="3" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="B1733" s="3" t="s">
         <v>174</v>
@@ -63477,7 +63453,7 @@
         <v>105</v>
       </c>
       <c r="E1733" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1733" s="3" t="s">
         <v>1283</v>
@@ -63499,7 +63475,7 @@
     </row>
     <row r="1734" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1734" s="3" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="B1734" s="3" t="s">
         <v>563</v>
@@ -63511,7 +63487,7 @@
         <v>868</v>
       </c>
       <c r="E1734" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1734" s="3" t="s">
         <v>1283</v>
@@ -63533,7 +63509,7 @@
     </row>
     <row r="1735" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1735" s="3" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="B1735" s="3" t="s">
         <v>154</v>
@@ -63545,7 +63521,7 @@
         <v>120</v>
       </c>
       <c r="E1735" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1735" s="3" t="s">
         <v>1283</v>
@@ -63567,7 +63543,7 @@
     </row>
     <row r="1736" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1736" s="3" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="B1736" s="3" t="s">
         <v>287</v>
@@ -63579,7 +63555,7 @@
         <v>1049</v>
       </c>
       <c r="E1736" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1736" s="3" t="s">
         <v>1283</v>
@@ -63601,7 +63577,7 @@
     </row>
     <row r="1737" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1737" s="3" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="B1737" s="3" t="s">
         <v>171</v>
@@ -63633,7 +63609,7 @@
     </row>
     <row r="1738" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1738" s="3" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="B1738" s="3" t="s">
         <v>353</v>
@@ -63665,7 +63641,7 @@
     </row>
     <row r="1739" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1739" s="3" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="B1739" s="3" t="s">
         <v>248</v>
@@ -63697,7 +63673,7 @@
     </row>
     <row r="1740" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1740" s="3" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="B1740" s="3" t="s">
         <v>171</v>
@@ -63729,7 +63705,7 @@
     </row>
     <row r="1741" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1741" s="3" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="B1741" s="3" t="s">
         <v>196</v>
@@ -63761,7 +63737,7 @@
     </row>
     <row r="1742" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1742" s="3" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B1742" s="3" t="s">
         <v>359</v>
@@ -63793,7 +63769,7 @@
     </row>
     <row r="1743" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1743" s="3" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B1743" s="3" t="s">
         <v>375</v>
@@ -63825,7 +63801,7 @@
     </row>
     <row r="1744" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1744" s="3" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B1744" s="3" t="s">
         <v>191</v>
@@ -63857,7 +63833,7 @@
     </row>
     <row r="1745" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1745" s="3" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B1745" s="3" t="s">
         <v>353</v>
@@ -63889,7 +63865,7 @@
     </row>
     <row r="1746" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1746" s="3" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="B1746" s="3" t="s">
         <v>287</v>
@@ -63921,7 +63897,7 @@
     </row>
     <row r="1747" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1747" s="3" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="B1747" s="3" t="s">
         <v>288</v>
@@ -63953,7 +63929,7 @@
     </row>
     <row r="1748" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1748" s="3" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="B1748" s="3" t="s">
         <v>353</v>
@@ -63985,7 +63961,7 @@
     </row>
     <row r="1749" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1749" s="3" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="B1749" s="3" t="s">
         <v>233</v>
@@ -64017,7 +63993,7 @@
     </row>
     <row r="1750" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1750" s="3" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="B1750" s="3" t="s">
         <v>149</v>
@@ -64049,7 +64025,7 @@
     </row>
     <row r="1751" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1751" s="3" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="B1751" s="3" t="s">
         <v>361</v>
@@ -64081,7 +64057,7 @@
     </row>
     <row r="1752" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1752" s="3" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="B1752" s="3" t="s">
         <v>134</v>
@@ -64113,7 +64089,7 @@
     </row>
     <row r="1753" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1753" s="3" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="B1753" s="3" t="s">
         <v>200</v>
@@ -64145,7 +64121,7 @@
     </row>
     <row r="1754" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1754" s="3" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="B1754" s="3" t="s">
         <v>459</v>
@@ -64177,7 +64153,7 @@
     </row>
     <row r="1755" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1755" s="3" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="B1755" s="3" t="s">
         <v>200</v>
@@ -64189,7 +64165,7 @@
         <v>868</v>
       </c>
       <c r="E1755" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1755" s="3" t="s">
         <v>1283</v>
@@ -64211,7 +64187,7 @@
     </row>
     <row r="1756" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1756" s="3" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="B1756" s="3" t="s">
         <v>233</v>
@@ -64243,7 +64219,7 @@
     </row>
     <row r="1757" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1757" s="3" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="B1757" s="3" t="s">
         <v>253</v>
@@ -64275,7 +64251,7 @@
     </row>
     <row r="1758" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1758" s="3" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="B1758" s="3" t="s">
         <v>149</v>
@@ -64307,7 +64283,7 @@
     </row>
     <row r="1759" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1759" s="3" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="B1759" s="3" t="s">
         <v>253</v>
@@ -64339,7 +64315,7 @@
     </row>
     <row r="1760" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1760" s="3" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="B1760" s="3" t="s">
         <v>202</v>
@@ -64351,7 +64327,7 @@
         <v>94</v>
       </c>
       <c r="E1760" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1760" s="3" t="s">
         <v>1283</v>
@@ -64373,7 +64349,7 @@
     </row>
     <row r="1761" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1761" s="3" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="B1761" s="3" t="s">
         <v>154</v>
@@ -64385,7 +64361,7 @@
         <v>184</v>
       </c>
       <c r="E1761" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1761" s="3" t="s">
         <v>1283</v>
@@ -64407,7 +64383,7 @@
     </row>
     <row r="1762" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1762" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="B1762" s="3" t="s">
         <v>202</v>
@@ -64419,7 +64395,7 @@
         <v>220</v>
       </c>
       <c r="E1762" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1762" s="3" t="s">
         <v>1283</v>
@@ -64441,7 +64417,7 @@
     </row>
     <row r="1763" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1763" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="B1763" s="3" t="s">
         <v>209</v>
@@ -64453,7 +64429,7 @@
         <v>111</v>
       </c>
       <c r="E1763" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1763" s="3" t="s">
         <v>1283</v>
@@ -64475,7 +64451,7 @@
     </row>
     <row r="1764" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1764" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="B1764" s="3" t="s">
         <v>119</v>
@@ -64487,7 +64463,7 @@
         <v>220</v>
       </c>
       <c r="E1764" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1764" s="3" t="s">
         <v>1283</v>
@@ -64509,7 +64485,7 @@
     </row>
     <row r="1765" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1765" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="B1765" s="3" t="s">
         <v>124</v>
@@ -64521,7 +64497,7 @@
         <v>193</v>
       </c>
       <c r="E1765" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1765" s="3" t="s">
         <v>1283</v>
@@ -64543,7 +64519,7 @@
     </row>
     <row r="1766" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1766" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="B1766" s="3" t="s">
         <v>135</v>
@@ -64555,7 +64531,7 @@
         <v>115</v>
       </c>
       <c r="E1766" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1766" s="3" t="s">
         <v>1283</v>
@@ -64577,7 +64553,7 @@
     </row>
     <row r="1767" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1767" s="3" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="B1767" s="3" t="s">
         <v>355</v>
@@ -64589,7 +64565,7 @@
         <v>9</v>
       </c>
       <c r="E1767" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1767" s="3" t="s">
         <v>1283</v>
@@ -64611,7 +64587,7 @@
     </row>
     <row r="1768" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1768" s="3" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="B1768" s="3" t="s">
         <v>124</v>
@@ -64623,7 +64599,7 @@
         <v>251</v>
       </c>
       <c r="E1768" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1768" s="3" t="s">
         <v>1283</v>
@@ -64645,7 +64621,7 @@
     </row>
     <row r="1769" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1769" s="3" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="B1769" s="3" t="s">
         <v>331</v>
@@ -64657,7 +64633,7 @@
         <v>9</v>
       </c>
       <c r="E1769" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1769" s="3" t="s">
         <v>1283</v>
@@ -64679,7 +64655,7 @@
     </row>
     <row r="1770" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1770" s="3" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="B1770" s="3" t="s">
         <v>209</v>
@@ -64691,7 +64667,7 @@
         <v>167</v>
       </c>
       <c r="E1770" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1770" s="3" t="s">
         <v>1283</v>
@@ -64713,7 +64689,7 @@
     </row>
     <row r="1771" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1771" s="3" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="B1771" s="3" t="s">
         <v>132</v>
@@ -64725,7 +64701,7 @@
         <v>873</v>
       </c>
       <c r="E1771" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1771" s="3" t="s">
         <v>1283</v>
@@ -64747,7 +64723,7 @@
     </row>
     <row r="1772" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1772" s="3" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="B1772" s="3" t="s">
         <v>353</v>
@@ -64759,7 +64735,7 @@
         <v>136</v>
       </c>
       <c r="E1772" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1772" s="3" t="s">
         <v>1283</v>
@@ -64781,7 +64757,7 @@
     </row>
     <row r="1773" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1773" s="3" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="B1773" s="3" t="s">
         <v>288</v>
@@ -64793,7 +64769,7 @@
         <v>272</v>
       </c>
       <c r="E1773" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1773" s="3" t="s">
         <v>1283</v>
@@ -64815,7 +64791,7 @@
     </row>
     <row r="1774" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1774" s="3" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="B1774" s="3" t="s">
         <v>241</v>
@@ -64827,7 +64803,7 @@
         <v>136</v>
       </c>
       <c r="E1774" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1774" s="3" t="s">
         <v>1283</v>
@@ -64849,7 +64825,7 @@
     </row>
     <row r="1775" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1775" s="3" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="B1775" s="3" t="s">
         <v>160</v>
@@ -64861,7 +64837,7 @@
         <v>136</v>
       </c>
       <c r="E1775" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1775" s="3" t="s">
         <v>1283</v>
@@ -64883,7 +64859,7 @@
     </row>
     <row r="1776" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1776" s="3" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="B1776" s="3" t="s">
         <v>134</v>
@@ -64895,7 +64871,7 @@
         <v>105</v>
       </c>
       <c r="E1776" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1776" s="3" t="s">
         <v>1283</v>
@@ -64917,7 +64893,7 @@
     </row>
     <row r="1777" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1777" s="3" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="B1777" s="3" t="s">
         <v>203</v>
@@ -64929,7 +64905,7 @@
         <v>115</v>
       </c>
       <c r="E1777" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1777" s="3" t="s">
         <v>1283</v>
@@ -64951,7 +64927,7 @@
     </row>
     <row r="1778" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1778" s="3" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="B1778" s="3" t="s">
         <v>133</v>
@@ -64963,7 +64939,7 @@
         <v>868</v>
       </c>
       <c r="E1778" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1778" s="3" t="s">
         <v>1283</v>
@@ -64985,7 +64961,7 @@
     </row>
     <row r="1779" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1779" s="3" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="B1779" s="3" t="s">
         <v>124</v>
@@ -64997,7 +64973,7 @@
         <v>217</v>
       </c>
       <c r="E1779" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1779" s="3" t="s">
         <v>1283</v>
@@ -65019,7 +64995,7 @@
     </row>
     <row r="1780" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1780" s="3" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="B1780" s="3" t="s">
         <v>336</v>
@@ -65031,7 +65007,7 @@
         <v>1303</v>
       </c>
       <c r="E1780" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1780" s="3" t="s">
         <v>1283</v>
@@ -65053,7 +65029,7 @@
     </row>
     <row r="1781" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1781" s="3" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="B1781" s="3" t="s">
         <v>157</v>
@@ -65065,7 +65041,7 @@
         <v>105</v>
       </c>
       <c r="E1781" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1781" s="3" t="s">
         <v>1283</v>
@@ -65087,7 +65063,7 @@
     </row>
     <row r="1782" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1782" s="3" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="B1782" s="3" t="s">
         <v>304</v>
@@ -65099,7 +65075,7 @@
         <v>115</v>
       </c>
       <c r="E1782" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1782" s="3" t="s">
         <v>1283</v>
@@ -65121,7 +65097,7 @@
     </row>
     <row r="1783" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1783" s="3" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="B1783" s="3" t="s">
         <v>200</v>
@@ -65133,7 +65109,7 @@
         <v>94</v>
       </c>
       <c r="E1783" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1783" s="3" t="s">
         <v>1283</v>
@@ -65155,7 +65131,7 @@
     </row>
     <row r="1784" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1784" s="3" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="B1784" s="3" t="s">
         <v>191</v>
@@ -65167,7 +65143,7 @@
         <v>193</v>
       </c>
       <c r="E1784" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1784" s="3" t="s">
         <v>1283</v>
@@ -65189,7 +65165,7 @@
     </row>
     <row r="1785" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1785" s="3" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="B1785" s="3" t="s">
         <v>387</v>
@@ -65201,7 +65177,7 @@
         <v>220</v>
       </c>
       <c r="E1785" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1785" s="3" t="s">
         <v>1283</v>
@@ -65223,7 +65199,7 @@
     </row>
     <row r="1786" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1786" s="3" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="B1786" s="3" t="s">
         <v>459</v>
@@ -65235,7 +65211,7 @@
         <v>272</v>
       </c>
       <c r="E1786" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1786" s="3" t="s">
         <v>1283</v>
@@ -65257,7 +65233,7 @@
     </row>
     <row r="1787" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1787" s="3" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="B1787" s="3" t="s">
         <v>160</v>
@@ -65269,7 +65245,7 @@
         <v>239</v>
       </c>
       <c r="E1787" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1787" s="3" t="s">
         <v>1283</v>
@@ -65291,7 +65267,7 @@
     </row>
     <row r="1788" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1788" s="3" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="B1788" s="3" t="s">
         <v>203</v>
@@ -65303,7 +65279,7 @@
         <v>115</v>
       </c>
       <c r="E1788" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1788" s="3" t="s">
         <v>1283</v>
@@ -65325,7 +65301,7 @@
     </row>
     <row r="1789" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1789" s="3" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="B1789" s="3" t="s">
         <v>209</v>
@@ -65337,7 +65313,7 @@
         <v>167</v>
       </c>
       <c r="E1789" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1789" s="3" t="s">
         <v>1283</v>
@@ -65359,7 +65335,7 @@
     </row>
     <row r="1790" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1790" s="3" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="B1790" s="3" t="s">
         <v>114</v>
@@ -65371,7 +65347,7 @@
         <v>126</v>
       </c>
       <c r="E1790" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1790" s="3" t="s">
         <v>1283</v>
@@ -65393,7 +65369,7 @@
     </row>
     <row r="1791" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1791" s="3" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="B1791" s="3" t="s">
         <v>271</v>
@@ -65405,7 +65381,7 @@
         <v>105</v>
       </c>
       <c r="E1791" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1791" s="3" t="s">
         <v>1283</v>
@@ -65427,7 +65403,7 @@
     </row>
     <row r="1792" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1792" s="3" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="B1792" s="3" t="s">
         <v>340</v>
@@ -65439,7 +65415,7 @@
         <v>873</v>
       </c>
       <c r="E1792" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1792" s="3" t="s">
         <v>1283</v>
@@ -65461,7 +65437,7 @@
     </row>
     <row r="1793" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1793" s="3" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="B1793" s="3" t="s">
         <v>114</v>
@@ -65473,7 +65449,7 @@
         <v>105</v>
       </c>
       <c r="E1793" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1793" s="3" t="s">
         <v>1283</v>
@@ -65495,7 +65471,7 @@
     </row>
     <row r="1794" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1794" s="3" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="B1794" s="3" t="s">
         <v>122</v>
@@ -65507,7 +65483,7 @@
         <v>389</v>
       </c>
       <c r="E1794" s="3" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F1794" s="3" t="s">
         <v>1283</v>
@@ -65529,7 +65505,7 @@
     </row>
     <row r="1795" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1795" s="3" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="B1795" s="3" t="s">
         <v>200</v>
@@ -65563,7 +65539,7 @@
     </row>
     <row r="1796" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1796" s="3" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="B1796" s="3" t="s">
         <v>210</v>
@@ -65578,7 +65554,7 @@
         <v>127</v>
       </c>
       <c r="F1796" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1796" s="8" t="s">
         <v>279</v>
@@ -65597,7 +65573,7 @@
     </row>
     <row r="1797" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1797" s="3" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="B1797" s="3" t="s">
         <v>336</v>
@@ -65612,7 +65588,7 @@
         <v>127</v>
       </c>
       <c r="F1797" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1797" s="8" t="s">
         <v>279</v>
@@ -65631,7 +65607,7 @@
     </row>
     <row r="1798" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1798" s="3" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="B1798" s="3" t="s">
         <v>135</v>
@@ -65646,7 +65622,7 @@
         <v>127</v>
       </c>
       <c r="F1798" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1798" s="8" t="s">
         <v>279</v>
@@ -65665,7 +65641,7 @@
     </row>
     <row r="1799" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1799" s="3" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="B1799" s="3" t="s">
         <v>361</v>
@@ -65680,7 +65656,7 @@
         <v>127</v>
       </c>
       <c r="F1799" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1799" s="8" t="s">
         <v>279</v>
@@ -65699,7 +65675,7 @@
     </row>
     <row r="1800" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1800" s="3" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="B1800" s="3" t="s">
         <v>119</v>
@@ -65714,7 +65690,7 @@
         <v>127</v>
       </c>
       <c r="F1800" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1800" s="8" t="s">
         <v>279</v>
@@ -65733,7 +65709,7 @@
     </row>
     <row r="1801" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1801" s="3" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="B1801" s="3" t="s">
         <v>285</v>
@@ -65748,7 +65724,7 @@
         <v>127</v>
       </c>
       <c r="F1801" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1801" s="8" t="s">
         <v>279</v>
@@ -65767,7 +65743,7 @@
     </row>
     <row r="1802" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1802" s="3" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="B1802" s="3" t="s">
         <v>147</v>
@@ -65782,7 +65758,7 @@
         <v>127</v>
       </c>
       <c r="F1802" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1802" s="8" t="s">
         <v>279</v>
@@ -65801,7 +65777,7 @@
     </row>
     <row r="1803" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1803" s="3" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="B1803" s="3" t="s">
         <v>288</v>
@@ -65810,13 +65786,13 @@
         <v>124</v>
       </c>
       <c r="D1803" s="3" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="E1803" s="3" t="s">
         <v>127</v>
       </c>
       <c r="F1803" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1803" s="8" t="s">
         <v>279</v>
@@ -65835,7 +65811,7 @@
     </row>
     <row r="1804" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1804" s="3" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="B1804" s="3" t="s">
         <v>203</v>
@@ -65850,7 +65826,7 @@
         <v>127</v>
       </c>
       <c r="F1804" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="G1804" s="8" t="s">
         <v>279</v>
@@ -65869,7 +65845,7 @@
     </row>
     <row r="1805" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1805" s="3" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="B1805" s="3" t="s">
         <v>150</v>
@@ -65884,7 +65860,7 @@
         <v>127</v>
       </c>
       <c r="F1805" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1805" s="8" t="s">
         <v>279</v>
@@ -65903,7 +65879,7 @@
     </row>
     <row r="1806" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1806" s="3" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="B1806" s="3" t="s">
         <v>160</v>
@@ -65918,7 +65894,7 @@
         <v>127</v>
       </c>
       <c r="F1806" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1806" s="8" t="s">
         <v>279</v>
@@ -65937,7 +65913,7 @@
     </row>
     <row r="1807" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1807" s="3" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="B1807" s="3" t="s">
         <v>353</v>
@@ -65952,7 +65928,7 @@
         <v>127</v>
       </c>
       <c r="F1807" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1807" s="8" t="s">
         <v>279</v>
@@ -65971,7 +65947,7 @@
     </row>
     <row r="1808" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1808" s="3" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="B1808" s="3" t="s">
         <v>288</v>
@@ -65986,7 +65962,7 @@
         <v>127</v>
       </c>
       <c r="F1808" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1808" s="8" t="s">
         <v>279</v>
@@ -66005,7 +65981,7 @@
     </row>
     <row r="1809" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1809" s="3" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="B1809" s="3" t="s">
         <v>233</v>
@@ -66020,7 +65996,7 @@
         <v>127</v>
       </c>
       <c r="F1809" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1809" s="8" t="s">
         <v>279</v>
@@ -66039,7 +66015,7 @@
     </row>
     <row r="1810" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1810" s="3" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="B1810" s="3" t="s">
         <v>304</v>
@@ -66054,7 +66030,7 @@
         <v>127</v>
       </c>
       <c r="F1810" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1810" s="8" t="s">
         <v>279</v>
@@ -66073,7 +66049,7 @@
     </row>
     <row r="1811" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1811" s="3" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="B1811" s="3" t="s">
         <v>327</v>
@@ -66088,7 +66064,7 @@
         <v>127</v>
       </c>
       <c r="F1811" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1811" s="8" t="s">
         <v>279</v>
@@ -66107,7 +66083,7 @@
     </row>
     <row r="1812" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1812" s="3" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="B1812" s="3" t="s">
         <v>211</v>
@@ -66122,7 +66098,7 @@
         <v>127</v>
       </c>
       <c r="F1812" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1812" s="8" t="s">
         <v>279</v>
@@ -66141,7 +66117,7 @@
     </row>
     <row r="1813" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1813" s="3" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B1813" s="3" t="s">
         <v>123</v>
@@ -66156,7 +66132,7 @@
         <v>127</v>
       </c>
       <c r="F1813" s="3" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G1813" s="8" t="s">
         <v>279</v>
@@ -66175,7 +66151,7 @@
     </row>
     <row r="1814" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1814" s="3" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B1814" s="3" t="s">
         <v>233</v>
@@ -66207,7 +66183,7 @@
     </row>
     <row r="1815" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1815" s="3" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B1815" s="3" t="s">
         <v>271</v>
@@ -66222,7 +66198,7 @@
         <v>127</v>
       </c>
       <c r="F1815" s="3" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="G1815" s="8" t="s">
         <v>279</v>
@@ -66241,7 +66217,7 @@
     </row>
     <row r="1816" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1816" s="3" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B1816" s="3" t="s">
         <v>204</v>
@@ -66256,7 +66232,7 @@
         <v>127</v>
       </c>
       <c r="F1816" s="3" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="G1816" s="8" t="s">
         <v>279</v>
@@ -66275,7 +66251,7 @@
     </row>
     <row r="1817" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1817" s="3" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="B1817" s="3" t="s">
         <v>333</v>
@@ -66290,7 +66266,7 @@
         <v>127</v>
       </c>
       <c r="F1817" s="3" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="G1817" s="8" t="s">
         <v>279</v>
@@ -66309,7 +66285,7 @@
     </row>
     <row r="1818" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1818" s="3" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="B1818" s="3" t="s">
         <v>340</v>
@@ -66324,7 +66300,7 @@
         <v>127</v>
       </c>
       <c r="F1818" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1818" s="8" t="s">
         <v>279</v>
@@ -66343,7 +66319,7 @@
     </row>
     <row r="1819" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1819" s="3" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="B1819" s="3" t="s">
         <v>459</v>
@@ -66358,7 +66334,7 @@
         <v>127</v>
       </c>
       <c r="F1819" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1819" s="8" t="s">
         <v>279</v>
@@ -66377,7 +66353,7 @@
     </row>
     <row r="1820" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1820" s="3" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="B1820" s="3" t="s">
         <v>271</v>
@@ -66392,7 +66368,7 @@
         <v>127</v>
       </c>
       <c r="F1820" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1820" s="8" t="s">
         <v>279</v>
@@ -66411,7 +66387,7 @@
     </row>
     <row r="1821" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1821" s="3" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="B1821" s="3" t="s">
         <v>302</v>
@@ -66426,7 +66402,7 @@
         <v>127</v>
       </c>
       <c r="F1821" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1821" s="8" t="s">
         <v>279</v>
@@ -66445,7 +66421,7 @@
     </row>
     <row r="1822" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1822" s="3" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="B1822" s="3" t="s">
         <v>288</v>
@@ -66460,7 +66436,7 @@
         <v>127</v>
       </c>
       <c r="F1822" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1822" s="8" t="s">
         <v>279</v>
@@ -66479,7 +66455,7 @@
     </row>
     <row r="1823" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1823" s="3" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="B1823" s="3" t="s">
         <v>124</v>
@@ -66494,7 +66470,7 @@
         <v>127</v>
       </c>
       <c r="F1823" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1823" s="8" t="s">
         <v>279</v>
@@ -66513,7 +66489,7 @@
     </row>
     <row r="1824" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1824" s="3" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="B1824" s="3" t="s">
         <v>135</v>
@@ -66528,7 +66504,7 @@
         <v>127</v>
       </c>
       <c r="F1824" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1824" s="8" t="s">
         <v>279</v>
@@ -66547,7 +66523,7 @@
     </row>
     <row r="1825" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1825" s="3" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="B1825" s="3" t="s">
         <v>271</v>
@@ -66562,7 +66538,7 @@
         <v>127</v>
       </c>
       <c r="F1825" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1825" s="8" t="s">
         <v>279</v>
@@ -66581,7 +66557,7 @@
     </row>
     <row r="1826" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1826" s="3" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="B1826" s="3" t="s">
         <v>149</v>
@@ -66596,7 +66572,7 @@
         <v>127</v>
       </c>
       <c r="F1826" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1826" s="8" t="s">
         <v>279</v>
@@ -66615,7 +66591,7 @@
     </row>
     <row r="1827" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1827" s="3" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="B1827" s="3" t="s">
         <v>387</v>
@@ -66630,7 +66606,7 @@
         <v>127</v>
       </c>
       <c r="F1827" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1827" s="8" t="s">
         <v>279</v>
@@ -66649,7 +66625,7 @@
     </row>
     <row r="1828" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1828" s="3" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="B1828" s="3" t="s">
         <v>302</v>
@@ -66664,7 +66640,7 @@
         <v>127</v>
       </c>
       <c r="F1828" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1828" s="8" t="s">
         <v>279</v>
@@ -66683,7 +66659,7 @@
     </row>
     <row r="1829" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1829" s="3" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B1829" s="3" t="s">
         <v>200</v>
@@ -66698,7 +66674,7 @@
         <v>127</v>
       </c>
       <c r="F1829" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1829" s="8" t="s">
         <v>279</v>
@@ -66717,7 +66693,7 @@
     </row>
     <row r="1830" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1830" s="3" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B1830" s="3" t="s">
         <v>459</v>
@@ -66732,7 +66708,7 @@
         <v>127</v>
       </c>
       <c r="F1830" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1830" s="8" t="s">
         <v>279</v>
@@ -66751,7 +66727,7 @@
     </row>
     <row r="1831" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1831" s="3" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B1831" s="3" t="s">
         <v>174</v>
@@ -66766,7 +66742,7 @@
         <v>127</v>
       </c>
       <c r="F1831" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1831" s="8" t="s">
         <v>279</v>
@@ -66785,7 +66761,7 @@
     </row>
     <row r="1832" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1832" s="3" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="B1832" s="3" t="s">
         <v>333</v>
@@ -66800,7 +66776,7 @@
         <v>127</v>
       </c>
       <c r="F1832" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1832" s="8" t="s">
         <v>279</v>
@@ -66819,7 +66795,7 @@
     </row>
     <row r="1833" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1833" s="3" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="B1833" s="3" t="s">
         <v>174</v>
@@ -66834,7 +66810,7 @@
         <v>127</v>
       </c>
       <c r="F1833" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1833" s="8" t="s">
         <v>279</v>
@@ -66853,7 +66829,7 @@
     </row>
     <row r="1834" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1834" s="3" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="B1834" s="3" t="s">
         <v>138</v>
@@ -66868,7 +66844,7 @@
         <v>127</v>
       </c>
       <c r="F1834" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1834" s="8" t="s">
         <v>279</v>
@@ -66887,7 +66863,7 @@
     </row>
     <row r="1835" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1835" s="3" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="B1835" s="3" t="s">
         <v>327</v>
@@ -66902,7 +66878,7 @@
         <v>127</v>
       </c>
       <c r="F1835" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1835" s="8" t="s">
         <v>279</v>
@@ -66921,7 +66897,7 @@
     </row>
     <row r="1836" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1836" s="3" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="B1836" s="3" t="s">
         <v>788</v>
@@ -66936,7 +66912,7 @@
         <v>127</v>
       </c>
       <c r="F1836" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1836" s="8" t="s">
         <v>279</v>
@@ -66955,7 +66931,7 @@
     </row>
     <row r="1837" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1837" s="3" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="B1837" s="3" t="s">
         <v>387</v>
@@ -66970,7 +66946,7 @@
         <v>127</v>
       </c>
       <c r="F1837" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1837" s="8" t="s">
         <v>279</v>
@@ -66989,7 +66965,7 @@
     </row>
     <row r="1838" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1838" s="3" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="B1838" s="3" t="s">
         <v>788</v>
@@ -67004,7 +66980,7 @@
         <v>127</v>
       </c>
       <c r="F1838" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1838" s="8" t="s">
         <v>279</v>
@@ -67023,7 +66999,7 @@
     </row>
     <row r="1839" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1839" s="3" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="B1839" s="3" t="s">
         <v>285</v>
@@ -67038,7 +67014,7 @@
         <v>127</v>
       </c>
       <c r="F1839" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1839" s="8" t="s">
         <v>279</v>
@@ -67057,7 +67033,7 @@
     </row>
     <row r="1840" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1840" s="3" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="B1840" s="3" t="s">
         <v>248</v>
@@ -67072,7 +67048,7 @@
         <v>127</v>
       </c>
       <c r="F1840" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1840" s="8" t="s">
         <v>279</v>
@@ -67091,7 +67067,7 @@
     </row>
     <row r="1841" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1841" s="3" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="B1841" s="3" t="s">
         <v>154</v>
@@ -67106,7 +67082,7 @@
         <v>127</v>
       </c>
       <c r="F1841" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1841" s="8" t="s">
         <v>279</v>
@@ -67125,7 +67101,7 @@
     </row>
     <row r="1842" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1842" s="3" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="B1842" s="3" t="s">
         <v>154</v>
@@ -67140,7 +67116,7 @@
         <v>127</v>
       </c>
       <c r="F1842" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1842" s="8" t="s">
         <v>279</v>
@@ -67159,7 +67135,7 @@
     </row>
     <row r="1843" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1843" s="3" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B1843" s="3" t="s">
         <v>161</v>
@@ -67174,7 +67150,7 @@
         <v>127</v>
       </c>
       <c r="F1843" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1843" s="8" t="s">
         <v>279</v>
@@ -67193,7 +67169,7 @@
     </row>
     <row r="1844" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1844" s="3" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B1844" s="3" t="s">
         <v>174</v>
@@ -67208,7 +67184,7 @@
         <v>127</v>
       </c>
       <c r="F1844" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1844" s="8" t="s">
         <v>279</v>
@@ -67227,7 +67203,7 @@
     </row>
     <row r="1845" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1845" s="3" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B1845" s="3" t="s">
         <v>363</v>
@@ -67242,7 +67218,7 @@
         <v>127</v>
       </c>
       <c r="F1845" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1845" s="8" t="s">
         <v>279</v>
@@ -67261,7 +67237,7 @@
     </row>
     <row r="1846" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1846" s="3" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="B1846" s="3" t="s">
         <v>132</v>
@@ -67276,7 +67252,7 @@
         <v>127</v>
       </c>
       <c r="F1846" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1846" s="8" t="s">
         <v>279</v>
@@ -67295,7 +67271,7 @@
     </row>
     <row r="1847" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1847" s="3" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="B1847" s="3" t="s">
         <v>123</v>
@@ -67310,7 +67286,7 @@
         <v>127</v>
       </c>
       <c r="F1847" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1847" s="8" t="s">
         <v>279</v>
@@ -67329,7 +67305,7 @@
     </row>
     <row r="1848" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1848" s="3" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="B1848" s="3" t="s">
         <v>174</v>
@@ -67344,7 +67320,7 @@
         <v>127</v>
       </c>
       <c r="F1848" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1848" s="8" t="s">
         <v>279</v>
@@ -67363,7 +67339,7 @@
     </row>
     <row r="1849" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1849" s="3" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="B1849" s="3" t="s">
         <v>160</v>
@@ -67378,7 +67354,7 @@
         <v>127</v>
       </c>
       <c r="F1849" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1849" s="8" t="s">
         <v>279</v>
@@ -67397,7 +67373,7 @@
     </row>
     <row r="1850" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1850" s="3" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="B1850" s="3" t="s">
         <v>123</v>
@@ -67409,10 +67385,10 @@
         <v>144</v>
       </c>
       <c r="E1850" s="3" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F1850" s="3" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="G1850" s="8" t="s">
         <v>279</v>
@@ -67431,7 +67407,7 @@
     </row>
     <row r="1851" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1851" s="3" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="B1851" s="3" t="s">
         <v>202</v>
@@ -67446,7 +67422,7 @@
         <v>127</v>
       </c>
       <c r="F1851" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1851" s="8" t="s">
         <v>279</v>
@@ -67465,7 +67441,7 @@
     </row>
     <row r="1852" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1852" s="3" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="B1852" s="3" t="s">
         <v>333</v>
@@ -67480,7 +67456,7 @@
         <v>127</v>
       </c>
       <c r="F1852" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1852" s="8" t="s">
         <v>279</v>
@@ -67499,7 +67475,7 @@
     </row>
     <row r="1853" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1853" s="3" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="B1853" s="3" t="s">
         <v>174</v>
@@ -67514,7 +67490,7 @@
         <v>127</v>
       </c>
       <c r="F1853" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1853" s="8" t="s">
         <v>279</v>
@@ -67533,7 +67509,7 @@
     </row>
     <row r="1854" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1854" s="3" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="B1854" s="3" t="s">
         <v>211</v>
@@ -67548,7 +67524,7 @@
         <v>127</v>
       </c>
       <c r="F1854" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1854" s="8" t="s">
         <v>279</v>
@@ -67567,7 +67543,7 @@
     </row>
     <row r="1855" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1855" s="3" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="B1855" s="3" t="s">
         <v>355</v>
@@ -67582,7 +67558,7 @@
         <v>127</v>
       </c>
       <c r="F1855" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1855" s="8" t="s">
         <v>279</v>
@@ -67601,7 +67577,7 @@
     </row>
     <row r="1856" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1856" s="3" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="B1856" s="3" t="s">
         <v>459</v>
@@ -67616,7 +67592,7 @@
         <v>127</v>
       </c>
       <c r="F1856" s="3" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="G1856" s="8" t="s">
         <v>279</v>
@@ -67635,7 +67611,7 @@
     </row>
     <row r="1857" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1857" s="3" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="B1857" s="3" t="s">
         <v>119</v>
@@ -67650,7 +67626,7 @@
         <v>127</v>
       </c>
       <c r="F1857" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1857" s="8" t="s">
         <v>279</v>
@@ -67669,7 +67645,7 @@
     </row>
     <row r="1858" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1858" s="3" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="B1858" s="3" t="s">
         <v>267</v>
@@ -67684,7 +67660,7 @@
         <v>127</v>
       </c>
       <c r="F1858" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1858" s="8" t="s">
         <v>279</v>
@@ -67703,7 +67679,7 @@
     </row>
     <row r="1859" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1859" s="3" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="B1859" s="3" t="s">
         <v>134</v>
@@ -67718,7 +67694,7 @@
         <v>127</v>
       </c>
       <c r="F1859" s="3" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="G1859" s="8" t="s">
         <v>279</v>
@@ -67737,7 +67713,7 @@
     </row>
     <row r="1860" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1860" s="3" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="B1860" s="3" t="s">
         <v>138</v>
@@ -67752,7 +67728,7 @@
         <v>127</v>
       </c>
       <c r="F1860" s="3" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="G1860" s="8" t="s">
         <v>279</v>
@@ -67771,7 +67747,7 @@
     </row>
     <row r="1861" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1861" s="3" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="B1861" s="3" t="s">
         <v>196</v>
@@ -67786,7 +67762,7 @@
         <v>127</v>
       </c>
       <c r="F1861" s="3" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="G1861" s="8" t="s">
         <v>279</v>
@@ -67805,7 +67781,7 @@
     </row>
     <row r="1862" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1862" s="3" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="B1862" s="3" t="s">
         <v>304</v>
@@ -67820,7 +67796,7 @@
         <v>127</v>
       </c>
       <c r="F1862" s="3" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="G1862" s="8" t="s">
         <v>279</v>
@@ -67839,7 +67815,7 @@
     </row>
     <row r="1863" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1863" s="3" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="B1863" s="3" t="s">
         <v>183</v>
@@ -67854,7 +67830,7 @@
         <v>127</v>
       </c>
       <c r="F1863" s="3" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="G1863" s="8" t="s">
         <v>279</v>
@@ -67873,7 +67849,7 @@
     </row>
     <row r="1864" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1864" s="3" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="B1864" s="3" t="s">
         <v>207</v>
@@ -67888,7 +67864,7 @@
         <v>127</v>
       </c>
       <c r="F1864" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1864" s="8" t="s">
         <v>279</v>
@@ -67907,7 +67883,7 @@
     </row>
     <row r="1865" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1865" s="3" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="B1865" s="3" t="s">
         <v>124</v>
@@ -67922,7 +67898,7 @@
         <v>127</v>
       </c>
       <c r="F1865" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1865" s="8" t="s">
         <v>279</v>
@@ -67941,7 +67917,7 @@
     </row>
     <row r="1866" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1866" s="3" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="B1866" s="3" t="s">
         <v>204</v>
@@ -67956,7 +67932,7 @@
         <v>127</v>
       </c>
       <c r="F1866" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1866" s="8" t="s">
         <v>279</v>
@@ -67975,7 +67951,7 @@
     </row>
     <row r="1867" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1867" s="3" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="B1867" s="3" t="s">
         <v>333</v>
@@ -67990,7 +67966,7 @@
         <v>127</v>
       </c>
       <c r="F1867" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1867" s="8" t="s">
         <v>279</v>
@@ -68009,7 +67985,7 @@
     </row>
     <row r="1868" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1868" s="3" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="B1868" s="3" t="s">
         <v>233</v>
@@ -68024,7 +68000,7 @@
         <v>127</v>
       </c>
       <c r="F1868" s="3" t="s">
-        <v>1553</v>
+        <v>1619</v>
       </c>
       <c r="G1868" s="8" t="s">
         <v>279</v>
@@ -68043,7 +68019,7 @@
     </row>
     <row r="1869" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1869" s="3" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="B1869" s="3" t="s">
         <v>123</v>
@@ -68058,7 +68034,7 @@
         <v>127</v>
       </c>
       <c r="F1869" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1869" s="8" t="s">
         <v>279</v>
@@ -68077,7 +68053,7 @@
     </row>
     <row r="1870" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1870" s="3" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="B1870" s="3" t="s">
         <v>174</v>
@@ -68092,7 +68068,7 @@
         <v>127</v>
       </c>
       <c r="F1870" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1870" s="8" t="s">
         <v>279</v>
@@ -68111,7 +68087,7 @@
     </row>
     <row r="1871" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1871" s="3" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="B1871" s="3" t="s">
         <v>200</v>
@@ -68126,7 +68102,7 @@
         <v>127</v>
       </c>
       <c r="F1871" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1871" s="8" t="s">
         <v>279</v>
@@ -68145,7 +68121,7 @@
     </row>
     <row r="1872" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1872" s="3" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="B1872" s="3" t="s">
         <v>149</v>
@@ -68160,7 +68136,7 @@
         <v>127</v>
       </c>
       <c r="F1872" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1872" s="8" t="s">
         <v>279</v>
@@ -68179,7 +68155,7 @@
     </row>
     <row r="1873" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1873" s="3" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="B1873" s="3" t="s">
         <v>183</v>
@@ -68194,7 +68170,7 @@
         <v>127</v>
       </c>
       <c r="F1873" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1873" s="8" t="s">
         <v>279</v>
@@ -68213,7 +68189,7 @@
     </row>
     <row r="1874" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1874" s="3" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="B1874" s="3" t="s">
         <v>248</v>
@@ -68228,7 +68204,7 @@
         <v>127</v>
       </c>
       <c r="F1874" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1874" s="8" t="s">
         <v>279</v>
@@ -68247,7 +68223,7 @@
     </row>
     <row r="1875" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1875" s="3" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="B1875" s="3" t="s">
         <v>196</v>
@@ -68262,7 +68238,7 @@
         <v>127</v>
       </c>
       <c r="F1875" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1875" s="8" t="s">
         <v>279</v>
@@ -68281,7 +68257,7 @@
     </row>
     <row r="1876" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1876" s="3" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="B1876" s="3" t="s">
         <v>285</v>
@@ -68296,7 +68272,7 @@
         <v>127</v>
       </c>
       <c r="F1876" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1876" s="8" t="s">
         <v>279</v>
@@ -68315,7 +68291,7 @@
     </row>
     <row r="1877" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1877" s="3" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="B1877" s="3" t="s">
         <v>139</v>
@@ -68330,7 +68306,7 @@
         <v>127</v>
       </c>
       <c r="F1877" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="G1877" s="8" t="s">
         <v>279</v>
@@ -68349,7 +68325,7 @@
     </row>
     <row r="1878" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1878" s="3" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B1878" s="3" t="s">
         <v>171</v>
@@ -68361,10 +68337,10 @@
         <v>184</v>
       </c>
       <c r="E1878" s="3" t="s">
-        <v>140</v>
+        <v>1583</v>
       </c>
       <c r="F1878" s="3" t="s">
-        <v>1580</v>
+        <v>1619</v>
       </c>
       <c r="G1878" s="8" t="s">
         <v>280</v>
@@ -68383,7 +68359,7 @@
     </row>
     <row r="1879" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1879" s="3" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B1879" s="3" t="s">
         <v>157</v>
@@ -68395,10 +68371,10 @@
         <v>115</v>
       </c>
       <c r="E1879" s="3" t="s">
-        <v>140</v>
+        <v>1583</v>
       </c>
       <c r="F1879" s="3" t="s">
-        <v>1580</v>
+        <v>1619</v>
       </c>
       <c r="G1879" s="8" t="s">
         <v>280</v>
@@ -68417,7 +68393,7 @@
     </row>
     <row r="1880" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1880" s="3" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B1880" s="3" t="s">
         <v>134</v>
@@ -68429,10 +68405,10 @@
         <v>111</v>
       </c>
       <c r="E1880" s="3" t="s">
-        <v>140</v>
+        <v>1583</v>
       </c>
       <c r="F1880" s="3" t="s">
-        <v>1580</v>
+        <v>1619</v>
       </c>
       <c r="G1880" s="8" t="s">
         <v>280</v>
@@ -68451,7 +68427,7 @@
     </row>
     <row r="1881" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1881" s="3" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B1881" s="3" t="s">
         <v>204</v>
@@ -68463,10 +68439,10 @@
         <v>126</v>
       </c>
       <c r="E1881" s="3" t="s">
-        <v>140</v>
+        <v>1583</v>
       </c>
       <c r="F1881" s="3" t="s">
-        <v>1580</v>
+        <v>1619</v>
       </c>
       <c r="G1881" s="8" t="s">
         <v>280</v>
@@ -68485,7 +68461,7 @@
     </row>
     <row r="1882" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1882" s="3" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="B1882" s="3" t="s">
         <v>123</v>
@@ -68497,10 +68473,10 @@
         <v>144</v>
       </c>
       <c r="E1882" s="3" t="s">
-        <v>140</v>
+        <v>1583</v>
       </c>
       <c r="F1882" s="3" t="s">
-        <v>1582</v>
+        <v>1619</v>
       </c>
       <c r="G1882" s="8" t="s">
         <v>280</v>
@@ -68519,7 +68495,7 @@
     </row>
     <row r="1883" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1883" s="3" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="B1883" s="3" t="s">
         <v>114</v>
@@ -68531,10 +68507,10 @@
         <v>144</v>
       </c>
       <c r="E1883" s="3" t="s">
-        <v>140</v>
+        <v>1583</v>
       </c>
       <c r="F1883" s="3" t="s">
-        <v>1582</v>
+        <v>1619</v>
       </c>
       <c r="G1883" s="8" t="s">
         <v>280</v>
@@ -68553,7 +68529,7 @@
     </row>
     <row r="1884" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1884" s="3" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="B1884" s="3" t="s">
         <v>124</v>
@@ -68562,13 +68538,13 @@
         <v>207</v>
       </c>
       <c r="D1884" s="3" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="E1884" s="3" t="s">
         <v>433</v>
       </c>
       <c r="F1884" s="3" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="G1884" s="8" t="s">
         <v>279</v>
@@ -68587,7 +68563,7 @@
     </row>
     <row r="1885" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1885" s="3" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="B1885" s="3" t="s">
         <v>359</v>
@@ -68602,7 +68578,7 @@
         <v>433</v>
       </c>
       <c r="F1885" s="3" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="G1885" s="8" t="s">
         <v>279</v>
@@ -68621,7 +68597,7 @@
     </row>
     <row r="1886" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1886" s="3" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="B1886" s="3" t="s">
         <v>196</v>
@@ -68636,7 +68612,7 @@
         <v>433</v>
       </c>
       <c r="F1886" s="3" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="G1886" s="8" t="s">
         <v>279</v>
@@ -68655,7 +68631,7 @@
     </row>
     <row r="1887" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1887" s="3" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="B1887" s="3" t="s">
         <v>353</v>
@@ -68670,7 +68646,7 @@
         <v>433</v>
       </c>
       <c r="F1887" s="3" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="G1887" s="8" t="s">
         <v>279</v>
@@ -68689,7 +68665,7 @@
     </row>
     <row r="1888" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1888" s="3" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="B1888" s="3" t="s">
         <v>139</v>
@@ -68704,7 +68680,7 @@
         <v>433</v>
       </c>
       <c r="F1888" s="3" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="G1888" s="8" t="s">
         <v>279</v>
@@ -68723,7 +68699,7 @@
     </row>
     <row r="1889" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1889" s="3" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B1889" s="3" t="s">
         <v>133</v>
@@ -68738,7 +68714,7 @@
         <v>433</v>
       </c>
       <c r="F1889" s="3" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="G1889" s="8" t="s">
         <v>279</v>
@@ -68757,7 +68733,7 @@
     </row>
     <row r="1890" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1890" s="3" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B1890" s="3" t="s">
         <v>123</v>
@@ -68772,7 +68748,7 @@
         <v>433</v>
       </c>
       <c r="F1890" s="3" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="G1890" s="8" t="s">
         <v>279</v>
@@ -68791,7 +68767,7 @@
     </row>
     <row r="1891" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1891" s="3" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B1891" s="3" t="s">
         <v>149</v>
@@ -68803,10 +68779,10 @@
         <v>105</v>
       </c>
       <c r="E1891" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1891" s="3" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
       <c r="G1891" s="8" t="s">
         <v>279</v>
@@ -68825,7 +68801,7 @@
     </row>
     <row r="1892" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1892" s="3" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B1892" s="3" t="s">
         <v>150</v>
@@ -68840,7 +68816,7 @@
         <v>155</v>
       </c>
       <c r="F1892" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1892" s="8" t="s">
         <v>279</v>
@@ -68859,7 +68835,7 @@
     </row>
     <row r="1893" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1893" s="3" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B1893" s="3" t="s">
         <v>114</v>
@@ -68874,7 +68850,7 @@
         <v>155</v>
       </c>
       <c r="F1893" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1893" s="8" t="s">
         <v>279</v>
@@ -68893,7 +68869,7 @@
     </row>
     <row r="1894" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1894" s="3" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B1894" s="3" t="s">
         <v>139</v>
@@ -68908,7 +68884,7 @@
         <v>155</v>
       </c>
       <c r="F1894" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1894" s="8" t="s">
         <v>279</v>
@@ -68927,7 +68903,7 @@
     </row>
     <row r="1895" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1895" s="3" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="B1895" s="3" t="s">
         <v>336</v>
@@ -68942,7 +68918,7 @@
         <v>155</v>
       </c>
       <c r="F1895" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1895" s="8" t="s">
         <v>279</v>
@@ -68961,7 +68937,7 @@
     </row>
     <row r="1896" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1896" s="3" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="B1896" s="3" t="s">
         <v>233</v>
@@ -68976,7 +68952,7 @@
         <v>155</v>
       </c>
       <c r="F1896" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1896" s="8" t="s">
         <v>279</v>
@@ -68995,7 +68971,7 @@
     </row>
     <row r="1897" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1897" s="3" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="B1897" s="3" t="s">
         <v>134</v>
@@ -69010,7 +68986,7 @@
         <v>140</v>
       </c>
       <c r="F1897" s="3" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="G1897" s="8" t="s">
         <v>280</v>
@@ -69029,7 +69005,7 @@
     </row>
     <row r="1898" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1898" s="3" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="B1898" s="3" t="s">
         <v>123</v>
@@ -69044,7 +69020,7 @@
         <v>155</v>
       </c>
       <c r="F1898" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1898" s="8" t="s">
         <v>279</v>
@@ -69063,7 +69039,7 @@
     </row>
     <row r="1899" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1899" s="3" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="B1899" s="3" t="s">
         <v>285</v>
@@ -69078,7 +69054,7 @@
         <v>155</v>
       </c>
       <c r="F1899" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1899" s="8" t="s">
         <v>279</v>
@@ -69097,7 +69073,7 @@
     </row>
     <row r="1900" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1900" s="3" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="B1900" s="3" t="s">
         <v>311</v>
@@ -69129,7 +69105,7 @@
     </row>
     <row r="1901" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1901" s="3" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="B1901" s="3" t="s">
         <v>157</v>
@@ -69144,7 +69120,7 @@
         <v>155</v>
       </c>
       <c r="F1901" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1901" s="8" t="s">
         <v>279</v>
@@ -69163,7 +69139,7 @@
     </row>
     <row r="1902" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1902" s="3" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="B1902" s="3" t="s">
         <v>114</v>
@@ -69178,7 +69154,7 @@
         <v>155</v>
       </c>
       <c r="F1902" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1902" s="8" t="s">
         <v>279</v>
@@ -69197,7 +69173,7 @@
     </row>
     <row r="1903" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1903" s="3" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="B1903" s="3" t="s">
         <v>248</v>
@@ -69212,7 +69188,7 @@
         <v>155</v>
       </c>
       <c r="F1903" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1903" s="8" t="s">
         <v>279</v>
@@ -69231,7 +69207,7 @@
     </row>
     <row r="1904" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1904" s="3" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="B1904" s="3" t="s">
         <v>149</v>
@@ -69246,7 +69222,7 @@
         <v>155</v>
       </c>
       <c r="F1904" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1904" s="8" t="s">
         <v>279</v>
@@ -69265,7 +69241,7 @@
     </row>
     <row r="1905" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1905" s="3" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="B1905" s="3" t="s">
         <v>124</v>
@@ -69280,7 +69256,7 @@
         <v>155</v>
       </c>
       <c r="F1905" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1905" s="8" t="s">
         <v>279</v>
@@ -69299,7 +69275,7 @@
     </row>
     <row r="1906" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1906" s="3" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="B1906" s="3" t="s">
         <v>161</v>
@@ -69314,7 +69290,7 @@
         <v>155</v>
       </c>
       <c r="F1906" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1906" s="8" t="s">
         <v>279</v>
@@ -69333,7 +69309,7 @@
     </row>
     <row r="1907" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1907" s="3" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="B1907" s="3" t="s">
         <v>285</v>
@@ -69348,7 +69324,7 @@
         <v>155</v>
       </c>
       <c r="F1907" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1907" s="8" t="s">
         <v>279</v>
@@ -69367,7 +69343,7 @@
     </row>
     <row r="1908" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1908" s="3" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="B1908" s="3" t="s">
         <v>211</v>
@@ -69382,7 +69358,7 @@
         <v>155</v>
       </c>
       <c r="F1908" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1908" s="8" t="s">
         <v>279</v>
@@ -69401,7 +69377,7 @@
     </row>
     <row r="1909" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1909" s="3" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="B1909" s="3" t="s">
         <v>200</v>
@@ -69416,7 +69392,7 @@
         <v>155</v>
       </c>
       <c r="F1909" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1909" s="8" t="s">
         <v>279</v>
@@ -69435,7 +69411,7 @@
     </row>
     <row r="1910" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1910" s="3" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="B1910" s="3" t="s">
         <v>210</v>
@@ -69450,7 +69426,7 @@
         <v>155</v>
       </c>
       <c r="F1910" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1910" s="8" t="s">
         <v>279</v>
@@ -69469,7 +69445,7 @@
     </row>
     <row r="1911" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1911" s="3" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="B1911" s="3" t="s">
         <v>174</v>
@@ -69484,7 +69460,7 @@
         <v>155</v>
       </c>
       <c r="F1911" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1911" s="8" t="s">
         <v>279</v>
@@ -69503,7 +69479,7 @@
     </row>
     <row r="1912" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1912" s="3" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="B1912" s="3" t="s">
         <v>271</v>
@@ -69518,7 +69494,7 @@
         <v>155</v>
       </c>
       <c r="F1912" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1912" s="8" t="s">
         <v>279</v>
@@ -69537,7 +69513,7 @@
     </row>
     <row r="1913" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1913" s="3" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="B1913" s="3" t="s">
         <v>122</v>
@@ -69552,7 +69528,7 @@
         <v>155</v>
       </c>
       <c r="F1913" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1913" s="8" t="s">
         <v>279</v>
@@ -69571,7 +69547,7 @@
     </row>
     <row r="1914" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1914" s="3" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="B1914" s="3" t="s">
         <v>124</v>
@@ -69586,7 +69562,7 @@
         <v>155</v>
       </c>
       <c r="F1914" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1914" s="8" t="s">
         <v>279</v>
@@ -69605,7 +69581,7 @@
     </row>
     <row r="1915" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1915" s="3" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="B1915" s="3" t="s">
         <v>207</v>
@@ -69620,7 +69596,7 @@
         <v>155</v>
       </c>
       <c r="F1915" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1915" s="8" t="s">
         <v>279</v>
@@ -69639,7 +69615,7 @@
     </row>
     <row r="1916" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1916" s="3" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="B1916" s="3" t="s">
         <v>340</v>
@@ -69654,7 +69630,7 @@
         <v>155</v>
       </c>
       <c r="F1916" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1916" s="8" t="s">
         <v>279</v>
@@ -69673,7 +69649,7 @@
     </row>
     <row r="1917" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1917" s="3" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="B1917" s="3" t="s">
         <v>233</v>
@@ -69688,7 +69664,7 @@
         <v>155</v>
       </c>
       <c r="F1917" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1917" s="8" t="s">
         <v>279</v>
@@ -69707,7 +69683,7 @@
     </row>
     <row r="1918" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1918" s="3" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="B1918" s="3" t="s">
         <v>271</v>
@@ -69722,7 +69698,7 @@
         <v>155</v>
       </c>
       <c r="F1918" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1918" s="8" t="s">
         <v>279</v>
@@ -69741,7 +69717,7 @@
     </row>
     <row r="1919" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1919" s="3" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="B1919" s="3" t="s">
         <v>248</v>
@@ -69756,7 +69732,7 @@
         <v>155</v>
       </c>
       <c r="F1919" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1919" s="8" t="s">
         <v>279</v>
@@ -69775,7 +69751,7 @@
     </row>
     <row r="1920" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1920" s="3" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="B1920" s="3" t="s">
         <v>219</v>
@@ -69790,7 +69766,7 @@
         <v>155</v>
       </c>
       <c r="F1920" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1920" s="8" t="s">
         <v>279</v>
@@ -69809,7 +69785,7 @@
     </row>
     <row r="1921" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1921" s="3" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="B1921" s="3" t="s">
         <v>248</v>
@@ -69824,7 +69800,7 @@
         <v>155</v>
       </c>
       <c r="F1921" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1921" s="8" t="s">
         <v>279</v>
@@ -69843,7 +69819,7 @@
     </row>
     <row r="1922" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1922" s="3" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="B1922" s="3" t="s">
         <v>149</v>
@@ -69858,7 +69834,7 @@
         <v>155</v>
       </c>
       <c r="F1922" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1922" s="8" t="s">
         <v>279</v>
@@ -69877,7 +69853,7 @@
     </row>
     <row r="1923" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1923" s="3" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="B1923" s="3" t="s">
         <v>132</v>
@@ -69892,7 +69868,7 @@
         <v>155</v>
       </c>
       <c r="F1923" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1923" s="8" t="s">
         <v>279</v>
@@ -69911,7 +69887,7 @@
     </row>
     <row r="1924" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1924" s="3" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="B1924" s="3" t="s">
         <v>327</v>
@@ -69926,7 +69902,7 @@
         <v>155</v>
       </c>
       <c r="F1924" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1924" s="8" t="s">
         <v>279</v>
@@ -69945,7 +69921,7 @@
     </row>
     <row r="1925" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1925" s="3" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="B1925" s="3" t="s">
         <v>355</v>
@@ -69954,13 +69930,13 @@
         <v>113</v>
       </c>
       <c r="D1925" s="3" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="E1925" s="3" t="s">
         <v>155</v>
       </c>
       <c r="F1925" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1925" s="8" t="s">
         <v>279</v>
@@ -69979,7 +69955,7 @@
     </row>
     <row r="1926" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1926" s="3" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="B1926" s="3" t="s">
         <v>124</v>
@@ -69994,7 +69970,7 @@
         <v>155</v>
       </c>
       <c r="F1926" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1926" s="8" t="s">
         <v>279</v>
@@ -70013,7 +69989,7 @@
     </row>
     <row r="1927" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1927" s="3" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="B1927" s="3" t="s">
         <v>241</v>
@@ -70028,7 +70004,7 @@
         <v>155</v>
       </c>
       <c r="F1927" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1927" s="8" t="s">
         <v>279</v>
@@ -70047,7 +70023,7 @@
     </row>
     <row r="1928" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1928" s="3" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="B1928" s="3" t="s">
         <v>285</v>
@@ -70062,7 +70038,7 @@
         <v>155</v>
       </c>
       <c r="F1928" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1928" s="8" t="s">
         <v>279</v>
@@ -70081,7 +70057,7 @@
     </row>
     <row r="1929" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1929" s="3" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="B1929" s="3" t="s">
         <v>359</v>
@@ -70096,7 +70072,7 @@
         <v>155</v>
       </c>
       <c r="F1929" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1929" s="8" t="s">
         <v>279</v>
@@ -70115,7 +70091,7 @@
     </row>
     <row r="1930" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1930" s="3" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="B1930" s="3" t="s">
         <v>340</v>
@@ -70130,7 +70106,7 @@
         <v>155</v>
       </c>
       <c r="F1930" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1930" s="8" t="s">
         <v>279</v>
@@ -70149,7 +70125,7 @@
     </row>
     <row r="1931" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1931" s="3" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="B1931" s="3" t="s">
         <v>285</v>
@@ -70164,7 +70140,7 @@
         <v>155</v>
       </c>
       <c r="F1931" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1931" s="8" t="s">
         <v>279</v>
@@ -70183,7 +70159,7 @@
     </row>
     <row r="1932" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1932" s="3" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="B1932" s="3" t="s">
         <v>359</v>
@@ -70198,7 +70174,7 @@
         <v>155</v>
       </c>
       <c r="F1932" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1932" s="8" t="s">
         <v>279</v>
@@ -70217,7 +70193,7 @@
     </row>
     <row r="1933" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1933" s="3" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="B1933" s="3" t="s">
         <v>333</v>
@@ -70229,10 +70205,10 @@
         <v>144</v>
       </c>
       <c r="E1933" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1933" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1933" s="8" t="s">
         <v>279</v>
@@ -70251,7 +70227,7 @@
     </row>
     <row r="1934" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1934" s="3" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="B1934" s="3" t="s">
         <v>183</v>
@@ -70263,10 +70239,10 @@
         <v>220</v>
       </c>
       <c r="E1934" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1934" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1934" s="8" t="s">
         <v>279</v>
@@ -70285,7 +70261,7 @@
     </row>
     <row r="1935" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1935" s="3" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="B1935" s="3" t="s">
         <v>387</v>
@@ -70297,10 +70273,10 @@
         <v>105</v>
       </c>
       <c r="E1935" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1935" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1935" s="8" t="s">
         <v>279</v>
@@ -70319,7 +70295,7 @@
     </row>
     <row r="1936" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1936" s="3" t="s">
-        <v>1616</v>
+        <v>1607</v>
       </c>
       <c r="B1936" s="3" t="s">
         <v>114</v>
@@ -70331,10 +70307,10 @@
         <v>105</v>
       </c>
       <c r="E1936" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1936" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1936" s="8" t="s">
         <v>279</v>
@@ -70353,7 +70329,7 @@
     </row>
     <row r="1937" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1937" s="3" t="s">
-        <v>1616</v>
+        <v>1607</v>
       </c>
       <c r="B1937" s="3" t="s">
         <v>124</v>
@@ -70365,10 +70341,10 @@
         <v>184</v>
       </c>
       <c r="E1937" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1937" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1937" s="8" t="s">
         <v>279</v>
@@ -70387,7 +70363,7 @@
     </row>
     <row r="1938" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1938" s="3" t="s">
-        <v>1617</v>
+        <v>1608</v>
       </c>
       <c r="B1938" s="3" t="s">
         <v>219</v>
@@ -70399,10 +70375,10 @@
         <v>193</v>
       </c>
       <c r="E1938" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1938" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1938" s="8" t="s">
         <v>279</v>
@@ -70421,7 +70397,7 @@
     </row>
     <row r="1939" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1939" s="3" t="s">
-        <v>1617</v>
+        <v>1608</v>
       </c>
       <c r="B1939" s="3" t="s">
         <v>174</v>
@@ -70433,10 +70409,10 @@
         <v>105</v>
       </c>
       <c r="E1939" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1939" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1939" s="8" t="s">
         <v>279</v>
@@ -70455,7 +70431,7 @@
     </row>
     <row r="1940" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1940" s="3" t="s">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="B1940" s="3" t="s">
         <v>359</v>
@@ -70470,7 +70446,7 @@
         <v>155</v>
       </c>
       <c r="F1940" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1940" s="8" t="s">
         <v>279</v>
@@ -70489,7 +70465,7 @@
     </row>
     <row r="1941" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1941" s="3" t="s">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="B1941" s="3" t="s">
         <v>192</v>
@@ -70504,7 +70480,7 @@
         <v>155</v>
       </c>
       <c r="F1941" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1941" s="8" t="s">
         <v>279</v>
@@ -70523,7 +70499,7 @@
     </row>
     <row r="1942" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1942" s="3" t="s">
-        <v>1618</v>
+        <v>1609</v>
       </c>
       <c r="B1942" s="3" t="s">
         <v>135</v>
@@ -70538,7 +70514,7 @@
         <v>155</v>
       </c>
       <c r="F1942" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1942" s="8" t="s">
         <v>279</v>
@@ -70557,7 +70533,7 @@
     </row>
     <row r="1943" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1943" s="3" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="B1943" s="3" t="s">
         <v>248</v>
@@ -70572,7 +70548,7 @@
         <v>155</v>
       </c>
       <c r="F1943" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1943" s="8" t="s">
         <v>279</v>
@@ -70591,7 +70567,7 @@
     </row>
     <row r="1944" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1944" s="3" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="B1944" s="3" t="s">
         <v>149</v>
@@ -70606,7 +70582,7 @@
         <v>155</v>
       </c>
       <c r="F1944" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1944" s="8" t="s">
         <v>279</v>
@@ -70625,7 +70601,7 @@
     </row>
     <row r="1945" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1945" s="3" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="B1945" s="3" t="s">
         <v>114</v>
@@ -70640,7 +70616,7 @@
         <v>155</v>
       </c>
       <c r="F1945" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1945" s="8" t="s">
         <v>279</v>
@@ -70659,7 +70635,7 @@
     </row>
     <row r="1946" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1946" s="3" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
       <c r="B1946" s="3" t="s">
         <v>248</v>
@@ -70674,7 +70650,7 @@
         <v>155</v>
       </c>
       <c r="F1946" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1946" s="8" t="s">
         <v>279</v>
@@ -70693,7 +70669,7 @@
     </row>
     <row r="1947" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1947" s="3" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
       <c r="B1947" s="3" t="s">
         <v>219</v>
@@ -70708,7 +70684,7 @@
         <v>155</v>
       </c>
       <c r="F1947" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1947" s="8" t="s">
         <v>279</v>
@@ -70727,7 +70703,7 @@
     </row>
     <row r="1948" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1948" s="3" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
       <c r="B1948" s="3" t="s">
         <v>138</v>
@@ -70742,7 +70718,7 @@
         <v>155</v>
       </c>
       <c r="F1948" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1948" s="8" t="s">
         <v>279</v>
@@ -70761,7 +70737,7 @@
     </row>
     <row r="1949" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1949" s="3" t="s">
-        <v>1621</v>
+        <v>1612</v>
       </c>
       <c r="B1949" s="3" t="s">
         <v>242</v>
@@ -70793,7 +70769,7 @@
     </row>
     <row r="1950" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1950" s="3" t="s">
-        <v>1621</v>
+        <v>1612</v>
       </c>
       <c r="B1950" s="3" t="s">
         <v>124</v>
@@ -70825,7 +70801,7 @@
     </row>
     <row r="1951" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1951" s="3" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="B1951" s="3" t="s">
         <v>180</v>
@@ -70857,7 +70833,7 @@
     </row>
     <row r="1952" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1952" s="3" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="B1952" s="3" t="s">
         <v>122</v>
@@ -70872,7 +70848,7 @@
         <v>155</v>
       </c>
       <c r="F1952" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1952" s="8" t="s">
         <v>279</v>
@@ -70891,7 +70867,7 @@
     </row>
     <row r="1953" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1953" s="3" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="B1953" s="3" t="s">
         <v>219</v>
@@ -70906,7 +70882,7 @@
         <v>155</v>
       </c>
       <c r="F1953" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1953" s="8" t="s">
         <v>279</v>
@@ -70925,7 +70901,7 @@
     </row>
     <row r="1954" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1954" s="3" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="B1954" s="3" t="s">
         <v>233</v>
@@ -70940,7 +70916,7 @@
         <v>155</v>
       </c>
       <c r="F1954" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1954" s="8" t="s">
         <v>279</v>
@@ -70959,7 +70935,7 @@
     </row>
     <row r="1955" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1955" s="3" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="B1955" s="3" t="s">
         <v>355</v>
@@ -70974,7 +70950,7 @@
         <v>155</v>
       </c>
       <c r="F1955" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1955" s="8" t="s">
         <v>279</v>
@@ -70993,7 +70969,7 @@
     </row>
     <row r="1956" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1956" s="3" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="B1956" s="3" t="s">
         <v>233</v>
@@ -71008,7 +70984,7 @@
         <v>155</v>
       </c>
       <c r="F1956" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1956" s="8" t="s">
         <v>279</v>
@@ -71027,7 +71003,7 @@
     </row>
     <row r="1957" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1957" s="3" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="B1957" s="3" t="s">
         <v>133</v>
@@ -71042,7 +71018,7 @@
         <v>155</v>
       </c>
       <c r="F1957" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1957" s="8" t="s">
         <v>279</v>
@@ -71061,7 +71037,7 @@
     </row>
     <row r="1958" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1958" s="3" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="B1958" s="3" t="s">
         <v>203</v>
@@ -71076,7 +71052,7 @@
         <v>155</v>
       </c>
       <c r="F1958" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1958" s="8" t="s">
         <v>279</v>
@@ -71095,7 +71071,7 @@
     </row>
     <row r="1959" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1959" s="3" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="B1959" s="3" t="s">
         <v>154</v>
@@ -71110,7 +71086,7 @@
         <v>155</v>
       </c>
       <c r="F1959" s="3" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="G1959" s="8" t="s">
         <v>279</v>
@@ -71129,7 +71105,7 @@
     </row>
     <row r="1960" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1960" s="3" t="s">
-        <v>1626</v>
+        <v>1617</v>
       </c>
       <c r="B1960" s="3" t="s">
         <v>248</v>
@@ -71141,10 +71117,10 @@
         <v>184</v>
       </c>
       <c r="E1960" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1960" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1960" s="8" t="s">
         <v>279</v>
@@ -71163,7 +71139,7 @@
     </row>
     <row r="1961" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1961" s="3" t="s">
-        <v>1627</v>
+        <v>1618</v>
       </c>
       <c r="B1961" s="3" t="s">
         <v>248</v>
@@ -71175,10 +71151,10 @@
         <v>184</v>
       </c>
       <c r="E1961" s="3" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F1961" s="3" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="G1961" s="8" t="s">
         <v>279</v>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15285" uniqueCount="1620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15469" uniqueCount="1628">
   <si>
     <t>Year</t>
   </si>
@@ -4885,6 +4885,30 @@
   </si>
   <si>
     <t>nwbuilders v1.0.0</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
   </si>
 </sst>
 </file>
@@ -5293,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1998"/>
+  <dimension ref="A1:J2019"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -71163,289 +71187,795 @@
         <v>280</v>
       </c>
       <c r="I1961" s="4">
-        <f t="shared" ref="I1961" si="904">YEAR(A1961)</f>
+        <f t="shared" ref="I1961:I1962" si="904">YEAR(A1961)</f>
         <v>2026</v>
       </c>
       <c r="J1961" s="4">
-        <f t="shared" ref="J1961" si="905">MONTH(A1961)</f>
+        <f t="shared" ref="J1961:J1962" si="905">MONTH(A1961)</f>
         <v>3</v>
       </c>
     </row>
     <row r="1962" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1962" s="3"/>
-      <c r="B1962" s="3"/>
-      <c r="C1962" s="3"/>
-      <c r="D1962" s="3"/>
-      <c r="E1962" s="3"/>
-      <c r="F1962" s="3"/>
-      <c r="G1962" s="3"/>
-      <c r="H1962" s="3"/>
-      <c r="I1962" s="4"/>
-      <c r="J1962" s="4"/>
+      <c r="A1962" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1962" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C1962" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1962" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1962" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1962" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1962" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1962" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1962" s="4">
+        <f t="shared" si="904"/>
+        <v>2026</v>
+      </c>
+      <c r="J1962" s="4">
+        <f t="shared" si="905"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1963" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1963" s="3"/>
-      <c r="B1963" s="3"/>
-      <c r="C1963" s="3"/>
-      <c r="D1963" s="3"/>
-      <c r="E1963" s="3"/>
-      <c r="F1963" s="3"/>
-      <c r="G1963" s="3"/>
-      <c r="H1963" s="3"/>
-      <c r="I1963" s="4"/>
-      <c r="J1963" s="4"/>
+      <c r="A1963" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1963" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1963" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1963" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E1963" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1963" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1963" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1963" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1963" s="4">
+        <f t="shared" ref="I1963:I1968" si="906">YEAR(A1963)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1963" s="4">
+        <f t="shared" ref="J1963:J1968" si="907">MONTH(A1963)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1964" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1964" s="3"/>
-      <c r="B1964" s="3"/>
-      <c r="C1964" s="3"/>
-      <c r="D1964" s="3"/>
-      <c r="E1964" s="3"/>
-      <c r="F1964" s="3"/>
-      <c r="G1964" s="3"/>
-      <c r="H1964" s="3"/>
-      <c r="I1964" s="4"/>
-      <c r="J1964" s="4"/>
+      <c r="A1964" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1964" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1964" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1964" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1964" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1964" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1964" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1964" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1964" s="4">
+        <f t="shared" si="906"/>
+        <v>2026</v>
+      </c>
+      <c r="J1964" s="4">
+        <f t="shared" si="907"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1965" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1965" s="3"/>
-      <c r="B1965" s="3"/>
-      <c r="C1965" s="3"/>
-      <c r="D1965" s="3"/>
-      <c r="E1965" s="3"/>
-      <c r="F1965" s="3"/>
-      <c r="G1965" s="3"/>
-      <c r="H1965" s="3"/>
-      <c r="I1965" s="4"/>
-      <c r="J1965" s="4"/>
+      <c r="A1965" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1965" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1965" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1965" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1965" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1965" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1965" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1965" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1965" s="4">
+        <f t="shared" si="906"/>
+        <v>2026</v>
+      </c>
+      <c r="J1965" s="4">
+        <f t="shared" si="907"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1966" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1966" s="3"/>
-      <c r="B1966" s="3"/>
-      <c r="C1966" s="3"/>
-      <c r="D1966" s="3"/>
-      <c r="E1966" s="3"/>
-      <c r="F1966" s="3"/>
-      <c r="G1966" s="3"/>
-      <c r="H1966" s="3"/>
-      <c r="I1966" s="4"/>
-      <c r="J1966" s="4"/>
+      <c r="A1966" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1966" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1966" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1966" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1966" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1966" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1966" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1966" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1966" s="4">
+        <f t="shared" si="906"/>
+        <v>2026</v>
+      </c>
+      <c r="J1966" s="4">
+        <f t="shared" si="907"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1967" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1967" s="3"/>
-      <c r="B1967" s="3"/>
-      <c r="C1967" s="3"/>
-      <c r="D1967" s="3"/>
-      <c r="E1967" s="3"/>
-      <c r="F1967" s="3"/>
-      <c r="G1967" s="3"/>
-      <c r="H1967" s="3"/>
-      <c r="I1967" s="4"/>
-      <c r="J1967" s="4"/>
+      <c r="A1967" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1967" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1967" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1967" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="E1967" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1967" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1967" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1967" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1967" s="4">
+        <f t="shared" si="906"/>
+        <v>2026</v>
+      </c>
+      <c r="J1967" s="4">
+        <f t="shared" si="907"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1968" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1968" s="3"/>
-      <c r="B1968" s="3"/>
-      <c r="C1968" s="3"/>
-      <c r="D1968" s="3"/>
-      <c r="E1968" s="3"/>
-      <c r="F1968" s="3"/>
-      <c r="G1968" s="3"/>
-      <c r="H1968" s="3"/>
-      <c r="I1968" s="4"/>
-      <c r="J1968" s="4"/>
+      <c r="A1968" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1968" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1968" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1968" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1968" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1968" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1968" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1968" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1968" s="4">
+        <f t="shared" si="906"/>
+        <v>2026</v>
+      </c>
+      <c r="J1968" s="4">
+        <f t="shared" si="907"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1969" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1969" s="3"/>
-      <c r="B1969" s="3"/>
-      <c r="C1969" s="3"/>
-      <c r="D1969" s="3"/>
-      <c r="E1969" s="3"/>
-      <c r="F1969" s="3"/>
-      <c r="G1969" s="3"/>
-      <c r="H1969" s="3"/>
-      <c r="I1969" s="4"/>
-      <c r="J1969" s="4"/>
+      <c r="A1969" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1969" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1969" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1969" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1969" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1969" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1969" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1969" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1969" s="4">
+        <f t="shared" ref="I1969:I1970" si="908">YEAR(A1969)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1969" s="4">
+        <f t="shared" ref="J1969:J1970" si="909">MONTH(A1969)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1970" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1970" s="3"/>
-      <c r="B1970" s="3"/>
-      <c r="C1970" s="3"/>
-      <c r="D1970" s="3"/>
-      <c r="E1970" s="3"/>
-      <c r="F1970" s="3"/>
-      <c r="G1970" s="3"/>
-      <c r="H1970" s="3"/>
-      <c r="I1970" s="4"/>
-      <c r="J1970" s="4"/>
+      <c r="A1970" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1970" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1970" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1970" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1970" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1970" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1970" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1970" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1970" s="4">
+        <f t="shared" si="908"/>
+        <v>2026</v>
+      </c>
+      <c r="J1970" s="4">
+        <f t="shared" si="909"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1971" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1971" s="3"/>
-      <c r="B1971" s="3"/>
-      <c r="C1971" s="3"/>
-      <c r="D1971" s="3"/>
-      <c r="E1971" s="3"/>
-      <c r="F1971" s="3"/>
-      <c r="G1971" s="3"/>
-      <c r="H1971" s="3"/>
-      <c r="I1971" s="4"/>
-      <c r="J1971" s="4"/>
+      <c r="A1971" s="3" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1971" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1971" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1971" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1971" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1971" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1971" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1971" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1971" s="4">
+        <f t="shared" ref="I1971:I1973" si="910">YEAR(A1971)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1971" s="4">
+        <f t="shared" ref="J1971:J1973" si="911">MONTH(A1971)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1972" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1972" s="3"/>
-      <c r="B1972" s="3"/>
-      <c r="C1972" s="3"/>
-      <c r="D1972" s="3"/>
-      <c r="E1972" s="3"/>
-      <c r="F1972" s="3"/>
-      <c r="G1972" s="3"/>
-      <c r="H1972" s="3"/>
-      <c r="I1972" s="4"/>
-      <c r="J1972" s="4"/>
+      <c r="A1972" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1972" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1972" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1972" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1972" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1972" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1972" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1972" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1972" s="4">
+        <f t="shared" si="910"/>
+        <v>2026</v>
+      </c>
+      <c r="J1972" s="4">
+        <f t="shared" si="911"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1973" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1973" s="3"/>
-      <c r="B1973" s="3"/>
-      <c r="C1973" s="3"/>
-      <c r="D1973" s="3"/>
-      <c r="E1973" s="3"/>
-      <c r="F1973" s="3"/>
-      <c r="G1973" s="3"/>
-      <c r="H1973" s="3"/>
-      <c r="I1973" s="4"/>
-      <c r="J1973" s="4"/>
+      <c r="A1973" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1973" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1973" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1973" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1973" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1973" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1973" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1973" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1973" s="4">
+        <f t="shared" si="910"/>
+        <v>2026</v>
+      </c>
+      <c r="J1973" s="4">
+        <f t="shared" si="911"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1974" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1974" s="3"/>
-      <c r="B1974" s="3"/>
-      <c r="C1974" s="3"/>
-      <c r="D1974" s="3"/>
-      <c r="E1974" s="3"/>
-      <c r="F1974" s="3"/>
-      <c r="G1974" s="3"/>
-      <c r="H1974" s="3"/>
-      <c r="I1974" s="4"/>
-      <c r="J1974" s="4"/>
+      <c r="A1974" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1974" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1974" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1974" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1974" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1974" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1974" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1974" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1974" s="4">
+        <f t="shared" ref="I1974:I1976" si="912">YEAR(A1974)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1974" s="4">
+        <f t="shared" ref="J1974:J1976" si="913">MONTH(A1974)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1975" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1975" s="3"/>
-      <c r="B1975" s="3"/>
-      <c r="C1975" s="3"/>
-      <c r="D1975" s="3"/>
-      <c r="E1975" s="3"/>
-      <c r="F1975" s="3"/>
-      <c r="G1975" s="3"/>
-      <c r="H1975" s="3"/>
-      <c r="I1975" s="4"/>
-      <c r="J1975" s="4"/>
+      <c r="A1975" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1975" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1975" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1975" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1975" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1975" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1975" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1975" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1975" s="4">
+        <f t="shared" si="912"/>
+        <v>2026</v>
+      </c>
+      <c r="J1975" s="4">
+        <f t="shared" si="913"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1976" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1976" s="3"/>
-      <c r="B1976" s="3"/>
-      <c r="C1976" s="3"/>
-      <c r="D1976" s="3"/>
-      <c r="E1976" s="3"/>
-      <c r="F1976" s="3"/>
-      <c r="G1976" s="3"/>
-      <c r="H1976" s="3"/>
-      <c r="I1976" s="4"/>
-      <c r="J1976" s="4"/>
+      <c r="A1976" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1976" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1976" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1976" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1976" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1976" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1976" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1976" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1976" s="4">
+        <f t="shared" si="912"/>
+        <v>2026</v>
+      </c>
+      <c r="J1976" s="4">
+        <f t="shared" si="913"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1977" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1977" s="3"/>
-      <c r="B1977" s="3"/>
-      <c r="C1977" s="3"/>
-      <c r="D1977" s="3"/>
-      <c r="E1977" s="3"/>
-      <c r="F1977" s="3"/>
-      <c r="G1977" s="3"/>
-      <c r="H1977" s="3"/>
-      <c r="I1977" s="4"/>
-      <c r="J1977" s="4"/>
+      <c r="A1977" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1977" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1977" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1977" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1977" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1977" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1977" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1977" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1977" s="4">
+        <f t="shared" ref="I1977:I1980" si="914">YEAR(A1977)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1977" s="4">
+        <f t="shared" ref="J1977:J1980" si="915">MONTH(A1977)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1978" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1978" s="3"/>
-      <c r="B1978" s="3"/>
-      <c r="C1978" s="3"/>
-      <c r="D1978" s="3"/>
-      <c r="E1978" s="3"/>
-      <c r="F1978" s="3"/>
-      <c r="G1978" s="3"/>
-      <c r="H1978" s="3"/>
-      <c r="I1978" s="4"/>
-      <c r="J1978" s="4"/>
+      <c r="A1978" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1978" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1978" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1978" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1978" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1978" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1978" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1978" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1978" s="4">
+        <f t="shared" si="914"/>
+        <v>2026</v>
+      </c>
+      <c r="J1978" s="4">
+        <f t="shared" si="915"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1979" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1979" s="3"/>
-      <c r="B1979" s="3"/>
-      <c r="C1979" s="3"/>
-      <c r="D1979" s="3"/>
-      <c r="E1979" s="3"/>
-      <c r="F1979" s="3"/>
-      <c r="G1979" s="3"/>
-      <c r="H1979" s="3"/>
-      <c r="I1979" s="4"/>
-      <c r="J1979" s="4"/>
+      <c r="A1979" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1979" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1979" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1979" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1979" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1979" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1979" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1979" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1979" s="4">
+        <f t="shared" si="914"/>
+        <v>2026</v>
+      </c>
+      <c r="J1979" s="4">
+        <f t="shared" si="915"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1980" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1980" s="3"/>
-      <c r="B1980" s="3"/>
-      <c r="C1980" s="3"/>
-      <c r="D1980" s="3"/>
-      <c r="E1980" s="3"/>
-      <c r="F1980" s="3"/>
-      <c r="G1980" s="3"/>
-      <c r="H1980" s="3"/>
-      <c r="I1980" s="4"/>
-      <c r="J1980" s="4"/>
+      <c r="A1980" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1980" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1980" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1980" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1980" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1980" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1980" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1980" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1980" s="4">
+        <f t="shared" si="914"/>
+        <v>2026</v>
+      </c>
+      <c r="J1980" s="4">
+        <f t="shared" si="915"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1981" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1981" s="3"/>
-      <c r="B1981" s="3"/>
-      <c r="C1981" s="3"/>
-      <c r="D1981" s="3"/>
-      <c r="E1981" s="3"/>
-      <c r="F1981" s="3"/>
-      <c r="G1981" s="3"/>
-      <c r="H1981" s="3"/>
-      <c r="I1981" s="4"/>
-      <c r="J1981" s="4"/>
+      <c r="A1981" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B1981" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1981" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1981" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1981" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1981" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1981" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1981" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1981" s="4">
+        <f t="shared" ref="I1981:I1983" si="916">YEAR(A1981)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1981" s="4">
+        <f t="shared" ref="J1981:J1983" si="917">MONTH(A1981)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1982" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1982" s="3"/>
-      <c r="B1982" s="3"/>
-      <c r="C1982" s="3"/>
-      <c r="D1982" s="3"/>
-      <c r="E1982" s="3"/>
-      <c r="F1982" s="3"/>
-      <c r="G1982" s="3"/>
-      <c r="H1982" s="3"/>
-      <c r="I1982" s="4"/>
-      <c r="J1982" s="4"/>
+      <c r="A1982" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1982" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1982" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1982" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E1982" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1982" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1982" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1982" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1982" s="4">
+        <f t="shared" si="916"/>
+        <v>2026</v>
+      </c>
+      <c r="J1982" s="4">
+        <f t="shared" si="917"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1983" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1983" s="3"/>
-      <c r="B1983" s="3"/>
-      <c r="C1983" s="3"/>
-      <c r="D1983" s="3"/>
-      <c r="E1983" s="3"/>
-      <c r="F1983" s="3"/>
-      <c r="G1983" s="3"/>
-      <c r="H1983" s="3"/>
-      <c r="I1983" s="4"/>
-      <c r="J1983" s="4"/>
+      <c r="A1983" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1983" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1983" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1983" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1983" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1983" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1983" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1983" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1983" s="4">
+        <f t="shared" si="916"/>
+        <v>2026</v>
+      </c>
+      <c r="J1983" s="4">
+        <f t="shared" si="917"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1984" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1984" s="3"/>
-      <c r="B1984" s="3"/>
-      <c r="C1984" s="3"/>
-      <c r="D1984" s="3"/>
-      <c r="E1984" s="3"/>
-      <c r="F1984" s="3"/>
-      <c r="G1984" s="3"/>
-      <c r="H1984" s="3"/>
-      <c r="I1984" s="4"/>
-      <c r="J1984" s="4"/>
+      <c r="A1984" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1984" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1984" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1984" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1984" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1984" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1984" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1984" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1984" s="4">
+        <f t="shared" ref="I1984" si="918">YEAR(A1984)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1984" s="4">
+        <f t="shared" ref="J1984" si="919">MONTH(A1984)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1985" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1985" s="3"/>
@@ -71615,6 +72145,258 @@
       <c r="I1998" s="4"/>
       <c r="J1998" s="4"/>
     </row>
+    <row r="1999" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1999" s="3"/>
+      <c r="B1999" s="3"/>
+      <c r="C1999" s="3"/>
+      <c r="D1999" s="3"/>
+      <c r="E1999" s="3"/>
+      <c r="F1999" s="3"/>
+      <c r="G1999" s="3"/>
+      <c r="H1999" s="3"/>
+      <c r="I1999" s="4"/>
+      <c r="J1999" s="4"/>
+    </row>
+    <row r="2000" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2000" s="3"/>
+      <c r="B2000" s="3"/>
+      <c r="C2000" s="3"/>
+      <c r="D2000" s="3"/>
+      <c r="E2000" s="3"/>
+      <c r="F2000" s="3"/>
+      <c r="G2000" s="3"/>
+      <c r="H2000" s="3"/>
+      <c r="I2000" s="4"/>
+      <c r="J2000" s="4"/>
+    </row>
+    <row r="2001" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2001" s="3"/>
+      <c r="B2001" s="3"/>
+      <c r="C2001" s="3"/>
+      <c r="D2001" s="3"/>
+      <c r="E2001" s="3"/>
+      <c r="F2001" s="3"/>
+      <c r="G2001" s="3"/>
+      <c r="H2001" s="3"/>
+      <c r="I2001" s="4"/>
+      <c r="J2001" s="4"/>
+    </row>
+    <row r="2002" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2002" s="3"/>
+      <c r="B2002" s="3"/>
+      <c r="C2002" s="3"/>
+      <c r="D2002" s="3"/>
+      <c r="E2002" s="3"/>
+      <c r="F2002" s="3"/>
+      <c r="G2002" s="3"/>
+      <c r="H2002" s="3"/>
+      <c r="I2002" s="4"/>
+      <c r="J2002" s="4"/>
+    </row>
+    <row r="2003" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2003" s="3"/>
+      <c r="B2003" s="3"/>
+      <c r="C2003" s="3"/>
+      <c r="D2003" s="3"/>
+      <c r="E2003" s="3"/>
+      <c r="F2003" s="3"/>
+      <c r="G2003" s="3"/>
+      <c r="H2003" s="3"/>
+      <c r="I2003" s="4"/>
+      <c r="J2003" s="4"/>
+    </row>
+    <row r="2004" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2004" s="3"/>
+      <c r="B2004" s="3"/>
+      <c r="C2004" s="3"/>
+      <c r="D2004" s="3"/>
+      <c r="E2004" s="3"/>
+      <c r="F2004" s="3"/>
+      <c r="G2004" s="3"/>
+      <c r="H2004" s="3"/>
+      <c r="I2004" s="4"/>
+      <c r="J2004" s="4"/>
+    </row>
+    <row r="2005" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2005" s="3"/>
+      <c r="B2005" s="3"/>
+      <c r="C2005" s="3"/>
+      <c r="D2005" s="3"/>
+      <c r="E2005" s="3"/>
+      <c r="F2005" s="3"/>
+      <c r="G2005" s="3"/>
+      <c r="H2005" s="3"/>
+      <c r="I2005" s="4"/>
+      <c r="J2005" s="4"/>
+    </row>
+    <row r="2006" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2006" s="3"/>
+      <c r="B2006" s="3"/>
+      <c r="C2006" s="3"/>
+      <c r="D2006" s="3"/>
+      <c r="E2006" s="3"/>
+      <c r="F2006" s="3"/>
+      <c r="G2006" s="3"/>
+      <c r="H2006" s="3"/>
+      <c r="I2006" s="4"/>
+      <c r="J2006" s="4"/>
+    </row>
+    <row r="2007" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2007" s="3"/>
+      <c r="B2007" s="3"/>
+      <c r="C2007" s="3"/>
+      <c r="D2007" s="3"/>
+      <c r="E2007" s="3"/>
+      <c r="F2007" s="3"/>
+      <c r="G2007" s="3"/>
+      <c r="H2007" s="3"/>
+      <c r="I2007" s="4"/>
+      <c r="J2007" s="4"/>
+    </row>
+    <row r="2008" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2008" s="3"/>
+      <c r="B2008" s="3"/>
+      <c r="C2008" s="3"/>
+      <c r="D2008" s="3"/>
+      <c r="E2008" s="3"/>
+      <c r="F2008" s="3"/>
+      <c r="G2008" s="3"/>
+      <c r="H2008" s="3"/>
+      <c r="I2008" s="4"/>
+      <c r="J2008" s="4"/>
+    </row>
+    <row r="2009" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2009" s="3"/>
+      <c r="B2009" s="3"/>
+      <c r="C2009" s="3"/>
+      <c r="D2009" s="3"/>
+      <c r="E2009" s="3"/>
+      <c r="F2009" s="3"/>
+      <c r="G2009" s="3"/>
+      <c r="H2009" s="3"/>
+      <c r="I2009" s="4"/>
+      <c r="J2009" s="4"/>
+    </row>
+    <row r="2010" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2010" s="3"/>
+      <c r="B2010" s="3"/>
+      <c r="C2010" s="3"/>
+      <c r="D2010" s="3"/>
+      <c r="E2010" s="3"/>
+      <c r="F2010" s="3"/>
+      <c r="G2010" s="3"/>
+      <c r="H2010" s="3"/>
+      <c r="I2010" s="4"/>
+      <c r="J2010" s="4"/>
+    </row>
+    <row r="2011" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2011" s="3"/>
+      <c r="B2011" s="3"/>
+      <c r="C2011" s="3"/>
+      <c r="D2011" s="3"/>
+      <c r="E2011" s="3"/>
+      <c r="F2011" s="3"/>
+      <c r="G2011" s="3"/>
+      <c r="H2011" s="3"/>
+      <c r="I2011" s="4"/>
+      <c r="J2011" s="4"/>
+    </row>
+    <row r="2012" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2012" s="3"/>
+      <c r="B2012" s="3"/>
+      <c r="C2012" s="3"/>
+      <c r="D2012" s="3"/>
+      <c r="E2012" s="3"/>
+      <c r="F2012" s="3"/>
+      <c r="G2012" s="3"/>
+      <c r="H2012" s="3"/>
+      <c r="I2012" s="4"/>
+      <c r="J2012" s="4"/>
+    </row>
+    <row r="2013" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2013" s="3"/>
+      <c r="B2013" s="3"/>
+      <c r="C2013" s="3"/>
+      <c r="D2013" s="3"/>
+      <c r="E2013" s="3"/>
+      <c r="F2013" s="3"/>
+      <c r="G2013" s="3"/>
+      <c r="H2013" s="3"/>
+      <c r="I2013" s="4"/>
+      <c r="J2013" s="4"/>
+    </row>
+    <row r="2014" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2014" s="3"/>
+      <c r="B2014" s="3"/>
+      <c r="C2014" s="3"/>
+      <c r="D2014" s="3"/>
+      <c r="E2014" s="3"/>
+      <c r="F2014" s="3"/>
+      <c r="G2014" s="3"/>
+      <c r="H2014" s="3"/>
+      <c r="I2014" s="4"/>
+      <c r="J2014" s="4"/>
+    </row>
+    <row r="2015" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2015" s="3"/>
+      <c r="B2015" s="3"/>
+      <c r="C2015" s="3"/>
+      <c r="D2015" s="3"/>
+      <c r="E2015" s="3"/>
+      <c r="F2015" s="3"/>
+      <c r="G2015" s="3"/>
+      <c r="H2015" s="3"/>
+      <c r="I2015" s="4"/>
+      <c r="J2015" s="4"/>
+    </row>
+    <row r="2016" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2016" s="3"/>
+      <c r="B2016" s="3"/>
+      <c r="C2016" s="3"/>
+      <c r="D2016" s="3"/>
+      <c r="E2016" s="3"/>
+      <c r="F2016" s="3"/>
+      <c r="G2016" s="3"/>
+      <c r="H2016" s="3"/>
+      <c r="I2016" s="4"/>
+      <c r="J2016" s="4"/>
+    </row>
+    <row r="2017" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2017" s="3"/>
+      <c r="B2017" s="3"/>
+      <c r="C2017" s="3"/>
+      <c r="D2017" s="3"/>
+      <c r="E2017" s="3"/>
+      <c r="F2017" s="3"/>
+      <c r="G2017" s="3"/>
+      <c r="H2017" s="3"/>
+      <c r="I2017" s="4"/>
+      <c r="J2017" s="4"/>
+    </row>
+    <row r="2018" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2018" s="3"/>
+      <c r="B2018" s="3"/>
+      <c r="C2018" s="3"/>
+      <c r="D2018" s="3"/>
+      <c r="E2018" s="3"/>
+      <c r="F2018" s="3"/>
+      <c r="G2018" s="3"/>
+      <c r="H2018" s="3"/>
+      <c r="I2018" s="4"/>
+      <c r="J2018" s="4"/>
+    </row>
+    <row r="2019" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2019" s="3"/>
+      <c r="B2019" s="3"/>
+      <c r="C2019" s="3"/>
+      <c r="D2019" s="3"/>
+      <c r="E2019" s="3"/>
+      <c r="F2019" s="3"/>
+      <c r="G2019" s="3"/>
+      <c r="H2019" s="3"/>
+      <c r="I2019" s="4"/>
+      <c r="J2019" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15469" uniqueCount="1628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15581" uniqueCount="1636">
   <si>
     <t>Year</t>
   </si>
@@ -4909,6 +4909,30 @@
   </si>
   <si>
     <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>nwcommitaverages v2.0.0</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
   </si>
 </sst>
 </file>
@@ -71969,181 +71993,489 @@
         <v>280</v>
       </c>
       <c r="I1984" s="4">
-        <f t="shared" ref="I1984" si="918">YEAR(A1984)</f>
+        <f t="shared" ref="I1984:I1986" si="918">YEAR(A1984)</f>
         <v>2026</v>
       </c>
       <c r="J1984" s="4">
-        <f t="shared" ref="J1984" si="919">MONTH(A1984)</f>
+        <f t="shared" ref="J1984:J1986" si="919">MONTH(A1984)</f>
         <v>3</v>
       </c>
     </row>
     <row r="1985" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1985" s="3"/>
-      <c r="B1985" s="3"/>
-      <c r="C1985" s="3"/>
-      <c r="D1985" s="3"/>
-      <c r="E1985" s="3"/>
-      <c r="F1985" s="3"/>
-      <c r="G1985" s="3"/>
-      <c r="H1985" s="3"/>
-      <c r="I1985" s="4"/>
-      <c r="J1985" s="4"/>
+      <c r="A1985" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1985" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1985" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1985" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1985" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1985" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1985" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1985" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1985" s="4">
+        <f t="shared" si="918"/>
+        <v>2026</v>
+      </c>
+      <c r="J1985" s="4">
+        <f t="shared" si="919"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1986" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1986" s="3"/>
-      <c r="B1986" s="3"/>
-      <c r="C1986" s="3"/>
-      <c r="D1986" s="3"/>
-      <c r="E1986" s="3"/>
-      <c r="F1986" s="3"/>
-      <c r="G1986" s="3"/>
-      <c r="H1986" s="3"/>
-      <c r="I1986" s="4"/>
-      <c r="J1986" s="4"/>
+      <c r="A1986" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1986" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1986" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1986" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1986" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1986" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G1986" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1986" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1986" s="4">
+        <f t="shared" si="918"/>
+        <v>2026</v>
+      </c>
+      <c r="J1986" s="4">
+        <f t="shared" si="919"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="1987" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1987" s="3"/>
-      <c r="B1987" s="3"/>
-      <c r="C1987" s="3"/>
-      <c r="D1987" s="3"/>
-      <c r="E1987" s="3"/>
-      <c r="F1987" s="3"/>
-      <c r="G1987" s="3"/>
-      <c r="H1987" s="3"/>
-      <c r="I1987" s="4"/>
-      <c r="J1987" s="4"/>
+      <c r="A1987" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1987" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1987" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1987" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1987" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1987" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G1987" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1987" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1987" s="4">
+        <f t="shared" ref="I1987" si="920">YEAR(A1987)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1987" s="4">
+        <f t="shared" ref="J1987" si="921">MONTH(A1987)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1988" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1988" s="3"/>
-      <c r="B1988" s="3"/>
-      <c r="C1988" s="3"/>
-      <c r="D1988" s="3"/>
-      <c r="E1988" s="3"/>
-      <c r="F1988" s="3"/>
-      <c r="G1988" s="3"/>
-      <c r="H1988" s="3"/>
-      <c r="I1988" s="4"/>
-      <c r="J1988" s="4"/>
+      <c r="A1988" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1988" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1988" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1988" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1988" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1988" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G1988" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1988" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1988" s="4">
+        <f t="shared" ref="I1988" si="922">YEAR(A1988)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1988" s="4">
+        <f t="shared" ref="J1988" si="923">MONTH(A1988)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="1989" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1989" s="3"/>
-      <c r="B1989" s="3"/>
-      <c r="C1989" s="3"/>
-      <c r="D1989" s="3"/>
-      <c r="E1989" s="3"/>
-      <c r="F1989" s="3"/>
-      <c r="G1989" s="3"/>
-      <c r="H1989" s="3"/>
-      <c r="I1989" s="4"/>
-      <c r="J1989" s="4"/>
+      <c r="A1989" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1989" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1989" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1989" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1989" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1989" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G1989" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1989" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1989" s="4">
+        <f t="shared" ref="I1989:I1990" si="924">YEAR(A1989)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1989" s="4">
+        <f t="shared" ref="J1989:J1990" si="925">MONTH(A1989)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="1990" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1990" s="3"/>
-      <c r="B1990" s="3"/>
-      <c r="C1990" s="3"/>
-      <c r="D1990" s="3"/>
-      <c r="E1990" s="3"/>
-      <c r="F1990" s="3"/>
-      <c r="G1990" s="3"/>
-      <c r="H1990" s="3"/>
-      <c r="I1990" s="4"/>
-      <c r="J1990" s="4"/>
+      <c r="A1990" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1990" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="C1990" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1990" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1990" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1990" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G1990" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1990" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1990" s="4">
+        <f t="shared" si="924"/>
+        <v>2026</v>
+      </c>
+      <c r="J1990" s="4">
+        <f t="shared" si="925"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="1991" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1991" s="3"/>
-      <c r="B1991" s="3"/>
-      <c r="C1991" s="3"/>
-      <c r="D1991" s="3"/>
-      <c r="E1991" s="3"/>
-      <c r="F1991" s="3"/>
-      <c r="G1991" s="3"/>
-      <c r="H1991" s="3"/>
-      <c r="I1991" s="4"/>
-      <c r="J1991" s="4"/>
+      <c r="A1991" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1991" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1991" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1991" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1991" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1991" s="3" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G1991" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1991" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1991" s="4">
+        <f t="shared" ref="I1991:I1992" si="926">YEAR(A1991)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1991" s="4">
+        <f t="shared" ref="J1991:J1992" si="927">MONTH(A1991)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="1992" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1992" s="3"/>
-      <c r="B1992" s="3"/>
-      <c r="C1992" s="3"/>
-      <c r="D1992" s="3"/>
-      <c r="E1992" s="3"/>
-      <c r="F1992" s="3"/>
-      <c r="G1992" s="3"/>
-      <c r="H1992" s="3"/>
-      <c r="I1992" s="4"/>
-      <c r="J1992" s="4"/>
+      <c r="A1992" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1992" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1992" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1992" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1992" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1992" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1992" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1992" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1992" s="4">
+        <f t="shared" si="926"/>
+        <v>2026</v>
+      </c>
+      <c r="J1992" s="4">
+        <f t="shared" si="927"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="1993" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1993" s="3"/>
-      <c r="B1993" s="3"/>
-      <c r="C1993" s="3"/>
-      <c r="D1993" s="3"/>
-      <c r="E1993" s="3"/>
-      <c r="F1993" s="3"/>
-      <c r="G1993" s="3"/>
-      <c r="H1993" s="3"/>
-      <c r="I1993" s="4"/>
-      <c r="J1993" s="4"/>
+      <c r="A1993" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B1993" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1993" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1993" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1993" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1993" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1993" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1993" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1993" s="4">
+        <f t="shared" ref="I1993:I1994" si="928">YEAR(A1993)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1993" s="4">
+        <f t="shared" ref="J1993:J1994" si="929">MONTH(A1993)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="1994" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1994" s="3"/>
-      <c r="B1994" s="3"/>
-      <c r="C1994" s="3"/>
-      <c r="D1994" s="3"/>
-      <c r="E1994" s="3"/>
-      <c r="F1994" s="3"/>
-      <c r="G1994" s="3"/>
-      <c r="H1994" s="3"/>
-      <c r="I1994" s="4"/>
-      <c r="J1994" s="4"/>
+      <c r="A1994" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B1994" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1994" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1994" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1994" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1994" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1994" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1994" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1994" s="4">
+        <f t="shared" si="928"/>
+        <v>2026</v>
+      </c>
+      <c r="J1994" s="4">
+        <f t="shared" si="929"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="1995" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1995" s="3"/>
-      <c r="B1995" s="3"/>
-      <c r="C1995" s="3"/>
-      <c r="D1995" s="3"/>
-      <c r="E1995" s="3"/>
-      <c r="F1995" s="3"/>
-      <c r="G1995" s="3"/>
-      <c r="H1995" s="3"/>
-      <c r="I1995" s="4"/>
-      <c r="J1995" s="4"/>
+      <c r="A1995" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1995" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1995" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1995" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1995" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1995" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1995" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1995" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1995" s="4">
+        <f t="shared" ref="I1995:I1996" si="930">YEAR(A1995)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1995" s="4">
+        <f t="shared" ref="J1995:J1996" si="931">MONTH(A1995)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="1996" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1996" s="3"/>
-      <c r="B1996" s="3"/>
-      <c r="C1996" s="3"/>
-      <c r="D1996" s="3"/>
-      <c r="E1996" s="3"/>
-      <c r="F1996" s="3"/>
-      <c r="G1996" s="3"/>
-      <c r="H1996" s="3"/>
-      <c r="I1996" s="4"/>
-      <c r="J1996" s="4"/>
+      <c r="A1996" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1996" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1996" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1996" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1996" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1996" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1996" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1996" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1996" s="4">
+        <f t="shared" si="930"/>
+        <v>2026</v>
+      </c>
+      <c r="J1996" s="4">
+        <f t="shared" si="931"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="1997" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1997" s="3"/>
-      <c r="B1997" s="3"/>
-      <c r="C1997" s="3"/>
-      <c r="D1997" s="3"/>
-      <c r="E1997" s="3"/>
-      <c r="F1997" s="3"/>
-      <c r="G1997" s="3"/>
-      <c r="H1997" s="3"/>
-      <c r="I1997" s="4"/>
-      <c r="J1997" s="4"/>
+      <c r="A1997" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1997" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1997" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1997" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1997" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1997" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1997" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1997" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1997" s="4">
+        <f t="shared" ref="I1997:I1998" si="932">YEAR(A1997)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1997" s="4">
+        <f t="shared" ref="J1997:J1998" si="933">MONTH(A1997)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="1998" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1998" s="3"/>
-      <c r="B1998" s="3"/>
-      <c r="C1998" s="3"/>
-      <c r="D1998" s="3"/>
-      <c r="E1998" s="3"/>
-      <c r="F1998" s="3"/>
-      <c r="G1998" s="3"/>
-      <c r="H1998" s="3"/>
-      <c r="I1998" s="4"/>
-      <c r="J1998" s="4"/>
+      <c r="A1998" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1998" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1998" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1998" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1998" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1998" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1998" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1998" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1998" s="4">
+        <f t="shared" si="932"/>
+        <v>2026</v>
+      </c>
+      <c r="J1998" s="4">
+        <f t="shared" si="933"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="1999" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1999" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15581" uniqueCount="1636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15700" uniqueCount="1648">
   <si>
     <t>Year</t>
   </si>
@@ -4933,6 +4933,42 @@
   </si>
   <si>
     <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>nwpackageversions v2.0.0</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
   </si>
 </sst>
 </file>
@@ -5341,7 +5377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2019"/>
+  <dimension ref="A1:J2034"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -71910,7 +71946,7 @@
         <v>255</v>
       </c>
       <c r="D1982" s="3" t="s">
-        <v>431</v>
+        <v>1601</v>
       </c>
       <c r="E1982" s="3" t="s">
         <v>155</v>
@@ -72478,196 +72514,530 @@
       </c>
     </row>
     <row r="1999" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1999" s="3"/>
-      <c r="B1999" s="3"/>
-      <c r="C1999" s="3"/>
-      <c r="D1999" s="3"/>
-      <c r="E1999" s="3"/>
-      <c r="F1999" s="3"/>
-      <c r="G1999" s="3"/>
-      <c r="H1999" s="3"/>
-      <c r="I1999" s="4"/>
-      <c r="J1999" s="4"/>
+      <c r="A1999" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1999" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1999" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1999" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1999" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1999" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G1999" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1999" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I1999" s="4">
+        <f t="shared" ref="I1999:I2000" si="934">YEAR(A1999)</f>
+        <v>2026</v>
+      </c>
+      <c r="J1999" s="4">
+        <f t="shared" ref="J1999:J2000" si="935">MONTH(A1999)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="2000" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2000" s="3"/>
-      <c r="B2000" s="3"/>
-      <c r="C2000" s="3"/>
-      <c r="D2000" s="3"/>
-      <c r="E2000" s="3"/>
+      <c r="A2000" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B2000" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2000" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2000" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2000" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2000" s="3"/>
-      <c r="G2000" s="3"/>
-      <c r="H2000" s="3"/>
-      <c r="I2000" s="4"/>
-      <c r="J2000" s="4"/>
+      <c r="G2000" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2000" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2000" s="4">
+        <f t="shared" si="934"/>
+        <v>2026</v>
+      </c>
+      <c r="J2000" s="4">
+        <f t="shared" si="935"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2001" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2001" s="3"/>
-      <c r="B2001" s="3"/>
-      <c r="C2001" s="3"/>
-      <c r="D2001" s="3"/>
-      <c r="E2001" s="3"/>
+      <c r="A2001" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B2001" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2001" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2001" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E2001" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2001" s="3"/>
-      <c r="G2001" s="3"/>
-      <c r="H2001" s="3"/>
-      <c r="I2001" s="4"/>
-      <c r="J2001" s="4"/>
+      <c r="G2001" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2001" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2001" s="4">
+        <f t="shared" ref="I2001" si="936">YEAR(A2001)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2001" s="4">
+        <f t="shared" ref="J2001" si="937">MONTH(A2001)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="2002" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2002" s="3"/>
-      <c r="B2002" s="3"/>
-      <c r="C2002" s="3"/>
-      <c r="D2002" s="3"/>
-      <c r="E2002" s="3"/>
+      <c r="A2002" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B2002" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2002" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2002" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2002" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2002" s="3"/>
-      <c r="G2002" s="3"/>
-      <c r="H2002" s="3"/>
-      <c r="I2002" s="4"/>
-      <c r="J2002" s="4"/>
+      <c r="G2002" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2002" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2002" s="4">
+        <f t="shared" ref="I2002" si="938">YEAR(A2002)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2002" s="4">
+        <f t="shared" ref="J2002" si="939">MONTH(A2002)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="2003" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2003" s="3"/>
-      <c r="B2003" s="3"/>
-      <c r="C2003" s="3"/>
-      <c r="D2003" s="3"/>
-      <c r="E2003" s="3"/>
+      <c r="A2003" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B2003" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2003" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2003" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2003" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2003" s="3"/>
-      <c r="G2003" s="3"/>
-      <c r="H2003" s="3"/>
-      <c r="I2003" s="4"/>
-      <c r="J2003" s="4"/>
+      <c r="G2003" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2003" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2003" s="4">
+        <f t="shared" ref="I2003:I2010" si="940">YEAR(A2003)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2003" s="4">
+        <f t="shared" ref="J2003:J2010" si="941">MONTH(A2003)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="2004" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2004" s="3"/>
-      <c r="B2004" s="3"/>
-      <c r="C2004" s="3"/>
-      <c r="D2004" s="3"/>
-      <c r="E2004" s="3"/>
-      <c r="F2004" s="3"/>
-      <c r="G2004" s="3"/>
-      <c r="H2004" s="3"/>
-      <c r="I2004" s="4"/>
-      <c r="J2004" s="4"/>
+      <c r="A2004" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B2004" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2004" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2004" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2004" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2004" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G2004" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2004" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2004" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2004" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2005" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2005" s="3"/>
-      <c r="B2005" s="3"/>
-      <c r="C2005" s="3"/>
-      <c r="D2005" s="3"/>
-      <c r="E2005" s="3"/>
-      <c r="F2005" s="3"/>
-      <c r="G2005" s="3"/>
-      <c r="H2005" s="3"/>
-      <c r="I2005" s="4"/>
-      <c r="J2005" s="4"/>
+      <c r="A2005" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B2005" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2005" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2005" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2005" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2005" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G2005" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2005" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2005" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2005" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2006" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2006" s="3"/>
-      <c r="B2006" s="3"/>
-      <c r="C2006" s="3"/>
-      <c r="D2006" s="3"/>
-      <c r="E2006" s="3"/>
-      <c r="F2006" s="3"/>
-      <c r="G2006" s="3"/>
-      <c r="H2006" s="3"/>
-      <c r="I2006" s="4"/>
-      <c r="J2006" s="4"/>
+      <c r="A2006" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B2006" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2006" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2006" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2006" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2006" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G2006" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2006" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2006" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2006" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2007" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2007" s="3"/>
-      <c r="B2007" s="3"/>
-      <c r="C2007" s="3"/>
-      <c r="D2007" s="3"/>
-      <c r="E2007" s="3"/>
-      <c r="F2007" s="3"/>
-      <c r="G2007" s="3"/>
-      <c r="H2007" s="3"/>
-      <c r="I2007" s="4"/>
-      <c r="J2007" s="4"/>
+      <c r="A2007" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B2007" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2007" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2007" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2007" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2007" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G2007" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2007" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2007" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2007" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2008" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2008" s="3"/>
-      <c r="B2008" s="3"/>
-      <c r="C2008" s="3"/>
-      <c r="D2008" s="3"/>
-      <c r="E2008" s="3"/>
-      <c r="F2008" s="3"/>
-      <c r="G2008" s="3"/>
-      <c r="H2008" s="3"/>
-      <c r="I2008" s="4"/>
-      <c r="J2008" s="4"/>
+      <c r="A2008" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B2008" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2008" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D2008" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2008" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2008" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G2008" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2008" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2008" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2008" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2009" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2009" s="3"/>
-      <c r="B2009" s="3"/>
-      <c r="C2009" s="3"/>
-      <c r="D2009" s="3"/>
-      <c r="E2009" s="3"/>
-      <c r="F2009" s="3"/>
-      <c r="G2009" s="3"/>
-      <c r="H2009" s="3"/>
-      <c r="I2009" s="4"/>
-      <c r="J2009" s="4"/>
+      <c r="A2009" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B2009" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2009" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2009" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2009" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2009" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G2009" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2009" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2009" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2009" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2010" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2010" s="3"/>
-      <c r="B2010" s="3"/>
-      <c r="C2010" s="3"/>
-      <c r="D2010" s="3"/>
-      <c r="E2010" s="3"/>
+      <c r="A2010" s="3" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B2010" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2010" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2010" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2010" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2010" s="3"/>
-      <c r="G2010" s="3"/>
-      <c r="H2010" s="3"/>
-      <c r="I2010" s="4"/>
-      <c r="J2010" s="4"/>
+      <c r="G2010" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2010" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2010" s="4">
+        <f t="shared" si="940"/>
+        <v>2026</v>
+      </c>
+      <c r="J2010" s="4">
+        <f t="shared" si="941"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2011" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2011" s="3"/>
-      <c r="B2011" s="3"/>
-      <c r="C2011" s="3"/>
-      <c r="D2011" s="3"/>
-      <c r="E2011" s="3"/>
+      <c r="A2011" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B2011" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2011" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2011" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2011" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2011" s="3"/>
-      <c r="G2011" s="3"/>
-      <c r="H2011" s="3"/>
-      <c r="I2011" s="4"/>
-      <c r="J2011" s="4"/>
+      <c r="G2011" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2011" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2011" s="4">
+        <f t="shared" ref="I2011:I2012" si="942">YEAR(A2011)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2011" s="4">
+        <f t="shared" ref="J2011:J2012" si="943">MONTH(A2011)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="2012" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2012" s="3"/>
-      <c r="B2012" s="3"/>
-      <c r="C2012" s="3"/>
-      <c r="D2012" s="3"/>
-      <c r="E2012" s="3"/>
+      <c r="A2012" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B2012" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2012" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2012" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2012" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2012" s="3"/>
-      <c r="G2012" s="3"/>
-      <c r="H2012" s="3"/>
-      <c r="I2012" s="4"/>
-      <c r="J2012" s="4"/>
+      <c r="G2012" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2012" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2012" s="4">
+        <f t="shared" si="942"/>
+        <v>2026</v>
+      </c>
+      <c r="J2012" s="4">
+        <f t="shared" si="943"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2013" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2013" s="3"/>
-      <c r="B2013" s="3"/>
-      <c r="C2013" s="3"/>
-      <c r="D2013" s="3"/>
-      <c r="E2013" s="3"/>
+      <c r="A2013" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B2013" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2013" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D2013" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2013" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2013" s="3"/>
-      <c r="G2013" s="3"/>
-      <c r="H2013" s="3"/>
-      <c r="I2013" s="4"/>
-      <c r="J2013" s="4"/>
+      <c r="G2013" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2013" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2013" s="4">
+        <f t="shared" ref="I2013:I2014" si="944">YEAR(A2013)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2013" s="4">
+        <f t="shared" ref="J2013:J2014" si="945">MONTH(A2013)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="2014" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2014" s="3"/>
-      <c r="B2014" s="3"/>
-      <c r="C2014" s="3"/>
-      <c r="D2014" s="3"/>
-      <c r="E2014" s="3"/>
+      <c r="A2014" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B2014" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2014" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2014" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2014" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2014" s="3"/>
-      <c r="G2014" s="3"/>
-      <c r="H2014" s="3"/>
-      <c r="I2014" s="4"/>
-      <c r="J2014" s="4"/>
+      <c r="G2014" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2014" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2014" s="4">
+        <f t="shared" si="944"/>
+        <v>2026</v>
+      </c>
+      <c r="J2014" s="4">
+        <f t="shared" si="945"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="2015" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2015" s="3"/>
@@ -72729,6 +73099,186 @@
       <c r="I2019" s="4"/>
       <c r="J2019" s="4"/>
     </row>
+    <row r="2020" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2020" s="3"/>
+      <c r="B2020" s="3"/>
+      <c r="C2020" s="3"/>
+      <c r="D2020" s="3"/>
+      <c r="E2020" s="3"/>
+      <c r="F2020" s="3"/>
+      <c r="G2020" s="3"/>
+      <c r="H2020" s="3"/>
+      <c r="I2020" s="4"/>
+      <c r="J2020" s="4"/>
+    </row>
+    <row r="2021" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2021" s="3"/>
+      <c r="B2021" s="3"/>
+      <c r="C2021" s="3"/>
+      <c r="D2021" s="3"/>
+      <c r="E2021" s="3"/>
+      <c r="F2021" s="3"/>
+      <c r="G2021" s="3"/>
+      <c r="H2021" s="3"/>
+      <c r="I2021" s="4"/>
+      <c r="J2021" s="4"/>
+    </row>
+    <row r="2022" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2022" s="3"/>
+      <c r="B2022" s="3"/>
+      <c r="C2022" s="3"/>
+      <c r="D2022" s="3"/>
+      <c r="E2022" s="3"/>
+      <c r="F2022" s="3"/>
+      <c r="G2022" s="3"/>
+      <c r="H2022" s="3"/>
+      <c r="I2022" s="4"/>
+      <c r="J2022" s="4"/>
+    </row>
+    <row r="2023" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2023" s="3"/>
+      <c r="B2023" s="3"/>
+      <c r="C2023" s="3"/>
+      <c r="D2023" s="3"/>
+      <c r="E2023" s="3"/>
+      <c r="F2023" s="3"/>
+      <c r="G2023" s="3"/>
+      <c r="H2023" s="3"/>
+      <c r="I2023" s="4"/>
+      <c r="J2023" s="4"/>
+    </row>
+    <row r="2024" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2024" s="3"/>
+      <c r="B2024" s="3"/>
+      <c r="C2024" s="3"/>
+      <c r="D2024" s="3"/>
+      <c r="E2024" s="3"/>
+      <c r="F2024" s="3"/>
+      <c r="G2024" s="3"/>
+      <c r="H2024" s="3"/>
+      <c r="I2024" s="4"/>
+      <c r="J2024" s="4"/>
+    </row>
+    <row r="2025" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2025" s="3"/>
+      <c r="B2025" s="3"/>
+      <c r="C2025" s="3"/>
+      <c r="D2025" s="3"/>
+      <c r="E2025" s="3"/>
+      <c r="F2025" s="3"/>
+      <c r="G2025" s="3"/>
+      <c r="H2025" s="3"/>
+      <c r="I2025" s="4"/>
+      <c r="J2025" s="4"/>
+    </row>
+    <row r="2026" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2026" s="3"/>
+      <c r="B2026" s="3"/>
+      <c r="C2026" s="3"/>
+      <c r="D2026" s="3"/>
+      <c r="E2026" s="3"/>
+      <c r="F2026" s="3"/>
+      <c r="G2026" s="3"/>
+      <c r="H2026" s="3"/>
+      <c r="I2026" s="4"/>
+      <c r="J2026" s="4"/>
+    </row>
+    <row r="2027" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2027" s="3"/>
+      <c r="B2027" s="3"/>
+      <c r="C2027" s="3"/>
+      <c r="D2027" s="3"/>
+      <c r="E2027" s="3"/>
+      <c r="F2027" s="3"/>
+      <c r="G2027" s="3"/>
+      <c r="H2027" s="3"/>
+      <c r="I2027" s="4"/>
+      <c r="J2027" s="4"/>
+    </row>
+    <row r="2028" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2028" s="3"/>
+      <c r="B2028" s="3"/>
+      <c r="C2028" s="3"/>
+      <c r="D2028" s="3"/>
+      <c r="E2028" s="3"/>
+      <c r="F2028" s="3"/>
+      <c r="G2028" s="3"/>
+      <c r="H2028" s="3"/>
+      <c r="I2028" s="4"/>
+      <c r="J2028" s="4"/>
+    </row>
+    <row r="2029" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2029" s="3"/>
+      <c r="B2029" s="3"/>
+      <c r="C2029" s="3"/>
+      <c r="D2029" s="3"/>
+      <c r="E2029" s="3"/>
+      <c r="F2029" s="3"/>
+      <c r="G2029" s="3"/>
+      <c r="H2029" s="3"/>
+      <c r="I2029" s="4"/>
+      <c r="J2029" s="4"/>
+    </row>
+    <row r="2030" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2030" s="3"/>
+      <c r="B2030" s="3"/>
+      <c r="C2030" s="3"/>
+      <c r="D2030" s="3"/>
+      <c r="E2030" s="3"/>
+      <c r="F2030" s="3"/>
+      <c r="G2030" s="3"/>
+      <c r="H2030" s="3"/>
+      <c r="I2030" s="4"/>
+      <c r="J2030" s="4"/>
+    </row>
+    <row r="2031" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2031" s="3"/>
+      <c r="B2031" s="3"/>
+      <c r="C2031" s="3"/>
+      <c r="D2031" s="3"/>
+      <c r="E2031" s="3"/>
+      <c r="F2031" s="3"/>
+      <c r="G2031" s="3"/>
+      <c r="H2031" s="3"/>
+      <c r="I2031" s="4"/>
+      <c r="J2031" s="4"/>
+    </row>
+    <row r="2032" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2032" s="3"/>
+      <c r="B2032" s="3"/>
+      <c r="C2032" s="3"/>
+      <c r="D2032" s="3"/>
+      <c r="E2032" s="3"/>
+      <c r="F2032" s="3"/>
+      <c r="G2032" s="3"/>
+      <c r="H2032" s="3"/>
+      <c r="I2032" s="4"/>
+      <c r="J2032" s="4"/>
+    </row>
+    <row r="2033" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2033" s="3"/>
+      <c r="B2033" s="3"/>
+      <c r="C2033" s="3"/>
+      <c r="D2033" s="3"/>
+      <c r="E2033" s="3"/>
+      <c r="F2033" s="3"/>
+      <c r="G2033" s="3"/>
+      <c r="H2033" s="3"/>
+      <c r="I2033" s="4"/>
+      <c r="J2033" s="4"/>
+    </row>
+    <row r="2034" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2034" s="3"/>
+      <c r="B2034" s="3"/>
+      <c r="C2034" s="3"/>
+      <c r="D2034" s="3"/>
+      <c r="E2034" s="3"/>
+      <c r="F2034" s="3"/>
+      <c r="G2034" s="3"/>
+      <c r="H2034" s="3"/>
+      <c r="I2034" s="4"/>
+      <c r="J2034" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCA7306-2D74-42C9-949C-CE313002CDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23265" windowHeight="11970" tabRatio="398"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -12,12 +13,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sessions!$A$1:$J$1961</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15700" uniqueCount="1648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15902" uniqueCount="1662">
   <si>
     <t>Year</t>
   </si>
@@ -4969,13 +4975,55 @@
   </si>
   <si>
     <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>nwdocstringchecking v2.0.0</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>nwversioninfofiles v2.0.0</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>nwreadinglist v6.0.0</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4994,6 +5042,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5055,16 +5109,16 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5091,9 +5145,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5131,9 +5185,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5168,7 +5222,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5203,7 +5257,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5376,8 +5430,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2034"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J2065"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -73040,246 +73094,1179 @@
       </c>
     </row>
     <row r="2015" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2015" s="3"/>
-      <c r="B2015" s="3"/>
-      <c r="C2015" s="3"/>
-      <c r="D2015" s="3"/>
-      <c r="E2015" s="3"/>
+      <c r="A2015" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B2015" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2015" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2015" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2015" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2015" s="3"/>
-      <c r="G2015" s="3"/>
-      <c r="H2015" s="3"/>
-      <c r="I2015" s="4"/>
-      <c r="J2015" s="4"/>
+      <c r="G2015" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2015" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2015" s="4">
+        <f t="shared" ref="I2015:I2016" si="946">YEAR(A2015)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2015" s="4">
+        <f t="shared" ref="J2015:J2016" si="947">MONTH(A2015)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2016" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2016" s="3"/>
-      <c r="B2016" s="3"/>
-      <c r="C2016" s="3"/>
-      <c r="D2016" s="3"/>
-      <c r="E2016" s="3"/>
+      <c r="A2016" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B2016" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2016" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2016" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2016" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2016" s="3"/>
-      <c r="G2016" s="3"/>
-      <c r="H2016" s="3"/>
-      <c r="I2016" s="4"/>
-      <c r="J2016" s="4"/>
+      <c r="G2016" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2016" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2016" s="4">
+        <f t="shared" si="946"/>
+        <v>2026</v>
+      </c>
+      <c r="J2016" s="4">
+        <f t="shared" si="947"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2017" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2017" s="3"/>
-      <c r="B2017" s="3"/>
-      <c r="C2017" s="3"/>
-      <c r="D2017" s="3"/>
-      <c r="E2017" s="3"/>
+      <c r="A2017" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B2017" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2017" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2017" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2017" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2017" s="3"/>
-      <c r="G2017" s="3"/>
-      <c r="H2017" s="3"/>
-      <c r="I2017" s="4"/>
-      <c r="J2017" s="4"/>
+      <c r="G2017" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2017" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2017" s="4">
+        <f t="shared" ref="I2017" si="948">YEAR(A2017)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2017" s="4">
+        <f t="shared" ref="J2017" si="949">MONTH(A2017)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2018" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2018" s="3"/>
-      <c r="B2018" s="3"/>
-      <c r="C2018" s="3"/>
-      <c r="D2018" s="3"/>
-      <c r="E2018" s="3"/>
+      <c r="A2018" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B2018" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2018" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2018" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2018" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2018" s="3"/>
-      <c r="G2018" s="3"/>
-      <c r="H2018" s="3"/>
-      <c r="I2018" s="4"/>
-      <c r="J2018" s="4"/>
+      <c r="G2018" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2018" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2018" s="4">
+        <f t="shared" ref="I2018" si="950">YEAR(A2018)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2018" s="4">
+        <f t="shared" ref="J2018" si="951">MONTH(A2018)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2019" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2019" s="3"/>
-      <c r="B2019" s="3"/>
-      <c r="C2019" s="3"/>
-      <c r="D2019" s="3"/>
-      <c r="E2019" s="3"/>
+      <c r="A2019" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B2019" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2019" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2019" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2019" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2019" s="3"/>
-      <c r="G2019" s="3"/>
-      <c r="H2019" s="3"/>
-      <c r="I2019" s="4"/>
-      <c r="J2019" s="4"/>
+      <c r="G2019" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2019" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2019" s="4">
+        <f t="shared" ref="I2019:I2023" si="952">YEAR(A2019)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2019" s="4">
+        <f t="shared" ref="J2019:J2023" si="953">MONTH(A2019)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2020" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2020" s="3"/>
-      <c r="B2020" s="3"/>
-      <c r="C2020" s="3"/>
-      <c r="D2020" s="3"/>
-      <c r="E2020" s="3"/>
-      <c r="F2020" s="3"/>
-      <c r="G2020" s="3"/>
-      <c r="H2020" s="3"/>
-      <c r="I2020" s="4"/>
-      <c r="J2020" s="4"/>
+      <c r="A2020" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B2020" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2020" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2020" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2020" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2020" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G2020" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2020" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2020" s="4">
+        <f t="shared" si="952"/>
+        <v>2026</v>
+      </c>
+      <c r="J2020" s="4">
+        <f t="shared" si="953"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2021" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2021" s="3"/>
-      <c r="B2021" s="3"/>
-      <c r="C2021" s="3"/>
-      <c r="D2021" s="3"/>
-      <c r="E2021" s="3"/>
-      <c r="F2021" s="3"/>
-      <c r="G2021" s="3"/>
-      <c r="H2021" s="3"/>
-      <c r="I2021" s="4"/>
-      <c r="J2021" s="4"/>
+      <c r="A2021" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B2021" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2021" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2021" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E2021" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2021" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G2021" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2021" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2021" s="4">
+        <f t="shared" si="952"/>
+        <v>2026</v>
+      </c>
+      <c r="J2021" s="4">
+        <f t="shared" si="953"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2022" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2022" s="3"/>
-      <c r="B2022" s="3"/>
-      <c r="C2022" s="3"/>
-      <c r="D2022" s="3"/>
-      <c r="E2022" s="3"/>
-      <c r="F2022" s="3"/>
-      <c r="G2022" s="3"/>
-      <c r="H2022" s="3"/>
-      <c r="I2022" s="4"/>
-      <c r="J2022" s="4"/>
+      <c r="A2022" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B2022" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2022" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2022" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2022" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2022" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G2022" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2022" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2022" s="4">
+        <f t="shared" si="952"/>
+        <v>2026</v>
+      </c>
+      <c r="J2022" s="4">
+        <f t="shared" si="953"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2023" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2023" s="3"/>
-      <c r="B2023" s="3"/>
-      <c r="C2023" s="3"/>
-      <c r="D2023" s="3"/>
-      <c r="E2023" s="3"/>
-      <c r="F2023" s="3"/>
-      <c r="G2023" s="3"/>
-      <c r="H2023" s="3"/>
-      <c r="I2023" s="4"/>
-      <c r="J2023" s="4"/>
+      <c r="A2023" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B2023" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2023" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2023" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2023" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2023" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G2023" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2023" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2023" s="4">
+        <f t="shared" si="952"/>
+        <v>2026</v>
+      </c>
+      <c r="J2023" s="4">
+        <f t="shared" si="953"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2024" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2024" s="3"/>
-      <c r="B2024" s="3"/>
-      <c r="C2024" s="3"/>
-      <c r="D2024" s="3"/>
-      <c r="E2024" s="3"/>
-      <c r="F2024" s="3"/>
-      <c r="G2024" s="3"/>
-      <c r="H2024" s="3"/>
-      <c r="I2024" s="4"/>
-      <c r="J2024" s="4"/>
+      <c r="A2024" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B2024" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2024" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2024" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2024" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2024" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G2024" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2024" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2024" s="4">
+        <f t="shared" ref="I2024:I2028" si="954">YEAR(A2024)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2024" s="4">
+        <f t="shared" ref="J2024:J2028" si="955">MONTH(A2024)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2025" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2025" s="3"/>
-      <c r="B2025" s="3"/>
-      <c r="C2025" s="3"/>
-      <c r="D2025" s="3"/>
-      <c r="E2025" s="3"/>
-      <c r="F2025" s="3"/>
-      <c r="G2025" s="3"/>
-      <c r="H2025" s="3"/>
-      <c r="I2025" s="4"/>
-      <c r="J2025" s="4"/>
+      <c r="A2025" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B2025" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2025" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2025" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2025" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2025" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G2025" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2025" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2025" s="4">
+        <f t="shared" si="954"/>
+        <v>2026</v>
+      </c>
+      <c r="J2025" s="4">
+        <f t="shared" si="955"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2026" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2026" s="3"/>
-      <c r="B2026" s="3"/>
-      <c r="C2026" s="3"/>
-      <c r="D2026" s="3"/>
-      <c r="E2026" s="3"/>
-      <c r="F2026" s="3"/>
-      <c r="G2026" s="3"/>
-      <c r="H2026" s="3"/>
-      <c r="I2026" s="4"/>
-      <c r="J2026" s="4"/>
+      <c r="A2026" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B2026" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2026" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2026" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2026" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2026" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G2026" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2026" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2026" s="4">
+        <f t="shared" si="954"/>
+        <v>2026</v>
+      </c>
+      <c r="J2026" s="4">
+        <f t="shared" si="955"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2027" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2027" s="3"/>
-      <c r="B2027" s="3"/>
-      <c r="C2027" s="3"/>
-      <c r="D2027" s="3"/>
-      <c r="E2027" s="3"/>
-      <c r="F2027" s="3"/>
-      <c r="G2027" s="3"/>
-      <c r="H2027" s="3"/>
-      <c r="I2027" s="4"/>
-      <c r="J2027" s="4"/>
+      <c r="A2027" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B2027" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2027" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2027" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2027" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2027" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2027" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2027" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2027" s="4">
+        <f t="shared" si="954"/>
+        <v>2026</v>
+      </c>
+      <c r="J2027" s="4">
+        <f t="shared" si="955"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2028" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2028" s="3"/>
-      <c r="B2028" s="3"/>
-      <c r="C2028" s="3"/>
-      <c r="D2028" s="3"/>
-      <c r="E2028" s="3"/>
-      <c r="F2028" s="3"/>
-      <c r="G2028" s="3"/>
-      <c r="H2028" s="3"/>
-      <c r="I2028" s="4"/>
-      <c r="J2028" s="4"/>
+      <c r="A2028" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B2028" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2028" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2028" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2028" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2028" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2028" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2028" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2028" s="4">
+        <f t="shared" si="954"/>
+        <v>2026</v>
+      </c>
+      <c r="J2028" s="4">
+        <f t="shared" si="955"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2029" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2029" s="3"/>
-      <c r="B2029" s="3"/>
-      <c r="C2029" s="3"/>
-      <c r="D2029" s="3"/>
-      <c r="E2029" s="3"/>
-      <c r="F2029" s="3"/>
-      <c r="G2029" s="3"/>
-      <c r="H2029" s="3"/>
-      <c r="I2029" s="4"/>
-      <c r="J2029" s="4"/>
+      <c r="A2029" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B2029" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2029" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2029" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2029" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2029" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2029" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2029" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2029" s="4">
+        <f t="shared" ref="I2029:I2030" si="956">YEAR(A2029)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2029" s="4">
+        <f t="shared" ref="J2029:J2030" si="957">MONTH(A2029)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2030" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2030" s="3"/>
-      <c r="B2030" s="3"/>
-      <c r="C2030" s="3"/>
-      <c r="D2030" s="3"/>
-      <c r="E2030" s="3"/>
-      <c r="F2030" s="3"/>
-      <c r="G2030" s="3"/>
-      <c r="H2030" s="3"/>
-      <c r="I2030" s="4"/>
-      <c r="J2030" s="4"/>
+      <c r="A2030" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B2030" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C2030" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2030" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E2030" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2030" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2030" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2030" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2030" s="4">
+        <f t="shared" si="956"/>
+        <v>2026</v>
+      </c>
+      <c r="J2030" s="4">
+        <f t="shared" si="957"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2031" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2031" s="3"/>
-      <c r="B2031" s="3"/>
-      <c r="C2031" s="3"/>
-      <c r="D2031" s="3"/>
-      <c r="E2031" s="3"/>
-      <c r="F2031" s="3"/>
-      <c r="G2031" s="3"/>
-      <c r="H2031" s="3"/>
-      <c r="I2031" s="4"/>
-      <c r="J2031" s="4"/>
+      <c r="A2031" s="3" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B2031" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2031" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2031" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2031" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2031" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2031" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2031" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2031" s="4">
+        <f t="shared" ref="I2031:I2032" si="958">YEAR(A2031)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2031" s="4">
+        <f t="shared" ref="J2031:J2032" si="959">MONTH(A2031)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2032" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2032" s="3"/>
-      <c r="B2032" s="3"/>
-      <c r="C2032" s="3"/>
-      <c r="D2032" s="3"/>
-      <c r="E2032" s="3"/>
+      <c r="A2032" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B2032" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2032" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2032" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2032" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2032" s="3"/>
-      <c r="G2032" s="3"/>
-      <c r="H2032" s="3"/>
-      <c r="I2032" s="4"/>
-      <c r="J2032" s="4"/>
+      <c r="G2032" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2032" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2032" s="4">
+        <f t="shared" si="958"/>
+        <v>2026</v>
+      </c>
+      <c r="J2032" s="4">
+        <f t="shared" si="959"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2033" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2033" s="3"/>
-      <c r="B2033" s="3"/>
-      <c r="C2033" s="3"/>
-      <c r="D2033" s="3"/>
-      <c r="E2033" s="3"/>
-      <c r="F2033" s="3"/>
-      <c r="G2033" s="3"/>
-      <c r="H2033" s="3"/>
-      <c r="I2033" s="4"/>
-      <c r="J2033" s="4"/>
+      <c r="A2033" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B2033" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2033" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2033" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2033" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2033" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2033" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2033" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2033" s="4">
+        <f t="shared" ref="I2033:I2036" si="960">YEAR(A2033)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2033" s="4">
+        <f t="shared" ref="J2033:J2036" si="961">MONTH(A2033)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2034" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2034" s="3"/>
-      <c r="B2034" s="3"/>
-      <c r="C2034" s="3"/>
-      <c r="D2034" s="3"/>
-      <c r="E2034" s="3"/>
-      <c r="F2034" s="3"/>
-      <c r="G2034" s="3"/>
-      <c r="H2034" s="3"/>
-      <c r="I2034" s="4"/>
-      <c r="J2034" s="4"/>
+      <c r="A2034" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B2034" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2034" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2034" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2034" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2034" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2034" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2034" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2034" s="4">
+        <f t="shared" si="960"/>
+        <v>2026</v>
+      </c>
+      <c r="J2034" s="4">
+        <f t="shared" si="961"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2035" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B2035" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2035" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2035" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2035" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2035" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2035" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2035" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2035" s="4">
+        <f t="shared" si="960"/>
+        <v>2026</v>
+      </c>
+      <c r="J2035" s="4">
+        <f t="shared" si="961"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2036" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B2036" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2036" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2036" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2036" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2036" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2036" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2036" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2036" s="4">
+        <f t="shared" si="960"/>
+        <v>2026</v>
+      </c>
+      <c r="J2036" s="4">
+        <f t="shared" si="961"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2037" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B2037" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2037" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2037" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2037" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2037" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2037" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2037" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2037" s="4">
+        <f t="shared" ref="I2037:I2040" si="962">YEAR(A2037)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2037" s="4">
+        <f t="shared" ref="J2037:J2040" si="963">MONTH(A2037)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2038" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B2038" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2038" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2038" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2038" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2038" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2038" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2038" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2038" s="4">
+        <f t="shared" si="962"/>
+        <v>2026</v>
+      </c>
+      <c r="J2038" s="4">
+        <f t="shared" si="963"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2039" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B2039" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2039" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2039" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2039" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2039" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2039" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2039" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2039" s="4">
+        <f t="shared" si="962"/>
+        <v>2026</v>
+      </c>
+      <c r="J2039" s="4">
+        <f t="shared" si="963"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2040" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B2040" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2040" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2040" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2040" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2040" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G2040" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2040" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2040" s="4">
+        <f t="shared" si="962"/>
+        <v>2026</v>
+      </c>
+      <c r="J2040" s="4">
+        <f t="shared" si="963"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2041" s="3"/>
+      <c r="B2041" s="3"/>
+      <c r="C2041" s="3"/>
+      <c r="D2041" s="3"/>
+      <c r="E2041" s="3"/>
+      <c r="F2041" s="3"/>
+      <c r="G2041" s="3"/>
+      <c r="H2041" s="3"/>
+      <c r="I2041" s="4"/>
+      <c r="J2041" s="4"/>
+    </row>
+    <row r="2042" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2042" s="3"/>
+      <c r="B2042" s="3"/>
+      <c r="C2042" s="3"/>
+      <c r="D2042" s="3"/>
+      <c r="E2042" s="3"/>
+      <c r="F2042" s="3"/>
+      <c r="G2042" s="3"/>
+      <c r="H2042" s="3"/>
+      <c r="I2042" s="4"/>
+      <c r="J2042" s="4"/>
+    </row>
+    <row r="2043" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2043" s="3"/>
+      <c r="B2043" s="3"/>
+      <c r="C2043" s="3"/>
+      <c r="D2043" s="3"/>
+      <c r="E2043" s="3"/>
+      <c r="F2043" s="3"/>
+      <c r="G2043" s="3"/>
+      <c r="H2043" s="3"/>
+      <c r="I2043" s="4"/>
+      <c r="J2043" s="4"/>
+    </row>
+    <row r="2044" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2044" s="3"/>
+      <c r="B2044" s="3"/>
+      <c r="C2044" s="3"/>
+      <c r="D2044" s="3"/>
+      <c r="E2044" s="3"/>
+      <c r="F2044" s="3"/>
+      <c r="G2044" s="3"/>
+      <c r="H2044" s="3"/>
+      <c r="I2044" s="4"/>
+      <c r="J2044" s="4"/>
+    </row>
+    <row r="2045" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2045" s="3"/>
+      <c r="B2045" s="3"/>
+      <c r="C2045" s="3"/>
+      <c r="D2045" s="3"/>
+      <c r="E2045" s="3"/>
+      <c r="F2045" s="3"/>
+      <c r="G2045" s="3"/>
+      <c r="H2045" s="3"/>
+      <c r="I2045" s="4"/>
+      <c r="J2045" s="4"/>
+    </row>
+    <row r="2046" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2046" s="3"/>
+      <c r="B2046" s="3"/>
+      <c r="C2046" s="3"/>
+      <c r="D2046" s="3"/>
+      <c r="E2046" s="3"/>
+      <c r="F2046" s="3"/>
+      <c r="G2046" s="3"/>
+      <c r="H2046" s="3"/>
+      <c r="I2046" s="4"/>
+      <c r="J2046" s="4"/>
+    </row>
+    <row r="2047" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2047" s="3"/>
+      <c r="B2047" s="3"/>
+      <c r="C2047" s="3"/>
+      <c r="D2047" s="3"/>
+      <c r="E2047" s="3"/>
+      <c r="F2047" s="3"/>
+      <c r="G2047" s="3"/>
+      <c r="H2047" s="3"/>
+      <c r="I2047" s="4"/>
+      <c r="J2047" s="4"/>
+    </row>
+    <row r="2048" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2048" s="3"/>
+      <c r="B2048" s="3"/>
+      <c r="C2048" s="3"/>
+      <c r="D2048" s="3"/>
+      <c r="E2048" s="3"/>
+      <c r="F2048" s="3"/>
+      <c r="G2048" s="3"/>
+      <c r="H2048" s="3"/>
+      <c r="I2048" s="4"/>
+      <c r="J2048" s="4"/>
+    </row>
+    <row r="2049" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2049" s="3"/>
+      <c r="B2049" s="3"/>
+      <c r="C2049" s="3"/>
+      <c r="D2049" s="3"/>
+      <c r="E2049" s="3"/>
+      <c r="F2049" s="3"/>
+      <c r="G2049" s="3"/>
+      <c r="H2049" s="3"/>
+      <c r="I2049" s="4"/>
+      <c r="J2049" s="4"/>
+    </row>
+    <row r="2050" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2050" s="3"/>
+      <c r="B2050" s="3"/>
+      <c r="C2050" s="3"/>
+      <c r="D2050" s="3"/>
+      <c r="E2050" s="3"/>
+      <c r="F2050" s="3"/>
+      <c r="G2050" s="3"/>
+      <c r="H2050" s="3"/>
+      <c r="I2050" s="4"/>
+      <c r="J2050" s="4"/>
+    </row>
+    <row r="2051" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2051" s="3"/>
+      <c r="B2051" s="3"/>
+      <c r="C2051" s="3"/>
+      <c r="D2051" s="3"/>
+      <c r="E2051" s="3"/>
+      <c r="F2051" s="3"/>
+      <c r="G2051" s="3"/>
+      <c r="H2051" s="3"/>
+      <c r="I2051" s="4"/>
+      <c r="J2051" s="4"/>
+    </row>
+    <row r="2052" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2052" s="3"/>
+      <c r="B2052" s="3"/>
+      <c r="C2052" s="3"/>
+      <c r="D2052" s="3"/>
+      <c r="E2052" s="3"/>
+      <c r="F2052" s="3"/>
+      <c r="G2052" s="3"/>
+      <c r="H2052" s="3"/>
+      <c r="I2052" s="4"/>
+      <c r="J2052" s="4"/>
+    </row>
+    <row r="2053" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2053" s="3"/>
+      <c r="B2053" s="3"/>
+      <c r="C2053" s="3"/>
+      <c r="D2053" s="3"/>
+      <c r="E2053" s="3"/>
+      <c r="F2053" s="3"/>
+      <c r="G2053" s="3"/>
+      <c r="H2053" s="3"/>
+      <c r="I2053" s="4"/>
+      <c r="J2053" s="4"/>
+    </row>
+    <row r="2054" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2054" s="3"/>
+      <c r="B2054" s="3"/>
+      <c r="C2054" s="3"/>
+      <c r="D2054" s="3"/>
+      <c r="E2054" s="3"/>
+      <c r="F2054" s="3"/>
+      <c r="G2054" s="3"/>
+      <c r="H2054" s="3"/>
+      <c r="I2054" s="4"/>
+      <c r="J2054" s="4"/>
+    </row>
+    <row r="2055" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2055" s="3"/>
+      <c r="B2055" s="3"/>
+      <c r="C2055" s="3"/>
+      <c r="D2055" s="3"/>
+      <c r="E2055" s="3"/>
+      <c r="F2055" s="3"/>
+      <c r="G2055" s="3"/>
+      <c r="H2055" s="3"/>
+      <c r="I2055" s="4"/>
+      <c r="J2055" s="4"/>
+    </row>
+    <row r="2056" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2056" s="3"/>
+      <c r="B2056" s="3"/>
+      <c r="C2056" s="3"/>
+      <c r="D2056" s="3"/>
+      <c r="E2056" s="3"/>
+      <c r="F2056" s="3"/>
+      <c r="G2056" s="3"/>
+      <c r="H2056" s="3"/>
+      <c r="I2056" s="4"/>
+      <c r="J2056" s="4"/>
+    </row>
+    <row r="2057" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2057" s="3"/>
+      <c r="B2057" s="3"/>
+      <c r="C2057" s="3"/>
+      <c r="D2057" s="3"/>
+      <c r="E2057" s="3"/>
+      <c r="F2057" s="3"/>
+      <c r="G2057" s="3"/>
+      <c r="H2057" s="3"/>
+      <c r="I2057" s="4"/>
+      <c r="J2057" s="4"/>
+    </row>
+    <row r="2058" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2058" s="3"/>
+      <c r="B2058" s="3"/>
+      <c r="C2058" s="3"/>
+      <c r="D2058" s="3"/>
+      <c r="E2058" s="3"/>
+      <c r="F2058" s="3"/>
+      <c r="G2058" s="3"/>
+      <c r="H2058" s="3"/>
+      <c r="I2058" s="4"/>
+      <c r="J2058" s="4"/>
+    </row>
+    <row r="2059" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2059" s="3"/>
+      <c r="B2059" s="3"/>
+      <c r="C2059" s="3"/>
+      <c r="D2059" s="3"/>
+      <c r="E2059" s="3"/>
+      <c r="F2059" s="3"/>
+      <c r="G2059" s="3"/>
+      <c r="H2059" s="3"/>
+      <c r="I2059" s="4"/>
+      <c r="J2059" s="4"/>
+    </row>
+    <row r="2060" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2060" s="3"/>
+      <c r="B2060" s="3"/>
+      <c r="C2060" s="3"/>
+      <c r="D2060" s="3"/>
+      <c r="E2060" s="3"/>
+      <c r="F2060" s="3"/>
+      <c r="G2060" s="3"/>
+      <c r="H2060" s="3"/>
+      <c r="I2060" s="4"/>
+      <c r="J2060" s="4"/>
+    </row>
+    <row r="2061" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2061" s="3"/>
+      <c r="B2061" s="3"/>
+      <c r="C2061" s="3"/>
+      <c r="D2061" s="3"/>
+      <c r="E2061" s="3"/>
+      <c r="F2061" s="3"/>
+      <c r="G2061" s="3"/>
+      <c r="H2061" s="3"/>
+      <c r="I2061" s="4"/>
+      <c r="J2061" s="4"/>
+    </row>
+    <row r="2062" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2062" s="3"/>
+      <c r="B2062" s="3"/>
+      <c r="C2062" s="3"/>
+      <c r="D2062" s="3"/>
+      <c r="E2062" s="3"/>
+      <c r="F2062" s="3"/>
+      <c r="G2062" s="3"/>
+      <c r="H2062" s="3"/>
+      <c r="I2062" s="4"/>
+      <c r="J2062" s="4"/>
+    </row>
+    <row r="2063" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2063" s="3"/>
+      <c r="B2063" s="3"/>
+      <c r="C2063" s="3"/>
+      <c r="D2063" s="3"/>
+      <c r="E2063" s="3"/>
+      <c r="F2063" s="3"/>
+      <c r="G2063" s="3"/>
+      <c r="H2063" s="3"/>
+      <c r="I2063" s="4"/>
+      <c r="J2063" s="4"/>
+    </row>
+    <row r="2064" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2064" s="3"/>
+      <c r="B2064" s="3"/>
+      <c r="C2064" s="3"/>
+      <c r="D2064" s="3"/>
+      <c r="E2064" s="3"/>
+      <c r="F2064" s="3"/>
+      <c r="G2064" s="3"/>
+      <c r="H2064" s="3"/>
+      <c r="I2064" s="4"/>
+      <c r="J2064" s="4"/>
+    </row>
+    <row r="2065" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2065" s="3"/>
+      <c r="B2065" s="3"/>
+      <c r="C2065" s="3"/>
+      <c r="D2065" s="3"/>
+      <c r="E2065" s="3"/>
+      <c r="F2065" s="3"/>
+      <c r="G2065" s="3"/>
+      <c r="H2065" s="3"/>
+      <c r="I2065" s="4"/>
+      <c r="J2065" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCA7306-2D74-42C9-949C-CE313002CDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CF5BCA-A641-4D9E-B8E8-9B1E24DD6D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="435" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15902" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15981" uniqueCount="1669">
   <si>
     <t>Year</t>
   </si>
@@ -5017,6 +5017,27 @@
   </si>
   <si>
     <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>nwtimetracking v6.0.0</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -73966,136 +73987,360 @@
       </c>
     </row>
     <row r="2041" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2041" s="3"/>
-      <c r="B2041" s="3"/>
-      <c r="C2041" s="3"/>
-      <c r="D2041" s="3"/>
-      <c r="E2041" s="3"/>
-      <c r="F2041" s="3"/>
-      <c r="G2041" s="3"/>
-      <c r="H2041" s="3"/>
-      <c r="I2041" s="4"/>
-      <c r="J2041" s="4"/>
+      <c r="A2041" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B2041" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2041" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2041" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2041" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2041" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="G2041" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2041" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2041" s="4">
+        <f t="shared" ref="I2041:I2043" si="964">YEAR(A2041)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2041" s="4">
+        <f t="shared" ref="J2041:J2043" si="965">MONTH(A2041)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2042" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2042" s="3"/>
-      <c r="B2042" s="3"/>
-      <c r="C2042" s="3"/>
-      <c r="D2042" s="3"/>
-      <c r="E2042" s="3"/>
-      <c r="F2042" s="3"/>
-      <c r="G2042" s="3"/>
-      <c r="H2042" s="3"/>
-      <c r="I2042" s="4"/>
-      <c r="J2042" s="4"/>
+      <c r="A2042" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B2042" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2042" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2042" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2042" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2042" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="G2042" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2042" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2042" s="4">
+        <f t="shared" si="964"/>
+        <v>2026</v>
+      </c>
+      <c r="J2042" s="4">
+        <f t="shared" si="965"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2043" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2043" s="3"/>
-      <c r="B2043" s="3"/>
-      <c r="C2043" s="3"/>
-      <c r="D2043" s="3"/>
-      <c r="E2043" s="3"/>
+      <c r="A2043" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B2043" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2043" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2043" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2043" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2043" s="3"/>
-      <c r="G2043" s="3"/>
-      <c r="H2043" s="3"/>
-      <c r="I2043" s="4"/>
-      <c r="J2043" s="4"/>
+      <c r="G2043" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2043" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2043" s="4">
+        <f t="shared" si="964"/>
+        <v>2026</v>
+      </c>
+      <c r="J2043" s="4">
+        <f t="shared" si="965"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2044" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2044" s="3"/>
-      <c r="B2044" s="3"/>
-      <c r="C2044" s="3"/>
-      <c r="D2044" s="3"/>
-      <c r="E2044" s="3"/>
+      <c r="A2044" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B2044" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2044" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2044" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2044" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2044" s="3"/>
-      <c r="G2044" s="3"/>
-      <c r="H2044" s="3"/>
-      <c r="I2044" s="4"/>
-      <c r="J2044" s="4"/>
+      <c r="G2044" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2044" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2044" s="4">
+        <f t="shared" ref="I2044:I2045" si="966">YEAR(A2044)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2044" s="4">
+        <f t="shared" ref="J2044:J2045" si="967">MONTH(A2044)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2045" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2045" s="3"/>
-      <c r="B2045" s="3"/>
-      <c r="C2045" s="3"/>
-      <c r="D2045" s="3"/>
-      <c r="E2045" s="3"/>
+      <c r="A2045" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B2045" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C2045" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2045" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2045" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2045" s="3"/>
-      <c r="G2045" s="3"/>
-      <c r="H2045" s="3"/>
-      <c r="I2045" s="4"/>
-      <c r="J2045" s="4"/>
+      <c r="G2045" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2045" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2045" s="4">
+        <f t="shared" si="966"/>
+        <v>2026</v>
+      </c>
+      <c r="J2045" s="4">
+        <f t="shared" si="967"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2046" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2046" s="3"/>
-      <c r="B2046" s="3"/>
-      <c r="C2046" s="3"/>
-      <c r="D2046" s="3"/>
-      <c r="E2046" s="3"/>
+      <c r="A2046" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B2046" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2046" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2046" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2046" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2046" s="3"/>
-      <c r="G2046" s="3"/>
-      <c r="H2046" s="3"/>
-      <c r="I2046" s="4"/>
-      <c r="J2046" s="4"/>
+      <c r="G2046" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2046" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2046" s="4">
+        <f t="shared" ref="I2046:I2047" si="968">YEAR(A2046)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2046" s="4">
+        <f t="shared" ref="J2046:J2047" si="969">MONTH(A2046)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2047" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2047" s="3"/>
-      <c r="B2047" s="3"/>
-      <c r="C2047" s="3"/>
-      <c r="D2047" s="3"/>
-      <c r="E2047" s="3"/>
+      <c r="A2047" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B2047" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2047" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2047" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2047" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2047" s="3"/>
-      <c r="G2047" s="3"/>
-      <c r="H2047" s="3"/>
-      <c r="I2047" s="4"/>
-      <c r="J2047" s="4"/>
+      <c r="G2047" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2047" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2047" s="4">
+        <f t="shared" si="968"/>
+        <v>2026</v>
+      </c>
+      <c r="J2047" s="4">
+        <f t="shared" si="969"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2048" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2048" s="3"/>
-      <c r="B2048" s="3"/>
-      <c r="C2048" s="3"/>
-      <c r="D2048" s="3"/>
-      <c r="E2048" s="3"/>
+      <c r="A2048" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B2048" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2048" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2048" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2048" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2048" s="3"/>
-      <c r="G2048" s="3"/>
-      <c r="H2048" s="3"/>
-      <c r="I2048" s="4"/>
-      <c r="J2048" s="4"/>
+      <c r="G2048" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2048" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2048" s="4">
+        <f t="shared" ref="I2048:I2050" si="970">YEAR(A2048)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2048" s="4">
+        <f t="shared" ref="J2048:J2050" si="971">MONTH(A2048)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2049" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2049" s="3"/>
-      <c r="B2049" s="3"/>
-      <c r="C2049" s="3"/>
-      <c r="D2049" s="3"/>
-      <c r="E2049" s="3"/>
+      <c r="A2049" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B2049" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2049" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2049" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2049" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2049" s="3"/>
-      <c r="G2049" s="3"/>
-      <c r="H2049" s="3"/>
-      <c r="I2049" s="4"/>
-      <c r="J2049" s="4"/>
+      <c r="G2049" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2049" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2049" s="4">
+        <f t="shared" si="970"/>
+        <v>2026</v>
+      </c>
+      <c r="J2049" s="4">
+        <f t="shared" si="971"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2050" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2050" s="3"/>
-      <c r="B2050" s="3"/>
-      <c r="C2050" s="3"/>
-      <c r="D2050" s="3"/>
-      <c r="E2050" s="3"/>
+      <c r="A2050" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B2050" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2050" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D2050" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2050" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2050" s="3"/>
-      <c r="G2050" s="3"/>
-      <c r="H2050" s="3"/>
-      <c r="I2050" s="4"/>
-      <c r="J2050" s="4"/>
+      <c r="G2050" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2050" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2050" s="4">
+        <f t="shared" si="970"/>
+        <v>2026</v>
+      </c>
+      <c r="J2050" s="4">
+        <f t="shared" si="971"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="2051" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2051" s="3"/>
-      <c r="B2051" s="3"/>
-      <c r="C2051" s="3"/>
-      <c r="D2051" s="3"/>
-      <c r="E2051" s="3"/>
+      <c r="A2051" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B2051" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2051" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2051" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2051" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2051" s="3"/>
-      <c r="G2051" s="3"/>
-      <c r="H2051" s="3"/>
-      <c r="I2051" s="4"/>
-      <c r="J2051" s="4"/>
+      <c r="G2051" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2051" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2051" s="4">
+        <f t="shared" ref="I2051" si="972">YEAR(A2051)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2051" s="4">
+        <f t="shared" ref="J2051" si="973">MONTH(A2051)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="2052" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2052" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CF5BCA-A641-4D9E-B8E8-9B1E24DD6D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBF39F9-63C1-4EEA-9574-AECA13E7C251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="435" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1575" yWindow="465" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15981" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16215" uniqueCount="1689">
   <si>
     <t>Year</t>
   </si>
@@ -5038,6 +5038,66 @@
   </si>
   <si>
     <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>NW.ZooSketchDownloader v2.0.1</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>nwrefurbishedanalytics v1.0.1</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>#planning</t>
+  </si>
+  <si>
+    <t>Consolidate all tasks in Obsidian.</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>NW's Software Hub</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
   </si>
 </sst>
 </file>
@@ -5452,7 +5512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2065"/>
+  <dimension ref="A1:J2108"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -74334,181 +74394,1351 @@
         <v>280</v>
       </c>
       <c r="I2051" s="4">
-        <f t="shared" ref="I2051" si="972">YEAR(A2051)</f>
+        <f t="shared" ref="I2051:I2052" si="972">YEAR(A2051)</f>
         <v>2026</v>
       </c>
       <c r="J2051" s="4">
-        <f t="shared" ref="J2051" si="973">MONTH(A2051)</f>
+        <f t="shared" ref="J2051:J2052" si="973">MONTH(A2051)</f>
         <v>5</v>
       </c>
     </row>
     <row r="2052" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2052" s="3"/>
-      <c r="B2052" s="3"/>
-      <c r="C2052" s="3"/>
-      <c r="D2052" s="3"/>
-      <c r="E2052" s="3"/>
+      <c r="A2052" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B2052" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2052" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2052" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2052" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2052" s="3"/>
-      <c r="G2052" s="3"/>
-      <c r="H2052" s="3"/>
-      <c r="I2052" s="4"/>
-      <c r="J2052" s="4"/>
+      <c r="G2052" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2052" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2052" s="4">
+        <f t="shared" si="972"/>
+        <v>2026</v>
+      </c>
+      <c r="J2052" s="4">
+        <f t="shared" si="973"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2053" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2053" s="3"/>
-      <c r="B2053" s="3"/>
-      <c r="C2053" s="3"/>
-      <c r="D2053" s="3"/>
-      <c r="E2053" s="3"/>
+      <c r="A2053" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B2053" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2053" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2053" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2053" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2053" s="3"/>
-      <c r="G2053" s="3"/>
-      <c r="H2053" s="3"/>
-      <c r="I2053" s="4"/>
-      <c r="J2053" s="4"/>
+      <c r="G2053" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2053" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2053" s="4">
+        <f t="shared" ref="I2053:I2061" si="974">YEAR(A2053)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2053" s="4">
+        <f t="shared" ref="J2053:J2061" si="975">MONTH(A2053)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="2054" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2054" s="3"/>
-      <c r="B2054" s="3"/>
-      <c r="C2054" s="3"/>
-      <c r="D2054" s="3"/>
-      <c r="E2054" s="3"/>
+      <c r="A2054" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B2054" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2054" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2054" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2054" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2054" s="3"/>
-      <c r="G2054" s="3"/>
-      <c r="H2054" s="3"/>
-      <c r="I2054" s="4"/>
-      <c r="J2054" s="4"/>
+      <c r="G2054" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2054" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2054" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2054" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2055" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2055" s="3"/>
-      <c r="B2055" s="3"/>
-      <c r="C2055" s="3"/>
-      <c r="D2055" s="3"/>
-      <c r="E2055" s="3"/>
+      <c r="A2055" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B2055" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2055" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2055" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2055" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2055" s="3"/>
-      <c r="G2055" s="3"/>
-      <c r="H2055" s="3"/>
-      <c r="I2055" s="4"/>
-      <c r="J2055" s="4"/>
+      <c r="G2055" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2055" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2055" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2055" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2056" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2056" s="3"/>
-      <c r="B2056" s="3"/>
-      <c r="C2056" s="3"/>
-      <c r="D2056" s="3"/>
-      <c r="E2056" s="3"/>
+      <c r="A2056" s="3" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B2056" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2056" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2056" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2056" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2056" s="3"/>
-      <c r="G2056" s="3"/>
-      <c r="H2056" s="3"/>
-      <c r="I2056" s="4"/>
-      <c r="J2056" s="4"/>
+      <c r="G2056" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2056" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2056" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2056" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2057" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2057" s="3"/>
-      <c r="B2057" s="3"/>
-      <c r="C2057" s="3"/>
-      <c r="D2057" s="3"/>
-      <c r="E2057" s="3"/>
+      <c r="A2057" s="3" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B2057" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2057" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2057" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2057" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2057" s="3"/>
-      <c r="G2057" s="3"/>
-      <c r="H2057" s="3"/>
-      <c r="I2057" s="4"/>
-      <c r="J2057" s="4"/>
+      <c r="G2057" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2057" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2057" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2057" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2058" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2058" s="3"/>
-      <c r="B2058" s="3"/>
-      <c r="C2058" s="3"/>
-      <c r="D2058" s="3"/>
-      <c r="E2058" s="3"/>
+      <c r="A2058" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B2058" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2058" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2058" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2058" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2058" s="3"/>
-      <c r="G2058" s="3"/>
-      <c r="H2058" s="3"/>
-      <c r="I2058" s="4"/>
-      <c r="J2058" s="4"/>
+      <c r="G2058" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2058" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2058" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2058" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2059" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2059" s="3"/>
-      <c r="B2059" s="3"/>
-      <c r="C2059" s="3"/>
-      <c r="D2059" s="3"/>
-      <c r="E2059" s="3"/>
+      <c r="A2059" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B2059" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2059" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2059" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2059" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2059" s="3"/>
-      <c r="G2059" s="3"/>
-      <c r="H2059" s="3"/>
-      <c r="I2059" s="4"/>
-      <c r="J2059" s="4"/>
+      <c r="G2059" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2059" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2059" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2059" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2060" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2060" s="3"/>
-      <c r="B2060" s="3"/>
-      <c r="C2060" s="3"/>
-      <c r="D2060" s="3"/>
-      <c r="E2060" s="3"/>
+      <c r="A2060" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B2060" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2060" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2060" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2060" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2060" s="3"/>
-      <c r="G2060" s="3"/>
-      <c r="H2060" s="3"/>
-      <c r="I2060" s="4"/>
-      <c r="J2060" s="4"/>
+      <c r="G2060" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2060" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2060" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2060" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2061" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2061" s="3"/>
-      <c r="B2061" s="3"/>
-      <c r="C2061" s="3"/>
-      <c r="D2061" s="3"/>
-      <c r="E2061" s="3"/>
+      <c r="A2061" s="3" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B2061" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2061" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2061" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="E2061" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2061" s="3"/>
-      <c r="G2061" s="3"/>
-      <c r="H2061" s="3"/>
-      <c r="I2061" s="4"/>
-      <c r="J2061" s="4"/>
+      <c r="G2061" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2061" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2061" s="4">
+        <f t="shared" si="974"/>
+        <v>2026</v>
+      </c>
+      <c r="J2061" s="4">
+        <f t="shared" si="975"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2062" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2062" s="3"/>
-      <c r="B2062" s="3"/>
-      <c r="C2062" s="3"/>
-      <c r="D2062" s="3"/>
-      <c r="E2062" s="3"/>
+      <c r="A2062" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B2062" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2062" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2062" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2062" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2062" s="3"/>
-      <c r="G2062" s="3"/>
-      <c r="H2062" s="3"/>
-      <c r="I2062" s="4"/>
-      <c r="J2062" s="4"/>
+      <c r="G2062" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2062" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2062" s="4">
+        <f t="shared" ref="I2062:I2066" si="976">YEAR(A2062)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2062" s="4">
+        <f t="shared" ref="J2062:J2066" si="977">MONTH(A2062)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="2063" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2063" s="3"/>
-      <c r="B2063" s="3"/>
-      <c r="C2063" s="3"/>
-      <c r="D2063" s="3"/>
-      <c r="E2063" s="3"/>
+      <c r="A2063" s="3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B2063" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2063" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2063" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2063" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2063" s="3"/>
-      <c r="G2063" s="3"/>
-      <c r="H2063" s="3"/>
-      <c r="I2063" s="4"/>
-      <c r="J2063" s="4"/>
+      <c r="G2063" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2063" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2063" s="4">
+        <f t="shared" si="976"/>
+        <v>2026</v>
+      </c>
+      <c r="J2063" s="4">
+        <f t="shared" si="977"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2064" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2064" s="3"/>
-      <c r="B2064" s="3"/>
-      <c r="C2064" s="3"/>
-      <c r="D2064" s="3"/>
-      <c r="E2064" s="3"/>
-      <c r="F2064" s="3"/>
-      <c r="G2064" s="3"/>
-      <c r="H2064" s="3"/>
-      <c r="I2064" s="4"/>
-      <c r="J2064" s="4"/>
+      <c r="A2064" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B2064" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2064" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2064" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2064" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2064" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G2064" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2064" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2064" s="4">
+        <f t="shared" si="976"/>
+        <v>2026</v>
+      </c>
+      <c r="J2064" s="4">
+        <f t="shared" si="977"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="2065" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2065" s="3"/>
-      <c r="B2065" s="3"/>
-      <c r="C2065" s="3"/>
-      <c r="D2065" s="3"/>
-      <c r="E2065" s="3"/>
-      <c r="F2065" s="3"/>
-      <c r="G2065" s="3"/>
-      <c r="H2065" s="3"/>
-      <c r="I2065" s="4"/>
-      <c r="J2065" s="4"/>
+      <c r="A2065" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B2065" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2065" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2065" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2065" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2065" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G2065" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2065" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2065" s="4">
+        <f t="shared" si="976"/>
+        <v>2026</v>
+      </c>
+      <c r="J2065" s="4">
+        <f t="shared" si="977"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2066" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B2066" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2066" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D2066" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2066" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2066" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G2066" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2066" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2066" s="4">
+        <f t="shared" si="976"/>
+        <v>2026</v>
+      </c>
+      <c r="J2066" s="4">
+        <f t="shared" si="977"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2067" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B2067" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2067" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2067" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2067" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2067" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G2067" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2067" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2067" s="4">
+        <f t="shared" ref="I2067:I2078" si="978">YEAR(A2067)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2067" s="4">
+        <f t="shared" ref="J2067:J2078" si="979">MONTH(A2067)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2068" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B2068" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2068" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2068" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2068" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2068" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G2068" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2068" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2068" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2068" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2069" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B2069" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2069" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2069" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2069" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2069" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G2069" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2069" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2069" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2069" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2070" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B2070" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2070" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2070" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E2070" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2070" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2070" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2070" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2070" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2070" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2071" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B2071" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2071" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D2071" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2071" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2071" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2071" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2071" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2071" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2071" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2072" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B2072" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2072" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2072" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2072" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2072" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2072" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2072" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2072" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2072" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2073" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B2073" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2073" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2073" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="E2073" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2073" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2073" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2073" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2073" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2073" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2074" s="3" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B2074" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2074" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2074" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2074" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2074" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2074" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2074" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2074" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2074" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2075" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B2075" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2075" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2075" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2075" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2075" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G2075" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2075" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2075" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2075" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2076" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B2076" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2076" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2076" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2076" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2076" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G2076" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2076" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2076" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2076" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2077" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B2077" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2077" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2077" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2077" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2077" s="3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="G2077" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2077" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2077" s="4">
+        <f t="shared" si="978"/>
+        <v>2026</v>
+      </c>
+      <c r="J2077" s="4">
+        <f t="shared" si="979"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2078" s="3" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B2078" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2078" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2078" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2078" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2078" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2078" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2078" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2078" s="4">
+        <f t="shared" ref="I2078:I2082" si="980">YEAR(A2078)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2078" s="4">
+        <f t="shared" ref="J2078:J2082" si="981">MONTH(A2078)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2079" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B2079" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2079" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2079" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2079" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2079" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2079" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2079" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2079" s="4">
+        <f t="shared" si="980"/>
+        <v>2026</v>
+      </c>
+      <c r="J2079" s="4">
+        <f t="shared" si="981"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2080" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B2080" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2080" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2080" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2080" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2080" s="3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G2080" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2080" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2080" s="4">
+        <f t="shared" si="980"/>
+        <v>2026</v>
+      </c>
+      <c r="J2080" s="4">
+        <f t="shared" si="981"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2081" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B2081" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2081" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2081" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2081" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2081" s="3"/>
+      <c r="G2081" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2081" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2081" s="4">
+        <f t="shared" si="980"/>
+        <v>2026</v>
+      </c>
+      <c r="J2081" s="4">
+        <f t="shared" si="981"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2082" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B2082" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2082" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2082" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2082" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2082" s="3"/>
+      <c r="G2082" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2082" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2082" s="4">
+        <f t="shared" si="980"/>
+        <v>2026</v>
+      </c>
+      <c r="J2082" s="4">
+        <f t="shared" si="981"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2083" s="3"/>
+      <c r="B2083" s="3"/>
+      <c r="C2083" s="3"/>
+      <c r="D2083" s="3"/>
+      <c r="E2083" s="3"/>
+      <c r="F2083" s="3"/>
+      <c r="G2083" s="3"/>
+      <c r="H2083" s="3"/>
+      <c r="I2083" s="4"/>
+      <c r="J2083" s="4"/>
+    </row>
+    <row r="2084" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2084" s="3"/>
+      <c r="B2084" s="3"/>
+      <c r="C2084" s="3"/>
+      <c r="D2084" s="3"/>
+      <c r="E2084" s="3"/>
+      <c r="F2084" s="3"/>
+      <c r="G2084" s="3"/>
+      <c r="H2084" s="3"/>
+      <c r="I2084" s="4"/>
+      <c r="J2084" s="4"/>
+    </row>
+    <row r="2085" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2085" s="3"/>
+      <c r="B2085" s="3"/>
+      <c r="C2085" s="3"/>
+      <c r="D2085" s="3"/>
+      <c r="E2085" s="3"/>
+      <c r="F2085" s="3"/>
+      <c r="G2085" s="3"/>
+      <c r="H2085" s="3"/>
+      <c r="I2085" s="4"/>
+      <c r="J2085" s="4"/>
+    </row>
+    <row r="2086" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2086" s="3"/>
+      <c r="B2086" s="3"/>
+      <c r="C2086" s="3"/>
+      <c r="D2086" s="3"/>
+      <c r="E2086" s="3"/>
+      <c r="F2086" s="3"/>
+      <c r="G2086" s="3"/>
+      <c r="H2086" s="3"/>
+      <c r="I2086" s="4"/>
+      <c r="J2086" s="4"/>
+    </row>
+    <row r="2087" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2087" s="3"/>
+      <c r="B2087" s="3"/>
+      <c r="C2087" s="3"/>
+      <c r="D2087" s="3"/>
+      <c r="E2087" s="3"/>
+      <c r="F2087" s="3"/>
+      <c r="G2087" s="3"/>
+      <c r="H2087" s="3"/>
+      <c r="I2087" s="4"/>
+      <c r="J2087" s="4"/>
+    </row>
+    <row r="2088" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2088" s="3"/>
+      <c r="B2088" s="3"/>
+      <c r="C2088" s="3"/>
+      <c r="D2088" s="3"/>
+      <c r="E2088" s="3"/>
+      <c r="F2088" s="3"/>
+      <c r="G2088" s="3"/>
+      <c r="H2088" s="3"/>
+      <c r="I2088" s="4"/>
+      <c r="J2088" s="4"/>
+    </row>
+    <row r="2089" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2089" s="3"/>
+      <c r="B2089" s="3"/>
+      <c r="C2089" s="3"/>
+      <c r="D2089" s="3"/>
+      <c r="E2089" s="3"/>
+      <c r="F2089" s="3"/>
+      <c r="G2089" s="3"/>
+      <c r="H2089" s="3"/>
+      <c r="I2089" s="4"/>
+      <c r="J2089" s="4"/>
+    </row>
+    <row r="2090" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2090" s="3"/>
+      <c r="B2090" s="3"/>
+      <c r="C2090" s="3"/>
+      <c r="D2090" s="3"/>
+      <c r="E2090" s="3"/>
+      <c r="F2090" s="3"/>
+      <c r="G2090" s="3"/>
+      <c r="H2090" s="3"/>
+      <c r="I2090" s="4"/>
+      <c r="J2090" s="4"/>
+    </row>
+    <row r="2091" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2091" s="3"/>
+      <c r="B2091" s="3"/>
+      <c r="C2091" s="3"/>
+      <c r="D2091" s="3"/>
+      <c r="E2091" s="3"/>
+      <c r="F2091" s="3"/>
+      <c r="G2091" s="3"/>
+      <c r="H2091" s="3"/>
+      <c r="I2091" s="4"/>
+      <c r="J2091" s="4"/>
+    </row>
+    <row r="2092" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2092" s="3"/>
+      <c r="B2092" s="3"/>
+      <c r="C2092" s="3"/>
+      <c r="D2092" s="3"/>
+      <c r="E2092" s="3"/>
+      <c r="F2092" s="3"/>
+      <c r="G2092" s="3"/>
+      <c r="H2092" s="3"/>
+      <c r="I2092" s="4"/>
+      <c r="J2092" s="4"/>
+    </row>
+    <row r="2093" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2093" s="3"/>
+      <c r="B2093" s="3"/>
+      <c r="C2093" s="3"/>
+      <c r="D2093" s="3"/>
+      <c r="E2093" s="3"/>
+      <c r="F2093" s="3"/>
+      <c r="G2093" s="3"/>
+      <c r="H2093" s="3"/>
+      <c r="I2093" s="4"/>
+      <c r="J2093" s="4"/>
+    </row>
+    <row r="2094" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2094" s="3"/>
+      <c r="B2094" s="3"/>
+      <c r="C2094" s="3"/>
+      <c r="D2094" s="3"/>
+      <c r="E2094" s="3"/>
+      <c r="F2094" s="3"/>
+      <c r="G2094" s="3"/>
+      <c r="H2094" s="3"/>
+      <c r="I2094" s="4"/>
+      <c r="J2094" s="4"/>
+    </row>
+    <row r="2095" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2095" s="3"/>
+      <c r="B2095" s="3"/>
+      <c r="C2095" s="3"/>
+      <c r="D2095" s="3"/>
+      <c r="E2095" s="3"/>
+      <c r="F2095" s="3"/>
+      <c r="G2095" s="3"/>
+      <c r="H2095" s="3"/>
+      <c r="I2095" s="4"/>
+      <c r="J2095" s="4"/>
+    </row>
+    <row r="2096" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2096" s="3"/>
+      <c r="B2096" s="3"/>
+      <c r="C2096" s="3"/>
+      <c r="D2096" s="3"/>
+      <c r="E2096" s="3"/>
+      <c r="F2096" s="3"/>
+      <c r="G2096" s="3"/>
+      <c r="H2096" s="3"/>
+      <c r="I2096" s="4"/>
+      <c r="J2096" s="4"/>
+    </row>
+    <row r="2097" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2097" s="3"/>
+      <c r="B2097" s="3"/>
+      <c r="C2097" s="3"/>
+      <c r="D2097" s="3"/>
+      <c r="E2097" s="3"/>
+      <c r="F2097" s="3"/>
+      <c r="G2097" s="3"/>
+      <c r="H2097" s="3"/>
+      <c r="I2097" s="4"/>
+      <c r="J2097" s="4"/>
+    </row>
+    <row r="2098" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2098" s="3"/>
+      <c r="B2098" s="3"/>
+      <c r="C2098" s="3"/>
+      <c r="D2098" s="3"/>
+      <c r="E2098" s="3"/>
+      <c r="F2098" s="3"/>
+      <c r="G2098" s="3"/>
+      <c r="H2098" s="3"/>
+      <c r="I2098" s="4"/>
+      <c r="J2098" s="4"/>
+    </row>
+    <row r="2099" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2099" s="3"/>
+      <c r="B2099" s="3"/>
+      <c r="C2099" s="3"/>
+      <c r="D2099" s="3"/>
+      <c r="E2099" s="3"/>
+      <c r="F2099" s="3"/>
+      <c r="G2099" s="3"/>
+      <c r="H2099" s="3"/>
+      <c r="I2099" s="4"/>
+      <c r="J2099" s="4"/>
+    </row>
+    <row r="2100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2100" s="3"/>
+      <c r="B2100" s="3"/>
+      <c r="C2100" s="3"/>
+      <c r="D2100" s="3"/>
+      <c r="E2100" s="3"/>
+      <c r="F2100" s="3"/>
+      <c r="G2100" s="3"/>
+      <c r="H2100" s="3"/>
+      <c r="I2100" s="4"/>
+      <c r="J2100" s="4"/>
+    </row>
+    <row r="2101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2101" s="3"/>
+      <c r="B2101" s="3"/>
+      <c r="C2101" s="3"/>
+      <c r="D2101" s="3"/>
+      <c r="E2101" s="3"/>
+      <c r="F2101" s="3"/>
+      <c r="G2101" s="3"/>
+      <c r="H2101" s="3"/>
+      <c r="I2101" s="4"/>
+      <c r="J2101" s="4"/>
+    </row>
+    <row r="2102" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2102" s="3"/>
+      <c r="B2102" s="3"/>
+      <c r="C2102" s="3"/>
+      <c r="D2102" s="3"/>
+      <c r="E2102" s="3"/>
+      <c r="F2102" s="3"/>
+      <c r="G2102" s="3"/>
+      <c r="H2102" s="3"/>
+      <c r="I2102" s="4"/>
+      <c r="J2102" s="4"/>
+    </row>
+    <row r="2103" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2103" s="3"/>
+      <c r="B2103" s="3"/>
+      <c r="C2103" s="3"/>
+      <c r="D2103" s="3"/>
+      <c r="E2103" s="3"/>
+      <c r="F2103" s="3"/>
+      <c r="G2103" s="3"/>
+      <c r="H2103" s="3"/>
+      <c r="I2103" s="4"/>
+      <c r="J2103" s="4"/>
+    </row>
+    <row r="2104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2104" s="3"/>
+      <c r="B2104" s="3"/>
+      <c r="C2104" s="3"/>
+      <c r="D2104" s="3"/>
+      <c r="E2104" s="3"/>
+      <c r="F2104" s="3"/>
+      <c r="G2104" s="3"/>
+      <c r="H2104" s="3"/>
+      <c r="I2104" s="4"/>
+      <c r="J2104" s="4"/>
+    </row>
+    <row r="2105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2105" s="3"/>
+      <c r="B2105" s="3"/>
+      <c r="C2105" s="3"/>
+      <c r="D2105" s="3"/>
+      <c r="E2105" s="3"/>
+      <c r="F2105" s="3"/>
+      <c r="G2105" s="3"/>
+      <c r="H2105" s="3"/>
+      <c r="I2105" s="4"/>
+      <c r="J2105" s="4"/>
+    </row>
+    <row r="2106" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2106" s="3"/>
+      <c r="B2106" s="3"/>
+      <c r="C2106" s="3"/>
+      <c r="D2106" s="3"/>
+      <c r="E2106" s="3"/>
+      <c r="F2106" s="3"/>
+      <c r="G2106" s="3"/>
+      <c r="H2106" s="3"/>
+      <c r="I2106" s="4"/>
+      <c r="J2106" s="4"/>
+    </row>
+    <row r="2107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2107" s="3"/>
+      <c r="B2107" s="3"/>
+      <c r="C2107" s="3"/>
+      <c r="D2107" s="3"/>
+      <c r="E2107" s="3"/>
+      <c r="F2107" s="3"/>
+      <c r="G2107" s="3"/>
+      <c r="H2107" s="3"/>
+      <c r="I2107" s="4"/>
+      <c r="J2107" s="4"/>
+    </row>
+    <row r="2108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2108" s="3"/>
+      <c r="B2108" s="3"/>
+      <c r="C2108" s="3"/>
+      <c r="D2108" s="3"/>
+      <c r="E2108" s="3"/>
+      <c r="F2108" s="3"/>
+      <c r="G2108" s="3"/>
+      <c r="H2108" s="3"/>
+      <c r="I2108" s="4"/>
+      <c r="J2108" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBF39F9-63C1-4EEA-9574-AECA13E7C251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596647C3-6DDA-4C82-A8FD-13CFEE302792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1575" yWindow="465" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5082,9 +5082,6 @@
     <t>#planning</t>
   </si>
   <si>
-    <t>Consolidate all tasks in Obsidian.</t>
-  </si>
-  <si>
     <t>2026-06-23</t>
   </si>
   <si>
@@ -5098,6 +5095,9 @@
   </si>
   <si>
     <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>Consolidated all tasks in Obsidian.</t>
   </si>
 </sst>
 </file>
@@ -74914,11 +74914,11 @@
         <v>280</v>
       </c>
       <c r="I2067" s="4">
-        <f t="shared" ref="I2067:I2078" si="978">YEAR(A2067)</f>
+        <f t="shared" ref="I2067:I2077" si="978">YEAR(A2067)</f>
         <v>2026</v>
       </c>
       <c r="J2067" s="4">
-        <f t="shared" ref="J2067:J2078" si="979">MONTH(A2067)</f>
+        <f t="shared" ref="J2067:J2077" si="979">MONTH(A2067)</f>
         <v>6</v>
       </c>
     </row>
@@ -75007,7 +75007,7 @@
         <v>1682</v>
       </c>
       <c r="F2070" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2070" s="8" t="s">
         <v>280</v>
@@ -75041,7 +75041,7 @@
         <v>1682</v>
       </c>
       <c r="F2071" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2071" s="8" t="s">
         <v>280</v>
@@ -75075,7 +75075,7 @@
         <v>1682</v>
       </c>
       <c r="F2072" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2072" s="8" t="s">
         <v>280</v>
@@ -75094,7 +75094,7 @@
     </row>
     <row r="2073" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2073" s="3" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B2073" s="3" t="s">
         <v>241</v>
@@ -75109,7 +75109,7 @@
         <v>1682</v>
       </c>
       <c r="F2073" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2073" s="8" t="s">
         <v>280</v>
@@ -75128,7 +75128,7 @@
     </row>
     <row r="2074" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2074" s="3" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B2074" s="3" t="s">
         <v>150</v>
@@ -75143,7 +75143,7 @@
         <v>1682</v>
       </c>
       <c r="F2074" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2074" s="8" t="s">
         <v>280</v>
@@ -75162,7 +75162,7 @@
     </row>
     <row r="2075" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2075" s="3" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B2075" s="3" t="s">
         <v>150</v>
@@ -75177,7 +75177,7 @@
         <v>140</v>
       </c>
       <c r="F2075" s="3" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="G2075" s="8" t="s">
         <v>280</v>
@@ -75196,7 +75196,7 @@
     </row>
     <row r="2076" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2076" s="3" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B2076" s="3" t="s">
         <v>285</v>
@@ -75211,7 +75211,7 @@
         <v>140</v>
       </c>
       <c r="F2076" s="3" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="G2076" s="8" t="s">
         <v>280</v>
@@ -75230,7 +75230,7 @@
     </row>
     <row r="2077" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2077" s="3" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B2077" s="3" t="s">
         <v>203</v>
@@ -75245,7 +75245,7 @@
         <v>140</v>
       </c>
       <c r="F2077" s="3" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="G2077" s="8" t="s">
         <v>280</v>
@@ -75264,7 +75264,7 @@
     </row>
     <row r="2078" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2078" s="3" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="B2078" s="3" t="s">
         <v>248</v>
@@ -75279,7 +75279,7 @@
         <v>1682</v>
       </c>
       <c r="F2078" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2078" s="8" t="s">
         <v>280</v>
@@ -75298,7 +75298,7 @@
     </row>
     <row r="2079" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2079" s="3" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B2079" s="3" t="s">
         <v>132</v>
@@ -75313,7 +75313,7 @@
         <v>1682</v>
       </c>
       <c r="F2079" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2079" s="8" t="s">
         <v>280</v>
@@ -75332,7 +75332,7 @@
     </row>
     <row r="2080" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2080" s="3" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B2080" s="3" t="s">
         <v>209</v>
@@ -75347,7 +75347,7 @@
         <v>1682</v>
       </c>
       <c r="F2080" s="3" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G2080" s="8" t="s">
         <v>280</v>
@@ -75366,7 +75366,7 @@
     </row>
     <row r="2081" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2081" s="3" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B2081" s="3" t="s">
         <v>174</v>
@@ -75398,7 +75398,7 @@
     </row>
     <row r="2082" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2082" s="3" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B2082" s="3" t="s">
         <v>147</v>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596647C3-6DDA-4C82-A8FD-13CFEE302792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68414CF-31FB-4FB9-925A-DF59FEA549C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="465" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="-14730" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16215" uniqueCount="1689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16516" uniqueCount="1716">
   <si>
     <t>Year</t>
   </si>
@@ -5098,6 +5098,87 @@
   </si>
   <si>
     <t>Consolidated all tasks in Obsidian.</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>config-userguide</t>
+  </si>
+  <si>
+    <t>nwreadinglist v6.0.1</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>nwtimetracking v6.0.1</t>
+  </si>
+  <si>
+    <t>nwversioninfofiles v2.0.1</t>
+  </si>
+  <si>
+    <t>nwdocstringchecking v2.0.1</t>
+  </si>
+  <si>
+    <t>nwpackageversions v2.0.1</t>
+  </si>
+  <si>
+    <t>nwcommitaverages v2.0.1</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>nwrefurbishedanalytics v1.0.3</t>
+  </si>
+  <si>
+    <t>nwtraderaanalytics v4.5.3</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>NW.ZooSketchDownloader v2.0.2</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>NW.ZooSketchDownloader v2.0.3</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>NW.NGramTextClassification v4.2.1</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
   </si>
 </sst>
 </file>
@@ -5512,7 +5593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2108"/>
+  <dimension ref="A1:J2168"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -75103,7 +75184,7 @@
         <v>161</v>
       </c>
       <c r="D2073" s="3" t="s">
-        <v>873</v>
+        <v>272</v>
       </c>
       <c r="E2073" s="3" t="s">
         <v>1682</v>
@@ -75288,11 +75369,11 @@
         <v>280</v>
       </c>
       <c r="I2078" s="4">
-        <f t="shared" ref="I2078:I2082" si="980">YEAR(A2078)</f>
+        <f t="shared" ref="I2078" si="980">YEAR(A2078)</f>
         <v>2026</v>
       </c>
       <c r="J2078" s="4">
-        <f t="shared" ref="J2078:J2082" si="981">MONTH(A2078)</f>
+        <f t="shared" ref="J2078:J2121" si="981">MONTH(A2078)</f>
         <v>6</v>
       </c>
     </row>
@@ -75322,7 +75403,7 @@
         <v>280</v>
       </c>
       <c r="I2079" s="4">
-        <f t="shared" si="980"/>
+        <f>YEAR(A2079)</f>
         <v>2026</v>
       </c>
       <c r="J2079" s="4">
@@ -75356,7 +75437,7 @@
         <v>280</v>
       </c>
       <c r="I2080" s="4">
-        <f t="shared" si="980"/>
+        <f t="shared" ref="I2080:I2121" si="982">YEAR(A2080)</f>
         <v>2026</v>
       </c>
       <c r="J2080" s="4">
@@ -75388,7 +75469,7 @@
         <v>280</v>
       </c>
       <c r="I2081" s="4">
-        <f t="shared" si="980"/>
+        <f t="shared" si="982"/>
         <v>2026</v>
       </c>
       <c r="J2081" s="4">
@@ -75420,7 +75501,7 @@
         <v>280</v>
       </c>
       <c r="I2082" s="4">
-        <f t="shared" si="980"/>
+        <f t="shared" si="982"/>
         <v>2026</v>
       </c>
       <c r="J2082" s="4">
@@ -75429,316 +75510,1872 @@
       </c>
     </row>
     <row r="2083" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2083" s="3"/>
-      <c r="B2083" s="3"/>
-      <c r="C2083" s="3"/>
-      <c r="D2083" s="3"/>
-      <c r="E2083" s="3"/>
-      <c r="F2083" s="3"/>
-      <c r="G2083" s="3"/>
-      <c r="H2083" s="3"/>
-      <c r="I2083" s="4"/>
-      <c r="J2083" s="4"/>
+      <c r="A2083" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B2083" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2083" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2083" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2083" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2083" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G2083" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2083" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2083" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2083" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2084" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2084" s="3"/>
-      <c r="B2084" s="3"/>
-      <c r="C2084" s="3"/>
-      <c r="D2084" s="3"/>
-      <c r="E2084" s="3"/>
-      <c r="F2084" s="3"/>
-      <c r="G2084" s="3"/>
-      <c r="H2084" s="3"/>
-      <c r="I2084" s="4"/>
-      <c r="J2084" s="4"/>
+      <c r="A2084" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B2084" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2084" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2084" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2084" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2084" s="3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G2084" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2084" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2084" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2084" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2085" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2085" s="3"/>
-      <c r="B2085" s="3"/>
-      <c r="C2085" s="3"/>
-      <c r="D2085" s="3"/>
-      <c r="E2085" s="3"/>
-      <c r="F2085" s="3"/>
-      <c r="G2085" s="3"/>
-      <c r="H2085" s="3"/>
-      <c r="I2085" s="4"/>
-      <c r="J2085" s="4"/>
+      <c r="A2085" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B2085" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2085" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2085" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2085" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2085" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G2085" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2085" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2085" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2085" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2086" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2086" s="3"/>
-      <c r="B2086" s="3"/>
-      <c r="C2086" s="3"/>
-      <c r="D2086" s="3"/>
-      <c r="E2086" s="3"/>
-      <c r="F2086" s="3"/>
-      <c r="G2086" s="3"/>
-      <c r="H2086" s="3"/>
-      <c r="I2086" s="4"/>
-      <c r="J2086" s="4"/>
+      <c r="A2086" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2086" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2086" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2086" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2086" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2086" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G2086" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2086" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2086" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2086" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2087" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2087" s="3"/>
-      <c r="B2087" s="3"/>
-      <c r="C2087" s="3"/>
-      <c r="D2087" s="3"/>
-      <c r="E2087" s="3"/>
-      <c r="F2087" s="3"/>
-      <c r="G2087" s="3"/>
-      <c r="H2087" s="3"/>
-      <c r="I2087" s="4"/>
-      <c r="J2087" s="4"/>
+      <c r="A2087" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2087" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2087" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2087" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2087" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2087" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G2087" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2087" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2087" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2087" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2088" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2088" s="3"/>
-      <c r="B2088" s="3"/>
-      <c r="C2088" s="3"/>
-      <c r="D2088" s="3"/>
-      <c r="E2088" s="3"/>
-      <c r="F2088" s="3"/>
-      <c r="G2088" s="3"/>
-      <c r="H2088" s="3"/>
-      <c r="I2088" s="4"/>
-      <c r="J2088" s="4"/>
+      <c r="A2088" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2088" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2088" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2088" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2088" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2088" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G2088" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2088" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2088" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2088" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2089" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2089" s="3"/>
-      <c r="B2089" s="3"/>
-      <c r="C2089" s="3"/>
-      <c r="D2089" s="3"/>
-      <c r="E2089" s="3"/>
-      <c r="F2089" s="3"/>
-      <c r="G2089" s="3"/>
-      <c r="H2089" s="3"/>
-      <c r="I2089" s="4"/>
-      <c r="J2089" s="4"/>
+      <c r="A2089" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2089" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2089" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2089" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2089" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2089" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G2089" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2089" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2089" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2089" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2090" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2090" s="3"/>
-      <c r="B2090" s="3"/>
-      <c r="C2090" s="3"/>
-      <c r="D2090" s="3"/>
-      <c r="E2090" s="3"/>
-      <c r="F2090" s="3"/>
-      <c r="G2090" s="3"/>
-      <c r="H2090" s="3"/>
-      <c r="I2090" s="4"/>
-      <c r="J2090" s="4"/>
+      <c r="A2090" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2090" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2090" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2090" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2090" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2090" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G2090" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2090" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2090" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2090" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2091" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2091" s="3"/>
-      <c r="B2091" s="3"/>
-      <c r="C2091" s="3"/>
-      <c r="D2091" s="3"/>
-      <c r="E2091" s="3"/>
-      <c r="F2091" s="3"/>
-      <c r="G2091" s="3"/>
-      <c r="H2091" s="3"/>
-      <c r="I2091" s="4"/>
-      <c r="J2091" s="4"/>
+      <c r="A2091" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2091" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2091" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2091" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2091" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2091" s="3" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G2091" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2091" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2091" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2091" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2092" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2092" s="3"/>
-      <c r="B2092" s="3"/>
-      <c r="C2092" s="3"/>
-      <c r="D2092" s="3"/>
-      <c r="E2092" s="3"/>
-      <c r="F2092" s="3"/>
-      <c r="G2092" s="3"/>
-      <c r="H2092" s="3"/>
-      <c r="I2092" s="4"/>
-      <c r="J2092" s="4"/>
+      <c r="A2092" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2092" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2092" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2092" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2092" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2092" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="G2092" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2092" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2092" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2092" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2093" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2093" s="3"/>
-      <c r="B2093" s="3"/>
-      <c r="C2093" s="3"/>
-      <c r="D2093" s="3"/>
-      <c r="E2093" s="3"/>
-      <c r="F2093" s="3"/>
-      <c r="G2093" s="3"/>
-      <c r="H2093" s="3"/>
-      <c r="I2093" s="4"/>
-      <c r="J2093" s="4"/>
+      <c r="A2093" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B2093" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2093" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2093" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2093" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2093" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="G2093" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2093" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2093" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2093" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2094" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2094" s="3"/>
-      <c r="B2094" s="3"/>
-      <c r="C2094" s="3"/>
-      <c r="D2094" s="3"/>
-      <c r="E2094" s="3"/>
-      <c r="F2094" s="3"/>
-      <c r="G2094" s="3"/>
-      <c r="H2094" s="3"/>
-      <c r="I2094" s="4"/>
-      <c r="J2094" s="4"/>
+      <c r="A2094" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B2094" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2094" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2094" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2094" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2094" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="G2094" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2094" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2094" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2094" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2095" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2095" s="3"/>
-      <c r="B2095" s="3"/>
-      <c r="C2095" s="3"/>
-      <c r="D2095" s="3"/>
-      <c r="E2095" s="3"/>
-      <c r="F2095" s="3"/>
-      <c r="G2095" s="3"/>
-      <c r="H2095" s="3"/>
-      <c r="I2095" s="4"/>
-      <c r="J2095" s="4"/>
+      <c r="A2095" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B2095" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2095" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2095" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2095" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2095" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G2095" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2095" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2095" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2095" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2096" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2096" s="3"/>
-      <c r="B2096" s="3"/>
-      <c r="C2096" s="3"/>
-      <c r="D2096" s="3"/>
-      <c r="E2096" s="3"/>
-      <c r="F2096" s="3"/>
-      <c r="G2096" s="3"/>
-      <c r="H2096" s="3"/>
-      <c r="I2096" s="4"/>
-      <c r="J2096" s="4"/>
+      <c r="A2096" s="3" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B2096" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2096" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2096" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2096" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2096" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G2096" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2096" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2096" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2096" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2097" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2097" s="3"/>
-      <c r="B2097" s="3"/>
-      <c r="C2097" s="3"/>
-      <c r="D2097" s="3"/>
-      <c r="E2097" s="3"/>
-      <c r="F2097" s="3"/>
-      <c r="G2097" s="3"/>
-      <c r="H2097" s="3"/>
-      <c r="I2097" s="4"/>
-      <c r="J2097" s="4"/>
+      <c r="A2097" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B2097" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2097" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2097" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2097" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2097" s="3" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G2097" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2097" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2097" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2097" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2098" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2098" s="3"/>
-      <c r="B2098" s="3"/>
-      <c r="C2098" s="3"/>
-      <c r="D2098" s="3"/>
-      <c r="E2098" s="3"/>
+      <c r="A2098" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B2098" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2098" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2098" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2098" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2098" s="3"/>
-      <c r="G2098" s="3"/>
-      <c r="H2098" s="3"/>
-      <c r="I2098" s="4"/>
-      <c r="J2098" s="4"/>
+      <c r="G2098" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2098" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2098" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2098" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2099" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2099" s="3"/>
-      <c r="B2099" s="3"/>
-      <c r="C2099" s="3"/>
-      <c r="D2099" s="3"/>
-      <c r="E2099" s="3"/>
+      <c r="A2099" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B2099" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2099" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2099" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2099" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2099" s="3"/>
-      <c r="G2099" s="3"/>
-      <c r="H2099" s="3"/>
-      <c r="I2099" s="4"/>
-      <c r="J2099" s="4"/>
+      <c r="G2099" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2099" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2099" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2099" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2100" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2100" s="3"/>
-      <c r="B2100" s="3"/>
-      <c r="C2100" s="3"/>
-      <c r="D2100" s="3"/>
-      <c r="E2100" s="3"/>
+      <c r="A2100" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B2100" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2100" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2100" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2100" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2100" s="3"/>
-      <c r="G2100" s="3"/>
-      <c r="H2100" s="3"/>
-      <c r="I2100" s="4"/>
-      <c r="J2100" s="4"/>
+      <c r="G2100" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2100" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2100" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2100" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2101" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2101" s="3"/>
-      <c r="B2101" s="3"/>
-      <c r="C2101" s="3"/>
-      <c r="D2101" s="3"/>
-      <c r="E2101" s="3"/>
+      <c r="A2101" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B2101" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2101" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2101" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2101" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2101" s="3"/>
-      <c r="G2101" s="3"/>
-      <c r="H2101" s="3"/>
-      <c r="I2101" s="4"/>
-      <c r="J2101" s="4"/>
+      <c r="G2101" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2101" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2101" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2101" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2102" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2102" s="3"/>
-      <c r="B2102" s="3"/>
-      <c r="C2102" s="3"/>
-      <c r="D2102" s="3"/>
-      <c r="E2102" s="3"/>
+      <c r="A2102" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B2102" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2102" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2102" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2102" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2102" s="3"/>
-      <c r="G2102" s="3"/>
-      <c r="H2102" s="3"/>
-      <c r="I2102" s="4"/>
-      <c r="J2102" s="4"/>
+      <c r="G2102" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2102" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2102" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2102" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2103" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2103" s="3"/>
-      <c r="B2103" s="3"/>
-      <c r="C2103" s="3"/>
-      <c r="D2103" s="3"/>
-      <c r="E2103" s="3"/>
+      <c r="A2103" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B2103" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2103" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2103" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2103" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2103" s="3"/>
-      <c r="G2103" s="3"/>
-      <c r="H2103" s="3"/>
-      <c r="I2103" s="4"/>
-      <c r="J2103" s="4"/>
+      <c r="G2103" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2103" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2103" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2103" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2104" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2104" s="3"/>
-      <c r="B2104" s="3"/>
-      <c r="C2104" s="3"/>
-      <c r="D2104" s="3"/>
-      <c r="E2104" s="3"/>
+      <c r="A2104" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B2104" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2104" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2104" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2104" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2104" s="3"/>
-      <c r="G2104" s="3"/>
-      <c r="H2104" s="3"/>
-      <c r="I2104" s="4"/>
-      <c r="J2104" s="4"/>
+      <c r="G2104" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2104" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2104" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2104" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2105" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2105" s="3"/>
-      <c r="B2105" s="3"/>
-      <c r="C2105" s="3"/>
-      <c r="D2105" s="3"/>
-      <c r="E2105" s="3"/>
-      <c r="F2105" s="3"/>
-      <c r="G2105" s="3"/>
-      <c r="H2105" s="3"/>
-      <c r="I2105" s="4"/>
-      <c r="J2105" s="4"/>
+      <c r="A2105" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B2105" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2105" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2105" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2105" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2105" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G2105" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2105" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2105" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2105" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2106" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2106" s="3"/>
-      <c r="B2106" s="3"/>
-      <c r="C2106" s="3"/>
-      <c r="D2106" s="3"/>
-      <c r="E2106" s="3"/>
-      <c r="F2106" s="3"/>
-      <c r="G2106" s="3"/>
-      <c r="H2106" s="3"/>
-      <c r="I2106" s="4"/>
-      <c r="J2106" s="4"/>
+      <c r="A2106" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B2106" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2106" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2106" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2106" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2106" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G2106" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2106" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2106" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2106" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2107" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2107" s="3"/>
-      <c r="B2107" s="3"/>
-      <c r="C2107" s="3"/>
-      <c r="D2107" s="3"/>
-      <c r="E2107" s="3"/>
-      <c r="F2107" s="3"/>
-      <c r="G2107" s="3"/>
-      <c r="H2107" s="3"/>
-      <c r="I2107" s="4"/>
-      <c r="J2107" s="4"/>
+      <c r="A2107" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B2107" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2107" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2107" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2107" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2107" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G2107" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2107" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2107" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2107" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2108" s="3"/>
-      <c r="B2108" s="3"/>
-      <c r="C2108" s="3"/>
-      <c r="D2108" s="3"/>
-      <c r="E2108" s="3"/>
-      <c r="F2108" s="3"/>
-      <c r="G2108" s="3"/>
-      <c r="H2108" s="3"/>
-      <c r="I2108" s="4"/>
-      <c r="J2108" s="4"/>
+      <c r="A2108" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B2108" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2108" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2108" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2108" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2108" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G2108" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2108" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2108" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2108" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2109" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B2109" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2109" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2109" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2109" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2109" s="3"/>
+      <c r="G2109" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2109" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2109" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2109" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2110" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B2110" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2110" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2110" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2110" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2110" s="3"/>
+      <c r="G2110" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2110" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2110" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2110" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2111" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B2111" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2111" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2111" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2111" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2111" s="3"/>
+      <c r="G2111" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2111" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2111" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2111" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2112" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B2112" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2112" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2112" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2112" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2112" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2112" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2112" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2112" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2112" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2113" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B2113" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2113" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2113" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2113" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F2113" s="3"/>
+      <c r="G2113" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2113" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2113" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2113" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2114" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B2114" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2114" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2114" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2114" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2114" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2114" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2114" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2114" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2114" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2115" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B2115" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2115" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2115" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2115" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2115" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2115" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2115" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2115" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2115" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2116" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B2116" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2116" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2116" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E2116" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2116" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2116" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2116" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2116" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2116" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2117" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B2117" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2117" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2117" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2117" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2117" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2117" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2117" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2117" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2117" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2118" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B2118" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2118" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2118" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2118" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2118" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2118" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2118" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2118" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2118" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2119" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B2119" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2119" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2119" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2119" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2119" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2119" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2119" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2119" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2119" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2120" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B2120" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2120" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2120" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2120" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2120" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2120" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2120" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2120" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2120" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2121" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B2121" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2121" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2121" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2121" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2121" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G2121" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2121" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2121" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2121" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2122" s="3"/>
+      <c r="B2122" s="3"/>
+      <c r="C2122" s="3"/>
+      <c r="D2122" s="3"/>
+      <c r="E2122" s="3"/>
+      <c r="F2122" s="3"/>
+      <c r="G2122" s="3"/>
+      <c r="H2122" s="3"/>
+      <c r="I2122" s="4"/>
+      <c r="J2122" s="4"/>
+    </row>
+    <row r="2123" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2123" s="3"/>
+      <c r="B2123" s="3"/>
+      <c r="C2123" s="3"/>
+      <c r="D2123" s="3"/>
+      <c r="E2123" s="3"/>
+      <c r="F2123" s="3"/>
+      <c r="G2123" s="3"/>
+      <c r="H2123" s="3"/>
+      <c r="I2123" s="4"/>
+      <c r="J2123" s="4"/>
+    </row>
+    <row r="2124" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2124" s="3"/>
+      <c r="B2124" s="3"/>
+      <c r="C2124" s="3"/>
+      <c r="D2124" s="3"/>
+      <c r="E2124" s="3"/>
+      <c r="F2124" s="3"/>
+      <c r="G2124" s="3"/>
+      <c r="H2124" s="3"/>
+      <c r="I2124" s="4"/>
+      <c r="J2124" s="4"/>
+    </row>
+    <row r="2125" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2125" s="3"/>
+      <c r="B2125" s="3"/>
+      <c r="C2125" s="3"/>
+      <c r="D2125" s="3"/>
+      <c r="E2125" s="3"/>
+      <c r="F2125" s="3"/>
+      <c r="G2125" s="3"/>
+      <c r="H2125" s="3"/>
+      <c r="I2125" s="4"/>
+      <c r="J2125" s="4"/>
+    </row>
+    <row r="2126" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2126" s="3"/>
+      <c r="B2126" s="3"/>
+      <c r="C2126" s="3"/>
+      <c r="D2126" s="3"/>
+      <c r="E2126" s="3"/>
+      <c r="F2126" s="3"/>
+      <c r="G2126" s="3"/>
+      <c r="H2126" s="3"/>
+      <c r="I2126" s="4"/>
+      <c r="J2126" s="4"/>
+    </row>
+    <row r="2127" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2127" s="3"/>
+      <c r="B2127" s="3"/>
+      <c r="C2127" s="3"/>
+      <c r="D2127" s="3"/>
+      <c r="E2127" s="3"/>
+      <c r="F2127" s="3"/>
+      <c r="G2127" s="3"/>
+      <c r="H2127" s="3"/>
+      <c r="I2127" s="4"/>
+      <c r="J2127" s="4"/>
+    </row>
+    <row r="2128" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2128" s="3"/>
+      <c r="B2128" s="3"/>
+      <c r="C2128" s="3"/>
+      <c r="D2128" s="3"/>
+      <c r="E2128" s="3"/>
+      <c r="F2128" s="3"/>
+      <c r="G2128" s="3"/>
+      <c r="H2128" s="3"/>
+      <c r="I2128" s="4"/>
+      <c r="J2128" s="4"/>
+    </row>
+    <row r="2129" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2129" s="3"/>
+      <c r="B2129" s="3"/>
+      <c r="C2129" s="3"/>
+      <c r="D2129" s="3"/>
+      <c r="E2129" s="3"/>
+      <c r="F2129" s="3"/>
+      <c r="G2129" s="3"/>
+      <c r="H2129" s="3"/>
+      <c r="I2129" s="4"/>
+      <c r="J2129" s="4"/>
+    </row>
+    <row r="2130" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2130" s="3"/>
+      <c r="B2130" s="3"/>
+      <c r="C2130" s="3"/>
+      <c r="D2130" s="3"/>
+      <c r="E2130" s="3"/>
+      <c r="F2130" s="3"/>
+      <c r="G2130" s="3"/>
+      <c r="H2130" s="3"/>
+      <c r="I2130" s="4"/>
+      <c r="J2130" s="4"/>
+    </row>
+    <row r="2131" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2131" s="3"/>
+      <c r="B2131" s="3"/>
+      <c r="C2131" s="3"/>
+      <c r="D2131" s="3"/>
+      <c r="E2131" s="3"/>
+      <c r="F2131" s="3"/>
+      <c r="G2131" s="3"/>
+      <c r="H2131" s="3"/>
+      <c r="I2131" s="4"/>
+      <c r="J2131" s="4"/>
+    </row>
+    <row r="2132" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2132" s="3"/>
+      <c r="B2132" s="3"/>
+      <c r="C2132" s="3"/>
+      <c r="D2132" s="3"/>
+      <c r="E2132" s="3"/>
+      <c r="F2132" s="3"/>
+      <c r="G2132" s="3"/>
+      <c r="H2132" s="3"/>
+      <c r="I2132" s="4"/>
+      <c r="J2132" s="4"/>
+    </row>
+    <row r="2133" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2133" s="3"/>
+      <c r="B2133" s="3"/>
+      <c r="C2133" s="3"/>
+      <c r="D2133" s="3"/>
+      <c r="E2133" s="3"/>
+      <c r="F2133" s="3"/>
+      <c r="G2133" s="3"/>
+      <c r="H2133" s="3"/>
+      <c r="I2133" s="4"/>
+      <c r="J2133" s="4"/>
+    </row>
+    <row r="2134" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2134" s="3"/>
+      <c r="B2134" s="3"/>
+      <c r="C2134" s="3"/>
+      <c r="D2134" s="3"/>
+      <c r="E2134" s="3"/>
+      <c r="F2134" s="3"/>
+      <c r="G2134" s="3"/>
+      <c r="H2134" s="3"/>
+      <c r="I2134" s="4"/>
+      <c r="J2134" s="4"/>
+    </row>
+    <row r="2135" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2135" s="3"/>
+      <c r="B2135" s="3"/>
+      <c r="C2135" s="3"/>
+      <c r="D2135" s="3"/>
+      <c r="E2135" s="3"/>
+      <c r="F2135" s="3"/>
+      <c r="G2135" s="3"/>
+      <c r="H2135" s="3"/>
+      <c r="I2135" s="4"/>
+      <c r="J2135" s="4"/>
+    </row>
+    <row r="2136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2136" s="3"/>
+      <c r="B2136" s="3"/>
+      <c r="C2136" s="3"/>
+      <c r="D2136" s="3"/>
+      <c r="E2136" s="3"/>
+      <c r="F2136" s="3"/>
+      <c r="G2136" s="3"/>
+      <c r="H2136" s="3"/>
+      <c r="I2136" s="4"/>
+      <c r="J2136" s="4"/>
+    </row>
+    <row r="2137" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2137" s="3"/>
+      <c r="B2137" s="3"/>
+      <c r="C2137" s="3"/>
+      <c r="D2137" s="3"/>
+      <c r="E2137" s="3"/>
+      <c r="F2137" s="3"/>
+      <c r="G2137" s="3"/>
+      <c r="H2137" s="3"/>
+      <c r="I2137" s="4"/>
+      <c r="J2137" s="4"/>
+    </row>
+    <row r="2138" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2138" s="3"/>
+      <c r="B2138" s="3"/>
+      <c r="C2138" s="3"/>
+      <c r="D2138" s="3"/>
+      <c r="E2138" s="3"/>
+      <c r="F2138" s="3"/>
+      <c r="G2138" s="3"/>
+      <c r="H2138" s="3"/>
+      <c r="I2138" s="4"/>
+      <c r="J2138" s="4"/>
+    </row>
+    <row r="2139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2139" s="3"/>
+      <c r="B2139" s="3"/>
+      <c r="C2139" s="3"/>
+      <c r="D2139" s="3"/>
+      <c r="E2139" s="3"/>
+      <c r="F2139" s="3"/>
+      <c r="G2139" s="3"/>
+      <c r="H2139" s="3"/>
+      <c r="I2139" s="4"/>
+      <c r="J2139" s="4"/>
+    </row>
+    <row r="2140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2140" s="3"/>
+      <c r="B2140" s="3"/>
+      <c r="C2140" s="3"/>
+      <c r="D2140" s="3"/>
+      <c r="E2140" s="3"/>
+      <c r="F2140" s="3"/>
+      <c r="G2140" s="3"/>
+      <c r="H2140" s="3"/>
+      <c r="I2140" s="4"/>
+      <c r="J2140" s="4"/>
+    </row>
+    <row r="2141" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2141" s="3"/>
+      <c r="B2141" s="3"/>
+      <c r="C2141" s="3"/>
+      <c r="D2141" s="3"/>
+      <c r="E2141" s="3"/>
+      <c r="F2141" s="3"/>
+      <c r="G2141" s="3"/>
+      <c r="H2141" s="3"/>
+      <c r="I2141" s="4"/>
+      <c r="J2141" s="4"/>
+    </row>
+    <row r="2142" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2142" s="3"/>
+      <c r="B2142" s="3"/>
+      <c r="C2142" s="3"/>
+      <c r="D2142" s="3"/>
+      <c r="E2142" s="3"/>
+      <c r="F2142" s="3"/>
+      <c r="G2142" s="3"/>
+      <c r="H2142" s="3"/>
+      <c r="I2142" s="4"/>
+      <c r="J2142" s="4"/>
+    </row>
+    <row r="2143" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2143" s="3"/>
+      <c r="B2143" s="3"/>
+      <c r="C2143" s="3"/>
+      <c r="D2143" s="3"/>
+      <c r="E2143" s="3"/>
+      <c r="F2143" s="3"/>
+      <c r="G2143" s="3"/>
+      <c r="H2143" s="3"/>
+      <c r="I2143" s="4"/>
+      <c r="J2143" s="4"/>
+    </row>
+    <row r="2144" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2144" s="3"/>
+      <c r="B2144" s="3"/>
+      <c r="C2144" s="3"/>
+      <c r="D2144" s="3"/>
+      <c r="E2144" s="3"/>
+      <c r="F2144" s="3"/>
+      <c r="G2144" s="3"/>
+      <c r="H2144" s="3"/>
+      <c r="I2144" s="4"/>
+      <c r="J2144" s="4"/>
+    </row>
+    <row r="2145" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2145" s="3"/>
+      <c r="B2145" s="3"/>
+      <c r="C2145" s="3"/>
+      <c r="D2145" s="3"/>
+      <c r="E2145" s="3"/>
+      <c r="F2145" s="3"/>
+      <c r="G2145" s="3"/>
+      <c r="H2145" s="3"/>
+      <c r="I2145" s="4"/>
+      <c r="J2145" s="4"/>
+    </row>
+    <row r="2146" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2146" s="3"/>
+      <c r="B2146" s="3"/>
+      <c r="C2146" s="3"/>
+      <c r="D2146" s="3"/>
+      <c r="E2146" s="3"/>
+      <c r="F2146" s="3"/>
+      <c r="G2146" s="3"/>
+      <c r="H2146" s="3"/>
+      <c r="I2146" s="4"/>
+      <c r="J2146" s="4"/>
+    </row>
+    <row r="2147" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2147" s="3"/>
+      <c r="B2147" s="3"/>
+      <c r="C2147" s="3"/>
+      <c r="D2147" s="3"/>
+      <c r="E2147" s="3"/>
+      <c r="F2147" s="3"/>
+      <c r="G2147" s="3"/>
+      <c r="H2147" s="3"/>
+      <c r="I2147" s="4"/>
+      <c r="J2147" s="4"/>
+    </row>
+    <row r="2148" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2148" s="3"/>
+      <c r="B2148" s="3"/>
+      <c r="C2148" s="3"/>
+      <c r="D2148" s="3"/>
+      <c r="E2148" s="3"/>
+      <c r="F2148" s="3"/>
+      <c r="G2148" s="3"/>
+      <c r="H2148" s="3"/>
+      <c r="I2148" s="4"/>
+      <c r="J2148" s="4"/>
+    </row>
+    <row r="2149" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2149" s="3"/>
+      <c r="B2149" s="3"/>
+      <c r="C2149" s="3"/>
+      <c r="D2149" s="3"/>
+      <c r="E2149" s="3"/>
+      <c r="F2149" s="3"/>
+      <c r="G2149" s="3"/>
+      <c r="H2149" s="3"/>
+      <c r="I2149" s="4"/>
+      <c r="J2149" s="4"/>
+    </row>
+    <row r="2150" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2150" s="3"/>
+      <c r="B2150" s="3"/>
+      <c r="C2150" s="3"/>
+      <c r="D2150" s="3"/>
+      <c r="E2150" s="3"/>
+      <c r="F2150" s="3"/>
+      <c r="G2150" s="3"/>
+      <c r="H2150" s="3"/>
+      <c r="I2150" s="4"/>
+      <c r="J2150" s="4"/>
+    </row>
+    <row r="2151" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2151" s="3"/>
+      <c r="B2151" s="3"/>
+      <c r="C2151" s="3"/>
+      <c r="D2151" s="3"/>
+      <c r="E2151" s="3"/>
+      <c r="F2151" s="3"/>
+      <c r="G2151" s="3"/>
+      <c r="H2151" s="3"/>
+      <c r="I2151" s="4"/>
+      <c r="J2151" s="4"/>
+    </row>
+    <row r="2152" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2152" s="3"/>
+      <c r="B2152" s="3"/>
+      <c r="C2152" s="3"/>
+      <c r="D2152" s="3"/>
+      <c r="E2152" s="3"/>
+      <c r="F2152" s="3"/>
+      <c r="G2152" s="3"/>
+      <c r="H2152" s="3"/>
+      <c r="I2152" s="4"/>
+      <c r="J2152" s="4"/>
+    </row>
+    <row r="2153" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2153" s="3"/>
+      <c r="B2153" s="3"/>
+      <c r="C2153" s="3"/>
+      <c r="D2153" s="3"/>
+      <c r="E2153" s="3"/>
+      <c r="F2153" s="3"/>
+      <c r="G2153" s="3"/>
+      <c r="H2153" s="3"/>
+      <c r="I2153" s="4"/>
+      <c r="J2153" s="4"/>
+    </row>
+    <row r="2154" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2154" s="3"/>
+      <c r="B2154" s="3"/>
+      <c r="C2154" s="3"/>
+      <c r="D2154" s="3"/>
+      <c r="E2154" s="3"/>
+      <c r="F2154" s="3"/>
+      <c r="G2154" s="3"/>
+      <c r="H2154" s="3"/>
+      <c r="I2154" s="4"/>
+      <c r="J2154" s="4"/>
+    </row>
+    <row r="2155" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2155" s="3"/>
+      <c r="B2155" s="3"/>
+      <c r="C2155" s="3"/>
+      <c r="D2155" s="3"/>
+      <c r="E2155" s="3"/>
+      <c r="F2155" s="3"/>
+      <c r="G2155" s="3"/>
+      <c r="H2155" s="3"/>
+      <c r="I2155" s="4"/>
+      <c r="J2155" s="4"/>
+    </row>
+    <row r="2156" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2156" s="3"/>
+      <c r="B2156" s="3"/>
+      <c r="C2156" s="3"/>
+      <c r="D2156" s="3"/>
+      <c r="E2156" s="3"/>
+      <c r="F2156" s="3"/>
+      <c r="G2156" s="3"/>
+      <c r="H2156" s="3"/>
+      <c r="I2156" s="4"/>
+      <c r="J2156" s="4"/>
+    </row>
+    <row r="2157" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2157" s="3"/>
+      <c r="B2157" s="3"/>
+      <c r="C2157" s="3"/>
+      <c r="D2157" s="3"/>
+      <c r="E2157" s="3"/>
+      <c r="F2157" s="3"/>
+      <c r="G2157" s="3"/>
+      <c r="H2157" s="3"/>
+      <c r="I2157" s="4"/>
+      <c r="J2157" s="4"/>
+    </row>
+    <row r="2158" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2158" s="3"/>
+      <c r="B2158" s="3"/>
+      <c r="C2158" s="3"/>
+      <c r="D2158" s="3"/>
+      <c r="E2158" s="3"/>
+      <c r="F2158" s="3"/>
+      <c r="G2158" s="3"/>
+      <c r="H2158" s="3"/>
+      <c r="I2158" s="4"/>
+      <c r="J2158" s="4"/>
+    </row>
+    <row r="2159" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2159" s="3"/>
+      <c r="B2159" s="3"/>
+      <c r="C2159" s="3"/>
+      <c r="D2159" s="3"/>
+      <c r="E2159" s="3"/>
+      <c r="F2159" s="3"/>
+      <c r="G2159" s="3"/>
+      <c r="H2159" s="3"/>
+      <c r="I2159" s="4"/>
+      <c r="J2159" s="4"/>
+    </row>
+    <row r="2160" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2160" s="3"/>
+      <c r="B2160" s="3"/>
+      <c r="C2160" s="3"/>
+      <c r="D2160" s="3"/>
+      <c r="E2160" s="3"/>
+      <c r="F2160" s="3"/>
+      <c r="G2160" s="3"/>
+      <c r="H2160" s="3"/>
+      <c r="I2160" s="4"/>
+      <c r="J2160" s="4"/>
+    </row>
+    <row r="2161" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2161" s="3"/>
+      <c r="B2161" s="3"/>
+      <c r="C2161" s="3"/>
+      <c r="D2161" s="3"/>
+      <c r="E2161" s="3"/>
+      <c r="F2161" s="3"/>
+      <c r="G2161" s="3"/>
+      <c r="H2161" s="3"/>
+      <c r="I2161" s="4"/>
+      <c r="J2161" s="4"/>
+    </row>
+    <row r="2162" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2162" s="3"/>
+      <c r="B2162" s="3"/>
+      <c r="C2162" s="3"/>
+      <c r="D2162" s="3"/>
+      <c r="E2162" s="3"/>
+      <c r="F2162" s="3"/>
+      <c r="G2162" s="3"/>
+      <c r="H2162" s="3"/>
+      <c r="I2162" s="4"/>
+      <c r="J2162" s="4"/>
+    </row>
+    <row r="2163" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2163" s="3"/>
+      <c r="B2163" s="3"/>
+      <c r="C2163" s="3"/>
+      <c r="D2163" s="3"/>
+      <c r="E2163" s="3"/>
+      <c r="F2163" s="3"/>
+      <c r="G2163" s="3"/>
+      <c r="H2163" s="3"/>
+      <c r="I2163" s="4"/>
+      <c r="J2163" s="4"/>
+    </row>
+    <row r="2164" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2164" s="3"/>
+      <c r="B2164" s="3"/>
+      <c r="C2164" s="3"/>
+      <c r="D2164" s="3"/>
+      <c r="E2164" s="3"/>
+      <c r="F2164" s="3"/>
+      <c r="G2164" s="3"/>
+      <c r="H2164" s="3"/>
+      <c r="I2164" s="4"/>
+      <c r="J2164" s="4"/>
+    </row>
+    <row r="2165" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2165" s="3"/>
+      <c r="B2165" s="3"/>
+      <c r="C2165" s="3"/>
+      <c r="D2165" s="3"/>
+      <c r="E2165" s="3"/>
+      <c r="F2165" s="3"/>
+      <c r="G2165" s="3"/>
+      <c r="H2165" s="3"/>
+      <c r="I2165" s="4"/>
+      <c r="J2165" s="4"/>
+    </row>
+    <row r="2166" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2166" s="3"/>
+      <c r="B2166" s="3"/>
+      <c r="C2166" s="3"/>
+      <c r="D2166" s="3"/>
+      <c r="E2166" s="3"/>
+      <c r="F2166" s="3"/>
+      <c r="G2166" s="3"/>
+      <c r="H2166" s="3"/>
+      <c r="I2166" s="4"/>
+      <c r="J2166" s="4"/>
+    </row>
+    <row r="2167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2167" s="3"/>
+      <c r="B2167" s="3"/>
+      <c r="C2167" s="3"/>
+      <c r="D2167" s="3"/>
+      <c r="E2167" s="3"/>
+      <c r="F2167" s="3"/>
+      <c r="G2167" s="3"/>
+      <c r="H2167" s="3"/>
+      <c r="I2167" s="4"/>
+      <c r="J2167" s="4"/>
+    </row>
+    <row r="2168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2168" s="3"/>
+      <c r="B2168" s="3"/>
+      <c r="C2168" s="3"/>
+      <c r="D2168" s="3"/>
+      <c r="E2168" s="3"/>
+      <c r="F2168" s="3"/>
+      <c r="G2168" s="3"/>
+      <c r="H2168" s="3"/>
+      <c r="I2168" s="4"/>
+      <c r="J2168" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68414CF-31FB-4FB9-925A-DF59FEA549C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA9DE65-F63B-4923-BE7A-0515A192E185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="-14730" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="765" yWindow="690" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16516" uniqueCount="1716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16800" uniqueCount="1739">
   <si>
     <t>Year</t>
   </si>
@@ -5179,6 +5179,75 @@
   </si>
   <si>
     <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>config-contributionguide</t>
+  </si>
+  <si>
+    <t>config-developerguide</t>
+  </si>
+  <si>
+    <t>config-nwbuilders</t>
+  </si>
+  <si>
+    <t>config-nwbuilders, config-nwmakefiles</t>
+  </si>
+  <si>
+    <t>NW.UnivariateForecasting v4.2.1</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>NW.MetaLinks v1.0.0</t>
+  </si>
+  <si>
+    <t>NW.LibrarySurfaceArea v1.0.0</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>config-debianpreseed</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
   </si>
 </sst>
 </file>
@@ -75373,7 +75442,7 @@
         <v>2026</v>
       </c>
       <c r="J2078" s="4">
-        <f t="shared" ref="J2078:J2121" si="981">MONTH(A2078)</f>
+        <f t="shared" ref="J2078:J2124" si="981">MONTH(A2078)</f>
         <v>6</v>
       </c>
     </row>
@@ -75437,7 +75506,7 @@
         <v>280</v>
       </c>
       <c r="I2080" s="4">
-        <f t="shared" ref="I2080:I2121" si="982">YEAR(A2080)</f>
+        <f t="shared" ref="I2080:I2124" si="982">YEAR(A2080)</f>
         <v>2026</v>
       </c>
       <c r="J2080" s="4">
@@ -76814,460 +76883,1256 @@
       </c>
     </row>
     <row r="2122" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2122" s="3"/>
-      <c r="B2122" s="3"/>
-      <c r="C2122" s="3"/>
-      <c r="D2122" s="3"/>
-      <c r="E2122" s="3"/>
+      <c r="A2122" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B2122" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2122" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2122" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2122" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2122" s="3"/>
-      <c r="G2122" s="3"/>
-      <c r="H2122" s="3"/>
-      <c r="I2122" s="4"/>
-      <c r="J2122" s="4"/>
+      <c r="G2122" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2122" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2122" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2122" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2123" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2123" s="3"/>
-      <c r="B2123" s="3"/>
-      <c r="C2123" s="3"/>
-      <c r="D2123" s="3"/>
-      <c r="E2123" s="3"/>
+      <c r="A2123" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B2123" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2123" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2123" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2123" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2123" s="3"/>
-      <c r="G2123" s="3"/>
-      <c r="H2123" s="3"/>
-      <c r="I2123" s="4"/>
-      <c r="J2123" s="4"/>
+      <c r="G2123" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2123" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2123" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2123" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2124" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2124" s="3"/>
-      <c r="B2124" s="3"/>
-      <c r="C2124" s="3"/>
-      <c r="D2124" s="3"/>
-      <c r="E2124" s="3"/>
+      <c r="A2124" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B2124" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2124" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2124" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2124" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2124" s="3"/>
-      <c r="G2124" s="3"/>
-      <c r="H2124" s="3"/>
-      <c r="I2124" s="4"/>
-      <c r="J2124" s="4"/>
+      <c r="G2124" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2124" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2124" s="4">
+        <f t="shared" si="982"/>
+        <v>2026</v>
+      </c>
+      <c r="J2124" s="4">
+        <f t="shared" si="981"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2125" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2125" s="3"/>
-      <c r="B2125" s="3"/>
-      <c r="C2125" s="3"/>
-      <c r="D2125" s="3"/>
-      <c r="E2125" s="3"/>
+      <c r="A2125" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B2125" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2125" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2125" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2125" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2125" s="3"/>
-      <c r="G2125" s="3"/>
-      <c r="H2125" s="3"/>
-      <c r="I2125" s="4"/>
-      <c r="J2125" s="4"/>
+      <c r="G2125" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2125" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2125" s="4">
+        <f t="shared" ref="I2125:I2130" si="983">YEAR(A2125)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2125" s="4">
+        <f t="shared" ref="J2125:J2130" si="984">MONTH(A2125)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2126" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2126" s="3"/>
-      <c r="B2126" s="3"/>
-      <c r="C2126" s="3"/>
-      <c r="D2126" s="3"/>
-      <c r="E2126" s="3"/>
+      <c r="A2126" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B2126" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2126" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2126" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2126" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2126" s="3"/>
-      <c r="G2126" s="3"/>
-      <c r="H2126" s="3"/>
-      <c r="I2126" s="4"/>
-      <c r="J2126" s="4"/>
+      <c r="G2126" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2126" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2126" s="4">
+        <f t="shared" si="983"/>
+        <v>2026</v>
+      </c>
+      <c r="J2126" s="4">
+        <f t="shared" si="984"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2127" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2127" s="3"/>
-      <c r="B2127" s="3"/>
-      <c r="C2127" s="3"/>
-      <c r="D2127" s="3"/>
-      <c r="E2127" s="3"/>
+      <c r="A2127" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B2127" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2127" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2127" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2127" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2127" s="3"/>
-      <c r="G2127" s="3"/>
-      <c r="H2127" s="3"/>
-      <c r="I2127" s="4"/>
-      <c r="J2127" s="4"/>
+      <c r="G2127" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2127" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2127" s="4">
+        <f t="shared" si="983"/>
+        <v>2026</v>
+      </c>
+      <c r="J2127" s="4">
+        <f t="shared" si="984"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2128" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2128" s="3"/>
-      <c r="B2128" s="3"/>
-      <c r="C2128" s="3"/>
-      <c r="D2128" s="3"/>
-      <c r="E2128" s="3"/>
+      <c r="A2128" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B2128" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2128" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2128" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2128" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2128" s="3"/>
-      <c r="G2128" s="3"/>
-      <c r="H2128" s="3"/>
-      <c r="I2128" s="4"/>
-      <c r="J2128" s="4"/>
+      <c r="G2128" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2128" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2128" s="4">
+        <f t="shared" si="983"/>
+        <v>2026</v>
+      </c>
+      <c r="J2128" s="4">
+        <f t="shared" si="984"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2129" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2129" s="3"/>
-      <c r="B2129" s="3"/>
-      <c r="C2129" s="3"/>
-      <c r="D2129" s="3"/>
-      <c r="E2129" s="3"/>
+      <c r="A2129" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B2129" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2129" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2129" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2129" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2129" s="3"/>
-      <c r="G2129" s="3"/>
-      <c r="H2129" s="3"/>
-      <c r="I2129" s="4"/>
-      <c r="J2129" s="4"/>
+      <c r="G2129" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2129" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2129" s="4">
+        <f t="shared" si="983"/>
+        <v>2026</v>
+      </c>
+      <c r="J2129" s="4">
+        <f t="shared" si="984"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2130" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2130" s="3"/>
-      <c r="B2130" s="3"/>
-      <c r="C2130" s="3"/>
-      <c r="D2130" s="3"/>
-      <c r="E2130" s="3"/>
+      <c r="A2130" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B2130" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2130" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2130" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2130" s="3" t="s">
+        <v>1682</v>
+      </c>
       <c r="F2130" s="3"/>
-      <c r="G2130" s="3"/>
-      <c r="H2130" s="3"/>
-      <c r="I2130" s="4"/>
-      <c r="J2130" s="4"/>
+      <c r="G2130" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2130" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2130" s="4">
+        <f t="shared" si="983"/>
+        <v>2026</v>
+      </c>
+      <c r="J2130" s="4">
+        <f t="shared" si="984"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2131" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2131" s="3"/>
-      <c r="B2131" s="3"/>
-      <c r="C2131" s="3"/>
-      <c r="D2131" s="3"/>
-      <c r="E2131" s="3"/>
-      <c r="F2131" s="3"/>
-      <c r="G2131" s="3"/>
-      <c r="H2131" s="3"/>
-      <c r="I2131" s="4"/>
-      <c r="J2131" s="4"/>
+      <c r="A2131" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B2131" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2131" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2131" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2131" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2131" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="G2131" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2131" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2131" s="4">
+        <f t="shared" ref="I2131:I2134" si="985">YEAR(A2131)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2131" s="4">
+        <f t="shared" ref="J2131:J2134" si="986">MONTH(A2131)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2132" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2132" s="3"/>
-      <c r="B2132" s="3"/>
-      <c r="C2132" s="3"/>
-      <c r="D2132" s="3"/>
-      <c r="E2132" s="3"/>
-      <c r="F2132" s="3"/>
-      <c r="G2132" s="3"/>
-      <c r="H2132" s="3"/>
-      <c r="I2132" s="4"/>
-      <c r="J2132" s="4"/>
+      <c r="A2132" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B2132" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2132" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2132" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2132" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2132" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G2132" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2132" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2132" s="4">
+        <f t="shared" si="985"/>
+        <v>2026</v>
+      </c>
+      <c r="J2132" s="4">
+        <f t="shared" si="986"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2133" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2133" s="3"/>
-      <c r="B2133" s="3"/>
-      <c r="C2133" s="3"/>
-      <c r="D2133" s="3"/>
-      <c r="E2133" s="3"/>
-      <c r="F2133" s="3"/>
-      <c r="G2133" s="3"/>
-      <c r="H2133" s="3"/>
-      <c r="I2133" s="4"/>
-      <c r="J2133" s="4"/>
+      <c r="A2133" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B2133" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2133" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2133" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2133" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2133" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G2133" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2133" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2133" s="4">
+        <f t="shared" si="985"/>
+        <v>2026</v>
+      </c>
+      <c r="J2133" s="4">
+        <f t="shared" si="986"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="2134" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2134" s="3"/>
-      <c r="B2134" s="3"/>
-      <c r="C2134" s="3"/>
-      <c r="D2134" s="3"/>
-      <c r="E2134" s="3"/>
-      <c r="F2134" s="3"/>
-      <c r="G2134" s="3"/>
-      <c r="H2134" s="3"/>
-      <c r="I2134" s="4"/>
-      <c r="J2134" s="4"/>
+      <c r="A2134" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B2134" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2134" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2134" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2134" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2134" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G2134" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2134" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2134" s="4">
+        <f>YEAR(A2134)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2134" s="4">
+        <f>MONTH(A2134)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2135" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2135" s="3"/>
-      <c r="B2135" s="3"/>
-      <c r="C2135" s="3"/>
-      <c r="D2135" s="3"/>
-      <c r="E2135" s="3"/>
-      <c r="F2135" s="3"/>
-      <c r="G2135" s="3"/>
-      <c r="H2135" s="3"/>
-      <c r="I2135" s="4"/>
-      <c r="J2135" s="4"/>
+      <c r="A2135" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B2135" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2135" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2135" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2135" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2135" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G2135" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2135" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2135" s="4">
+        <f>YEAR(A2135)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2135" s="4">
+        <f>MONTH(A2135)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2136" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2136" s="3"/>
-      <c r="B2136" s="3"/>
-      <c r="C2136" s="3"/>
-      <c r="D2136" s="3"/>
-      <c r="E2136" s="3"/>
-      <c r="F2136" s="3"/>
-      <c r="G2136" s="3"/>
-      <c r="H2136" s="3"/>
-      <c r="I2136" s="4"/>
-      <c r="J2136" s="4"/>
+      <c r="A2136" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B2136" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2136" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2136" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2136" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2136" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G2136" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2136" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2136" s="4">
+        <f>YEAR(A2136)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2136" s="4">
+        <f>MONTH(A2136)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2137" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2137" s="3"/>
-      <c r="B2137" s="3"/>
-      <c r="C2137" s="3"/>
-      <c r="D2137" s="3"/>
-      <c r="E2137" s="3"/>
-      <c r="F2137" s="3"/>
-      <c r="G2137" s="3"/>
-      <c r="H2137" s="3"/>
-      <c r="I2137" s="4"/>
-      <c r="J2137" s="4"/>
+      <c r="A2137" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B2137" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2137" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2137" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2137" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2137" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G2137" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2137" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2137" s="4">
+        <f>YEAR(A2137)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2137" s="4">
+        <f>MONTH(A2137)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2138" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2138" s="3"/>
-      <c r="B2138" s="3"/>
-      <c r="C2138" s="3"/>
-      <c r="D2138" s="3"/>
-      <c r="E2138" s="3"/>
-      <c r="F2138" s="3"/>
-      <c r="G2138" s="3"/>
-      <c r="H2138" s="3"/>
-      <c r="I2138" s="4"/>
-      <c r="J2138" s="4"/>
+      <c r="A2138" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B2138" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2138" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2138" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2138" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2138" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G2138" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2138" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2138" s="4">
+        <f>YEAR(A2138)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2138" s="4">
+        <f>MONTH(A2138)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2139" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2139" s="3"/>
-      <c r="B2139" s="3"/>
-      <c r="C2139" s="3"/>
-      <c r="D2139" s="3"/>
-      <c r="E2139" s="3"/>
-      <c r="F2139" s="3"/>
-      <c r="G2139" s="3"/>
-      <c r="H2139" s="3"/>
-      <c r="I2139" s="4"/>
-      <c r="J2139" s="4"/>
+      <c r="A2139" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B2139" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2139" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2139" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2139" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2139" s="3" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G2139" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2139" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2139" s="4">
+        <f>YEAR(A2139)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2139" s="4">
+        <f>MONTH(A2139)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2140" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2140" s="3"/>
-      <c r="B2140" s="3"/>
-      <c r="C2140" s="3"/>
-      <c r="D2140" s="3"/>
-      <c r="E2140" s="3"/>
+      <c r="A2140" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B2140" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2140" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2140" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2140" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2140" s="3"/>
-      <c r="G2140" s="3"/>
-      <c r="H2140" s="3"/>
-      <c r="I2140" s="4"/>
-      <c r="J2140" s="4"/>
+      <c r="G2140" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2140" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2140" s="4">
+        <f>YEAR(A2140)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2140" s="4">
+        <f>MONTH(A2140)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2141" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2141" s="3"/>
-      <c r="B2141" s="3"/>
-      <c r="C2141" s="3"/>
-      <c r="D2141" s="3"/>
-      <c r="E2141" s="3"/>
+      <c r="A2141" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B2141" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2141" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2141" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2141" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2141" s="3"/>
-      <c r="G2141" s="3"/>
-      <c r="H2141" s="3"/>
-      <c r="I2141" s="4"/>
-      <c r="J2141" s="4"/>
+      <c r="G2141" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2141" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2141" s="4">
+        <f>YEAR(A2141)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2141" s="4">
+        <f>MONTH(A2141)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="2142" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2142" s="3"/>
-      <c r="B2142" s="3"/>
-      <c r="C2142" s="3"/>
-      <c r="D2142" s="3"/>
-      <c r="E2142" s="3"/>
+      <c r="A2142" s="3" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B2142" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2142" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2142" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2142" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2142" s="3"/>
-      <c r="G2142" s="3"/>
-      <c r="H2142" s="3"/>
-      <c r="I2142" s="4"/>
-      <c r="J2142" s="4"/>
+      <c r="G2142" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2142" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2142" s="4">
+        <f>YEAR(A2142)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2142" s="4">
+        <f>MONTH(A2142)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2143" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2143" s="3"/>
-      <c r="B2143" s="3"/>
-      <c r="C2143" s="3"/>
-      <c r="D2143" s="3"/>
-      <c r="E2143" s="3"/>
+      <c r="A2143" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B2143" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2143" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D2143" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2143" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2143" s="3"/>
-      <c r="G2143" s="3"/>
-      <c r="H2143" s="3"/>
-      <c r="I2143" s="4"/>
-      <c r="J2143" s="4"/>
+      <c r="G2143" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2143" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2143" s="4">
+        <f>YEAR(A2143)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2143" s="4">
+        <f>MONTH(A2143)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2144" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2144" s="3"/>
-      <c r="B2144" s="3"/>
-      <c r="C2144" s="3"/>
-      <c r="D2144" s="3"/>
-      <c r="E2144" s="3"/>
+      <c r="A2144" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B2144" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2144" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2144" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2144" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2144" s="3"/>
-      <c r="G2144" s="3"/>
-      <c r="H2144" s="3"/>
-      <c r="I2144" s="4"/>
-      <c r="J2144" s="4"/>
+      <c r="G2144" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2144" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2144" s="4">
+        <f>YEAR(A2144)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2144" s="4">
+        <f>MONTH(A2144)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2145" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2145" s="3"/>
-      <c r="B2145" s="3"/>
-      <c r="C2145" s="3"/>
-      <c r="D2145" s="3"/>
-      <c r="E2145" s="3"/>
-      <c r="F2145" s="3"/>
-      <c r="G2145" s="3"/>
-      <c r="H2145" s="3"/>
-      <c r="I2145" s="4"/>
-      <c r="J2145" s="4"/>
+      <c r="A2145" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B2145" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2145" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2145" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2145" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2145" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G2145" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2145" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2145" s="4">
+        <f>YEAR(A2145)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2145" s="4">
+        <f>MONTH(A2145)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2146" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2146" s="3"/>
-      <c r="B2146" s="3"/>
-      <c r="C2146" s="3"/>
-      <c r="D2146" s="3"/>
-      <c r="E2146" s="3"/>
-      <c r="F2146" s="3"/>
-      <c r="G2146" s="3"/>
-      <c r="H2146" s="3"/>
-      <c r="I2146" s="4"/>
-      <c r="J2146" s="4"/>
+      <c r="A2146" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B2146" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2146" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2146" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2146" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2146" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G2146" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2146" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2146" s="4">
+        <f>YEAR(A2146)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2146" s="4">
+        <f>MONTH(A2146)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2147" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2147" s="3"/>
-      <c r="B2147" s="3"/>
-      <c r="C2147" s="3"/>
-      <c r="D2147" s="3"/>
-      <c r="E2147" s="3"/>
-      <c r="F2147" s="3"/>
-      <c r="G2147" s="3"/>
-      <c r="H2147" s="3"/>
-      <c r="I2147" s="4"/>
-      <c r="J2147" s="4"/>
+      <c r="A2147" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B2147" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2147" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2147" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2147" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2147" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G2147" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2147" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2147" s="4">
+        <f>YEAR(A2147)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2147" s="4">
+        <f>MONTH(A2147)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2148" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2148" s="3"/>
-      <c r="B2148" s="3"/>
-      <c r="C2148" s="3"/>
-      <c r="D2148" s="3"/>
-      <c r="E2148" s="3"/>
-      <c r="F2148" s="3"/>
-      <c r="G2148" s="3"/>
-      <c r="H2148" s="3"/>
-      <c r="I2148" s="4"/>
-      <c r="J2148" s="4"/>
+      <c r="A2148" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B2148" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2148" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2148" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2148" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2148" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G2148" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2148" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2148" s="4">
+        <f>YEAR(A2148)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2148" s="4">
+        <f>MONTH(A2148)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2149" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2149" s="3"/>
-      <c r="B2149" s="3"/>
-      <c r="C2149" s="3"/>
-      <c r="D2149" s="3"/>
-      <c r="E2149" s="3"/>
-      <c r="F2149" s="3"/>
-      <c r="G2149" s="3"/>
-      <c r="H2149" s="3"/>
-      <c r="I2149" s="4"/>
-      <c r="J2149" s="4"/>
+      <c r="A2149" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B2149" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2149" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2149" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2149" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2149" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G2149" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2149" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2149" s="4">
+        <f>YEAR(A2149)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2149" s="4">
+        <f>MONTH(A2149)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2150" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2150" s="3"/>
-      <c r="B2150" s="3"/>
-      <c r="C2150" s="3"/>
-      <c r="D2150" s="3"/>
-      <c r="E2150" s="3"/>
-      <c r="F2150" s="3"/>
-      <c r="G2150" s="3"/>
-      <c r="H2150" s="3"/>
-      <c r="I2150" s="4"/>
-      <c r="J2150" s="4"/>
+      <c r="A2150" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B2150" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2150" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2150" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2150" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2150" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G2150" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2150" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2150" s="4">
+        <f>YEAR(A2150)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2150" s="4">
+        <f>MONTH(A2150)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2151" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2151" s="3"/>
-      <c r="B2151" s="3"/>
-      <c r="C2151" s="3"/>
-      <c r="D2151" s="3"/>
-      <c r="E2151" s="3"/>
-      <c r="F2151" s="3"/>
-      <c r="G2151" s="3"/>
-      <c r="H2151" s="3"/>
-      <c r="I2151" s="4"/>
-      <c r="J2151" s="4"/>
+      <c r="A2151" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B2151" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C2151" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2151" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2151" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2151" s="3" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G2151" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2151" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2151" s="4">
+        <f>YEAR(A2151)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2151" s="4">
+        <f>MONTH(A2151)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2152" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2152" s="3"/>
-      <c r="B2152" s="3"/>
-      <c r="C2152" s="3"/>
-      <c r="D2152" s="3"/>
-      <c r="E2152" s="3"/>
-      <c r="F2152" s="3"/>
-      <c r="G2152" s="3"/>
-      <c r="H2152" s="3"/>
-      <c r="I2152" s="4"/>
-      <c r="J2152" s="4"/>
+      <c r="A2152" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B2152" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2152" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2152" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2152" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F2152" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G2152" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2152" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2152" s="4">
+        <f>YEAR(A2152)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2152" s="4">
+        <f>MONTH(A2152)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2153" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2153" s="3"/>
-      <c r="B2153" s="3"/>
-      <c r="C2153" s="3"/>
-      <c r="D2153" s="3"/>
-      <c r="E2153" s="3"/>
-      <c r="F2153" s="3"/>
-      <c r="G2153" s="3"/>
-      <c r="H2153" s="3"/>
-      <c r="I2153" s="4"/>
-      <c r="J2153" s="4"/>
+      <c r="A2153" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B2153" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2153" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D2153" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2153" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F2153" s="3" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G2153" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2153" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2153" s="4">
+        <f>YEAR(A2153)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2153" s="4">
+        <f>MONTH(A2153)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2154" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2154" s="3"/>
-      <c r="B2154" s="3"/>
-      <c r="C2154" s="3"/>
-      <c r="D2154" s="3"/>
-      <c r="E2154" s="3"/>
+      <c r="A2154" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B2154" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2154" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2154" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2154" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2154" s="3"/>
-      <c r="G2154" s="3"/>
-      <c r="H2154" s="3"/>
-      <c r="I2154" s="4"/>
-      <c r="J2154" s="4"/>
+      <c r="G2154" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2154" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2154" s="4">
+        <f>YEAR(A2154)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2154" s="4">
+        <f>MONTH(A2154)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2155" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2155" s="3"/>
-      <c r="B2155" s="3"/>
-      <c r="C2155" s="3"/>
-      <c r="D2155" s="3"/>
-      <c r="E2155" s="3"/>
+      <c r="A2155" s="3" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B2155" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2155" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2155" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2155" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2155" s="3"/>
-      <c r="G2155" s="3"/>
-      <c r="H2155" s="3"/>
-      <c r="I2155" s="4"/>
-      <c r="J2155" s="4"/>
+      <c r="G2155" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2155" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2155" s="4">
+        <f>YEAR(A2155)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2155" s="4">
+        <f>MONTH(A2155)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2156" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2156" s="3"/>
-      <c r="B2156" s="3"/>
-      <c r="C2156" s="3"/>
-      <c r="D2156" s="3"/>
-      <c r="E2156" s="3"/>
+      <c r="A2156" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B2156" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2156" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2156" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2156" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2156" s="3"/>
-      <c r="G2156" s="3"/>
-      <c r="H2156" s="3"/>
-      <c r="I2156" s="4"/>
-      <c r="J2156" s="4"/>
+      <c r="G2156" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2156" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2156" s="4">
+        <f>YEAR(A2156)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2156" s="4">
+        <f>MONTH(A2156)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2157" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2157" s="3"/>
-      <c r="B2157" s="3"/>
-      <c r="C2157" s="3"/>
-      <c r="D2157" s="3"/>
-      <c r="E2157" s="3"/>
+      <c r="A2157" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B2157" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2157" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2157" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2157" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2157" s="3"/>
-      <c r="G2157" s="3"/>
-      <c r="H2157" s="3"/>
-      <c r="I2157" s="4"/>
-      <c r="J2157" s="4"/>
+      <c r="G2157" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2157" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2157" s="4">
+        <f>YEAR(A2157)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2157" s="4">
+        <f>MONTH(A2157)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2158" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2158" s="3"/>
-      <c r="B2158" s="3"/>
-      <c r="C2158" s="3"/>
-      <c r="D2158" s="3"/>
-      <c r="E2158" s="3"/>
+      <c r="A2158" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B2158" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2158" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2158" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2158" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2158" s="3"/>
-      <c r="G2158" s="3"/>
-      <c r="H2158" s="3"/>
-      <c r="I2158" s="4"/>
-      <c r="J2158" s="4"/>
+      <c r="G2158" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2158" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2158" s="4">
+        <f>YEAR(A2158)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2158" s="4">
+        <f>MONTH(A2158)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2159" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2159" s="3"/>
-      <c r="B2159" s="3"/>
-      <c r="C2159" s="3"/>
-      <c r="D2159" s="3"/>
-      <c r="E2159" s="3"/>
+      <c r="A2159" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B2159" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2159" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2159" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2159" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2159" s="3"/>
-      <c r="G2159" s="3"/>
-      <c r="H2159" s="3"/>
-      <c r="I2159" s="4"/>
-      <c r="J2159" s="4"/>
+      <c r="G2159" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2159" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2159" s="4">
+        <f>YEAR(A2159)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2159" s="4">
+        <f>MONTH(A2159)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2160" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA9DE65-F63B-4923-BE7A-0515A192E185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E6212-B495-4456-95DE-38084075CA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="690" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="660" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16800" uniqueCount="1739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16837" uniqueCount="1743">
   <si>
     <t>Year</t>
   </si>
@@ -5248,6 +5248,18 @@
   </si>
   <si>
     <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>Fixing devcontainers on Surface Go</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
   </si>
 </sst>
 </file>
@@ -5662,7 +5674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2168"/>
+  <dimension ref="A1:J2179"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -77196,11 +77208,11 @@
         <v>280</v>
       </c>
       <c r="I2131" s="4">
-        <f t="shared" ref="I2131:I2134" si="985">YEAR(A2131)</f>
+        <f t="shared" ref="I2131:I2133" si="985">YEAR(A2131)</f>
         <v>2026</v>
       </c>
       <c r="J2131" s="4">
-        <f t="shared" ref="J2131:J2134" si="986">MONTH(A2131)</f>
+        <f t="shared" ref="J2131:J2133" si="986">MONTH(A2131)</f>
         <v>7</v>
       </c>
     </row>
@@ -77298,11 +77310,11 @@
         <v>280</v>
       </c>
       <c r="I2134" s="4">
-        <f>YEAR(A2134)</f>
+        <f t="shared" ref="I2134:I2160" si="987">YEAR(A2134)</f>
         <v>2026</v>
       </c>
       <c r="J2134" s="4">
-        <f>MONTH(A2134)</f>
+        <f t="shared" ref="J2134:J2160" si="988">MONTH(A2134)</f>
         <v>7</v>
       </c>
     </row>
@@ -77332,11 +77344,11 @@
         <v>280</v>
       </c>
       <c r="I2135" s="4">
-        <f>YEAR(A2135)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2135" s="4">
-        <f>MONTH(A2135)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77366,11 +77378,11 @@
         <v>280</v>
       </c>
       <c r="I2136" s="4">
-        <f>YEAR(A2136)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2136" s="4">
-        <f>MONTH(A2136)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77400,11 +77412,11 @@
         <v>280</v>
       </c>
       <c r="I2137" s="4">
-        <f>YEAR(A2137)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2137" s="4">
-        <f>MONTH(A2137)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77434,11 +77446,11 @@
         <v>279</v>
       </c>
       <c r="I2138" s="4">
-        <f>YEAR(A2138)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2138" s="4">
-        <f>MONTH(A2138)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77468,11 +77480,11 @@
         <v>279</v>
       </c>
       <c r="I2139" s="4">
-        <f>YEAR(A2139)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2139" s="4">
-        <f>MONTH(A2139)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77500,11 +77512,11 @@
         <v>280</v>
       </c>
       <c r="I2140" s="4">
-        <f>YEAR(A2140)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2140" s="4">
-        <f>MONTH(A2140)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77532,11 +77544,11 @@
         <v>280</v>
       </c>
       <c r="I2141" s="4">
-        <f>YEAR(A2141)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2141" s="4">
-        <f>MONTH(A2141)</f>
+        <f t="shared" si="988"/>
         <v>7</v>
       </c>
     </row>
@@ -77564,11 +77576,11 @@
         <v>280</v>
       </c>
       <c r="I2142" s="4">
-        <f>YEAR(A2142)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2142" s="4">
-        <f>MONTH(A2142)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77596,11 +77608,11 @@
         <v>280</v>
       </c>
       <c r="I2143" s="4">
-        <f>YEAR(A2143)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2143" s="4">
-        <f>MONTH(A2143)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77628,11 +77640,11 @@
         <v>280</v>
       </c>
       <c r="I2144" s="4">
-        <f>YEAR(A2144)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2144" s="4">
-        <f>MONTH(A2144)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77662,11 +77674,11 @@
         <v>280</v>
       </c>
       <c r="I2145" s="4">
-        <f>YEAR(A2145)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2145" s="4">
-        <f>MONTH(A2145)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77696,11 +77708,11 @@
         <v>279</v>
       </c>
       <c r="I2146" s="4">
-        <f>YEAR(A2146)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2146" s="4">
-        <f>MONTH(A2146)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77730,11 +77742,11 @@
         <v>279</v>
       </c>
       <c r="I2147" s="4">
-        <f>YEAR(A2147)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2147" s="4">
-        <f>MONTH(A2147)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77764,11 +77776,11 @@
         <v>280</v>
       </c>
       <c r="I2148" s="4">
-        <f>YEAR(A2148)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2148" s="4">
-        <f>MONTH(A2148)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77798,11 +77810,11 @@
         <v>280</v>
       </c>
       <c r="I2149" s="4">
-        <f>YEAR(A2149)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2149" s="4">
-        <f>MONTH(A2149)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77832,11 +77844,11 @@
         <v>280</v>
       </c>
       <c r="I2150" s="4">
-        <f>YEAR(A2150)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2150" s="4">
-        <f>MONTH(A2150)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77866,11 +77878,11 @@
         <v>279</v>
       </c>
       <c r="I2151" s="4">
-        <f>YEAR(A2151)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2151" s="4">
-        <f>MONTH(A2151)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77900,11 +77912,11 @@
         <v>280</v>
       </c>
       <c r="I2152" s="4">
-        <f>YEAR(A2152)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2152" s="4">
-        <f>MONTH(A2152)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77934,11 +77946,11 @@
         <v>280</v>
       </c>
       <c r="I2153" s="4">
-        <f>YEAR(A2153)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2153" s="4">
-        <f>MONTH(A2153)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77966,11 +77978,11 @@
         <v>280</v>
       </c>
       <c r="I2154" s="4">
-        <f>YEAR(A2154)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2154" s="4">
-        <f>MONTH(A2154)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -77998,11 +78010,11 @@
         <v>280</v>
       </c>
       <c r="I2155" s="4">
-        <f>YEAR(A2155)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2155" s="4">
-        <f>MONTH(A2155)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -78030,11 +78042,11 @@
         <v>280</v>
       </c>
       <c r="I2156" s="4">
-        <f>YEAR(A2156)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2156" s="4">
-        <f>MONTH(A2156)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -78062,11 +78074,11 @@
         <v>280</v>
       </c>
       <c r="I2157" s="4">
-        <f>YEAR(A2157)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2157" s="4">
-        <f>MONTH(A2157)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -78094,11 +78106,11 @@
         <v>280</v>
       </c>
       <c r="I2158" s="4">
-        <f>YEAR(A2158)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2158" s="4">
-        <f>MONTH(A2158)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
@@ -78126,73 +78138,177 @@
         <v>280</v>
       </c>
       <c r="I2159" s="4">
-        <f>YEAR(A2159)</f>
+        <f t="shared" si="987"/>
         <v>2026</v>
       </c>
       <c r="J2159" s="4">
-        <f>MONTH(A2159)</f>
+        <f t="shared" si="988"/>
         <v>8</v>
       </c>
     </row>
     <row r="2160" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2160" s="3"/>
-      <c r="B2160" s="3"/>
-      <c r="C2160" s="3"/>
-      <c r="D2160" s="3"/>
-      <c r="E2160" s="3"/>
-      <c r="F2160" s="3"/>
-      <c r="G2160" s="3"/>
-      <c r="H2160" s="3"/>
-      <c r="I2160" s="4"/>
-      <c r="J2160" s="4"/>
+      <c r="A2160" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B2160" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2160" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2160" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2160" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F2160" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G2160" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2160" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2160" s="4">
+        <f t="shared" si="987"/>
+        <v>2026</v>
+      </c>
+      <c r="J2160" s="4">
+        <f t="shared" si="988"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2161" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2161" s="3"/>
-      <c r="B2161" s="3"/>
-      <c r="C2161" s="3"/>
-      <c r="D2161" s="3"/>
-      <c r="E2161" s="3"/>
-      <c r="F2161" s="3"/>
-      <c r="G2161" s="3"/>
-      <c r="H2161" s="3"/>
-      <c r="I2161" s="4"/>
-      <c r="J2161" s="4"/>
+      <c r="A2161" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B2161" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2161" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2161" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2161" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F2161" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G2161" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2161" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2161" s="4">
+        <f t="shared" ref="I2161" si="989">YEAR(A2161)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2161" s="4">
+        <f t="shared" ref="J2161" si="990">MONTH(A2161)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2162" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2162" s="3"/>
-      <c r="B2162" s="3"/>
-      <c r="C2162" s="3"/>
-      <c r="D2162" s="3"/>
-      <c r="E2162" s="3"/>
+      <c r="A2162" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B2162" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2162" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2162" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E2162" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2162" s="3"/>
-      <c r="G2162" s="3"/>
-      <c r="H2162" s="3"/>
-      <c r="I2162" s="4"/>
-      <c r="J2162" s="4"/>
+      <c r="G2162" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2162" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2162" s="4">
+        <f t="shared" ref="I2162:I2164" si="991">YEAR(A2162)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2162" s="4">
+        <f t="shared" ref="J2162:J2164" si="992">MONTH(A2162)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2163" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2163" s="3"/>
-      <c r="B2163" s="3"/>
-      <c r="C2163" s="3"/>
-      <c r="D2163" s="3"/>
-      <c r="E2163" s="3"/>
+      <c r="A2163" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B2163" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2163" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2163" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2163" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2163" s="3"/>
-      <c r="G2163" s="3"/>
-      <c r="H2163" s="3"/>
-      <c r="I2163" s="4"/>
-      <c r="J2163" s="4"/>
+      <c r="G2163" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2163" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2163" s="4">
+        <f t="shared" si="991"/>
+        <v>2026</v>
+      </c>
+      <c r="J2163" s="4">
+        <f t="shared" si="992"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2164" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2164" s="3"/>
-      <c r="B2164" s="3"/>
-      <c r="C2164" s="3"/>
-      <c r="D2164" s="3"/>
-      <c r="E2164" s="3"/>
+      <c r="A2164" s="3" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B2164" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2164" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2164" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2164" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2164" s="3"/>
-      <c r="G2164" s="3"/>
-      <c r="H2164" s="3"/>
-      <c r="I2164" s="4"/>
-      <c r="J2164" s="4"/>
+      <c r="G2164" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2164" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2164" s="4">
+        <f t="shared" si="991"/>
+        <v>2026</v>
+      </c>
+      <c r="J2164" s="4">
+        <f t="shared" si="992"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2165" s="3"/>
@@ -78242,6 +78358,138 @@
       <c r="I2168" s="4"/>
       <c r="J2168" s="4"/>
     </row>
+    <row r="2169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2169" s="3"/>
+      <c r="B2169" s="3"/>
+      <c r="C2169" s="3"/>
+      <c r="D2169" s="3"/>
+      <c r="E2169" s="3"/>
+      <c r="F2169" s="3"/>
+      <c r="G2169" s="3"/>
+      <c r="H2169" s="3"/>
+      <c r="I2169" s="4"/>
+      <c r="J2169" s="4"/>
+    </row>
+    <row r="2170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2170" s="3"/>
+      <c r="B2170" s="3"/>
+      <c r="C2170" s="3"/>
+      <c r="D2170" s="3"/>
+      <c r="E2170" s="3"/>
+      <c r="F2170" s="3"/>
+      <c r="G2170" s="3"/>
+      <c r="H2170" s="3"/>
+      <c r="I2170" s="4"/>
+      <c r="J2170" s="4"/>
+    </row>
+    <row r="2171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2171" s="3"/>
+      <c r="B2171" s="3"/>
+      <c r="C2171" s="3"/>
+      <c r="D2171" s="3"/>
+      <c r="E2171" s="3"/>
+      <c r="F2171" s="3"/>
+      <c r="G2171" s="3"/>
+      <c r="H2171" s="3"/>
+      <c r="I2171" s="4"/>
+      <c r="J2171" s="4"/>
+    </row>
+    <row r="2172" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2172" s="3"/>
+      <c r="B2172" s="3"/>
+      <c r="C2172" s="3"/>
+      <c r="D2172" s="3"/>
+      <c r="E2172" s="3"/>
+      <c r="F2172" s="3"/>
+      <c r="G2172" s="3"/>
+      <c r="H2172" s="3"/>
+      <c r="I2172" s="4"/>
+      <c r="J2172" s="4"/>
+    </row>
+    <row r="2173" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2173" s="3"/>
+      <c r="B2173" s="3"/>
+      <c r="C2173" s="3"/>
+      <c r="D2173" s="3"/>
+      <c r="E2173" s="3"/>
+      <c r="F2173" s="3"/>
+      <c r="G2173" s="3"/>
+      <c r="H2173" s="3"/>
+      <c r="I2173" s="4"/>
+      <c r="J2173" s="4"/>
+    </row>
+    <row r="2174" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2174" s="3"/>
+      <c r="B2174" s="3"/>
+      <c r="C2174" s="3"/>
+      <c r="D2174" s="3"/>
+      <c r="E2174" s="3"/>
+      <c r="F2174" s="3"/>
+      <c r="G2174" s="3"/>
+      <c r="H2174" s="3"/>
+      <c r="I2174" s="4"/>
+      <c r="J2174" s="4"/>
+    </row>
+    <row r="2175" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2175" s="3"/>
+      <c r="B2175" s="3"/>
+      <c r="C2175" s="3"/>
+      <c r="D2175" s="3"/>
+      <c r="E2175" s="3"/>
+      <c r="F2175" s="3"/>
+      <c r="G2175" s="3"/>
+      <c r="H2175" s="3"/>
+      <c r="I2175" s="4"/>
+      <c r="J2175" s="4"/>
+    </row>
+    <row r="2176" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2176" s="3"/>
+      <c r="B2176" s="3"/>
+      <c r="C2176" s="3"/>
+      <c r="D2176" s="3"/>
+      <c r="E2176" s="3"/>
+      <c r="F2176" s="3"/>
+      <c r="G2176" s="3"/>
+      <c r="H2176" s="3"/>
+      <c r="I2176" s="4"/>
+      <c r="J2176" s="4"/>
+    </row>
+    <row r="2177" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2177" s="3"/>
+      <c r="B2177" s="3"/>
+      <c r="C2177" s="3"/>
+      <c r="D2177" s="3"/>
+      <c r="E2177" s="3"/>
+      <c r="F2177" s="3"/>
+      <c r="G2177" s="3"/>
+      <c r="H2177" s="3"/>
+      <c r="I2177" s="4"/>
+      <c r="J2177" s="4"/>
+    </row>
+    <row r="2178" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2178" s="3"/>
+      <c r="B2178" s="3"/>
+      <c r="C2178" s="3"/>
+      <c r="D2178" s="3"/>
+      <c r="E2178" s="3"/>
+      <c r="F2178" s="3"/>
+      <c r="G2178" s="3"/>
+      <c r="H2178" s="3"/>
+      <c r="I2178" s="4"/>
+      <c r="J2178" s="4"/>
+    </row>
+    <row r="2179" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2179" s="3"/>
+      <c r="B2179" s="3"/>
+      <c r="C2179" s="3"/>
+      <c r="D2179" s="3"/>
+      <c r="E2179" s="3"/>
+      <c r="F2179" s="3"/>
+      <c r="G2179" s="3"/>
+      <c r="H2179" s="3"/>
+      <c r="I2179" s="4"/>
+      <c r="J2179" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E6212-B495-4456-95DE-38084075CA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8608FA29-98B3-4C0F-8AB7-936E981D4669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="660" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16837" uniqueCount="1743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17077" uniqueCount="1762">
   <si>
     <t>Year</t>
   </si>
@@ -5260,6 +5260,63 @@
   </si>
   <si>
     <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>P0006_C# And Devcontainers_A Tribute To Determinism</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Data-Driven Continuous Learning.odp</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>config-nwpublishers</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
   </si>
 </sst>
 </file>
@@ -5674,7 +5731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2179"/>
+  <dimension ref="A1:J2248"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="5" customWidth="1"/>
@@ -78238,11 +78295,11 @@
         <v>280</v>
       </c>
       <c r="I2162" s="4">
-        <f t="shared" ref="I2162:I2164" si="991">YEAR(A2162)</f>
+        <f t="shared" ref="I2162:I2165" si="991">YEAR(A2162)</f>
         <v>2026</v>
       </c>
       <c r="J2162" s="4">
-        <f t="shared" ref="J2162:J2164" si="992">MONTH(A2162)</f>
+        <f t="shared" ref="J2162:J2165" si="992">MONTH(A2162)</f>
         <v>8</v>
       </c>
     </row>
@@ -78311,184 +78368,1690 @@
       </c>
     </row>
     <row r="2165" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2165" s="3"/>
-      <c r="B2165" s="3"/>
-      <c r="C2165" s="3"/>
-      <c r="D2165" s="3"/>
-      <c r="E2165" s="3"/>
-      <c r="F2165" s="3"/>
-      <c r="G2165" s="3"/>
-      <c r="H2165" s="3"/>
-      <c r="I2165" s="4"/>
-      <c r="J2165" s="4"/>
+      <c r="A2165" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B2165" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2165" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2165" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2165" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2165" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G2165" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2165" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2165" s="4">
+        <f t="shared" si="991"/>
+        <v>2026</v>
+      </c>
+      <c r="J2165" s="4">
+        <f t="shared" si="992"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2166" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2166" s="3"/>
-      <c r="B2166" s="3"/>
-      <c r="C2166" s="3"/>
-      <c r="D2166" s="3"/>
-      <c r="E2166" s="3"/>
-      <c r="F2166" s="3"/>
-      <c r="G2166" s="3"/>
-      <c r="H2166" s="3"/>
-      <c r="I2166" s="4"/>
-      <c r="J2166" s="4"/>
+      <c r="A2166" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B2166" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2166" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2166" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2166" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2166" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G2166" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2166" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2166" s="4">
+        <f t="shared" ref="I2166:I2168" si="993">YEAR(A2166)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2166" s="4">
+        <f t="shared" ref="J2166:J2168" si="994">MONTH(A2166)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2167" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2167" s="3"/>
-      <c r="B2167" s="3"/>
-      <c r="C2167" s="3"/>
-      <c r="D2167" s="3"/>
-      <c r="E2167" s="3"/>
-      <c r="F2167" s="3"/>
-      <c r="G2167" s="3"/>
-      <c r="H2167" s="3"/>
-      <c r="I2167" s="4"/>
-      <c r="J2167" s="4"/>
+      <c r="A2167" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B2167" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2167" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2167" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2167" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2167" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G2167" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2167" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2167" s="4">
+        <f t="shared" si="993"/>
+        <v>2026</v>
+      </c>
+      <c r="J2167" s="4">
+        <f t="shared" si="994"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2168" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2168" s="3"/>
-      <c r="B2168" s="3"/>
-      <c r="C2168" s="3"/>
-      <c r="D2168" s="3"/>
-      <c r="E2168" s="3"/>
-      <c r="F2168" s="3"/>
-      <c r="G2168" s="3"/>
-      <c r="H2168" s="3"/>
-      <c r="I2168" s="4"/>
-      <c r="J2168" s="4"/>
+      <c r="A2168" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B2168" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2168" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2168" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2168" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2168" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G2168" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2168" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2168" s="4">
+        <f t="shared" si="993"/>
+        <v>2026</v>
+      </c>
+      <c r="J2168" s="4">
+        <f t="shared" si="994"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2169" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2169" s="3"/>
-      <c r="B2169" s="3"/>
-      <c r="C2169" s="3"/>
-      <c r="D2169" s="3"/>
-      <c r="E2169" s="3"/>
-      <c r="F2169" s="3"/>
-      <c r="G2169" s="3"/>
-      <c r="H2169" s="3"/>
-      <c r="I2169" s="4"/>
-      <c r="J2169" s="4"/>
+      <c r="A2169" s="3" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B2169" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2169" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2169" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2169" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2169" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G2169" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2169" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2169" s="4">
+        <f>YEAR(A2169)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2169" s="4">
+        <f t="shared" ref="J2169:J2177" si="995">MONTH(A2169)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="2170" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2170" s="3"/>
-      <c r="B2170" s="3"/>
-      <c r="C2170" s="3"/>
-      <c r="D2170" s="3"/>
-      <c r="E2170" s="3"/>
+      <c r="A2170" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B2170" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2170" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2170" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E2170" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2170" s="3"/>
-      <c r="G2170" s="3"/>
-      <c r="H2170" s="3"/>
-      <c r="I2170" s="4"/>
-      <c r="J2170" s="4"/>
+      <c r="G2170" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2170" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2170" s="4">
+        <f t="shared" ref="I2170:I2177" si="996">YEAR(A2170)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2170" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2171" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2171" s="3"/>
-      <c r="B2171" s="3"/>
-      <c r="C2171" s="3"/>
-      <c r="D2171" s="3"/>
-      <c r="E2171" s="3"/>
+      <c r="A2171" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B2171" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2171" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2171" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2171" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2171" s="3"/>
-      <c r="G2171" s="3"/>
-      <c r="H2171" s="3"/>
-      <c r="I2171" s="4"/>
-      <c r="J2171" s="4"/>
+      <c r="G2171" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2171" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2171" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2171" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2172" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2172" s="3"/>
-      <c r="B2172" s="3"/>
-      <c r="C2172" s="3"/>
-      <c r="D2172" s="3"/>
-      <c r="E2172" s="3"/>
+      <c r="A2172" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B2172" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2172" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2172" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2172" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2172" s="3"/>
-      <c r="G2172" s="3"/>
-      <c r="H2172" s="3"/>
-      <c r="I2172" s="4"/>
-      <c r="J2172" s="4"/>
+      <c r="G2172" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2172" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2172" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2172" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2173" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2173" s="3"/>
-      <c r="B2173" s="3"/>
-      <c r="C2173" s="3"/>
-      <c r="D2173" s="3"/>
-      <c r="E2173" s="3"/>
-      <c r="F2173" s="3"/>
-      <c r="G2173" s="3"/>
-      <c r="H2173" s="3"/>
-      <c r="I2173" s="4"/>
-      <c r="J2173" s="4"/>
+      <c r="A2173" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B2173" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2173" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2173" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2173" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2173" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="G2173" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2173" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2173" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2173" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2174" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2174" s="3"/>
-      <c r="B2174" s="3"/>
-      <c r="C2174" s="3"/>
-      <c r="D2174" s="3"/>
-      <c r="E2174" s="3"/>
+      <c r="A2174" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B2174" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2174" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2174" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2174" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2174" s="3"/>
-      <c r="G2174" s="3"/>
-      <c r="H2174" s="3"/>
-      <c r="I2174" s="4"/>
-      <c r="J2174" s="4"/>
+      <c r="G2174" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2174" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2174" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2174" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2175" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2175" s="3"/>
-      <c r="B2175" s="3"/>
-      <c r="C2175" s="3"/>
-      <c r="D2175" s="3"/>
-      <c r="E2175" s="3"/>
+      <c r="A2175" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B2175" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2175" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2175" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2175" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2175" s="3"/>
-      <c r="G2175" s="3"/>
-      <c r="H2175" s="3"/>
-      <c r="I2175" s="4"/>
-      <c r="J2175" s="4"/>
+      <c r="G2175" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2175" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2175" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2175" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2176" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2176" s="3"/>
-      <c r="B2176" s="3"/>
-      <c r="C2176" s="3"/>
-      <c r="D2176" s="3"/>
-      <c r="E2176" s="3"/>
+      <c r="A2176" s="3" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B2176" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2176" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D2176" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2176" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2176" s="3"/>
-      <c r="G2176" s="3"/>
-      <c r="H2176" s="3"/>
-      <c r="I2176" s="4"/>
-      <c r="J2176" s="4"/>
+      <c r="G2176" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2176" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2176" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2176" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2177" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2177" s="3"/>
-      <c r="B2177" s="3"/>
-      <c r="C2177" s="3"/>
-      <c r="D2177" s="3"/>
-      <c r="E2177" s="3"/>
+      <c r="A2177" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B2177" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2177" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2177" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2177" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2177" s="3"/>
-      <c r="G2177" s="3"/>
-      <c r="H2177" s="3"/>
-      <c r="I2177" s="4"/>
-      <c r="J2177" s="4"/>
+      <c r="G2177" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2177" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2177" s="4">
+        <f t="shared" si="996"/>
+        <v>2026</v>
+      </c>
+      <c r="J2177" s="4">
+        <f t="shared" si="995"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="2178" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2178" s="3"/>
-      <c r="B2178" s="3"/>
-      <c r="C2178" s="3"/>
-      <c r="D2178" s="3"/>
-      <c r="E2178" s="3"/>
+      <c r="A2178" s="3" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B2178" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2178" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2178" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2178" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2178" s="3"/>
-      <c r="G2178" s="3"/>
-      <c r="H2178" s="3"/>
-      <c r="I2178" s="4"/>
-      <c r="J2178" s="4"/>
+      <c r="G2178" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2178" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2178" s="4">
+        <f t="shared" ref="I2178:I2179" si="997">YEAR(A2178)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2178" s="4">
+        <f t="shared" ref="J2178:J2179" si="998">MONTH(A2178)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="2179" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2179" s="3"/>
-      <c r="B2179" s="3"/>
-      <c r="C2179" s="3"/>
-      <c r="D2179" s="3"/>
-      <c r="E2179" s="3"/>
+      <c r="A2179" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B2179" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2179" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2179" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2179" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2179" s="3"/>
-      <c r="G2179" s="3"/>
-      <c r="H2179" s="3"/>
-      <c r="I2179" s="4"/>
-      <c r="J2179" s="4"/>
+      <c r="G2179" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2179" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2179" s="4">
+        <f t="shared" si="997"/>
+        <v>2026</v>
+      </c>
+      <c r="J2179" s="4">
+        <f t="shared" si="998"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2180" s="3" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B2180" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2180" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2180" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2180" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2180" s="3"/>
+      <c r="G2180" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2180" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2180" s="4">
+        <f t="shared" ref="I2180:I2181" si="999">YEAR(A2180)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2180" s="4">
+        <f t="shared" ref="J2180:J2181" si="1000">MONTH(A2180)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2181" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B2181" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2181" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2181" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2181" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2181" s="3"/>
+      <c r="G2181" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2181" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2181" s="4">
+        <f t="shared" si="999"/>
+        <v>2026</v>
+      </c>
+      <c r="J2181" s="4">
+        <f t="shared" si="1000"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2182" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B2182" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2182" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2182" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2182" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2182" s="3"/>
+      <c r="G2182" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2182" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2182" s="4">
+        <f t="shared" ref="I2182" si="1001">YEAR(A2182)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2182" s="4">
+        <f t="shared" ref="J2182" si="1002">MONTH(A2182)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2183" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B2183" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2183" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2183" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2183" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2183" s="3"/>
+      <c r="G2183" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2183" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2183" s="4">
+        <f t="shared" ref="I2183" si="1003">YEAR(A2183)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2183" s="4">
+        <f t="shared" ref="J2183" si="1004">MONTH(A2183)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2184" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B2184" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C2184" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D2184" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2184" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2184" s="3"/>
+      <c r="G2184" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2184" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2184" s="4">
+        <f t="shared" ref="I2184:I2188" si="1005">YEAR(A2184)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2184" s="4">
+        <f t="shared" ref="J2184:J2188" si="1006">MONTH(A2184)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2185" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B2185" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2185" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D2185" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2185" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2185" s="3"/>
+      <c r="G2185" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2185" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2185" s="4">
+        <f t="shared" si="1005"/>
+        <v>2026</v>
+      </c>
+      <c r="J2185" s="4">
+        <f t="shared" si="1006"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2186" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B2186" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2186" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2186" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2186" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2186" s="3"/>
+      <c r="G2186" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2186" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2186" s="4">
+        <f t="shared" si="1005"/>
+        <v>2026</v>
+      </c>
+      <c r="J2186" s="4">
+        <f t="shared" si="1006"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2187" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B2187" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2187" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2187" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2187" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2187" s="3"/>
+      <c r="G2187" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2187" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2187" s="4">
+        <f t="shared" si="1005"/>
+        <v>2026</v>
+      </c>
+      <c r="J2187" s="4">
+        <f t="shared" si="1006"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2188" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B2188" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2188" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2188" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2188" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2188" s="3"/>
+      <c r="G2188" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2188" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2188" s="4">
+        <f t="shared" si="1005"/>
+        <v>2026</v>
+      </c>
+      <c r="J2188" s="4">
+        <f t="shared" si="1006"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2189" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B2189" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2189" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2189" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2189" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2189" s="3" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G2189" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2189" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2189" s="4">
+        <f t="shared" ref="I2189:I2190" si="1007">YEAR(A2189)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2189" s="4">
+        <f t="shared" ref="J2189:J2190" si="1008">MONTH(A2189)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2190" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B2190" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2190" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2190" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2190" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2190" s="3" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G2190" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2190" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2190" s="4">
+        <f t="shared" si="1007"/>
+        <v>2026</v>
+      </c>
+      <c r="J2190" s="4">
+        <f t="shared" si="1008"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2191" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B2191" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2191" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2191" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2191" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2191" s="3" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G2191" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2191" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2191" s="4">
+        <f t="shared" ref="I2191:I2193" si="1009">YEAR(A2191)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2191" s="4">
+        <f t="shared" ref="J2191:J2193" si="1010">MONTH(A2191)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2192" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B2192" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2192" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2192" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2192" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2192" s="3"/>
+      <c r="G2192" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2192" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2192" s="4">
+        <f t="shared" si="1009"/>
+        <v>2026</v>
+      </c>
+      <c r="J2192" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2193" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B2193" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2193" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2193" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2193" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2193" s="3"/>
+      <c r="G2193" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2193" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2193" s="4">
+        <f t="shared" si="1009"/>
+        <v>2026</v>
+      </c>
+      <c r="J2193" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2194" s="3" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B2194" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2194" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2194" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2194" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2194" s="3"/>
+      <c r="G2194" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2194" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2194" s="4">
+        <f t="shared" ref="I2194:I2196" si="1011">YEAR(A2194)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2194" s="4">
+        <f t="shared" ref="J2194:J2196" si="1012">MONTH(A2194)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2195" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B2195" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2195" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2195" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2195" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2195" s="3"/>
+      <c r="G2195" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2195" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2195" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2195" s="4">
+        <f t="shared" si="1012"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2196" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B2196" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2196" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2196" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2196" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2196" s="3"/>
+      <c r="G2196" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2196" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2196" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2196" s="4">
+        <f t="shared" si="1012"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2197" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B2197" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2197" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2197" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2197" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2197" s="3"/>
+      <c r="G2197" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2197" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2197" s="4">
+        <f t="shared" ref="I2197" si="1013">YEAR(A2197)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2197" s="4">
+        <f t="shared" ref="J2197" si="1014">MONTH(A2197)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2198" s="3"/>
+      <c r="B2198" s="3"/>
+      <c r="C2198" s="3"/>
+      <c r="D2198" s="3"/>
+      <c r="E2198" s="3"/>
+      <c r="F2198" s="3"/>
+      <c r="G2198" s="3"/>
+      <c r="H2198" s="3"/>
+      <c r="I2198" s="4"/>
+      <c r="J2198" s="4"/>
+    </row>
+    <row r="2199" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2199" s="3"/>
+      <c r="B2199" s="3"/>
+      <c r="C2199" s="3"/>
+      <c r="D2199" s="3"/>
+      <c r="E2199" s="3"/>
+      <c r="F2199" s="3"/>
+      <c r="G2199" s="3"/>
+      <c r="H2199" s="3"/>
+      <c r="I2199" s="4"/>
+      <c r="J2199" s="4"/>
+    </row>
+    <row r="2200" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2200" s="3"/>
+      <c r="B2200" s="3"/>
+      <c r="C2200" s="3"/>
+      <c r="D2200" s="3"/>
+      <c r="E2200" s="3"/>
+      <c r="F2200" s="3"/>
+      <c r="G2200" s="3"/>
+      <c r="H2200" s="3"/>
+      <c r="I2200" s="4"/>
+      <c r="J2200" s="4"/>
+    </row>
+    <row r="2201" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2201" s="3"/>
+      <c r="B2201" s="3"/>
+      <c r="C2201" s="3"/>
+      <c r="D2201" s="3"/>
+      <c r="E2201" s="3"/>
+      <c r="F2201" s="3"/>
+      <c r="G2201" s="3"/>
+      <c r="H2201" s="3"/>
+      <c r="I2201" s="4"/>
+      <c r="J2201" s="4"/>
+    </row>
+    <row r="2202" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2202" s="3"/>
+      <c r="B2202" s="3"/>
+      <c r="C2202" s="3"/>
+      <c r="D2202" s="3"/>
+      <c r="E2202" s="3"/>
+      <c r="F2202" s="3"/>
+      <c r="G2202" s="3"/>
+      <c r="H2202" s="3"/>
+      <c r="I2202" s="4"/>
+      <c r="J2202" s="4"/>
+    </row>
+    <row r="2203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2203" s="3"/>
+      <c r="B2203" s="3"/>
+      <c r="C2203" s="3"/>
+      <c r="D2203" s="3"/>
+      <c r="E2203" s="3"/>
+      <c r="F2203" s="3"/>
+      <c r="G2203" s="3"/>
+      <c r="H2203" s="3"/>
+      <c r="I2203" s="4"/>
+      <c r="J2203" s="4"/>
+    </row>
+    <row r="2204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2204" s="3"/>
+      <c r="B2204" s="3"/>
+      <c r="C2204" s="3"/>
+      <c r="D2204" s="3"/>
+      <c r="E2204" s="3"/>
+      <c r="F2204" s="3"/>
+      <c r="G2204" s="3"/>
+      <c r="H2204" s="3"/>
+      <c r="I2204" s="4"/>
+      <c r="J2204" s="4"/>
+    </row>
+    <row r="2205" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2205" s="3"/>
+      <c r="B2205" s="3"/>
+      <c r="C2205" s="3"/>
+      <c r="D2205" s="3"/>
+      <c r="E2205" s="3"/>
+      <c r="F2205" s="3"/>
+      <c r="G2205" s="3"/>
+      <c r="H2205" s="3"/>
+      <c r="I2205" s="4"/>
+      <c r="J2205" s="4"/>
+    </row>
+    <row r="2206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2206" s="3"/>
+      <c r="B2206" s="3"/>
+      <c r="C2206" s="3"/>
+      <c r="D2206" s="3"/>
+      <c r="E2206" s="3"/>
+      <c r="F2206" s="3"/>
+      <c r="G2206" s="3"/>
+      <c r="H2206" s="3"/>
+      <c r="I2206" s="4"/>
+      <c r="J2206" s="4"/>
+    </row>
+    <row r="2207" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2207" s="3"/>
+      <c r="B2207" s="3"/>
+      <c r="C2207" s="3"/>
+      <c r="D2207" s="3"/>
+      <c r="E2207" s="3"/>
+      <c r="F2207" s="3"/>
+      <c r="G2207" s="3"/>
+      <c r="H2207" s="3"/>
+      <c r="I2207" s="4"/>
+      <c r="J2207" s="4"/>
+    </row>
+    <row r="2208" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2208" s="3"/>
+      <c r="B2208" s="3"/>
+      <c r="C2208" s="3"/>
+      <c r="D2208" s="3"/>
+      <c r="E2208" s="3"/>
+      <c r="F2208" s="3"/>
+      <c r="G2208" s="3"/>
+      <c r="H2208" s="3"/>
+      <c r="I2208" s="4"/>
+      <c r="J2208" s="4"/>
+    </row>
+    <row r="2209" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2209" s="3"/>
+      <c r="B2209" s="3"/>
+      <c r="C2209" s="3"/>
+      <c r="D2209" s="3"/>
+      <c r="E2209" s="3"/>
+      <c r="F2209" s="3"/>
+      <c r="G2209" s="3"/>
+      <c r="H2209" s="3"/>
+      <c r="I2209" s="4"/>
+      <c r="J2209" s="4"/>
+    </row>
+    <row r="2210" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2210" s="3"/>
+      <c r="B2210" s="3"/>
+      <c r="C2210" s="3"/>
+      <c r="D2210" s="3"/>
+      <c r="E2210" s="3"/>
+      <c r="F2210" s="3"/>
+      <c r="G2210" s="3"/>
+      <c r="H2210" s="3"/>
+      <c r="I2210" s="4"/>
+      <c r="J2210" s="4"/>
+    </row>
+    <row r="2211" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2211" s="3"/>
+      <c r="B2211" s="3"/>
+      <c r="C2211" s="3"/>
+      <c r="D2211" s="3"/>
+      <c r="E2211" s="3"/>
+      <c r="F2211" s="3"/>
+      <c r="G2211" s="3"/>
+      <c r="H2211" s="3"/>
+      <c r="I2211" s="4"/>
+      <c r="J2211" s="4"/>
+    </row>
+    <row r="2212" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2212" s="3"/>
+      <c r="B2212" s="3"/>
+      <c r="C2212" s="3"/>
+      <c r="D2212" s="3"/>
+      <c r="E2212" s="3"/>
+      <c r="F2212" s="3"/>
+      <c r="G2212" s="3"/>
+      <c r="H2212" s="3"/>
+      <c r="I2212" s="4"/>
+      <c r="J2212" s="4"/>
+    </row>
+    <row r="2213" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2213" s="3"/>
+      <c r="B2213" s="3"/>
+      <c r="C2213" s="3"/>
+      <c r="D2213" s="3"/>
+      <c r="E2213" s="3"/>
+      <c r="F2213" s="3"/>
+      <c r="G2213" s="3"/>
+      <c r="H2213" s="3"/>
+      <c r="I2213" s="4"/>
+      <c r="J2213" s="4"/>
+    </row>
+    <row r="2214" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2214" s="3"/>
+      <c r="B2214" s="3"/>
+      <c r="C2214" s="3"/>
+      <c r="D2214" s="3"/>
+      <c r="E2214" s="3"/>
+      <c r="F2214" s="3"/>
+      <c r="G2214" s="3"/>
+      <c r="H2214" s="3"/>
+      <c r="I2214" s="4"/>
+      <c r="J2214" s="4"/>
+    </row>
+    <row r="2215" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2215" s="3"/>
+      <c r="B2215" s="3"/>
+      <c r="C2215" s="3"/>
+      <c r="D2215" s="3"/>
+      <c r="E2215" s="3"/>
+      <c r="F2215" s="3"/>
+      <c r="G2215" s="3"/>
+      <c r="H2215" s="3"/>
+      <c r="I2215" s="4"/>
+      <c r="J2215" s="4"/>
+    </row>
+    <row r="2216" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2216" s="3"/>
+      <c r="B2216" s="3"/>
+      <c r="C2216" s="3"/>
+      <c r="D2216" s="3"/>
+      <c r="E2216" s="3"/>
+      <c r="F2216" s="3"/>
+      <c r="G2216" s="3"/>
+      <c r="H2216" s="3"/>
+      <c r="I2216" s="4"/>
+      <c r="J2216" s="4"/>
+    </row>
+    <row r="2217" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2217" s="3"/>
+      <c r="B2217" s="3"/>
+      <c r="C2217" s="3"/>
+      <c r="D2217" s="3"/>
+      <c r="E2217" s="3"/>
+      <c r="F2217" s="3"/>
+      <c r="G2217" s="3"/>
+      <c r="H2217" s="3"/>
+      <c r="I2217" s="4"/>
+      <c r="J2217" s="4"/>
+    </row>
+    <row r="2218" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2218" s="3"/>
+      <c r="B2218" s="3"/>
+      <c r="C2218" s="3"/>
+      <c r="D2218" s="3"/>
+      <c r="E2218" s="3"/>
+      <c r="F2218" s="3"/>
+      <c r="G2218" s="3"/>
+      <c r="H2218" s="3"/>
+      <c r="I2218" s="4"/>
+      <c r="J2218" s="4"/>
+    </row>
+    <row r="2219" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2219" s="3"/>
+      <c r="B2219" s="3"/>
+      <c r="C2219" s="3"/>
+      <c r="D2219" s="3"/>
+      <c r="E2219" s="3"/>
+      <c r="F2219" s="3"/>
+      <c r="G2219" s="3"/>
+      <c r="H2219" s="3"/>
+      <c r="I2219" s="4"/>
+      <c r="J2219" s="4"/>
+    </row>
+    <row r="2220" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2220" s="3"/>
+      <c r="B2220" s="3"/>
+      <c r="C2220" s="3"/>
+      <c r="D2220" s="3"/>
+      <c r="E2220" s="3"/>
+      <c r="F2220" s="3"/>
+      <c r="G2220" s="3"/>
+      <c r="H2220" s="3"/>
+      <c r="I2220" s="4"/>
+      <c r="J2220" s="4"/>
+    </row>
+    <row r="2221" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2221" s="3"/>
+      <c r="B2221" s="3"/>
+      <c r="C2221" s="3"/>
+      <c r="D2221" s="3"/>
+      <c r="E2221" s="3"/>
+      <c r="F2221" s="3"/>
+      <c r="G2221" s="3"/>
+      <c r="H2221" s="3"/>
+      <c r="I2221" s="4"/>
+      <c r="J2221" s="4"/>
+    </row>
+    <row r="2222" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2222" s="3"/>
+      <c r="B2222" s="3"/>
+      <c r="C2222" s="3"/>
+      <c r="D2222" s="3"/>
+      <c r="E2222" s="3"/>
+      <c r="F2222" s="3"/>
+      <c r="G2222" s="3"/>
+      <c r="H2222" s="3"/>
+      <c r="I2222" s="4"/>
+      <c r="J2222" s="4"/>
+    </row>
+    <row r="2223" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2223" s="3"/>
+      <c r="B2223" s="3"/>
+      <c r="C2223" s="3"/>
+      <c r="D2223" s="3"/>
+      <c r="E2223" s="3"/>
+      <c r="F2223" s="3"/>
+      <c r="G2223" s="3"/>
+      <c r="H2223" s="3"/>
+      <c r="I2223" s="4"/>
+      <c r="J2223" s="4"/>
+    </row>
+    <row r="2224" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2224" s="3"/>
+      <c r="B2224" s="3"/>
+      <c r="C2224" s="3"/>
+      <c r="D2224" s="3"/>
+      <c r="E2224" s="3"/>
+      <c r="F2224" s="3"/>
+      <c r="G2224" s="3"/>
+      <c r="H2224" s="3"/>
+      <c r="I2224" s="4"/>
+      <c r="J2224" s="4"/>
+    </row>
+    <row r="2225" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2225" s="3"/>
+      <c r="B2225" s="3"/>
+      <c r="C2225" s="3"/>
+      <c r="D2225" s="3"/>
+      <c r="E2225" s="3"/>
+      <c r="F2225" s="3"/>
+      <c r="G2225" s="3"/>
+      <c r="H2225" s="3"/>
+      <c r="I2225" s="4"/>
+      <c r="J2225" s="4"/>
+    </row>
+    <row r="2226" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2226" s="3"/>
+      <c r="B2226" s="3"/>
+      <c r="C2226" s="3"/>
+      <c r="D2226" s="3"/>
+      <c r="E2226" s="3"/>
+      <c r="F2226" s="3"/>
+      <c r="G2226" s="3"/>
+      <c r="H2226" s="3"/>
+      <c r="I2226" s="4"/>
+      <c r="J2226" s="4"/>
+    </row>
+    <row r="2227" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2227" s="3"/>
+      <c r="B2227" s="3"/>
+      <c r="C2227" s="3"/>
+      <c r="D2227" s="3"/>
+      <c r="E2227" s="3"/>
+      <c r="F2227" s="3"/>
+      <c r="G2227" s="3"/>
+      <c r="H2227" s="3"/>
+      <c r="I2227" s="4"/>
+      <c r="J2227" s="4"/>
+    </row>
+    <row r="2228" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2228" s="3"/>
+      <c r="B2228" s="3"/>
+      <c r="C2228" s="3"/>
+      <c r="D2228" s="3"/>
+      <c r="E2228" s="3"/>
+      <c r="F2228" s="3"/>
+      <c r="G2228" s="3"/>
+      <c r="H2228" s="3"/>
+      <c r="I2228" s="4"/>
+      <c r="J2228" s="4"/>
+    </row>
+    <row r="2229" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2229" s="3"/>
+      <c r="B2229" s="3"/>
+      <c r="C2229" s="3"/>
+      <c r="D2229" s="3"/>
+      <c r="E2229" s="3"/>
+      <c r="F2229" s="3"/>
+      <c r="G2229" s="3"/>
+      <c r="H2229" s="3"/>
+      <c r="I2229" s="4"/>
+      <c r="J2229" s="4"/>
+    </row>
+    <row r="2230" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2230" s="3"/>
+      <c r="B2230" s="3"/>
+      <c r="C2230" s="3"/>
+      <c r="D2230" s="3"/>
+      <c r="E2230" s="3"/>
+      <c r="F2230" s="3"/>
+      <c r="G2230" s="3"/>
+      <c r="H2230" s="3"/>
+      <c r="I2230" s="4"/>
+      <c r="J2230" s="4"/>
+    </row>
+    <row r="2231" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2231" s="3"/>
+      <c r="B2231" s="3"/>
+      <c r="C2231" s="3"/>
+      <c r="D2231" s="3"/>
+      <c r="E2231" s="3"/>
+      <c r="F2231" s="3"/>
+      <c r="G2231" s="3"/>
+      <c r="H2231" s="3"/>
+      <c r="I2231" s="4"/>
+      <c r="J2231" s="4"/>
+    </row>
+    <row r="2232" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2232" s="3"/>
+      <c r="B2232" s="3"/>
+      <c r="C2232" s="3"/>
+      <c r="D2232" s="3"/>
+      <c r="E2232" s="3"/>
+      <c r="F2232" s="3"/>
+      <c r="G2232" s="3"/>
+      <c r="H2232" s="3"/>
+      <c r="I2232" s="4"/>
+      <c r="J2232" s="4"/>
+    </row>
+    <row r="2233" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2233" s="3"/>
+      <c r="B2233" s="3"/>
+      <c r="C2233" s="3"/>
+      <c r="D2233" s="3"/>
+      <c r="E2233" s="3"/>
+      <c r="F2233" s="3"/>
+      <c r="G2233" s="3"/>
+      <c r="H2233" s="3"/>
+      <c r="I2233" s="4"/>
+      <c r="J2233" s="4"/>
+    </row>
+    <row r="2234" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2234" s="3"/>
+      <c r="B2234" s="3"/>
+      <c r="C2234" s="3"/>
+      <c r="D2234" s="3"/>
+      <c r="E2234" s="3"/>
+      <c r="F2234" s="3"/>
+      <c r="G2234" s="3"/>
+      <c r="H2234" s="3"/>
+      <c r="I2234" s="4"/>
+      <c r="J2234" s="4"/>
+    </row>
+    <row r="2235" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2235" s="3"/>
+      <c r="B2235" s="3"/>
+      <c r="C2235" s="3"/>
+      <c r="D2235" s="3"/>
+      <c r="E2235" s="3"/>
+      <c r="F2235" s="3"/>
+      <c r="G2235" s="3"/>
+      <c r="H2235" s="3"/>
+      <c r="I2235" s="4"/>
+      <c r="J2235" s="4"/>
+    </row>
+    <row r="2236" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2236" s="3"/>
+      <c r="B2236" s="3"/>
+      <c r="C2236" s="3"/>
+      <c r="D2236" s="3"/>
+      <c r="E2236" s="3"/>
+      <c r="F2236" s="3"/>
+      <c r="G2236" s="3"/>
+      <c r="H2236" s="3"/>
+      <c r="I2236" s="4"/>
+      <c r="J2236" s="4"/>
+    </row>
+    <row r="2237" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2237" s="3"/>
+      <c r="B2237" s="3"/>
+      <c r="C2237" s="3"/>
+      <c r="D2237" s="3"/>
+      <c r="E2237" s="3"/>
+      <c r="F2237" s="3"/>
+      <c r="G2237" s="3"/>
+      <c r="H2237" s="3"/>
+      <c r="I2237" s="4"/>
+      <c r="J2237" s="4"/>
+    </row>
+    <row r="2238" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2238" s="3"/>
+      <c r="B2238" s="3"/>
+      <c r="C2238" s="3"/>
+      <c r="D2238" s="3"/>
+      <c r="E2238" s="3"/>
+      <c r="F2238" s="3"/>
+      <c r="G2238" s="3"/>
+      <c r="H2238" s="3"/>
+      <c r="I2238" s="4"/>
+      <c r="J2238" s="4"/>
+    </row>
+    <row r="2239" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2239" s="3"/>
+      <c r="B2239" s="3"/>
+      <c r="C2239" s="3"/>
+      <c r="D2239" s="3"/>
+      <c r="E2239" s="3"/>
+      <c r="F2239" s="3"/>
+      <c r="G2239" s="3"/>
+      <c r="H2239" s="3"/>
+      <c r="I2239" s="4"/>
+      <c r="J2239" s="4"/>
+    </row>
+    <row r="2240" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2240" s="3"/>
+      <c r="B2240" s="3"/>
+      <c r="C2240" s="3"/>
+      <c r="D2240" s="3"/>
+      <c r="E2240" s="3"/>
+      <c r="F2240" s="3"/>
+      <c r="G2240" s="3"/>
+      <c r="H2240" s="3"/>
+      <c r="I2240" s="4"/>
+      <c r="J2240" s="4"/>
+    </row>
+    <row r="2241" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2241" s="3"/>
+      <c r="B2241" s="3"/>
+      <c r="C2241" s="3"/>
+      <c r="D2241" s="3"/>
+      <c r="E2241" s="3"/>
+      <c r="F2241" s="3"/>
+      <c r="G2241" s="3"/>
+      <c r="H2241" s="3"/>
+      <c r="I2241" s="4"/>
+      <c r="J2241" s="4"/>
+    </row>
+    <row r="2242" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2242" s="3"/>
+      <c r="B2242" s="3"/>
+      <c r="C2242" s="3"/>
+      <c r="D2242" s="3"/>
+      <c r="E2242" s="3"/>
+      <c r="F2242" s="3"/>
+      <c r="G2242" s="3"/>
+      <c r="H2242" s="3"/>
+      <c r="I2242" s="4"/>
+      <c r="J2242" s="4"/>
+    </row>
+    <row r="2243" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2243" s="3"/>
+      <c r="B2243" s="3"/>
+      <c r="C2243" s="3"/>
+      <c r="D2243" s="3"/>
+      <c r="E2243" s="3"/>
+      <c r="F2243" s="3"/>
+      <c r="G2243" s="3"/>
+      <c r="H2243" s="3"/>
+      <c r="I2243" s="4"/>
+      <c r="J2243" s="4"/>
+    </row>
+    <row r="2244" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2244" s="3"/>
+      <c r="B2244" s="3"/>
+      <c r="C2244" s="3"/>
+      <c r="D2244" s="3"/>
+      <c r="E2244" s="3"/>
+      <c r="F2244" s="3"/>
+      <c r="G2244" s="3"/>
+      <c r="H2244" s="3"/>
+      <c r="I2244" s="4"/>
+      <c r="J2244" s="4"/>
+    </row>
+    <row r="2245" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2245" s="3"/>
+      <c r="B2245" s="3"/>
+      <c r="C2245" s="3"/>
+      <c r="D2245" s="3"/>
+      <c r="E2245" s="3"/>
+      <c r="F2245" s="3"/>
+      <c r="G2245" s="3"/>
+      <c r="H2245" s="3"/>
+      <c r="I2245" s="4"/>
+      <c r="J2245" s="4"/>
+    </row>
+    <row r="2246" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2246" s="3"/>
+      <c r="B2246" s="3"/>
+      <c r="C2246" s="3"/>
+      <c r="D2246" s="3"/>
+      <c r="E2246" s="3"/>
+      <c r="F2246" s="3"/>
+      <c r="G2246" s="3"/>
+      <c r="H2246" s="3"/>
+      <c r="I2246" s="4"/>
+      <c r="J2246" s="4"/>
+    </row>
+    <row r="2247" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2247" s="3"/>
+      <c r="B2247" s="3"/>
+      <c r="C2247" s="3"/>
+      <c r="D2247" s="3"/>
+      <c r="E2247" s="3"/>
+      <c r="F2247" s="3"/>
+      <c r="G2247" s="3"/>
+      <c r="H2247" s="3"/>
+      <c r="I2247" s="4"/>
+      <c r="J2247" s="4"/>
+    </row>
+    <row r="2248" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2248" s="3"/>
+      <c r="B2248" s="3"/>
+      <c r="C2248" s="3"/>
+      <c r="D2248" s="3"/>
+      <c r="E2248" s="3"/>
+      <c r="F2248" s="3"/>
+      <c r="G2248" s="3"/>
+      <c r="H2248" s="3"/>
+      <c r="I2248" s="4"/>
+      <c r="J2248" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8608FA29-98B3-4C0F-8AB7-936E981D4669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE6F554-3549-4C52-9FAE-45B72860A58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="660" windowWidth="27105" windowHeight="13995" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="990" windowWidth="18765" windowHeight="13665" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17077" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17211" uniqueCount="1771">
   <si>
     <t>Year</t>
   </si>
@@ -5317,6 +5317,33 @@
   </si>
   <si>
     <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>P0007_CAE Committee Results 2026 + DDSC Under My Perspective</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
   </si>
 </sst>
 </file>
@@ -5739,7 +5766,7 @@
     <col min="3" max="3" width="7.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" style="5" customWidth="1"/>
     <col min="5" max="5" width="13.140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="43.85546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="49.85546875" style="5" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="4.42578125" style="7" bestFit="1" customWidth="1"/>
@@ -79245,7 +79272,7 @@
         <v>2026</v>
       </c>
       <c r="J2191" s="4">
-        <f t="shared" ref="J2191:J2193" si="1010">MONTH(A2191)</f>
+        <f t="shared" ref="J2191:J2214" si="1010">MONTH(A2191)</f>
         <v>9</v>
       </c>
     </row>
@@ -79305,7 +79332,7 @@
         <v>280</v>
       </c>
       <c r="I2193" s="4">
-        <f t="shared" si="1009"/>
+        <f>YEAR(A2193)</f>
         <v>2026</v>
       </c>
       <c r="J2193" s="4">
@@ -79337,11 +79364,11 @@
         <v>280</v>
       </c>
       <c r="I2194" s="4">
-        <f t="shared" ref="I2194:I2196" si="1011">YEAR(A2194)</f>
+        <f t="shared" ref="I2194:I2213" si="1011">YEAR(A2194)</f>
         <v>2026</v>
       </c>
       <c r="J2194" s="4">
-        <f t="shared" ref="J2194:J2196" si="1012">MONTH(A2194)</f>
+        <f t="shared" si="1010"/>
         <v>10</v>
       </c>
     </row>
@@ -79373,7 +79400,7 @@
         <v>2026</v>
       </c>
       <c r="J2195" s="4">
-        <f t="shared" si="1012"/>
+        <f t="shared" si="1010"/>
         <v>10</v>
       </c>
     </row>
@@ -79405,7 +79432,7 @@
         <v>2026</v>
       </c>
       <c r="J2196" s="4">
-        <f t="shared" si="1012"/>
+        <f t="shared" si="1010"/>
         <v>10</v>
       </c>
     </row>
@@ -79433,241 +79460,623 @@
         <v>280</v>
       </c>
       <c r="I2197" s="4">
-        <f t="shared" ref="I2197" si="1013">YEAR(A2197)</f>
+        <f t="shared" si="1011"/>
         <v>2026</v>
       </c>
       <c r="J2197" s="4">
-        <f t="shared" ref="J2197" si="1014">MONTH(A2197)</f>
+        <f t="shared" si="1010"/>
         <v>10</v>
       </c>
     </row>
     <row r="2198" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2198" s="3"/>
-      <c r="B2198" s="3"/>
-      <c r="C2198" s="3"/>
-      <c r="D2198" s="3"/>
-      <c r="E2198" s="3"/>
+      <c r="A2198" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B2198" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2198" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D2198" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2198" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2198" s="3"/>
-      <c r="G2198" s="3"/>
-      <c r="H2198" s="3"/>
-      <c r="I2198" s="4"/>
-      <c r="J2198" s="4"/>
+      <c r="G2198" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2198" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2198" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2198" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2199" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2199" s="3"/>
-      <c r="B2199" s="3"/>
-      <c r="C2199" s="3"/>
-      <c r="D2199" s="3"/>
-      <c r="E2199" s="3"/>
+      <c r="A2199" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B2199" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2199" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2199" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2199" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2199" s="3"/>
-      <c r="G2199" s="3"/>
-      <c r="H2199" s="3"/>
-      <c r="I2199" s="4"/>
-      <c r="J2199" s="4"/>
+      <c r="G2199" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2199" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2199" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2199" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2200" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2200" s="3"/>
-      <c r="B2200" s="3"/>
-      <c r="C2200" s="3"/>
-      <c r="D2200" s="3"/>
-      <c r="E2200" s="3"/>
+      <c r="A2200" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B2200" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2200" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2200" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2200" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2200" s="3"/>
-      <c r="G2200" s="3"/>
-      <c r="H2200" s="3"/>
-      <c r="I2200" s="4"/>
-      <c r="J2200" s="4"/>
+      <c r="G2200" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2200" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2200" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2200" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2201" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2201" s="3"/>
-      <c r="B2201" s="3"/>
-      <c r="C2201" s="3"/>
-      <c r="D2201" s="3"/>
-      <c r="E2201" s="3"/>
-      <c r="F2201" s="3"/>
-      <c r="G2201" s="3"/>
-      <c r="H2201" s="3"/>
-      <c r="I2201" s="4"/>
-      <c r="J2201" s="4"/>
+      <c r="A2201" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B2201" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2201" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2201" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2201" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2201" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G2201" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2201" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2201" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2201" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2202" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2202" s="3"/>
-      <c r="B2202" s="3"/>
-      <c r="C2202" s="3"/>
-      <c r="D2202" s="3"/>
-      <c r="E2202" s="3"/>
+      <c r="A2202" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B2202" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2202" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2202" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2202" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2202" s="3"/>
-      <c r="G2202" s="3"/>
-      <c r="H2202" s="3"/>
-      <c r="I2202" s="4"/>
-      <c r="J2202" s="4"/>
+      <c r="G2202" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2202" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2202" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2202" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2203" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2203" s="3"/>
-      <c r="B2203" s="3"/>
-      <c r="C2203" s="3"/>
-      <c r="D2203" s="3"/>
-      <c r="E2203" s="3"/>
+      <c r="A2203" s="3" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B2203" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2203" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2203" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2203" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2203" s="3"/>
-      <c r="G2203" s="3"/>
-      <c r="H2203" s="3"/>
-      <c r="I2203" s="4"/>
-      <c r="J2203" s="4"/>
+      <c r="G2203" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2203" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2203" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2203" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2204" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2204" s="3"/>
-      <c r="B2204" s="3"/>
-      <c r="C2204" s="3"/>
-      <c r="D2204" s="3"/>
-      <c r="E2204" s="3"/>
+      <c r="A2204" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B2204" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2204" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2204" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2204" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2204" s="3"/>
-      <c r="G2204" s="3"/>
-      <c r="H2204" s="3"/>
-      <c r="I2204" s="4"/>
-      <c r="J2204" s="4"/>
+      <c r="G2204" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2204" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2204" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2204" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2205" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2205" s="3"/>
-      <c r="B2205" s="3"/>
-      <c r="C2205" s="3"/>
-      <c r="D2205" s="3"/>
-      <c r="E2205" s="3"/>
+      <c r="A2205" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B2205" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2205" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2205" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2205" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2205" s="3"/>
-      <c r="G2205" s="3"/>
-      <c r="H2205" s="3"/>
-      <c r="I2205" s="4"/>
-      <c r="J2205" s="4"/>
+      <c r="G2205" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2205" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2205" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2205" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2206" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2206" s="3"/>
-      <c r="B2206" s="3"/>
-      <c r="C2206" s="3"/>
-      <c r="D2206" s="3"/>
-      <c r="E2206" s="3"/>
+      <c r="A2206" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B2206" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2206" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2206" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2206" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2206" s="3"/>
-      <c r="G2206" s="3"/>
-      <c r="H2206" s="3"/>
-      <c r="I2206" s="4"/>
-      <c r="J2206" s="4"/>
+      <c r="G2206" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2206" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2206" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2206" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2207" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2207" s="3"/>
-      <c r="B2207" s="3"/>
-      <c r="C2207" s="3"/>
-      <c r="D2207" s="3"/>
-      <c r="E2207" s="3"/>
+      <c r="A2207" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B2207" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2207" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2207" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2207" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2207" s="3"/>
-      <c r="G2207" s="3"/>
-      <c r="H2207" s="3"/>
-      <c r="I2207" s="4"/>
-      <c r="J2207" s="4"/>
+      <c r="G2207" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2207" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2207" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2207" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2208" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2208" s="3"/>
-      <c r="B2208" s="3"/>
-      <c r="C2208" s="3"/>
-      <c r="D2208" s="3"/>
-      <c r="E2208" s="3"/>
+      <c r="A2208" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B2208" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2208" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2208" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2208" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2208" s="3"/>
-      <c r="G2208" s="3"/>
-      <c r="H2208" s="3"/>
-      <c r="I2208" s="4"/>
-      <c r="J2208" s="4"/>
+      <c r="G2208" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2208" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2208" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2208" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2209" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2209" s="3"/>
-      <c r="B2209" s="3"/>
-      <c r="C2209" s="3"/>
-      <c r="D2209" s="3"/>
-      <c r="E2209" s="3"/>
+      <c r="A2209" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B2209" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2209" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2209" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2209" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2209" s="3"/>
-      <c r="G2209" s="3"/>
-      <c r="H2209" s="3"/>
-      <c r="I2209" s="4"/>
-      <c r="J2209" s="4"/>
+      <c r="G2209" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2209" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2209" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2209" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2210" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2210" s="3"/>
-      <c r="B2210" s="3"/>
-      <c r="C2210" s="3"/>
-      <c r="D2210" s="3"/>
-      <c r="E2210" s="3"/>
+      <c r="A2210" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B2210" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2210" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2210" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2210" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2210" s="3"/>
-      <c r="G2210" s="3"/>
-      <c r="H2210" s="3"/>
-      <c r="I2210" s="4"/>
-      <c r="J2210" s="4"/>
+      <c r="G2210" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2210" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2210" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2210" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2211" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2211" s="3"/>
-      <c r="B2211" s="3"/>
-      <c r="C2211" s="3"/>
-      <c r="D2211" s="3"/>
-      <c r="E2211" s="3"/>
+      <c r="A2211" s="3" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B2211" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2211" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2211" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2211" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2211" s="3"/>
-      <c r="G2211" s="3"/>
-      <c r="H2211" s="3"/>
-      <c r="I2211" s="4"/>
-      <c r="J2211" s="4"/>
+      <c r="G2211" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2211" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2211" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2211" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2212" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2212" s="3"/>
-      <c r="B2212" s="3"/>
-      <c r="C2212" s="3"/>
-      <c r="D2212" s="3"/>
-      <c r="E2212" s="3"/>
+      <c r="A2212" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B2212" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2212" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2212" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2212" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2212" s="3"/>
-      <c r="G2212" s="3"/>
-      <c r="H2212" s="3"/>
-      <c r="I2212" s="4"/>
-      <c r="J2212" s="4"/>
+      <c r="G2212" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2212" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2212" s="4">
+        <f t="shared" si="1011"/>
+        <v>2026</v>
+      </c>
+      <c r="J2212" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2213" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2213" s="3"/>
-      <c r="B2213" s="3"/>
-      <c r="C2213" s="3"/>
-      <c r="D2213" s="3"/>
-      <c r="E2213" s="3"/>
+      <c r="A2213" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B2213" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2213" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2213" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2213" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2213" s="3"/>
-      <c r="G2213" s="3"/>
-      <c r="H2213" s="3"/>
-      <c r="I2213" s="4"/>
-      <c r="J2213" s="4"/>
+      <c r="G2213" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2213" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2213" s="4">
+        <f>YEAR(A2213)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2213" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2214" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2214" s="3"/>
-      <c r="B2214" s="3"/>
-      <c r="C2214" s="3"/>
-      <c r="D2214" s="3"/>
-      <c r="E2214" s="3"/>
+      <c r="A2214" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B2214" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C2214" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2214" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2214" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2214" s="3"/>
-      <c r="G2214" s="3"/>
-      <c r="H2214" s="3"/>
-      <c r="I2214" s="4"/>
-      <c r="J2214" s="4"/>
+      <c r="G2214" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2214" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2214" s="4">
+        <f>YEAR(A2214)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2214" s="4">
+        <f t="shared" si="1010"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2215" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2215" s="3"/>
-      <c r="B2215" s="3"/>
-      <c r="C2215" s="3"/>
-      <c r="D2215" s="3"/>
-      <c r="E2215" s="3"/>
+      <c r="A2215" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B2215" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2215" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2215" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2215" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F2215" s="3"/>
-      <c r="G2215" s="3"/>
-      <c r="H2215" s="3"/>
-      <c r="I2215" s="4"/>
-      <c r="J2215" s="4"/>
+      <c r="G2215" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2215" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2215" s="4">
+        <f>YEAR(A2215)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2215" s="4">
+        <f t="shared" ref="J2215:J2216" si="1012">MONTH(A2215)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="2216" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2216" s="3"/>
-      <c r="B2216" s="3"/>
-      <c r="C2216" s="3"/>
-      <c r="D2216" s="3"/>
-      <c r="E2216" s="3"/>
+      <c r="A2216" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B2216" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2216" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2216" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2216" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="F2216" s="3"/>
-      <c r="G2216" s="3"/>
-      <c r="H2216" s="3"/>
-      <c r="I2216" s="4"/>
-      <c r="J2216" s="4"/>
+      <c r="G2216" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2216" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2216" s="4">
+        <f>YEAR(A2216)</f>
+        <v>2026</v>
+      </c>
+      <c r="J2216" s="4">
+        <f t="shared" si="1012"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="2217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2217" s="3"/>

--- a/data/Time Tracking.xlsx
+++ b/data/Time Tracking.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE6F554-3549-4C52-9FAE-45B72860A58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F8E8E6-A18F-4C71-AE1B-DDAA1359728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="990" windowWidth="18765" windowHeight="13665" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4710" yWindow="-14520" windowWidth="18765" windowHeight="13665" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sessions" sheetId="8" r:id="rId1"/>
@@ -79268,7 +79268,7 @@
         <v>280</v>
       </c>
       <c r="I2191" s="4">
-        <f t="shared" ref="I2191:I2193" si="1009">YEAR(A2191)</f>
+        <f t="shared" ref="I2191:I2192" si="1009">YEAR(A2191)</f>
         <v>2026</v>
       </c>
       <c r="J2191" s="4">
@@ -79364,7 +79364,7 @@
         <v>280</v>
       </c>
       <c r="I2194" s="4">
-        <f t="shared" ref="I2194:I2213" si="1011">YEAR(A2194)</f>
+        <f t="shared" ref="I2194:I2212" si="1011">YEAR(A2194)</f>
         <v>2026</v>
       </c>
       <c r="J2194" s="4">
@@ -79575,7 +79575,7 @@
         <v>114</v>
       </c>
       <c r="D2201" s="3" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E2201" s="3" t="s">
         <v>140</v>
